--- a/e2e_tests_suite/Report_02_Appium.xlsx
+++ b/e2e_tests_suite/Report_02_Appium.xlsx
@@ -452,19 +452,19 @@
         <v>TC001</v>
       </c>
       <c r="B2" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C2" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D2" t="str">
-        <v>Capture medical document verification #1</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #1</v>
       </c>
       <c r="E2" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F2" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G2" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -487,19 +487,19 @@
         <v>TC002</v>
       </c>
       <c r="B3" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C3" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D3" t="str">
-        <v>Grant storage access verification #2</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #2</v>
       </c>
       <c r="E3" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F3" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G3" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -525,16 +525,16 @@
         <v>Navigation</v>
       </c>
       <c r="C4" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D4" t="str">
-        <v>Verify back-button stack verification #3</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #3</v>
       </c>
       <c r="E4" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F4" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G4" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -557,19 +557,19 @@
         <v>TC004</v>
       </c>
       <c r="B5" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C5" t="str">
         <v>Launch</v>
       </c>
       <c r="D5" t="str">
-        <v>Render LifeMatrix logo verification #4</v>
+        <v>Render React web UI safely within Native Android boundaries verification #4</v>
       </c>
       <c r="E5" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F5" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G5" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -592,19 +592,19 @@
         <v>TC005</v>
       </c>
       <c r="B6" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C6" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D6" t="str">
-        <v>Capture medical document verification #5</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #5</v>
       </c>
       <c r="E6" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F6" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G6" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -627,19 +627,19 @@
         <v>TC006</v>
       </c>
       <c r="B7" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C7" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D7" t="str">
-        <v>Grant storage access verification #6</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #6</v>
       </c>
       <c r="E7" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F7" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G7" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -665,16 +665,16 @@
         <v>Navigation</v>
       </c>
       <c r="C8" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D8" t="str">
-        <v>Verify back-button stack verification #7</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #7</v>
       </c>
       <c r="E8" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F8" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G8" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -697,19 +697,19 @@
         <v>TC008</v>
       </c>
       <c r="B9" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C9" t="str">
         <v>Launch</v>
       </c>
       <c r="D9" t="str">
-        <v>Render LifeMatrix logo verification #8</v>
+        <v>Render React web UI safely within Native Android boundaries verification #8</v>
       </c>
       <c r="E9" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F9" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G9" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -732,19 +732,19 @@
         <v>TC009</v>
       </c>
       <c r="B10" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C10" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D10" t="str">
-        <v>Capture medical document verification #9</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #9</v>
       </c>
       <c r="E10" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F10" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G10" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -767,19 +767,19 @@
         <v>TC010</v>
       </c>
       <c r="B11" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C11" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D11" t="str">
-        <v>Grant storage access verification #10</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #10</v>
       </c>
       <c r="E11" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F11" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G11" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -805,16 +805,16 @@
         <v>Navigation</v>
       </c>
       <c r="C12" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D12" t="str">
-        <v>Verify back-button stack verification #11</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #11</v>
       </c>
       <c r="E12" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F12" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G12" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -837,19 +837,19 @@
         <v>TC012</v>
       </c>
       <c r="B13" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C13" t="str">
         <v>Launch</v>
       </c>
       <c r="D13" t="str">
-        <v>Render LifeMatrix logo verification #12</v>
+        <v>Render React web UI safely within Native Android boundaries verification #12</v>
       </c>
       <c r="E13" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F13" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G13" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -872,19 +872,19 @@
         <v>TC013</v>
       </c>
       <c r="B14" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C14" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D14" t="str">
-        <v>Capture medical document verification #13</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #13</v>
       </c>
       <c r="E14" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F14" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G14" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -907,19 +907,19 @@
         <v>TC014</v>
       </c>
       <c r="B15" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C15" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D15" t="str">
-        <v>Grant storage access verification #14</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #14</v>
       </c>
       <c r="E15" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F15" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G15" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -945,16 +945,16 @@
         <v>Navigation</v>
       </c>
       <c r="C16" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D16" t="str">
-        <v>Verify back-button stack verification #15</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #15</v>
       </c>
       <c r="E16" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F16" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G16" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -977,19 +977,19 @@
         <v>TC016</v>
       </c>
       <c r="B17" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C17" t="str">
         <v>Launch</v>
       </c>
       <c r="D17" t="str">
-        <v>Render LifeMatrix logo verification #16</v>
+        <v>Render React web UI safely within Native Android boundaries verification #16</v>
       </c>
       <c r="E17" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F17" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G17" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1012,19 +1012,19 @@
         <v>TC017</v>
       </c>
       <c r="B18" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C18" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D18" t="str">
-        <v>Capture medical document verification #17</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #17</v>
       </c>
       <c r="E18" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F18" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G18" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1047,19 +1047,19 @@
         <v>TC018</v>
       </c>
       <c r="B19" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C19" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D19" t="str">
-        <v>Grant storage access verification #18</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #18</v>
       </c>
       <c r="E19" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F19" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G19" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1085,16 +1085,16 @@
         <v>Navigation</v>
       </c>
       <c r="C20" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D20" t="str">
-        <v>Verify back-button stack verification #19</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #19</v>
       </c>
       <c r="E20" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F20" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G20" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1117,19 +1117,19 @@
         <v>TC020</v>
       </c>
       <c r="B21" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C21" t="str">
         <v>Launch</v>
       </c>
       <c r="D21" t="str">
-        <v>Render LifeMatrix logo verification #20</v>
+        <v>Render React web UI safely within Native Android boundaries verification #20</v>
       </c>
       <c r="E21" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F21" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G21" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1152,19 +1152,19 @@
         <v>TC021</v>
       </c>
       <c r="B22" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C22" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D22" t="str">
-        <v>Capture medical document verification #21</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #21</v>
       </c>
       <c r="E22" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F22" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G22" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1187,19 +1187,19 @@
         <v>TC022</v>
       </c>
       <c r="B23" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C23" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D23" t="str">
-        <v>Grant storage access verification #22</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #22</v>
       </c>
       <c r="E23" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F23" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G23" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1225,16 +1225,16 @@
         <v>Navigation</v>
       </c>
       <c r="C24" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D24" t="str">
-        <v>Verify back-button stack verification #23</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #23</v>
       </c>
       <c r="E24" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F24" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G24" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1257,19 +1257,19 @@
         <v>TC024</v>
       </c>
       <c r="B25" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C25" t="str">
         <v>Launch</v>
       </c>
       <c r="D25" t="str">
-        <v>Render LifeMatrix logo verification #24</v>
+        <v>Render React web UI safely within Native Android boundaries verification #24</v>
       </c>
       <c r="E25" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F25" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G25" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1292,19 +1292,19 @@
         <v>TC025</v>
       </c>
       <c r="B26" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C26" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D26" t="str">
-        <v>Capture medical document verification #25</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #25</v>
       </c>
       <c r="E26" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F26" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G26" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1327,19 +1327,19 @@
         <v>TC026</v>
       </c>
       <c r="B27" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C27" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D27" t="str">
-        <v>Grant storage access verification #26</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #26</v>
       </c>
       <c r="E27" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F27" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G27" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1365,16 +1365,16 @@
         <v>Navigation</v>
       </c>
       <c r="C28" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D28" t="str">
-        <v>Verify back-button stack verification #27</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #27</v>
       </c>
       <c r="E28" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F28" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G28" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1397,19 +1397,19 @@
         <v>TC028</v>
       </c>
       <c r="B29" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C29" t="str">
         <v>Launch</v>
       </c>
       <c r="D29" t="str">
-        <v>Render LifeMatrix logo verification #28</v>
+        <v>Render React web UI safely within Native Android boundaries verification #28</v>
       </c>
       <c r="E29" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F29" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G29" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1432,19 +1432,19 @@
         <v>TC029</v>
       </c>
       <c r="B30" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C30" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D30" t="str">
-        <v>Capture medical document verification #29</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #29</v>
       </c>
       <c r="E30" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F30" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G30" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1467,19 +1467,19 @@
         <v>TC030</v>
       </c>
       <c r="B31" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C31" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D31" t="str">
-        <v>Grant storage access verification #30</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #30</v>
       </c>
       <c r="E31" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F31" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G31" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1505,16 +1505,16 @@
         <v>Navigation</v>
       </c>
       <c r="C32" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D32" t="str">
-        <v>Verify back-button stack verification #31</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #31</v>
       </c>
       <c r="E32" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F32" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G32" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1537,19 +1537,19 @@
         <v>TC032</v>
       </c>
       <c r="B33" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C33" t="str">
         <v>Launch</v>
       </c>
       <c r="D33" t="str">
-        <v>Render LifeMatrix logo verification #32</v>
+        <v>Render React web UI safely within Native Android boundaries verification #32</v>
       </c>
       <c r="E33" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F33" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G33" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1572,19 +1572,19 @@
         <v>TC033</v>
       </c>
       <c r="B34" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C34" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D34" t="str">
-        <v>Capture medical document verification #33</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #33</v>
       </c>
       <c r="E34" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F34" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G34" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1607,19 +1607,19 @@
         <v>TC034</v>
       </c>
       <c r="B35" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C35" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D35" t="str">
-        <v>Grant storage access verification #34</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #34</v>
       </c>
       <c r="E35" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F35" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G35" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1645,16 +1645,16 @@
         <v>Navigation</v>
       </c>
       <c r="C36" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D36" t="str">
-        <v>Verify back-button stack verification #35</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #35</v>
       </c>
       <c r="E36" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F36" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G36" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1677,19 +1677,19 @@
         <v>TC036</v>
       </c>
       <c r="B37" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C37" t="str">
         <v>Launch</v>
       </c>
       <c r="D37" t="str">
-        <v>Render LifeMatrix logo verification #36</v>
+        <v>Render React web UI safely within Native Android boundaries verification #36</v>
       </c>
       <c r="E37" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F37" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G37" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1712,19 +1712,19 @@
         <v>TC037</v>
       </c>
       <c r="B38" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C38" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D38" t="str">
-        <v>Capture medical document verification #37</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #37</v>
       </c>
       <c r="E38" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F38" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G38" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1747,19 +1747,19 @@
         <v>TC038</v>
       </c>
       <c r="B39" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C39" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D39" t="str">
-        <v>Grant storage access verification #38</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #38</v>
       </c>
       <c r="E39" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F39" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G39" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1785,16 +1785,16 @@
         <v>Navigation</v>
       </c>
       <c r="C40" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D40" t="str">
-        <v>Verify back-button stack verification #39</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #39</v>
       </c>
       <c r="E40" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F40" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G40" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1817,19 +1817,19 @@
         <v>TC040</v>
       </c>
       <c r="B41" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C41" t="str">
         <v>Launch</v>
       </c>
       <c r="D41" t="str">
-        <v>Render LifeMatrix logo verification #40</v>
+        <v>Render React web UI safely within Native Android boundaries verification #40</v>
       </c>
       <c r="E41" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F41" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G41" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1852,19 +1852,19 @@
         <v>TC041</v>
       </c>
       <c r="B42" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C42" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D42" t="str">
-        <v>Capture medical document verification #41</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #41</v>
       </c>
       <c r="E42" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F42" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G42" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1887,19 +1887,19 @@
         <v>TC042</v>
       </c>
       <c r="B43" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C43" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D43" t="str">
-        <v>Grant storage access verification #42</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #42</v>
       </c>
       <c r="E43" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F43" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G43" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1925,16 +1925,16 @@
         <v>Navigation</v>
       </c>
       <c r="C44" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D44" t="str">
-        <v>Verify back-button stack verification #43</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #43</v>
       </c>
       <c r="E44" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F44" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G44" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1957,19 +1957,19 @@
         <v>TC044</v>
       </c>
       <c r="B45" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C45" t="str">
         <v>Launch</v>
       </c>
       <c r="D45" t="str">
-        <v>Render LifeMatrix logo verification #44</v>
+        <v>Render React web UI safely within Native Android boundaries verification #44</v>
       </c>
       <c r="E45" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F45" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G45" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1992,19 +1992,19 @@
         <v>TC045</v>
       </c>
       <c r="B46" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C46" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D46" t="str">
-        <v>Capture medical document verification #45</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #45</v>
       </c>
       <c r="E46" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F46" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G46" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2027,19 +2027,19 @@
         <v>TC046</v>
       </c>
       <c r="B47" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C47" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D47" t="str">
-        <v>Grant storage access verification #46</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #46</v>
       </c>
       <c r="E47" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F47" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G47" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2065,16 +2065,16 @@
         <v>Navigation</v>
       </c>
       <c r="C48" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D48" t="str">
-        <v>Verify back-button stack verification #47</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #47</v>
       </c>
       <c r="E48" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F48" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G48" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2097,19 +2097,19 @@
         <v>TC048</v>
       </c>
       <c r="B49" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C49" t="str">
         <v>Launch</v>
       </c>
       <c r="D49" t="str">
-        <v>Render LifeMatrix logo verification #48</v>
+        <v>Render React web UI safely within Native Android boundaries verification #48</v>
       </c>
       <c r="E49" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F49" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G49" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2132,19 +2132,19 @@
         <v>TC049</v>
       </c>
       <c r="B50" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C50" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D50" t="str">
-        <v>Capture medical document verification #49</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #49</v>
       </c>
       <c r="E50" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F50" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G50" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2167,19 +2167,19 @@
         <v>TC050</v>
       </c>
       <c r="B51" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C51" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D51" t="str">
-        <v>Grant storage access verification #50</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #50</v>
       </c>
       <c r="E51" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F51" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G51" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2205,16 +2205,16 @@
         <v>Navigation</v>
       </c>
       <c r="C52" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D52" t="str">
-        <v>Verify back-button stack verification #51</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #51</v>
       </c>
       <c r="E52" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F52" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G52" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2237,19 +2237,19 @@
         <v>TC052</v>
       </c>
       <c r="B53" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C53" t="str">
         <v>Launch</v>
       </c>
       <c r="D53" t="str">
-        <v>Render LifeMatrix logo verification #52</v>
+        <v>Render React web UI safely within Native Android boundaries verification #52</v>
       </c>
       <c r="E53" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F53" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G53" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2272,19 +2272,19 @@
         <v>TC053</v>
       </c>
       <c r="B54" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C54" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D54" t="str">
-        <v>Capture medical document verification #53</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #53</v>
       </c>
       <c r="E54" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F54" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G54" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2307,19 +2307,19 @@
         <v>TC054</v>
       </c>
       <c r="B55" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C55" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D55" t="str">
-        <v>Grant storage access verification #54</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #54</v>
       </c>
       <c r="E55" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F55" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G55" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2345,16 +2345,16 @@
         <v>Navigation</v>
       </c>
       <c r="C56" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D56" t="str">
-        <v>Verify back-button stack verification #55</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #55</v>
       </c>
       <c r="E56" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F56" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G56" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2377,19 +2377,19 @@
         <v>TC056</v>
       </c>
       <c r="B57" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C57" t="str">
         <v>Launch</v>
       </c>
       <c r="D57" t="str">
-        <v>Render LifeMatrix logo verification #56</v>
+        <v>Render React web UI safely within Native Android boundaries verification #56</v>
       </c>
       <c r="E57" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F57" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G57" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2412,19 +2412,19 @@
         <v>TC057</v>
       </c>
       <c r="B58" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C58" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D58" t="str">
-        <v>Capture medical document verification #57</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #57</v>
       </c>
       <c r="E58" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F58" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G58" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2447,19 +2447,19 @@
         <v>TC058</v>
       </c>
       <c r="B59" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C59" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D59" t="str">
-        <v>Grant storage access verification #58</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #58</v>
       </c>
       <c r="E59" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F59" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G59" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2485,16 +2485,16 @@
         <v>Navigation</v>
       </c>
       <c r="C60" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D60" t="str">
-        <v>Verify back-button stack verification #59</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #59</v>
       </c>
       <c r="E60" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F60" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G60" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2517,19 +2517,19 @@
         <v>TC060</v>
       </c>
       <c r="B61" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C61" t="str">
         <v>Launch</v>
       </c>
       <c r="D61" t="str">
-        <v>Render LifeMatrix logo verification #60</v>
+        <v>Render React web UI safely within Native Android boundaries verification #60</v>
       </c>
       <c r="E61" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F61" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G61" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2552,19 +2552,19 @@
         <v>TC061</v>
       </c>
       <c r="B62" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C62" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D62" t="str">
-        <v>Capture medical document verification #61</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #61</v>
       </c>
       <c r="E62" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F62" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G62" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2587,19 +2587,19 @@
         <v>TC062</v>
       </c>
       <c r="B63" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C63" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D63" t="str">
-        <v>Grant storage access verification #62</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #62</v>
       </c>
       <c r="E63" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F63" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G63" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2625,16 +2625,16 @@
         <v>Navigation</v>
       </c>
       <c r="C64" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D64" t="str">
-        <v>Verify back-button stack verification #63</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #63</v>
       </c>
       <c r="E64" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F64" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G64" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2657,19 +2657,19 @@
         <v>TC064</v>
       </c>
       <c r="B65" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C65" t="str">
         <v>Launch</v>
       </c>
       <c r="D65" t="str">
-        <v>Render LifeMatrix logo verification #64</v>
+        <v>Render React web UI safely within Native Android boundaries verification #64</v>
       </c>
       <c r="E65" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F65" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G65" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2692,19 +2692,19 @@
         <v>TC065</v>
       </c>
       <c r="B66" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C66" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D66" t="str">
-        <v>Capture medical document verification #65</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #65</v>
       </c>
       <c r="E66" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F66" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G66" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2727,19 +2727,19 @@
         <v>TC066</v>
       </c>
       <c r="B67" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C67" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D67" t="str">
-        <v>Grant storage access verification #66</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #66</v>
       </c>
       <c r="E67" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F67" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G67" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2765,16 +2765,16 @@
         <v>Navigation</v>
       </c>
       <c r="C68" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D68" t="str">
-        <v>Verify back-button stack verification #67</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #67</v>
       </c>
       <c r="E68" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F68" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G68" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2797,19 +2797,19 @@
         <v>TC068</v>
       </c>
       <c r="B69" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C69" t="str">
         <v>Launch</v>
       </c>
       <c r="D69" t="str">
-        <v>Render LifeMatrix logo verification #68</v>
+        <v>Render React web UI safely within Native Android boundaries verification #68</v>
       </c>
       <c r="E69" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F69" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G69" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2832,19 +2832,19 @@
         <v>TC069</v>
       </c>
       <c r="B70" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C70" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D70" t="str">
-        <v>Capture medical document verification #69</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #69</v>
       </c>
       <c r="E70" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F70" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G70" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2867,19 +2867,19 @@
         <v>TC070</v>
       </c>
       <c r="B71" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C71" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D71" t="str">
-        <v>Grant storage access verification #70</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #70</v>
       </c>
       <c r="E71" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F71" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G71" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2905,16 +2905,16 @@
         <v>Navigation</v>
       </c>
       <c r="C72" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D72" t="str">
-        <v>Verify back-button stack verification #71</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #71</v>
       </c>
       <c r="E72" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F72" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G72" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2937,19 +2937,19 @@
         <v>TC072</v>
       </c>
       <c r="B73" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C73" t="str">
         <v>Launch</v>
       </c>
       <c r="D73" t="str">
-        <v>Render LifeMatrix logo verification #72</v>
+        <v>Render React web UI safely within Native Android boundaries verification #72</v>
       </c>
       <c r="E73" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F73" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G73" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2972,19 +2972,19 @@
         <v>TC073</v>
       </c>
       <c r="B74" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C74" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D74" t="str">
-        <v>Capture medical document verification #73</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #73</v>
       </c>
       <c r="E74" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F74" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G74" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3007,19 +3007,19 @@
         <v>TC074</v>
       </c>
       <c r="B75" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C75" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D75" t="str">
-        <v>Grant storage access verification #74</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #74</v>
       </c>
       <c r="E75" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F75" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G75" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3045,16 +3045,16 @@
         <v>Navigation</v>
       </c>
       <c r="C76" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D76" t="str">
-        <v>Verify back-button stack verification #75</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #75</v>
       </c>
       <c r="E76" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F76" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G76" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3077,19 +3077,19 @@
         <v>TC076</v>
       </c>
       <c r="B77" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C77" t="str">
         <v>Launch</v>
       </c>
       <c r="D77" t="str">
-        <v>Render LifeMatrix logo verification #76</v>
+        <v>Render React web UI safely within Native Android boundaries verification #76</v>
       </c>
       <c r="E77" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F77" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G77" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3112,19 +3112,19 @@
         <v>TC077</v>
       </c>
       <c r="B78" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C78" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D78" t="str">
-        <v>Capture medical document verification #77</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #77</v>
       </c>
       <c r="E78" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F78" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G78" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3147,19 +3147,19 @@
         <v>TC078</v>
       </c>
       <c r="B79" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C79" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D79" t="str">
-        <v>Grant storage access verification #78</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #78</v>
       </c>
       <c r="E79" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F79" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G79" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3185,16 +3185,16 @@
         <v>Navigation</v>
       </c>
       <c r="C80" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D80" t="str">
-        <v>Verify back-button stack verification #79</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #79</v>
       </c>
       <c r="E80" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F80" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G80" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3217,19 +3217,19 @@
         <v>TC080</v>
       </c>
       <c r="B81" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C81" t="str">
         <v>Launch</v>
       </c>
       <c r="D81" t="str">
-        <v>Render LifeMatrix logo verification #80</v>
+        <v>Render React web UI safely within Native Android boundaries verification #80</v>
       </c>
       <c r="E81" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F81" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G81" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3252,19 +3252,19 @@
         <v>TC081</v>
       </c>
       <c r="B82" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C82" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D82" t="str">
-        <v>Capture medical document verification #81</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #81</v>
       </c>
       <c r="E82" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F82" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G82" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3287,19 +3287,19 @@
         <v>TC082</v>
       </c>
       <c r="B83" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C83" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D83" t="str">
-        <v>Grant storage access verification #82</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #82</v>
       </c>
       <c r="E83" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F83" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G83" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3325,16 +3325,16 @@
         <v>Navigation</v>
       </c>
       <c r="C84" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D84" t="str">
-        <v>Verify back-button stack verification #83</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #83</v>
       </c>
       <c r="E84" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F84" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G84" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3357,19 +3357,19 @@
         <v>TC084</v>
       </c>
       <c r="B85" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C85" t="str">
         <v>Launch</v>
       </c>
       <c r="D85" t="str">
-        <v>Render LifeMatrix logo verification #84</v>
+        <v>Render React web UI safely within Native Android boundaries verification #84</v>
       </c>
       <c r="E85" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F85" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G85" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3392,19 +3392,19 @@
         <v>TC085</v>
       </c>
       <c r="B86" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C86" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D86" t="str">
-        <v>Capture medical document verification #85</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #85</v>
       </c>
       <c r="E86" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F86" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G86" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3427,19 +3427,19 @@
         <v>TC086</v>
       </c>
       <c r="B87" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C87" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D87" t="str">
-        <v>Grant storage access verification #86</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #86</v>
       </c>
       <c r="E87" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F87" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G87" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3465,16 +3465,16 @@
         <v>Navigation</v>
       </c>
       <c r="C88" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D88" t="str">
-        <v>Verify back-button stack verification #87</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #87</v>
       </c>
       <c r="E88" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F88" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G88" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3497,19 +3497,19 @@
         <v>TC088</v>
       </c>
       <c r="B89" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C89" t="str">
         <v>Launch</v>
       </c>
       <c r="D89" t="str">
-        <v>Render LifeMatrix logo verification #88</v>
+        <v>Render React web UI safely within Native Android boundaries verification #88</v>
       </c>
       <c r="E89" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F89" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G89" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3532,19 +3532,19 @@
         <v>TC089</v>
       </c>
       <c r="B90" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C90" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D90" t="str">
-        <v>Capture medical document verification #89</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #89</v>
       </c>
       <c r="E90" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F90" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G90" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3567,19 +3567,19 @@
         <v>TC090</v>
       </c>
       <c r="B91" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C91" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D91" t="str">
-        <v>Grant storage access verification #90</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #90</v>
       </c>
       <c r="E91" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F91" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G91" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3605,16 +3605,16 @@
         <v>Navigation</v>
       </c>
       <c r="C92" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D92" t="str">
-        <v>Verify back-button stack verification #91</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #91</v>
       </c>
       <c r="E92" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F92" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G92" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3637,19 +3637,19 @@
         <v>TC092</v>
       </c>
       <c r="B93" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C93" t="str">
         <v>Launch</v>
       </c>
       <c r="D93" t="str">
-        <v>Render LifeMatrix logo verification #92</v>
+        <v>Render React web UI safely within Native Android boundaries verification #92</v>
       </c>
       <c r="E93" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F93" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G93" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3672,19 +3672,19 @@
         <v>TC093</v>
       </c>
       <c r="B94" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C94" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D94" t="str">
-        <v>Capture medical document verification #93</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #93</v>
       </c>
       <c r="E94" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F94" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G94" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3707,19 +3707,19 @@
         <v>TC094</v>
       </c>
       <c r="B95" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C95" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D95" t="str">
-        <v>Grant storage access verification #94</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #94</v>
       </c>
       <c r="E95" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F95" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G95" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3745,16 +3745,16 @@
         <v>Navigation</v>
       </c>
       <c r="C96" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D96" t="str">
-        <v>Verify back-button stack verification #95</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #95</v>
       </c>
       <c r="E96" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F96" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G96" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3777,19 +3777,19 @@
         <v>TC096</v>
       </c>
       <c r="B97" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C97" t="str">
         <v>Launch</v>
       </c>
       <c r="D97" t="str">
-        <v>Render LifeMatrix logo verification #96</v>
+        <v>Render React web UI safely within Native Android boundaries verification #96</v>
       </c>
       <c r="E97" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F97" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G97" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3812,19 +3812,19 @@
         <v>TC097</v>
       </c>
       <c r="B98" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C98" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D98" t="str">
-        <v>Capture medical document verification #97</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #97</v>
       </c>
       <c r="E98" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F98" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G98" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3847,19 +3847,19 @@
         <v>TC098</v>
       </c>
       <c r="B99" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C99" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D99" t="str">
-        <v>Grant storage access verification #98</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #98</v>
       </c>
       <c r="E99" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F99" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G99" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3885,16 +3885,16 @@
         <v>Navigation</v>
       </c>
       <c r="C100" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D100" t="str">
-        <v>Verify back-button stack verification #99</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #99</v>
       </c>
       <c r="E100" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F100" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G100" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3917,19 +3917,19 @@
         <v>TC100</v>
       </c>
       <c r="B101" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C101" t="str">
         <v>Launch</v>
       </c>
       <c r="D101" t="str">
-        <v>Render LifeMatrix logo verification #100</v>
+        <v>Render React web UI safely within Native Android boundaries verification #100</v>
       </c>
       <c r="E101" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F101" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G101" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3952,19 +3952,19 @@
         <v>TC101</v>
       </c>
       <c r="B102" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C102" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D102" t="str">
-        <v>Capture medical document verification #101</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #101</v>
       </c>
       <c r="E102" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F102" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G102" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3987,19 +3987,19 @@
         <v>TC102</v>
       </c>
       <c r="B103" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C103" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D103" t="str">
-        <v>Grant storage access verification #102</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #102</v>
       </c>
       <c r="E103" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F103" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G103" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4025,16 +4025,16 @@
         <v>Navigation</v>
       </c>
       <c r="C104" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D104" t="str">
-        <v>Verify back-button stack verification #103</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #103</v>
       </c>
       <c r="E104" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F104" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G104" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4057,19 +4057,19 @@
         <v>TC104</v>
       </c>
       <c r="B105" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C105" t="str">
         <v>Launch</v>
       </c>
       <c r="D105" t="str">
-        <v>Render LifeMatrix logo verification #104</v>
+        <v>Render React web UI safely within Native Android boundaries verification #104</v>
       </c>
       <c r="E105" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F105" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G105" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4092,19 +4092,19 @@
         <v>TC105</v>
       </c>
       <c r="B106" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C106" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D106" t="str">
-        <v>Capture medical document verification #105</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #105</v>
       </c>
       <c r="E106" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F106" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G106" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4127,19 +4127,19 @@
         <v>TC106</v>
       </c>
       <c r="B107" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C107" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D107" t="str">
-        <v>Grant storage access verification #106</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #106</v>
       </c>
       <c r="E107" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F107" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G107" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4165,16 +4165,16 @@
         <v>Navigation</v>
       </c>
       <c r="C108" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D108" t="str">
-        <v>Verify back-button stack verification #107</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #107</v>
       </c>
       <c r="E108" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F108" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G108" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4197,19 +4197,19 @@
         <v>TC108</v>
       </c>
       <c r="B109" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C109" t="str">
         <v>Launch</v>
       </c>
       <c r="D109" t="str">
-        <v>Render LifeMatrix logo verification #108</v>
+        <v>Render React web UI safely within Native Android boundaries verification #108</v>
       </c>
       <c r="E109" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F109" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G109" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4232,19 +4232,19 @@
         <v>TC109</v>
       </c>
       <c r="B110" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C110" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D110" t="str">
-        <v>Capture medical document verification #109</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #109</v>
       </c>
       <c r="E110" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F110" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G110" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4267,19 +4267,19 @@
         <v>TC110</v>
       </c>
       <c r="B111" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C111" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D111" t="str">
-        <v>Grant storage access verification #110</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #110</v>
       </c>
       <c r="E111" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F111" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G111" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4305,16 +4305,16 @@
         <v>Navigation</v>
       </c>
       <c r="C112" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D112" t="str">
-        <v>Verify back-button stack verification #111</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #111</v>
       </c>
       <c r="E112" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F112" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G112" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4337,19 +4337,19 @@
         <v>TC112</v>
       </c>
       <c r="B113" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C113" t="str">
         <v>Launch</v>
       </c>
       <c r="D113" t="str">
-        <v>Render LifeMatrix logo verification #112</v>
+        <v>Render React web UI safely within Native Android boundaries verification #112</v>
       </c>
       <c r="E113" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F113" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G113" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4372,19 +4372,19 @@
         <v>TC113</v>
       </c>
       <c r="B114" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C114" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D114" t="str">
-        <v>Capture medical document verification #113</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #113</v>
       </c>
       <c r="E114" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F114" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G114" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4407,19 +4407,19 @@
         <v>TC114</v>
       </c>
       <c r="B115" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C115" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D115" t="str">
-        <v>Grant storage access verification #114</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #114</v>
       </c>
       <c r="E115" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F115" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G115" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4445,16 +4445,16 @@
         <v>Navigation</v>
       </c>
       <c r="C116" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D116" t="str">
-        <v>Verify back-button stack verification #115</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #115</v>
       </c>
       <c r="E116" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F116" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G116" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4477,19 +4477,19 @@
         <v>TC116</v>
       </c>
       <c r="B117" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C117" t="str">
         <v>Launch</v>
       </c>
       <c r="D117" t="str">
-        <v>Render LifeMatrix logo verification #116</v>
+        <v>Render React web UI safely within Native Android boundaries verification #116</v>
       </c>
       <c r="E117" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F117" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G117" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4512,19 +4512,19 @@
         <v>TC117</v>
       </c>
       <c r="B118" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C118" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D118" t="str">
-        <v>Capture medical document verification #117</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #117</v>
       </c>
       <c r="E118" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F118" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G118" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4547,19 +4547,19 @@
         <v>TC118</v>
       </c>
       <c r="B119" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C119" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D119" t="str">
-        <v>Grant storage access verification #118</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #118</v>
       </c>
       <c r="E119" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F119" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G119" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4585,16 +4585,16 @@
         <v>Navigation</v>
       </c>
       <c r="C120" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D120" t="str">
-        <v>Verify back-button stack verification #119</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #119</v>
       </c>
       <c r="E120" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F120" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G120" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4617,19 +4617,19 @@
         <v>TC120</v>
       </c>
       <c r="B121" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C121" t="str">
         <v>Launch</v>
       </c>
       <c r="D121" t="str">
-        <v>Render LifeMatrix logo verification #120</v>
+        <v>Render React web UI safely within Native Android boundaries verification #120</v>
       </c>
       <c r="E121" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F121" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G121" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4652,19 +4652,19 @@
         <v>TC121</v>
       </c>
       <c r="B122" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C122" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D122" t="str">
-        <v>Capture medical document verification #121</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #121</v>
       </c>
       <c r="E122" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F122" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G122" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4687,19 +4687,19 @@
         <v>TC122</v>
       </c>
       <c r="B123" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C123" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D123" t="str">
-        <v>Grant storage access verification #122</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #122</v>
       </c>
       <c r="E123" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F123" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G123" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4725,16 +4725,16 @@
         <v>Navigation</v>
       </c>
       <c r="C124" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D124" t="str">
-        <v>Verify back-button stack verification #123</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #123</v>
       </c>
       <c r="E124" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F124" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G124" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4757,19 +4757,19 @@
         <v>TC124</v>
       </c>
       <c r="B125" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C125" t="str">
         <v>Launch</v>
       </c>
       <c r="D125" t="str">
-        <v>Render LifeMatrix logo verification #124</v>
+        <v>Render React web UI safely within Native Android boundaries verification #124</v>
       </c>
       <c r="E125" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F125" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G125" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4792,19 +4792,19 @@
         <v>TC125</v>
       </c>
       <c r="B126" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C126" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D126" t="str">
-        <v>Capture medical document verification #125</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #125</v>
       </c>
       <c r="E126" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F126" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G126" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4827,19 +4827,19 @@
         <v>TC126</v>
       </c>
       <c r="B127" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C127" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D127" t="str">
-        <v>Grant storage access verification #126</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #126</v>
       </c>
       <c r="E127" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F127" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G127" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4865,16 +4865,16 @@
         <v>Navigation</v>
       </c>
       <c r="C128" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D128" t="str">
-        <v>Verify back-button stack verification #127</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #127</v>
       </c>
       <c r="E128" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F128" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G128" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4897,19 +4897,19 @@
         <v>TC128</v>
       </c>
       <c r="B129" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C129" t="str">
         <v>Launch</v>
       </c>
       <c r="D129" t="str">
-        <v>Render LifeMatrix logo verification #128</v>
+        <v>Render React web UI safely within Native Android boundaries verification #128</v>
       </c>
       <c r="E129" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F129" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G129" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4932,19 +4932,19 @@
         <v>TC129</v>
       </c>
       <c r="B130" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C130" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D130" t="str">
-        <v>Capture medical document verification #129</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #129</v>
       </c>
       <c r="E130" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F130" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G130" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4967,19 +4967,19 @@
         <v>TC130</v>
       </c>
       <c r="B131" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C131" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D131" t="str">
-        <v>Grant storage access verification #130</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #130</v>
       </c>
       <c r="E131" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F131" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G131" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5005,16 +5005,16 @@
         <v>Navigation</v>
       </c>
       <c r="C132" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D132" t="str">
-        <v>Verify back-button stack verification #131</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #131</v>
       </c>
       <c r="E132" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F132" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G132" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5037,19 +5037,19 @@
         <v>TC132</v>
       </c>
       <c r="B133" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C133" t="str">
         <v>Launch</v>
       </c>
       <c r="D133" t="str">
-        <v>Render LifeMatrix logo verification #132</v>
+        <v>Render React web UI safely within Native Android boundaries verification #132</v>
       </c>
       <c r="E133" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F133" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G133" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5072,19 +5072,19 @@
         <v>TC133</v>
       </c>
       <c r="B134" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C134" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D134" t="str">
-        <v>Capture medical document verification #133</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #133</v>
       </c>
       <c r="E134" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F134" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G134" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5107,19 +5107,19 @@
         <v>TC134</v>
       </c>
       <c r="B135" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C135" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D135" t="str">
-        <v>Grant storage access verification #134</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #134</v>
       </c>
       <c r="E135" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F135" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G135" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5145,16 +5145,16 @@
         <v>Navigation</v>
       </c>
       <c r="C136" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D136" t="str">
-        <v>Verify back-button stack verification #135</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #135</v>
       </c>
       <c r="E136" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F136" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G136" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5177,19 +5177,19 @@
         <v>TC136</v>
       </c>
       <c r="B137" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C137" t="str">
         <v>Launch</v>
       </c>
       <c r="D137" t="str">
-        <v>Render LifeMatrix logo verification #136</v>
+        <v>Render React web UI safely within Native Android boundaries verification #136</v>
       </c>
       <c r="E137" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F137" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G137" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5212,19 +5212,19 @@
         <v>TC137</v>
       </c>
       <c r="B138" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C138" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D138" t="str">
-        <v>Capture medical document verification #137</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #137</v>
       </c>
       <c r="E138" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F138" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G138" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5247,19 +5247,19 @@
         <v>TC138</v>
       </c>
       <c r="B139" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C139" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D139" t="str">
-        <v>Grant storage access verification #138</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #138</v>
       </c>
       <c r="E139" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F139" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G139" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5285,16 +5285,16 @@
         <v>Navigation</v>
       </c>
       <c r="C140" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D140" t="str">
-        <v>Verify back-button stack verification #139</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #139</v>
       </c>
       <c r="E140" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F140" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G140" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5317,19 +5317,19 @@
         <v>TC140</v>
       </c>
       <c r="B141" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C141" t="str">
         <v>Launch</v>
       </c>
       <c r="D141" t="str">
-        <v>Render LifeMatrix logo verification #140</v>
+        <v>Render React web UI safely within Native Android boundaries verification #140</v>
       </c>
       <c r="E141" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F141" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G141" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5352,19 +5352,19 @@
         <v>TC141</v>
       </c>
       <c r="B142" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C142" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D142" t="str">
-        <v>Capture medical document verification #141</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #141</v>
       </c>
       <c r="E142" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F142" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G142" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5387,19 +5387,19 @@
         <v>TC142</v>
       </c>
       <c r="B143" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C143" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D143" t="str">
-        <v>Grant storage access verification #142</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #142</v>
       </c>
       <c r="E143" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F143" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G143" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5425,16 +5425,16 @@
         <v>Navigation</v>
       </c>
       <c r="C144" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D144" t="str">
-        <v>Verify back-button stack verification #143</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #143</v>
       </c>
       <c r="E144" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F144" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G144" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5457,19 +5457,19 @@
         <v>TC144</v>
       </c>
       <c r="B145" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C145" t="str">
         <v>Launch</v>
       </c>
       <c r="D145" t="str">
-        <v>Render LifeMatrix logo verification #144</v>
+        <v>Render React web UI safely within Native Android boundaries verification #144</v>
       </c>
       <c r="E145" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F145" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G145" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5492,19 +5492,19 @@
         <v>TC145</v>
       </c>
       <c r="B146" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C146" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D146" t="str">
-        <v>Capture medical document verification #145</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #145</v>
       </c>
       <c r="E146" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F146" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G146" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5527,19 +5527,19 @@
         <v>TC146</v>
       </c>
       <c r="B147" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C147" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D147" t="str">
-        <v>Grant storage access verification #146</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #146</v>
       </c>
       <c r="E147" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F147" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G147" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5565,16 +5565,16 @@
         <v>Navigation</v>
       </c>
       <c r="C148" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D148" t="str">
-        <v>Verify back-button stack verification #147</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #147</v>
       </c>
       <c r="E148" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F148" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G148" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5597,19 +5597,19 @@
         <v>TC148</v>
       </c>
       <c r="B149" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C149" t="str">
         <v>Launch</v>
       </c>
       <c r="D149" t="str">
-        <v>Render LifeMatrix logo verification #148</v>
+        <v>Render React web UI safely within Native Android boundaries verification #148</v>
       </c>
       <c r="E149" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F149" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G149" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5632,19 +5632,19 @@
         <v>TC149</v>
       </c>
       <c r="B150" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C150" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D150" t="str">
-        <v>Capture medical document verification #149</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #149</v>
       </c>
       <c r="E150" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F150" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G150" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5667,19 +5667,19 @@
         <v>TC150</v>
       </c>
       <c r="B151" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C151" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D151" t="str">
-        <v>Grant storage access verification #150</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #150</v>
       </c>
       <c r="E151" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F151" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G151" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5705,16 +5705,16 @@
         <v>Navigation</v>
       </c>
       <c r="C152" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D152" t="str">
-        <v>Verify back-button stack verification #151</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #151</v>
       </c>
       <c r="E152" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F152" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G152" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5737,19 +5737,19 @@
         <v>TC152</v>
       </c>
       <c r="B153" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C153" t="str">
         <v>Launch</v>
       </c>
       <c r="D153" t="str">
-        <v>Render LifeMatrix logo verification #152</v>
+        <v>Render React web UI safely within Native Android boundaries verification #152</v>
       </c>
       <c r="E153" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F153" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G153" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5772,19 +5772,19 @@
         <v>TC153</v>
       </c>
       <c r="B154" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C154" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D154" t="str">
-        <v>Capture medical document verification #153</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #153</v>
       </c>
       <c r="E154" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F154" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G154" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5807,19 +5807,19 @@
         <v>TC154</v>
       </c>
       <c r="B155" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C155" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D155" t="str">
-        <v>Grant storage access verification #154</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #154</v>
       </c>
       <c r="E155" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F155" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G155" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5845,16 +5845,16 @@
         <v>Navigation</v>
       </c>
       <c r="C156" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D156" t="str">
-        <v>Verify back-button stack verification #155</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #155</v>
       </c>
       <c r="E156" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F156" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G156" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5877,19 +5877,19 @@
         <v>TC156</v>
       </c>
       <c r="B157" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C157" t="str">
         <v>Launch</v>
       </c>
       <c r="D157" t="str">
-        <v>Render LifeMatrix logo verification #156</v>
+        <v>Render React web UI safely within Native Android boundaries verification #156</v>
       </c>
       <c r="E157" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F157" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G157" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5912,19 +5912,19 @@
         <v>TC157</v>
       </c>
       <c r="B158" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C158" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D158" t="str">
-        <v>Capture medical document verification #157</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #157</v>
       </c>
       <c r="E158" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F158" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G158" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5947,19 +5947,19 @@
         <v>TC158</v>
       </c>
       <c r="B159" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C159" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D159" t="str">
-        <v>Grant storage access verification #158</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #158</v>
       </c>
       <c r="E159" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F159" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G159" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5985,16 +5985,16 @@
         <v>Navigation</v>
       </c>
       <c r="C160" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D160" t="str">
-        <v>Verify back-button stack verification #159</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #159</v>
       </c>
       <c r="E160" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F160" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G160" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6017,19 +6017,19 @@
         <v>TC160</v>
       </c>
       <c r="B161" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C161" t="str">
         <v>Launch</v>
       </c>
       <c r="D161" t="str">
-        <v>Render LifeMatrix logo verification #160</v>
+        <v>Render React web UI safely within Native Android boundaries verification #160</v>
       </c>
       <c r="E161" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F161" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G161" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6052,19 +6052,19 @@
         <v>TC161</v>
       </c>
       <c r="B162" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C162" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D162" t="str">
-        <v>Capture medical document verification #161</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #161</v>
       </c>
       <c r="E162" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F162" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G162" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6087,19 +6087,19 @@
         <v>TC162</v>
       </c>
       <c r="B163" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C163" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D163" t="str">
-        <v>Grant storage access verification #162</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #162</v>
       </c>
       <c r="E163" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F163" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G163" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6125,16 +6125,16 @@
         <v>Navigation</v>
       </c>
       <c r="C164" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D164" t="str">
-        <v>Verify back-button stack verification #163</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #163</v>
       </c>
       <c r="E164" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F164" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G164" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6157,19 +6157,19 @@
         <v>TC164</v>
       </c>
       <c r="B165" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C165" t="str">
         <v>Launch</v>
       </c>
       <c r="D165" t="str">
-        <v>Render LifeMatrix logo verification #164</v>
+        <v>Render React web UI safely within Native Android boundaries verification #164</v>
       </c>
       <c r="E165" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F165" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G165" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6192,19 +6192,19 @@
         <v>TC165</v>
       </c>
       <c r="B166" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C166" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D166" t="str">
-        <v>Capture medical document verification #165</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #165</v>
       </c>
       <c r="E166" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F166" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G166" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6227,19 +6227,19 @@
         <v>TC166</v>
       </c>
       <c r="B167" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C167" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D167" t="str">
-        <v>Grant storage access verification #166</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #166</v>
       </c>
       <c r="E167" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F167" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G167" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6265,16 +6265,16 @@
         <v>Navigation</v>
       </c>
       <c r="C168" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D168" t="str">
-        <v>Verify back-button stack verification #167</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #167</v>
       </c>
       <c r="E168" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F168" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G168" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6297,19 +6297,19 @@
         <v>TC168</v>
       </c>
       <c r="B169" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C169" t="str">
         <v>Launch</v>
       </c>
       <c r="D169" t="str">
-        <v>Render LifeMatrix logo verification #168</v>
+        <v>Render React web UI safely within Native Android boundaries verification #168</v>
       </c>
       <c r="E169" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F169" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G169" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6332,19 +6332,19 @@
         <v>TC169</v>
       </c>
       <c r="B170" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C170" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D170" t="str">
-        <v>Capture medical document verification #169</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #169</v>
       </c>
       <c r="E170" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F170" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G170" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6367,19 +6367,19 @@
         <v>TC170</v>
       </c>
       <c r="B171" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C171" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D171" t="str">
-        <v>Grant storage access verification #170</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #170</v>
       </c>
       <c r="E171" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F171" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G171" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6405,16 +6405,16 @@
         <v>Navigation</v>
       </c>
       <c r="C172" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D172" t="str">
-        <v>Verify back-button stack verification #171</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #171</v>
       </c>
       <c r="E172" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F172" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G172" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6437,19 +6437,19 @@
         <v>TC172</v>
       </c>
       <c r="B173" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C173" t="str">
         <v>Launch</v>
       </c>
       <c r="D173" t="str">
-        <v>Render LifeMatrix logo verification #172</v>
+        <v>Render React web UI safely within Native Android boundaries verification #172</v>
       </c>
       <c r="E173" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F173" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G173" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6472,19 +6472,19 @@
         <v>TC173</v>
       </c>
       <c r="B174" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C174" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D174" t="str">
-        <v>Capture medical document verification #173</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #173</v>
       </c>
       <c r="E174" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F174" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G174" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6507,19 +6507,19 @@
         <v>TC174</v>
       </c>
       <c r="B175" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C175" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D175" t="str">
-        <v>Grant storage access verification #174</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #174</v>
       </c>
       <c r="E175" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F175" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G175" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6545,16 +6545,16 @@
         <v>Navigation</v>
       </c>
       <c r="C176" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D176" t="str">
-        <v>Verify back-button stack verification #175</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #175</v>
       </c>
       <c r="E176" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F176" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G176" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6577,19 +6577,19 @@
         <v>TC176</v>
       </c>
       <c r="B177" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C177" t="str">
         <v>Launch</v>
       </c>
       <c r="D177" t="str">
-        <v>Render LifeMatrix logo verification #176</v>
+        <v>Render React web UI safely within Native Android boundaries verification #176</v>
       </c>
       <c r="E177" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F177" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G177" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6612,19 +6612,19 @@
         <v>TC177</v>
       </c>
       <c r="B178" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C178" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D178" t="str">
-        <v>Capture medical document verification #177</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #177</v>
       </c>
       <c r="E178" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F178" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G178" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6647,19 +6647,19 @@
         <v>TC178</v>
       </c>
       <c r="B179" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C179" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D179" t="str">
-        <v>Grant storage access verification #178</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #178</v>
       </c>
       <c r="E179" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F179" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G179" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6685,16 +6685,16 @@
         <v>Navigation</v>
       </c>
       <c r="C180" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D180" t="str">
-        <v>Verify back-button stack verification #179</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #179</v>
       </c>
       <c r="E180" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F180" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G180" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6717,19 +6717,19 @@
         <v>TC180</v>
       </c>
       <c r="B181" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C181" t="str">
         <v>Launch</v>
       </c>
       <c r="D181" t="str">
-        <v>Render LifeMatrix logo verification #180</v>
+        <v>Render React web UI safely within Native Android boundaries verification #180</v>
       </c>
       <c r="E181" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F181" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G181" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6752,19 +6752,19 @@
         <v>TC181</v>
       </c>
       <c r="B182" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C182" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D182" t="str">
-        <v>Capture medical document verification #181</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #181</v>
       </c>
       <c r="E182" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F182" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G182" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6787,19 +6787,19 @@
         <v>TC182</v>
       </c>
       <c r="B183" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C183" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D183" t="str">
-        <v>Grant storage access verification #182</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #182</v>
       </c>
       <c r="E183" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F183" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G183" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6825,16 +6825,16 @@
         <v>Navigation</v>
       </c>
       <c r="C184" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D184" t="str">
-        <v>Verify back-button stack verification #183</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #183</v>
       </c>
       <c r="E184" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F184" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G184" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6857,19 +6857,19 @@
         <v>TC184</v>
       </c>
       <c r="B185" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C185" t="str">
         <v>Launch</v>
       </c>
       <c r="D185" t="str">
-        <v>Render LifeMatrix logo verification #184</v>
+        <v>Render React web UI safely within Native Android boundaries verification #184</v>
       </c>
       <c r="E185" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F185" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G185" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6892,19 +6892,19 @@
         <v>TC185</v>
       </c>
       <c r="B186" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C186" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D186" t="str">
-        <v>Capture medical document verification #185</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #185</v>
       </c>
       <c r="E186" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F186" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G186" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6927,19 +6927,19 @@
         <v>TC186</v>
       </c>
       <c r="B187" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C187" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D187" t="str">
-        <v>Grant storage access verification #186</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #186</v>
       </c>
       <c r="E187" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F187" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G187" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6965,16 +6965,16 @@
         <v>Navigation</v>
       </c>
       <c r="C188" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D188" t="str">
-        <v>Verify back-button stack verification #187</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #187</v>
       </c>
       <c r="E188" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F188" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G188" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6997,19 +6997,19 @@
         <v>TC188</v>
       </c>
       <c r="B189" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C189" t="str">
         <v>Launch</v>
       </c>
       <c r="D189" t="str">
-        <v>Render LifeMatrix logo verification #188</v>
+        <v>Render React web UI safely within Native Android boundaries verification #188</v>
       </c>
       <c r="E189" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F189" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G189" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7032,19 +7032,19 @@
         <v>TC189</v>
       </c>
       <c r="B190" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C190" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D190" t="str">
-        <v>Capture medical document verification #189</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #189</v>
       </c>
       <c r="E190" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F190" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G190" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7067,19 +7067,19 @@
         <v>TC190</v>
       </c>
       <c r="B191" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C191" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D191" t="str">
-        <v>Grant storage access verification #190</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #190</v>
       </c>
       <c r="E191" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F191" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G191" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7105,16 +7105,16 @@
         <v>Navigation</v>
       </c>
       <c r="C192" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D192" t="str">
-        <v>Verify back-button stack verification #191</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #191</v>
       </c>
       <c r="E192" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F192" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G192" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7137,19 +7137,19 @@
         <v>TC192</v>
       </c>
       <c r="B193" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C193" t="str">
         <v>Launch</v>
       </c>
       <c r="D193" t="str">
-        <v>Render LifeMatrix logo verification #192</v>
+        <v>Render React web UI safely within Native Android boundaries verification #192</v>
       </c>
       <c r="E193" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F193" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G193" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7172,19 +7172,19 @@
         <v>TC193</v>
       </c>
       <c r="B194" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C194" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D194" t="str">
-        <v>Capture medical document verification #193</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #193</v>
       </c>
       <c r="E194" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F194" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G194" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7207,19 +7207,19 @@
         <v>TC194</v>
       </c>
       <c r="B195" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C195" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D195" t="str">
-        <v>Grant storage access verification #194</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #194</v>
       </c>
       <c r="E195" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F195" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G195" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7245,16 +7245,16 @@
         <v>Navigation</v>
       </c>
       <c r="C196" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D196" t="str">
-        <v>Verify back-button stack verification #195</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #195</v>
       </c>
       <c r="E196" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F196" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G196" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7277,19 +7277,19 @@
         <v>TC196</v>
       </c>
       <c r="B197" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C197" t="str">
         <v>Launch</v>
       </c>
       <c r="D197" t="str">
-        <v>Render LifeMatrix logo verification #196</v>
+        <v>Render React web UI safely within Native Android boundaries verification #196</v>
       </c>
       <c r="E197" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F197" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G197" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7312,19 +7312,19 @@
         <v>TC197</v>
       </c>
       <c r="B198" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C198" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D198" t="str">
-        <v>Capture medical document verification #197</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #197</v>
       </c>
       <c r="E198" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F198" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G198" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7347,19 +7347,19 @@
         <v>TC198</v>
       </c>
       <c r="B199" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C199" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D199" t="str">
-        <v>Grant storage access verification #198</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #198</v>
       </c>
       <c r="E199" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F199" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G199" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7385,16 +7385,16 @@
         <v>Navigation</v>
       </c>
       <c r="C200" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D200" t="str">
-        <v>Verify back-button stack verification #199</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #199</v>
       </c>
       <c r="E200" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F200" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G200" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7417,19 +7417,19 @@
         <v>TC200</v>
       </c>
       <c r="B201" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C201" t="str">
         <v>Launch</v>
       </c>
       <c r="D201" t="str">
-        <v>Render LifeMatrix logo verification #200</v>
+        <v>Render React web UI safely within Native Android boundaries verification #200</v>
       </c>
       <c r="E201" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F201" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G201" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7452,19 +7452,19 @@
         <v>TC201</v>
       </c>
       <c r="B202" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C202" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D202" t="str">
-        <v>Capture medical document verification #201</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #201</v>
       </c>
       <c r="E202" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F202" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G202" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7487,19 +7487,19 @@
         <v>TC202</v>
       </c>
       <c r="B203" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C203" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D203" t="str">
-        <v>Grant storage access verification #202</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #202</v>
       </c>
       <c r="E203" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F203" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G203" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7525,16 +7525,16 @@
         <v>Navigation</v>
       </c>
       <c r="C204" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D204" t="str">
-        <v>Verify back-button stack verification #203</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #203</v>
       </c>
       <c r="E204" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F204" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G204" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7557,19 +7557,19 @@
         <v>TC204</v>
       </c>
       <c r="B205" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C205" t="str">
         <v>Launch</v>
       </c>
       <c r="D205" t="str">
-        <v>Render LifeMatrix logo verification #204</v>
+        <v>Render React web UI safely within Native Android boundaries verification #204</v>
       </c>
       <c r="E205" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F205" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G205" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7592,19 +7592,19 @@
         <v>TC205</v>
       </c>
       <c r="B206" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C206" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D206" t="str">
-        <v>Capture medical document verification #205</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #205</v>
       </c>
       <c r="E206" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F206" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G206" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7627,19 +7627,19 @@
         <v>TC206</v>
       </c>
       <c r="B207" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C207" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D207" t="str">
-        <v>Grant storage access verification #206</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #206</v>
       </c>
       <c r="E207" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F207" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G207" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7665,16 +7665,16 @@
         <v>Navigation</v>
       </c>
       <c r="C208" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D208" t="str">
-        <v>Verify back-button stack verification #207</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #207</v>
       </c>
       <c r="E208" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F208" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G208" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7697,19 +7697,19 @@
         <v>TC208</v>
       </c>
       <c r="B209" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C209" t="str">
         <v>Launch</v>
       </c>
       <c r="D209" t="str">
-        <v>Render LifeMatrix logo verification #208</v>
+        <v>Render React web UI safely within Native Android boundaries verification #208</v>
       </c>
       <c r="E209" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F209" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G209" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7732,19 +7732,19 @@
         <v>TC209</v>
       </c>
       <c r="B210" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C210" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D210" t="str">
-        <v>Capture medical document verification #209</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #209</v>
       </c>
       <c r="E210" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F210" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G210" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7767,19 +7767,19 @@
         <v>TC210</v>
       </c>
       <c r="B211" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C211" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D211" t="str">
-        <v>Grant storage access verification #210</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #210</v>
       </c>
       <c r="E211" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F211" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G211" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7805,16 +7805,16 @@
         <v>Navigation</v>
       </c>
       <c r="C212" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D212" t="str">
-        <v>Verify back-button stack verification #211</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #211</v>
       </c>
       <c r="E212" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F212" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G212" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7837,19 +7837,19 @@
         <v>TC212</v>
       </c>
       <c r="B213" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C213" t="str">
         <v>Launch</v>
       </c>
       <c r="D213" t="str">
-        <v>Render LifeMatrix logo verification #212</v>
+        <v>Render React web UI safely within Native Android boundaries verification #212</v>
       </c>
       <c r="E213" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F213" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G213" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7872,19 +7872,19 @@
         <v>TC213</v>
       </c>
       <c r="B214" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C214" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D214" t="str">
-        <v>Capture medical document verification #213</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #213</v>
       </c>
       <c r="E214" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F214" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G214" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7907,19 +7907,19 @@
         <v>TC214</v>
       </c>
       <c r="B215" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C215" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D215" t="str">
-        <v>Grant storage access verification #214</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #214</v>
       </c>
       <c r="E215" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F215" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G215" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7945,16 +7945,16 @@
         <v>Navigation</v>
       </c>
       <c r="C216" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D216" t="str">
-        <v>Verify back-button stack verification #215</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #215</v>
       </c>
       <c r="E216" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F216" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G216" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7977,19 +7977,19 @@
         <v>TC216</v>
       </c>
       <c r="B217" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C217" t="str">
         <v>Launch</v>
       </c>
       <c r="D217" t="str">
-        <v>Render LifeMatrix logo verification #216</v>
+        <v>Render React web UI safely within Native Android boundaries verification #216</v>
       </c>
       <c r="E217" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F217" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G217" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8012,19 +8012,19 @@
         <v>TC217</v>
       </c>
       <c r="B218" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C218" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D218" t="str">
-        <v>Capture medical document verification #217</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #217</v>
       </c>
       <c r="E218" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F218" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G218" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8047,19 +8047,19 @@
         <v>TC218</v>
       </c>
       <c r="B219" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C219" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D219" t="str">
-        <v>Grant storage access verification #218</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #218</v>
       </c>
       <c r="E219" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F219" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G219" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8085,16 +8085,16 @@
         <v>Navigation</v>
       </c>
       <c r="C220" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D220" t="str">
-        <v>Verify back-button stack verification #219</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #219</v>
       </c>
       <c r="E220" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F220" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G220" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8117,19 +8117,19 @@
         <v>TC220</v>
       </c>
       <c r="B221" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C221" t="str">
         <v>Launch</v>
       </c>
       <c r="D221" t="str">
-        <v>Render LifeMatrix logo verification #220</v>
+        <v>Render React web UI safely within Native Android boundaries verification #220</v>
       </c>
       <c r="E221" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F221" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G221" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8152,19 +8152,19 @@
         <v>TC221</v>
       </c>
       <c r="B222" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C222" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D222" t="str">
-        <v>Capture medical document verification #221</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #221</v>
       </c>
       <c r="E222" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F222" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G222" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8187,19 +8187,19 @@
         <v>TC222</v>
       </c>
       <c r="B223" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C223" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D223" t="str">
-        <v>Grant storage access verification #222</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #222</v>
       </c>
       <c r="E223" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F223" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G223" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8225,16 +8225,16 @@
         <v>Navigation</v>
       </c>
       <c r="C224" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D224" t="str">
-        <v>Verify back-button stack verification #223</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #223</v>
       </c>
       <c r="E224" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F224" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G224" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8257,19 +8257,19 @@
         <v>TC224</v>
       </c>
       <c r="B225" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C225" t="str">
         <v>Launch</v>
       </c>
       <c r="D225" t="str">
-        <v>Render LifeMatrix logo verification #224</v>
+        <v>Render React web UI safely within Native Android boundaries verification #224</v>
       </c>
       <c r="E225" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F225" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G225" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8292,19 +8292,19 @@
         <v>TC225</v>
       </c>
       <c r="B226" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C226" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D226" t="str">
-        <v>Capture medical document verification #225</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #225</v>
       </c>
       <c r="E226" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F226" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G226" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8327,19 +8327,19 @@
         <v>TC226</v>
       </c>
       <c r="B227" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C227" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D227" t="str">
-        <v>Grant storage access verification #226</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #226</v>
       </c>
       <c r="E227" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F227" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G227" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8365,16 +8365,16 @@
         <v>Navigation</v>
       </c>
       <c r="C228" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D228" t="str">
-        <v>Verify back-button stack verification #227</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #227</v>
       </c>
       <c r="E228" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F228" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G228" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8397,19 +8397,19 @@
         <v>TC228</v>
       </c>
       <c r="B229" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C229" t="str">
         <v>Launch</v>
       </c>
       <c r="D229" t="str">
-        <v>Render LifeMatrix logo verification #228</v>
+        <v>Render React web UI safely within Native Android boundaries verification #228</v>
       </c>
       <c r="E229" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F229" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G229" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8432,19 +8432,19 @@
         <v>TC229</v>
       </c>
       <c r="B230" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C230" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D230" t="str">
-        <v>Capture medical document verification #229</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #229</v>
       </c>
       <c r="E230" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F230" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G230" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8467,19 +8467,19 @@
         <v>TC230</v>
       </c>
       <c r="B231" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C231" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D231" t="str">
-        <v>Grant storage access verification #230</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #230</v>
       </c>
       <c r="E231" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F231" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G231" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8505,16 +8505,16 @@
         <v>Navigation</v>
       </c>
       <c r="C232" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D232" t="str">
-        <v>Verify back-button stack verification #231</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #231</v>
       </c>
       <c r="E232" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F232" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G232" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8537,19 +8537,19 @@
         <v>TC232</v>
       </c>
       <c r="B233" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C233" t="str">
         <v>Launch</v>
       </c>
       <c r="D233" t="str">
-        <v>Render LifeMatrix logo verification #232</v>
+        <v>Render React web UI safely within Native Android boundaries verification #232</v>
       </c>
       <c r="E233" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F233" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G233" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8572,19 +8572,19 @@
         <v>TC233</v>
       </c>
       <c r="B234" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C234" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D234" t="str">
-        <v>Capture medical document verification #233</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #233</v>
       </c>
       <c r="E234" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F234" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G234" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8607,19 +8607,19 @@
         <v>TC234</v>
       </c>
       <c r="B235" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C235" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D235" t="str">
-        <v>Grant storage access verification #234</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #234</v>
       </c>
       <c r="E235" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F235" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G235" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8645,16 +8645,16 @@
         <v>Navigation</v>
       </c>
       <c r="C236" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D236" t="str">
-        <v>Verify back-button stack verification #235</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #235</v>
       </c>
       <c r="E236" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F236" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G236" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8677,19 +8677,19 @@
         <v>TC236</v>
       </c>
       <c r="B237" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C237" t="str">
         <v>Launch</v>
       </c>
       <c r="D237" t="str">
-        <v>Render LifeMatrix logo verification #236</v>
+        <v>Render React web UI safely within Native Android boundaries verification #236</v>
       </c>
       <c r="E237" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F237" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G237" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8712,19 +8712,19 @@
         <v>TC237</v>
       </c>
       <c r="B238" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C238" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D238" t="str">
-        <v>Capture medical document verification #237</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #237</v>
       </c>
       <c r="E238" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F238" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G238" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8747,19 +8747,19 @@
         <v>TC238</v>
       </c>
       <c r="B239" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C239" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D239" t="str">
-        <v>Grant storage access verification #238</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #238</v>
       </c>
       <c r="E239" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F239" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G239" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8785,16 +8785,16 @@
         <v>Navigation</v>
       </c>
       <c r="C240" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D240" t="str">
-        <v>Verify back-button stack verification #239</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #239</v>
       </c>
       <c r="E240" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F240" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G240" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8817,19 +8817,19 @@
         <v>TC240</v>
       </c>
       <c r="B241" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C241" t="str">
         <v>Launch</v>
       </c>
       <c r="D241" t="str">
-        <v>Render LifeMatrix logo verification #240</v>
+        <v>Render React web UI safely within Native Android boundaries verification #240</v>
       </c>
       <c r="E241" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F241" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G241" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8852,19 +8852,19 @@
         <v>TC241</v>
       </c>
       <c r="B242" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C242" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D242" t="str">
-        <v>Capture medical document verification #241</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #241</v>
       </c>
       <c r="E242" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F242" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G242" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8887,19 +8887,19 @@
         <v>TC242</v>
       </c>
       <c r="B243" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C243" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D243" t="str">
-        <v>Grant storage access verification #242</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #242</v>
       </c>
       <c r="E243" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F243" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G243" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8925,16 +8925,16 @@
         <v>Navigation</v>
       </c>
       <c r="C244" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D244" t="str">
-        <v>Verify back-button stack verification #243</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #243</v>
       </c>
       <c r="E244" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F244" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G244" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8957,19 +8957,19 @@
         <v>TC244</v>
       </c>
       <c r="B245" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C245" t="str">
         <v>Launch</v>
       </c>
       <c r="D245" t="str">
-        <v>Render LifeMatrix logo verification #244</v>
+        <v>Render React web UI safely within Native Android boundaries verification #244</v>
       </c>
       <c r="E245" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F245" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G245" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8992,19 +8992,19 @@
         <v>TC245</v>
       </c>
       <c r="B246" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C246" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D246" t="str">
-        <v>Capture medical document verification #245</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #245</v>
       </c>
       <c r="E246" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F246" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G246" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9027,19 +9027,19 @@
         <v>TC246</v>
       </c>
       <c r="B247" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C247" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D247" t="str">
-        <v>Grant storage access verification #246</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #246</v>
       </c>
       <c r="E247" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F247" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G247" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9065,16 +9065,16 @@
         <v>Navigation</v>
       </c>
       <c r="C248" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D248" t="str">
-        <v>Verify back-button stack verification #247</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #247</v>
       </c>
       <c r="E248" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F248" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G248" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9097,19 +9097,19 @@
         <v>TC248</v>
       </c>
       <c r="B249" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C249" t="str">
         <v>Launch</v>
       </c>
       <c r="D249" t="str">
-        <v>Render LifeMatrix logo verification #248</v>
+        <v>Render React web UI safely within Native Android boundaries verification #248</v>
       </c>
       <c r="E249" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F249" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G249" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9132,19 +9132,19 @@
         <v>TC249</v>
       </c>
       <c r="B250" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C250" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D250" t="str">
-        <v>Capture medical document verification #249</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #249</v>
       </c>
       <c r="E250" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F250" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G250" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9167,19 +9167,19 @@
         <v>TC250</v>
       </c>
       <c r="B251" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C251" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D251" t="str">
-        <v>Grant storage access verification #250</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #250</v>
       </c>
       <c r="E251" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F251" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G251" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9205,16 +9205,16 @@
         <v>Navigation</v>
       </c>
       <c r="C252" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D252" t="str">
-        <v>Verify back-button stack verification #251</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #251</v>
       </c>
       <c r="E252" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F252" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G252" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9237,19 +9237,19 @@
         <v>TC252</v>
       </c>
       <c r="B253" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C253" t="str">
         <v>Launch</v>
       </c>
       <c r="D253" t="str">
-        <v>Render LifeMatrix logo verification #252</v>
+        <v>Render React web UI safely within Native Android boundaries verification #252</v>
       </c>
       <c r="E253" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F253" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G253" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9272,19 +9272,19 @@
         <v>TC253</v>
       </c>
       <c r="B254" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C254" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D254" t="str">
-        <v>Capture medical document verification #253</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #253</v>
       </c>
       <c r="E254" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F254" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G254" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9307,19 +9307,19 @@
         <v>TC254</v>
       </c>
       <c r="B255" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C255" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D255" t="str">
-        <v>Grant storage access verification #254</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #254</v>
       </c>
       <c r="E255" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F255" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G255" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9345,16 +9345,16 @@
         <v>Navigation</v>
       </c>
       <c r="C256" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D256" t="str">
-        <v>Verify back-button stack verification #255</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #255</v>
       </c>
       <c r="E256" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F256" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G256" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9377,19 +9377,19 @@
         <v>TC256</v>
       </c>
       <c r="B257" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C257" t="str">
         <v>Launch</v>
       </c>
       <c r="D257" t="str">
-        <v>Render LifeMatrix logo verification #256</v>
+        <v>Render React web UI safely within Native Android boundaries verification #256</v>
       </c>
       <c r="E257" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F257" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G257" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9412,19 +9412,19 @@
         <v>TC257</v>
       </c>
       <c r="B258" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C258" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D258" t="str">
-        <v>Capture medical document verification #257</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #257</v>
       </c>
       <c r="E258" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F258" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G258" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9447,19 +9447,19 @@
         <v>TC258</v>
       </c>
       <c r="B259" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C259" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D259" t="str">
-        <v>Grant storage access verification #258</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #258</v>
       </c>
       <c r="E259" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F259" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G259" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9485,16 +9485,16 @@
         <v>Navigation</v>
       </c>
       <c r="C260" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D260" t="str">
-        <v>Verify back-button stack verification #259</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #259</v>
       </c>
       <c r="E260" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F260" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G260" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9517,19 +9517,19 @@
         <v>TC260</v>
       </c>
       <c r="B261" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C261" t="str">
         <v>Launch</v>
       </c>
       <c r="D261" t="str">
-        <v>Render LifeMatrix logo verification #260</v>
+        <v>Render React web UI safely within Native Android boundaries verification #260</v>
       </c>
       <c r="E261" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F261" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G261" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9552,19 +9552,19 @@
         <v>TC261</v>
       </c>
       <c r="B262" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C262" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D262" t="str">
-        <v>Capture medical document verification #261</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #261</v>
       </c>
       <c r="E262" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F262" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G262" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9587,19 +9587,19 @@
         <v>TC262</v>
       </c>
       <c r="B263" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C263" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D263" t="str">
-        <v>Grant storage access verification #262</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #262</v>
       </c>
       <c r="E263" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F263" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G263" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9625,16 +9625,16 @@
         <v>Navigation</v>
       </c>
       <c r="C264" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D264" t="str">
-        <v>Verify back-button stack verification #263</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #263</v>
       </c>
       <c r="E264" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F264" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G264" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9657,19 +9657,19 @@
         <v>TC264</v>
       </c>
       <c r="B265" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C265" t="str">
         <v>Launch</v>
       </c>
       <c r="D265" t="str">
-        <v>Render LifeMatrix logo verification #264</v>
+        <v>Render React web UI safely within Native Android boundaries verification #264</v>
       </c>
       <c r="E265" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F265" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G265" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9692,19 +9692,19 @@
         <v>TC265</v>
       </c>
       <c r="B266" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C266" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D266" t="str">
-        <v>Capture medical document verification #265</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #265</v>
       </c>
       <c r="E266" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F266" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G266" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9727,19 +9727,19 @@
         <v>TC266</v>
       </c>
       <c r="B267" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C267" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D267" t="str">
-        <v>Grant storage access verification #266</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #266</v>
       </c>
       <c r="E267" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F267" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G267" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9765,16 +9765,16 @@
         <v>Navigation</v>
       </c>
       <c r="C268" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D268" t="str">
-        <v>Verify back-button stack verification #267</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #267</v>
       </c>
       <c r="E268" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F268" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G268" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9797,19 +9797,19 @@
         <v>TC268</v>
       </c>
       <c r="B269" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C269" t="str">
         <v>Launch</v>
       </c>
       <c r="D269" t="str">
-        <v>Render LifeMatrix logo verification #268</v>
+        <v>Render React web UI safely within Native Android boundaries verification #268</v>
       </c>
       <c r="E269" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F269" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G269" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9832,19 +9832,19 @@
         <v>TC269</v>
       </c>
       <c r="B270" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C270" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D270" t="str">
-        <v>Capture medical document verification #269</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #269</v>
       </c>
       <c r="E270" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F270" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G270" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9867,19 +9867,19 @@
         <v>TC270</v>
       </c>
       <c r="B271" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C271" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D271" t="str">
-        <v>Grant storage access verification #270</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #270</v>
       </c>
       <c r="E271" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F271" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G271" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9905,16 +9905,16 @@
         <v>Navigation</v>
       </c>
       <c r="C272" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D272" t="str">
-        <v>Verify back-button stack verification #271</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #271</v>
       </c>
       <c r="E272" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F272" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G272" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9937,19 +9937,19 @@
         <v>TC272</v>
       </c>
       <c r="B273" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C273" t="str">
         <v>Launch</v>
       </c>
       <c r="D273" t="str">
-        <v>Render LifeMatrix logo verification #272</v>
+        <v>Render React web UI safely within Native Android boundaries verification #272</v>
       </c>
       <c r="E273" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F273" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G273" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9972,19 +9972,19 @@
         <v>TC273</v>
       </c>
       <c r="B274" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C274" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D274" t="str">
-        <v>Capture medical document verification #273</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #273</v>
       </c>
       <c r="E274" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F274" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G274" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10007,19 +10007,19 @@
         <v>TC274</v>
       </c>
       <c r="B275" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C275" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D275" t="str">
-        <v>Grant storage access verification #274</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #274</v>
       </c>
       <c r="E275" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F275" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G275" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10045,16 +10045,16 @@
         <v>Navigation</v>
       </c>
       <c r="C276" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D276" t="str">
-        <v>Verify back-button stack verification #275</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #275</v>
       </c>
       <c r="E276" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F276" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G276" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10077,19 +10077,19 @@
         <v>TC276</v>
       </c>
       <c r="B277" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C277" t="str">
         <v>Launch</v>
       </c>
       <c r="D277" t="str">
-        <v>Render LifeMatrix logo verification #276</v>
+        <v>Render React web UI safely within Native Android boundaries verification #276</v>
       </c>
       <c r="E277" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F277" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G277" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10112,19 +10112,19 @@
         <v>TC277</v>
       </c>
       <c r="B278" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C278" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D278" t="str">
-        <v>Capture medical document verification #277</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #277</v>
       </c>
       <c r="E278" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F278" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G278" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10147,19 +10147,19 @@
         <v>TC278</v>
       </c>
       <c r="B279" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C279" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D279" t="str">
-        <v>Grant storage access verification #278</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #278</v>
       </c>
       <c r="E279" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F279" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G279" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10185,16 +10185,16 @@
         <v>Navigation</v>
       </c>
       <c r="C280" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D280" t="str">
-        <v>Verify back-button stack verification #279</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #279</v>
       </c>
       <c r="E280" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F280" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G280" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10217,19 +10217,19 @@
         <v>TC280</v>
       </c>
       <c r="B281" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C281" t="str">
         <v>Launch</v>
       </c>
       <c r="D281" t="str">
-        <v>Render LifeMatrix logo verification #280</v>
+        <v>Render React web UI safely within Native Android boundaries verification #280</v>
       </c>
       <c r="E281" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F281" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G281" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10252,19 +10252,19 @@
         <v>TC281</v>
       </c>
       <c r="B282" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C282" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D282" t="str">
-        <v>Capture medical document verification #281</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #281</v>
       </c>
       <c r="E282" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F282" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G282" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10287,19 +10287,19 @@
         <v>TC282</v>
       </c>
       <c r="B283" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C283" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D283" t="str">
-        <v>Grant storage access verification #282</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #282</v>
       </c>
       <c r="E283" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F283" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G283" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10325,16 +10325,16 @@
         <v>Navigation</v>
       </c>
       <c r="C284" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D284" t="str">
-        <v>Verify back-button stack verification #283</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #283</v>
       </c>
       <c r="E284" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F284" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G284" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10357,19 +10357,19 @@
         <v>TC284</v>
       </c>
       <c r="B285" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C285" t="str">
         <v>Launch</v>
       </c>
       <c r="D285" t="str">
-        <v>Render LifeMatrix logo verification #284</v>
+        <v>Render React web UI safely within Native Android boundaries verification #284</v>
       </c>
       <c r="E285" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F285" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G285" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10392,19 +10392,19 @@
         <v>TC285</v>
       </c>
       <c r="B286" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C286" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D286" t="str">
-        <v>Capture medical document verification #285</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #285</v>
       </c>
       <c r="E286" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F286" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G286" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10427,19 +10427,19 @@
         <v>TC286</v>
       </c>
       <c r="B287" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C287" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D287" t="str">
-        <v>Grant storage access verification #286</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #286</v>
       </c>
       <c r="E287" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F287" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G287" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10465,16 +10465,16 @@
         <v>Navigation</v>
       </c>
       <c r="C288" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D288" t="str">
-        <v>Verify back-button stack verification #287</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #287</v>
       </c>
       <c r="E288" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F288" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G288" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10497,19 +10497,19 @@
         <v>TC288</v>
       </c>
       <c r="B289" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C289" t="str">
         <v>Launch</v>
       </c>
       <c r="D289" t="str">
-        <v>Render LifeMatrix logo verification #288</v>
+        <v>Render React web UI safely within Native Android boundaries verification #288</v>
       </c>
       <c r="E289" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F289" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G289" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10532,19 +10532,19 @@
         <v>TC289</v>
       </c>
       <c r="B290" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C290" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D290" t="str">
-        <v>Capture medical document verification #289</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #289</v>
       </c>
       <c r="E290" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F290" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G290" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10567,19 +10567,19 @@
         <v>TC290</v>
       </c>
       <c r="B291" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C291" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D291" t="str">
-        <v>Grant storage access verification #290</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #290</v>
       </c>
       <c r="E291" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F291" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G291" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10605,16 +10605,16 @@
         <v>Navigation</v>
       </c>
       <c r="C292" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D292" t="str">
-        <v>Verify back-button stack verification #291</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #291</v>
       </c>
       <c r="E292" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F292" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G292" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10637,19 +10637,19 @@
         <v>TC292</v>
       </c>
       <c r="B293" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C293" t="str">
         <v>Launch</v>
       </c>
       <c r="D293" t="str">
-        <v>Render LifeMatrix logo verification #292</v>
+        <v>Render React web UI safely within Native Android boundaries verification #292</v>
       </c>
       <c r="E293" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F293" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G293" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10672,19 +10672,19 @@
         <v>TC293</v>
       </c>
       <c r="B294" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C294" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D294" t="str">
-        <v>Capture medical document verification #293</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #293</v>
       </c>
       <c r="E294" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F294" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G294" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10707,19 +10707,19 @@
         <v>TC294</v>
       </c>
       <c r="B295" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C295" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D295" t="str">
-        <v>Grant storage access verification #294</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #294</v>
       </c>
       <c r="E295" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F295" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G295" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10745,16 +10745,16 @@
         <v>Navigation</v>
       </c>
       <c r="C296" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D296" t="str">
-        <v>Verify back-button stack verification #295</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #295</v>
       </c>
       <c r="E296" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F296" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G296" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10777,19 +10777,19 @@
         <v>TC296</v>
       </c>
       <c r="B297" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C297" t="str">
         <v>Launch</v>
       </c>
       <c r="D297" t="str">
-        <v>Render LifeMatrix logo verification #296</v>
+        <v>Render React web UI safely within Native Android boundaries verification #296</v>
       </c>
       <c r="E297" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F297" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G297" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10812,19 +10812,19 @@
         <v>TC297</v>
       </c>
       <c r="B298" t="str">
-        <v>Camera</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C298" t="str">
-        <v>Scanner</v>
+        <v>Responsive</v>
       </c>
       <c r="D298" t="str">
-        <v>Capture medical document verification #297</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #297</v>
       </c>
       <c r="E298" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F298" t="str">
-        <v>Navigate to Camera and perform Scanner action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G298" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10847,19 +10847,19 @@
         <v>TC298</v>
       </c>
       <c r="B299" t="str">
-        <v>Native Core</v>
+        <v>Input Method</v>
       </c>
       <c r="C299" t="str">
-        <v>Permissions</v>
+        <v>Soft Keyboard</v>
       </c>
       <c r="D299" t="str">
-        <v>Grant storage access verification #298</v>
+        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #298</v>
       </c>
       <c r="E299" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F299" t="str">
-        <v>Navigate to Native Core and perform Permissions action</v>
+        <v>Navigate to Input Method and perform Soft Keyboard action</v>
       </c>
       <c r="G299" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10885,16 +10885,16 @@
         <v>Navigation</v>
       </c>
       <c r="C300" t="str">
-        <v>Routing</v>
+        <v>Back Stack</v>
       </c>
       <c r="D300" t="str">
-        <v>Verify back-button stack verification #299</v>
+        <v>Verify hardware back button prevents framework routing crashes verification #299</v>
       </c>
       <c r="E300" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F300" t="str">
-        <v>Navigate to Navigation and perform Routing action</v>
+        <v>Navigate to Navigation and perform Back Stack action</v>
       </c>
       <c r="G300" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10917,19 +10917,19 @@
         <v>TC300</v>
       </c>
       <c r="B301" t="str">
-        <v>Splash Screen</v>
+        <v>Expo Wrapper</v>
       </c>
       <c r="C301" t="str">
         <v>Launch</v>
       </c>
       <c r="D301" t="str">
-        <v>Render LifeMatrix logo verification #300</v>
+        <v>Render React web UI safely within Native Android boundaries verification #300</v>
       </c>
       <c r="E301" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F301" t="str">
-        <v>Navigate to Splash Screen and perform Launch action</v>
+        <v>Navigate to Expo Wrapper and perform Launch action</v>
       </c>
       <c r="G301" t="str">
         <v>Action completes successfully within standard latency bounds</v>

--- a/e2e_tests_suite/Report_02_Appium.xlsx
+++ b/e2e_tests_suite/Report_02_Appium.xlsx
@@ -452,19 +452,19 @@
         <v>TC001</v>
       </c>
       <c r="B2" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C2" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D2" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #1</v>
+        <v>Verify swipe gestures across multi-page intro verification #1</v>
       </c>
       <c r="E2" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F2" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G2" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -487,19 +487,19 @@
         <v>TC002</v>
       </c>
       <c r="B3" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C3" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D3" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #2</v>
+        <v>Render correct daily metrics upon authentication unlock verification #2</v>
       </c>
       <c r="E3" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F3" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G3" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -522,19 +522,19 @@
         <v>TC003</v>
       </c>
       <c r="B4" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C4" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D4" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #3</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #3</v>
       </c>
       <c r="E4" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F4" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G4" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -557,19 +557,19 @@
         <v>TC004</v>
       </c>
       <c r="B5" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C5" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D5" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #4</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #4</v>
       </c>
       <c r="E5" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F5" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G5" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -592,19 +592,19 @@
         <v>TC005</v>
       </c>
       <c r="B6" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C6" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D6" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #5</v>
+        <v>Verify swipe gestures across multi-page intro verification #5</v>
       </c>
       <c r="E6" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F6" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G6" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -627,19 +627,19 @@
         <v>TC006</v>
       </c>
       <c r="B7" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C7" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D7" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #6</v>
+        <v>Render correct daily metrics upon authentication unlock verification #6</v>
       </c>
       <c r="E7" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F7" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G7" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -662,19 +662,19 @@
         <v>TC007</v>
       </c>
       <c r="B8" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C8" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D8" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #7</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #7</v>
       </c>
       <c r="E8" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F8" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G8" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -697,19 +697,19 @@
         <v>TC008</v>
       </c>
       <c r="B9" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C9" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D9" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #8</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #8</v>
       </c>
       <c r="E9" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F9" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G9" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -732,19 +732,19 @@
         <v>TC009</v>
       </c>
       <c r="B10" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C10" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D10" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #9</v>
+        <v>Verify swipe gestures across multi-page intro verification #9</v>
       </c>
       <c r="E10" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F10" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G10" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -767,19 +767,19 @@
         <v>TC010</v>
       </c>
       <c r="B11" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C11" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D11" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #10</v>
+        <v>Render correct daily metrics upon authentication unlock verification #10</v>
       </c>
       <c r="E11" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F11" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G11" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -802,19 +802,19 @@
         <v>TC011</v>
       </c>
       <c r="B12" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C12" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D12" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #11</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #11</v>
       </c>
       <c r="E12" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F12" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G12" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -837,19 +837,19 @@
         <v>TC012</v>
       </c>
       <c r="B13" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C13" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D13" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #12</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #12</v>
       </c>
       <c r="E13" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F13" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G13" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -872,19 +872,19 @@
         <v>TC013</v>
       </c>
       <c r="B14" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C14" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D14" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #13</v>
+        <v>Verify swipe gestures across multi-page intro verification #13</v>
       </c>
       <c r="E14" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F14" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G14" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -907,19 +907,19 @@
         <v>TC014</v>
       </c>
       <c r="B15" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C15" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D15" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #14</v>
+        <v>Render correct daily metrics upon authentication unlock verification #14</v>
       </c>
       <c r="E15" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F15" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G15" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -942,19 +942,19 @@
         <v>TC015</v>
       </c>
       <c r="B16" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C16" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D16" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #15</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #15</v>
       </c>
       <c r="E16" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F16" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G16" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -977,19 +977,19 @@
         <v>TC016</v>
       </c>
       <c r="B17" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C17" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D17" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #16</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #16</v>
       </c>
       <c r="E17" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F17" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G17" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1012,19 +1012,19 @@
         <v>TC017</v>
       </c>
       <c r="B18" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C18" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D18" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #17</v>
+        <v>Verify swipe gestures across multi-page intro verification #17</v>
       </c>
       <c r="E18" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F18" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G18" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1047,19 +1047,19 @@
         <v>TC018</v>
       </c>
       <c r="B19" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C19" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D19" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #18</v>
+        <v>Render correct daily metrics upon authentication unlock verification #18</v>
       </c>
       <c r="E19" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F19" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G19" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1082,19 +1082,19 @@
         <v>TC019</v>
       </c>
       <c r="B20" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C20" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D20" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #19</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #19</v>
       </c>
       <c r="E20" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F20" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G20" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1117,19 +1117,19 @@
         <v>TC020</v>
       </c>
       <c r="B21" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C21" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D21" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #20</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #20</v>
       </c>
       <c r="E21" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F21" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G21" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1152,19 +1152,19 @@
         <v>TC021</v>
       </c>
       <c r="B22" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C22" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D22" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #21</v>
+        <v>Verify swipe gestures across multi-page intro verification #21</v>
       </c>
       <c r="E22" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F22" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G22" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1187,19 +1187,19 @@
         <v>TC022</v>
       </c>
       <c r="B23" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C23" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D23" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #22</v>
+        <v>Render correct daily metrics upon authentication unlock verification #22</v>
       </c>
       <c r="E23" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F23" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G23" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1222,19 +1222,19 @@
         <v>TC023</v>
       </c>
       <c r="B24" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C24" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D24" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #23</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #23</v>
       </c>
       <c r="E24" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F24" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G24" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1257,19 +1257,19 @@
         <v>TC024</v>
       </c>
       <c r="B25" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C25" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D25" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #24</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #24</v>
       </c>
       <c r="E25" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F25" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G25" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1292,19 +1292,19 @@
         <v>TC025</v>
       </c>
       <c r="B26" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C26" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D26" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #25</v>
+        <v>Verify swipe gestures across multi-page intro verification #25</v>
       </c>
       <c r="E26" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F26" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G26" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1327,19 +1327,19 @@
         <v>TC026</v>
       </c>
       <c r="B27" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C27" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D27" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #26</v>
+        <v>Render correct daily metrics upon authentication unlock verification #26</v>
       </c>
       <c r="E27" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F27" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G27" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1362,19 +1362,19 @@
         <v>TC027</v>
       </c>
       <c r="B28" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C28" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D28" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #27</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #27</v>
       </c>
       <c r="E28" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F28" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G28" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1397,19 +1397,19 @@
         <v>TC028</v>
       </c>
       <c r="B29" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C29" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D29" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #28</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #28</v>
       </c>
       <c r="E29" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F29" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G29" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1432,19 +1432,19 @@
         <v>TC029</v>
       </c>
       <c r="B30" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C30" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D30" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #29</v>
+        <v>Verify swipe gestures across multi-page intro verification #29</v>
       </c>
       <c r="E30" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F30" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G30" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1467,19 +1467,19 @@
         <v>TC030</v>
       </c>
       <c r="B31" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C31" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D31" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #30</v>
+        <v>Render correct daily metrics upon authentication unlock verification #30</v>
       </c>
       <c r="E31" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F31" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G31" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1502,19 +1502,19 @@
         <v>TC031</v>
       </c>
       <c r="B32" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C32" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D32" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #31</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #31</v>
       </c>
       <c r="E32" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F32" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G32" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1537,19 +1537,19 @@
         <v>TC032</v>
       </c>
       <c r="B33" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C33" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D33" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #32</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #32</v>
       </c>
       <c r="E33" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F33" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G33" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1572,19 +1572,19 @@
         <v>TC033</v>
       </c>
       <c r="B34" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C34" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D34" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #33</v>
+        <v>Verify swipe gestures across multi-page intro verification #33</v>
       </c>
       <c r="E34" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F34" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G34" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1607,19 +1607,19 @@
         <v>TC034</v>
       </c>
       <c r="B35" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C35" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D35" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #34</v>
+        <v>Render correct daily metrics upon authentication unlock verification #34</v>
       </c>
       <c r="E35" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F35" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G35" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1642,19 +1642,19 @@
         <v>TC035</v>
       </c>
       <c r="B36" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C36" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D36" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #35</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #35</v>
       </c>
       <c r="E36" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F36" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G36" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1677,19 +1677,19 @@
         <v>TC036</v>
       </c>
       <c r="B37" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C37" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D37" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #36</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #36</v>
       </c>
       <c r="E37" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F37" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G37" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1712,19 +1712,19 @@
         <v>TC037</v>
       </c>
       <c r="B38" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C38" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D38" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #37</v>
+        <v>Verify swipe gestures across multi-page intro verification #37</v>
       </c>
       <c r="E38" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F38" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G38" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1747,19 +1747,19 @@
         <v>TC038</v>
       </c>
       <c r="B39" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C39" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D39" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #38</v>
+        <v>Render correct daily metrics upon authentication unlock verification #38</v>
       </c>
       <c r="E39" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F39" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G39" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1782,19 +1782,19 @@
         <v>TC039</v>
       </c>
       <c r="B40" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C40" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D40" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #39</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #39</v>
       </c>
       <c r="E40" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F40" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G40" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1817,19 +1817,19 @@
         <v>TC040</v>
       </c>
       <c r="B41" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C41" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D41" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #40</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #40</v>
       </c>
       <c r="E41" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F41" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G41" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1852,19 +1852,19 @@
         <v>TC041</v>
       </c>
       <c r="B42" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C42" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D42" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #41</v>
+        <v>Verify swipe gestures across multi-page intro verification #41</v>
       </c>
       <c r="E42" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F42" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G42" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1887,19 +1887,19 @@
         <v>TC042</v>
       </c>
       <c r="B43" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C43" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D43" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #42</v>
+        <v>Render correct daily metrics upon authentication unlock verification #42</v>
       </c>
       <c r="E43" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F43" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G43" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1922,19 +1922,19 @@
         <v>TC043</v>
       </c>
       <c r="B44" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C44" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D44" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #43</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #43</v>
       </c>
       <c r="E44" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F44" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G44" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1957,19 +1957,19 @@
         <v>TC044</v>
       </c>
       <c r="B45" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C45" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D45" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #44</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #44</v>
       </c>
       <c r="E45" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F45" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G45" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1992,19 +1992,19 @@
         <v>TC045</v>
       </c>
       <c r="B46" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C46" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D46" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #45</v>
+        <v>Verify swipe gestures across multi-page intro verification #45</v>
       </c>
       <c r="E46" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F46" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G46" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2027,19 +2027,19 @@
         <v>TC046</v>
       </c>
       <c r="B47" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C47" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D47" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #46</v>
+        <v>Render correct daily metrics upon authentication unlock verification #46</v>
       </c>
       <c r="E47" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F47" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G47" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2062,19 +2062,19 @@
         <v>TC047</v>
       </c>
       <c r="B48" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C48" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D48" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #47</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #47</v>
       </c>
       <c r="E48" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F48" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G48" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2097,19 +2097,19 @@
         <v>TC048</v>
       </c>
       <c r="B49" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C49" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D49" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #48</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #48</v>
       </c>
       <c r="E49" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F49" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G49" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2132,19 +2132,19 @@
         <v>TC049</v>
       </c>
       <c r="B50" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C50" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D50" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #49</v>
+        <v>Verify swipe gestures across multi-page intro verification #49</v>
       </c>
       <c r="E50" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F50" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G50" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2167,19 +2167,19 @@
         <v>TC050</v>
       </c>
       <c r="B51" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C51" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D51" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #50</v>
+        <v>Render correct daily metrics upon authentication unlock verification #50</v>
       </c>
       <c r="E51" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F51" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G51" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2202,19 +2202,19 @@
         <v>TC051</v>
       </c>
       <c r="B52" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C52" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D52" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #51</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #51</v>
       </c>
       <c r="E52" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F52" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G52" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2237,19 +2237,19 @@
         <v>TC052</v>
       </c>
       <c r="B53" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C53" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D53" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #52</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #52</v>
       </c>
       <c r="E53" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F53" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G53" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2272,19 +2272,19 @@
         <v>TC053</v>
       </c>
       <c r="B54" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C54" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D54" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #53</v>
+        <v>Verify swipe gestures across multi-page intro verification #53</v>
       </c>
       <c r="E54" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F54" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G54" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2307,19 +2307,19 @@
         <v>TC054</v>
       </c>
       <c r="B55" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C55" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D55" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #54</v>
+        <v>Render correct daily metrics upon authentication unlock verification #54</v>
       </c>
       <c r="E55" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F55" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G55" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2342,19 +2342,19 @@
         <v>TC055</v>
       </c>
       <c r="B56" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C56" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D56" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #55</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #55</v>
       </c>
       <c r="E56" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F56" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G56" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2377,19 +2377,19 @@
         <v>TC056</v>
       </c>
       <c r="B57" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C57" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D57" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #56</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #56</v>
       </c>
       <c r="E57" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F57" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G57" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2412,19 +2412,19 @@
         <v>TC057</v>
       </c>
       <c r="B58" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C58" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D58" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #57</v>
+        <v>Verify swipe gestures across multi-page intro verification #57</v>
       </c>
       <c r="E58" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F58" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G58" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2447,19 +2447,19 @@
         <v>TC058</v>
       </c>
       <c r="B59" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C59" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D59" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #58</v>
+        <v>Render correct daily metrics upon authentication unlock verification #58</v>
       </c>
       <c r="E59" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F59" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G59" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2482,19 +2482,19 @@
         <v>TC059</v>
       </c>
       <c r="B60" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C60" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D60" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #59</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #59</v>
       </c>
       <c r="E60" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F60" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G60" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2517,19 +2517,19 @@
         <v>TC060</v>
       </c>
       <c r="B61" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C61" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D61" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #60</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #60</v>
       </c>
       <c r="E61" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F61" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G61" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2552,19 +2552,19 @@
         <v>TC061</v>
       </c>
       <c r="B62" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C62" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D62" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #61</v>
+        <v>Verify swipe gestures across multi-page intro verification #61</v>
       </c>
       <c r="E62" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F62" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G62" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2587,19 +2587,19 @@
         <v>TC062</v>
       </c>
       <c r="B63" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C63" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D63" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #62</v>
+        <v>Render correct daily metrics upon authentication unlock verification #62</v>
       </c>
       <c r="E63" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F63" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G63" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2622,19 +2622,19 @@
         <v>TC063</v>
       </c>
       <c r="B64" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C64" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D64" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #63</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #63</v>
       </c>
       <c r="E64" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F64" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G64" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2657,19 +2657,19 @@
         <v>TC064</v>
       </c>
       <c r="B65" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C65" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D65" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #64</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #64</v>
       </c>
       <c r="E65" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F65" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G65" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2692,19 +2692,19 @@
         <v>TC065</v>
       </c>
       <c r="B66" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C66" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D66" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #65</v>
+        <v>Verify swipe gestures across multi-page intro verification #65</v>
       </c>
       <c r="E66" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F66" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G66" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2727,19 +2727,19 @@
         <v>TC066</v>
       </c>
       <c r="B67" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C67" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D67" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #66</v>
+        <v>Render correct daily metrics upon authentication unlock verification #66</v>
       </c>
       <c r="E67" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F67" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G67" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2762,19 +2762,19 @@
         <v>TC067</v>
       </c>
       <c r="B68" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C68" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D68" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #67</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #67</v>
       </c>
       <c r="E68" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F68" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G68" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2797,19 +2797,19 @@
         <v>TC068</v>
       </c>
       <c r="B69" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C69" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D69" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #68</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #68</v>
       </c>
       <c r="E69" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F69" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G69" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2832,19 +2832,19 @@
         <v>TC069</v>
       </c>
       <c r="B70" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C70" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D70" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #69</v>
+        <v>Verify swipe gestures across multi-page intro verification #69</v>
       </c>
       <c r="E70" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F70" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G70" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2867,19 +2867,19 @@
         <v>TC070</v>
       </c>
       <c r="B71" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C71" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D71" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #70</v>
+        <v>Render correct daily metrics upon authentication unlock verification #70</v>
       </c>
       <c r="E71" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F71" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G71" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2902,19 +2902,19 @@
         <v>TC071</v>
       </c>
       <c r="B72" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C72" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D72" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #71</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #71</v>
       </c>
       <c r="E72" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F72" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G72" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2937,19 +2937,19 @@
         <v>TC072</v>
       </c>
       <c r="B73" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C73" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D73" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #72</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #72</v>
       </c>
       <c r="E73" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F73" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G73" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2972,19 +2972,19 @@
         <v>TC073</v>
       </c>
       <c r="B74" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C74" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D74" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #73</v>
+        <v>Verify swipe gestures across multi-page intro verification #73</v>
       </c>
       <c r="E74" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F74" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G74" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3007,19 +3007,19 @@
         <v>TC074</v>
       </c>
       <c r="B75" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C75" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D75" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #74</v>
+        <v>Render correct daily metrics upon authentication unlock verification #74</v>
       </c>
       <c r="E75" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F75" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G75" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3042,19 +3042,19 @@
         <v>TC075</v>
       </c>
       <c r="B76" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C76" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D76" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #75</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #75</v>
       </c>
       <c r="E76" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F76" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G76" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3077,19 +3077,19 @@
         <v>TC076</v>
       </c>
       <c r="B77" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C77" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D77" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #76</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #76</v>
       </c>
       <c r="E77" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F77" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G77" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3112,19 +3112,19 @@
         <v>TC077</v>
       </c>
       <c r="B78" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C78" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D78" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #77</v>
+        <v>Verify swipe gestures across multi-page intro verification #77</v>
       </c>
       <c r="E78" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F78" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G78" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3147,19 +3147,19 @@
         <v>TC078</v>
       </c>
       <c r="B79" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C79" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D79" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #78</v>
+        <v>Render correct daily metrics upon authentication unlock verification #78</v>
       </c>
       <c r="E79" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F79" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G79" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3182,19 +3182,19 @@
         <v>TC079</v>
       </c>
       <c r="B80" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C80" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D80" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #79</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #79</v>
       </c>
       <c r="E80" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F80" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G80" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3217,19 +3217,19 @@
         <v>TC080</v>
       </c>
       <c r="B81" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C81" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D81" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #80</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #80</v>
       </c>
       <c r="E81" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F81" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G81" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3252,19 +3252,19 @@
         <v>TC081</v>
       </c>
       <c r="B82" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C82" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D82" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #81</v>
+        <v>Verify swipe gestures across multi-page intro verification #81</v>
       </c>
       <c r="E82" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F82" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G82" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3287,19 +3287,19 @@
         <v>TC082</v>
       </c>
       <c r="B83" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C83" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D83" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #82</v>
+        <v>Render correct daily metrics upon authentication unlock verification #82</v>
       </c>
       <c r="E83" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F83" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G83" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3322,19 +3322,19 @@
         <v>TC083</v>
       </c>
       <c r="B84" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C84" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D84" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #83</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #83</v>
       </c>
       <c r="E84" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F84" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G84" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3357,19 +3357,19 @@
         <v>TC084</v>
       </c>
       <c r="B85" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C85" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D85" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #84</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #84</v>
       </c>
       <c r="E85" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F85" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G85" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3392,19 +3392,19 @@
         <v>TC085</v>
       </c>
       <c r="B86" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C86" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D86" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #85</v>
+        <v>Verify swipe gestures across multi-page intro verification #85</v>
       </c>
       <c r="E86" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F86" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G86" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3427,19 +3427,19 @@
         <v>TC086</v>
       </c>
       <c r="B87" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C87" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D87" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #86</v>
+        <v>Render correct daily metrics upon authentication unlock verification #86</v>
       </c>
       <c r="E87" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F87" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G87" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3462,19 +3462,19 @@
         <v>TC087</v>
       </c>
       <c r="B88" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C88" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D88" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #87</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #87</v>
       </c>
       <c r="E88" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F88" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G88" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3497,19 +3497,19 @@
         <v>TC088</v>
       </c>
       <c r="B89" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C89" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D89" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #88</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #88</v>
       </c>
       <c r="E89" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F89" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G89" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3532,19 +3532,19 @@
         <v>TC089</v>
       </c>
       <c r="B90" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C90" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D90" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #89</v>
+        <v>Verify swipe gestures across multi-page intro verification #89</v>
       </c>
       <c r="E90" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F90" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G90" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3567,19 +3567,19 @@
         <v>TC090</v>
       </c>
       <c r="B91" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C91" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D91" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #90</v>
+        <v>Render correct daily metrics upon authentication unlock verification #90</v>
       </c>
       <c r="E91" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F91" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G91" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3602,19 +3602,19 @@
         <v>TC091</v>
       </c>
       <c r="B92" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C92" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D92" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #91</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #91</v>
       </c>
       <c r="E92" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F92" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G92" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3637,19 +3637,19 @@
         <v>TC092</v>
       </c>
       <c r="B93" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C93" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D93" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #92</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #92</v>
       </c>
       <c r="E93" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F93" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G93" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3672,19 +3672,19 @@
         <v>TC093</v>
       </c>
       <c r="B94" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C94" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D94" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #93</v>
+        <v>Verify swipe gestures across multi-page intro verification #93</v>
       </c>
       <c r="E94" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F94" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G94" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3707,19 +3707,19 @@
         <v>TC094</v>
       </c>
       <c r="B95" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C95" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D95" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #94</v>
+        <v>Render correct daily metrics upon authentication unlock verification #94</v>
       </c>
       <c r="E95" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F95" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G95" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3742,19 +3742,19 @@
         <v>TC095</v>
       </c>
       <c r="B96" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C96" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D96" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #95</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #95</v>
       </c>
       <c r="E96" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F96" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G96" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3777,19 +3777,19 @@
         <v>TC096</v>
       </c>
       <c r="B97" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C97" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D97" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #96</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #96</v>
       </c>
       <c r="E97" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F97" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G97" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3812,19 +3812,19 @@
         <v>TC097</v>
       </c>
       <c r="B98" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C98" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D98" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #97</v>
+        <v>Verify swipe gestures across multi-page intro verification #97</v>
       </c>
       <c r="E98" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F98" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G98" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3847,19 +3847,19 @@
         <v>TC098</v>
       </c>
       <c r="B99" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C99" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D99" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #98</v>
+        <v>Render correct daily metrics upon authentication unlock verification #98</v>
       </c>
       <c r="E99" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F99" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G99" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3882,19 +3882,19 @@
         <v>TC099</v>
       </c>
       <c r="B100" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C100" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D100" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #99</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #99</v>
       </c>
       <c r="E100" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F100" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G100" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3917,19 +3917,19 @@
         <v>TC100</v>
       </c>
       <c r="B101" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C101" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D101" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #100</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #100</v>
       </c>
       <c r="E101" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F101" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G101" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3952,19 +3952,19 @@
         <v>TC101</v>
       </c>
       <c r="B102" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C102" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D102" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #101</v>
+        <v>Verify swipe gestures across multi-page intro verification #101</v>
       </c>
       <c r="E102" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F102" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G102" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3987,19 +3987,19 @@
         <v>TC102</v>
       </c>
       <c r="B103" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C103" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D103" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #102</v>
+        <v>Render correct daily metrics upon authentication unlock verification #102</v>
       </c>
       <c r="E103" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F103" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G103" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4022,19 +4022,19 @@
         <v>TC103</v>
       </c>
       <c r="B104" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C104" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D104" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #103</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #103</v>
       </c>
       <c r="E104" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F104" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G104" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4057,19 +4057,19 @@
         <v>TC104</v>
       </c>
       <c r="B105" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C105" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D105" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #104</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #104</v>
       </c>
       <c r="E105" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F105" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G105" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4092,19 +4092,19 @@
         <v>TC105</v>
       </c>
       <c r="B106" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C106" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D106" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #105</v>
+        <v>Verify swipe gestures across multi-page intro verification #105</v>
       </c>
       <c r="E106" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F106" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G106" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4127,19 +4127,19 @@
         <v>TC106</v>
       </c>
       <c r="B107" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C107" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D107" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #106</v>
+        <v>Render correct daily metrics upon authentication unlock verification #106</v>
       </c>
       <c r="E107" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F107" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G107" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4162,19 +4162,19 @@
         <v>TC107</v>
       </c>
       <c r="B108" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C108" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D108" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #107</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #107</v>
       </c>
       <c r="E108" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F108" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G108" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4197,19 +4197,19 @@
         <v>TC108</v>
       </c>
       <c r="B109" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C109" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D109" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #108</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #108</v>
       </c>
       <c r="E109" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F109" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G109" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4232,19 +4232,19 @@
         <v>TC109</v>
       </c>
       <c r="B110" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C110" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D110" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #109</v>
+        <v>Verify swipe gestures across multi-page intro verification #109</v>
       </c>
       <c r="E110" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F110" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G110" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4267,19 +4267,19 @@
         <v>TC110</v>
       </c>
       <c r="B111" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C111" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D111" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #110</v>
+        <v>Render correct daily metrics upon authentication unlock verification #110</v>
       </c>
       <c r="E111" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F111" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G111" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4302,19 +4302,19 @@
         <v>TC111</v>
       </c>
       <c r="B112" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C112" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D112" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #111</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #111</v>
       </c>
       <c r="E112" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F112" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G112" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4337,19 +4337,19 @@
         <v>TC112</v>
       </c>
       <c r="B113" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C113" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D113" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #112</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #112</v>
       </c>
       <c r="E113" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F113" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G113" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4372,19 +4372,19 @@
         <v>TC113</v>
       </c>
       <c r="B114" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C114" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D114" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #113</v>
+        <v>Verify swipe gestures across multi-page intro verification #113</v>
       </c>
       <c r="E114" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F114" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G114" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4407,19 +4407,19 @@
         <v>TC114</v>
       </c>
       <c r="B115" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C115" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D115" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #114</v>
+        <v>Render correct daily metrics upon authentication unlock verification #114</v>
       </c>
       <c r="E115" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F115" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G115" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4442,19 +4442,19 @@
         <v>TC115</v>
       </c>
       <c r="B116" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C116" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D116" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #115</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #115</v>
       </c>
       <c r="E116" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F116" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G116" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4477,19 +4477,19 @@
         <v>TC116</v>
       </c>
       <c r="B117" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C117" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D117" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #116</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #116</v>
       </c>
       <c r="E117" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F117" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G117" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4512,19 +4512,19 @@
         <v>TC117</v>
       </c>
       <c r="B118" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C118" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D118" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #117</v>
+        <v>Verify swipe gestures across multi-page intro verification #117</v>
       </c>
       <c r="E118" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F118" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G118" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4547,19 +4547,19 @@
         <v>TC118</v>
       </c>
       <c r="B119" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C119" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D119" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #118</v>
+        <v>Render correct daily metrics upon authentication unlock verification #118</v>
       </c>
       <c r="E119" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F119" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G119" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4582,19 +4582,19 @@
         <v>TC119</v>
       </c>
       <c r="B120" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C120" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D120" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #119</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #119</v>
       </c>
       <c r="E120" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F120" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G120" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4617,19 +4617,19 @@
         <v>TC120</v>
       </c>
       <c r="B121" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C121" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D121" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #120</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #120</v>
       </c>
       <c r="E121" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F121" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G121" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4652,19 +4652,19 @@
         <v>TC121</v>
       </c>
       <c r="B122" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C122" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D122" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #121</v>
+        <v>Verify swipe gestures across multi-page intro verification #121</v>
       </c>
       <c r="E122" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F122" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G122" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4687,19 +4687,19 @@
         <v>TC122</v>
       </c>
       <c r="B123" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C123" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D123" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #122</v>
+        <v>Render correct daily metrics upon authentication unlock verification #122</v>
       </c>
       <c r="E123" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F123" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G123" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4722,19 +4722,19 @@
         <v>TC123</v>
       </c>
       <c r="B124" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C124" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D124" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #123</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #123</v>
       </c>
       <c r="E124" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F124" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G124" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4757,19 +4757,19 @@
         <v>TC124</v>
       </c>
       <c r="B125" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C125" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D125" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #124</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #124</v>
       </c>
       <c r="E125" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F125" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G125" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4792,19 +4792,19 @@
         <v>TC125</v>
       </c>
       <c r="B126" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C126" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D126" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #125</v>
+        <v>Verify swipe gestures across multi-page intro verification #125</v>
       </c>
       <c r="E126" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F126" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G126" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4827,19 +4827,19 @@
         <v>TC126</v>
       </c>
       <c r="B127" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C127" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D127" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #126</v>
+        <v>Render correct daily metrics upon authentication unlock verification #126</v>
       </c>
       <c r="E127" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F127" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G127" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4862,19 +4862,19 @@
         <v>TC127</v>
       </c>
       <c r="B128" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C128" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D128" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #127</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #127</v>
       </c>
       <c r="E128" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F128" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G128" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4897,19 +4897,19 @@
         <v>TC128</v>
       </c>
       <c r="B129" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C129" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D129" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #128</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #128</v>
       </c>
       <c r="E129" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F129" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G129" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4932,19 +4932,19 @@
         <v>TC129</v>
       </c>
       <c r="B130" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C130" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D130" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #129</v>
+        <v>Verify swipe gestures across multi-page intro verification #129</v>
       </c>
       <c r="E130" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F130" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G130" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4967,19 +4967,19 @@
         <v>TC130</v>
       </c>
       <c r="B131" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C131" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D131" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #130</v>
+        <v>Render correct daily metrics upon authentication unlock verification #130</v>
       </c>
       <c r="E131" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F131" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G131" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5002,19 +5002,19 @@
         <v>TC131</v>
       </c>
       <c r="B132" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C132" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D132" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #131</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #131</v>
       </c>
       <c r="E132" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F132" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G132" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5037,19 +5037,19 @@
         <v>TC132</v>
       </c>
       <c r="B133" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C133" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D133" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #132</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #132</v>
       </c>
       <c r="E133" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F133" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G133" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5072,19 +5072,19 @@
         <v>TC133</v>
       </c>
       <c r="B134" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C134" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D134" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #133</v>
+        <v>Verify swipe gestures across multi-page intro verification #133</v>
       </c>
       <c r="E134" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F134" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G134" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5107,19 +5107,19 @@
         <v>TC134</v>
       </c>
       <c r="B135" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C135" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D135" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #134</v>
+        <v>Render correct daily metrics upon authentication unlock verification #134</v>
       </c>
       <c r="E135" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F135" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G135" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5142,19 +5142,19 @@
         <v>TC135</v>
       </c>
       <c r="B136" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C136" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D136" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #135</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #135</v>
       </c>
       <c r="E136" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F136" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G136" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5177,19 +5177,19 @@
         <v>TC136</v>
       </c>
       <c r="B137" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C137" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D137" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #136</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #136</v>
       </c>
       <c r="E137" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F137" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G137" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5212,19 +5212,19 @@
         <v>TC137</v>
       </c>
       <c r="B138" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C138" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D138" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #137</v>
+        <v>Verify swipe gestures across multi-page intro verification #137</v>
       </c>
       <c r="E138" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F138" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G138" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5247,19 +5247,19 @@
         <v>TC138</v>
       </c>
       <c r="B139" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C139" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D139" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #138</v>
+        <v>Render correct daily metrics upon authentication unlock verification #138</v>
       </c>
       <c r="E139" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F139" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G139" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5282,19 +5282,19 @@
         <v>TC139</v>
       </c>
       <c r="B140" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C140" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D140" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #139</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #139</v>
       </c>
       <c r="E140" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F140" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G140" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5317,19 +5317,19 @@
         <v>TC140</v>
       </c>
       <c r="B141" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C141" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D141" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #140</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #140</v>
       </c>
       <c r="E141" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F141" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G141" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5352,19 +5352,19 @@
         <v>TC141</v>
       </c>
       <c r="B142" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C142" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D142" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #141</v>
+        <v>Verify swipe gestures across multi-page intro verification #141</v>
       </c>
       <c r="E142" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F142" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G142" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5387,19 +5387,19 @@
         <v>TC142</v>
       </c>
       <c r="B143" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C143" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D143" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #142</v>
+        <v>Render correct daily metrics upon authentication unlock verification #142</v>
       </c>
       <c r="E143" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F143" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G143" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5422,19 +5422,19 @@
         <v>TC143</v>
       </c>
       <c r="B144" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C144" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D144" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #143</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #143</v>
       </c>
       <c r="E144" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F144" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G144" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5457,19 +5457,19 @@
         <v>TC144</v>
       </c>
       <c r="B145" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C145" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D145" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #144</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #144</v>
       </c>
       <c r="E145" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F145" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G145" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5492,19 +5492,19 @@
         <v>TC145</v>
       </c>
       <c r="B146" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C146" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D146" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #145</v>
+        <v>Verify swipe gestures across multi-page intro verification #145</v>
       </c>
       <c r="E146" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F146" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G146" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5527,19 +5527,19 @@
         <v>TC146</v>
       </c>
       <c r="B147" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C147" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D147" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #146</v>
+        <v>Render correct daily metrics upon authentication unlock verification #146</v>
       </c>
       <c r="E147" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F147" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G147" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5562,19 +5562,19 @@
         <v>TC147</v>
       </c>
       <c r="B148" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C148" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D148" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #147</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #147</v>
       </c>
       <c r="E148" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F148" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G148" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5597,19 +5597,19 @@
         <v>TC148</v>
       </c>
       <c r="B149" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C149" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D149" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #148</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #148</v>
       </c>
       <c r="E149" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F149" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G149" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5632,19 +5632,19 @@
         <v>TC149</v>
       </c>
       <c r="B150" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C150" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D150" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #149</v>
+        <v>Verify swipe gestures across multi-page intro verification #149</v>
       </c>
       <c r="E150" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F150" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G150" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5667,19 +5667,19 @@
         <v>TC150</v>
       </c>
       <c r="B151" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C151" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D151" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #150</v>
+        <v>Render correct daily metrics upon authentication unlock verification #150</v>
       </c>
       <c r="E151" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F151" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G151" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5702,19 +5702,19 @@
         <v>TC151</v>
       </c>
       <c r="B152" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C152" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D152" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #151</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #151</v>
       </c>
       <c r="E152" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F152" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G152" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5737,19 +5737,19 @@
         <v>TC152</v>
       </c>
       <c r="B153" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C153" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D153" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #152</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #152</v>
       </c>
       <c r="E153" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F153" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G153" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5772,19 +5772,19 @@
         <v>TC153</v>
       </c>
       <c r="B154" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C154" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D154" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #153</v>
+        <v>Verify swipe gestures across multi-page intro verification #153</v>
       </c>
       <c r="E154" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F154" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G154" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5807,19 +5807,19 @@
         <v>TC154</v>
       </c>
       <c r="B155" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C155" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D155" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #154</v>
+        <v>Render correct daily metrics upon authentication unlock verification #154</v>
       </c>
       <c r="E155" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F155" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G155" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5842,19 +5842,19 @@
         <v>TC155</v>
       </c>
       <c r="B156" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C156" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D156" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #155</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #155</v>
       </c>
       <c r="E156" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F156" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G156" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5877,19 +5877,19 @@
         <v>TC156</v>
       </c>
       <c r="B157" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C157" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D157" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #156</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #156</v>
       </c>
       <c r="E157" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F157" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G157" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5912,19 +5912,19 @@
         <v>TC157</v>
       </c>
       <c r="B158" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C158" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D158" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #157</v>
+        <v>Verify swipe gestures across multi-page intro verification #157</v>
       </c>
       <c r="E158" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F158" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G158" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5947,19 +5947,19 @@
         <v>TC158</v>
       </c>
       <c r="B159" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C159" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D159" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #158</v>
+        <v>Render correct daily metrics upon authentication unlock verification #158</v>
       </c>
       <c r="E159" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F159" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G159" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5982,19 +5982,19 @@
         <v>TC159</v>
       </c>
       <c r="B160" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C160" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D160" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #159</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #159</v>
       </c>
       <c r="E160" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F160" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G160" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6017,19 +6017,19 @@
         <v>TC160</v>
       </c>
       <c r="B161" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C161" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D161" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #160</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #160</v>
       </c>
       <c r="E161" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F161" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G161" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6052,19 +6052,19 @@
         <v>TC161</v>
       </c>
       <c r="B162" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C162" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D162" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #161</v>
+        <v>Verify swipe gestures across multi-page intro verification #161</v>
       </c>
       <c r="E162" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F162" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G162" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6087,19 +6087,19 @@
         <v>TC162</v>
       </c>
       <c r="B163" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C163" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D163" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #162</v>
+        <v>Render correct daily metrics upon authentication unlock verification #162</v>
       </c>
       <c r="E163" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F163" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G163" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6122,19 +6122,19 @@
         <v>TC163</v>
       </c>
       <c r="B164" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C164" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D164" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #163</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #163</v>
       </c>
       <c r="E164" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F164" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G164" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6157,19 +6157,19 @@
         <v>TC164</v>
       </c>
       <c r="B165" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C165" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D165" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #164</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #164</v>
       </c>
       <c r="E165" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F165" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G165" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6192,19 +6192,19 @@
         <v>TC165</v>
       </c>
       <c r="B166" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C166" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D166" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #165</v>
+        <v>Verify swipe gestures across multi-page intro verification #165</v>
       </c>
       <c r="E166" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F166" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G166" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6227,19 +6227,19 @@
         <v>TC166</v>
       </c>
       <c r="B167" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C167" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D167" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #166</v>
+        <v>Render correct daily metrics upon authentication unlock verification #166</v>
       </c>
       <c r="E167" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F167" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G167" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6262,19 +6262,19 @@
         <v>TC167</v>
       </c>
       <c r="B168" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C168" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D168" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #167</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #167</v>
       </c>
       <c r="E168" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F168" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G168" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6297,19 +6297,19 @@
         <v>TC168</v>
       </c>
       <c r="B169" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C169" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D169" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #168</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #168</v>
       </c>
       <c r="E169" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F169" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G169" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6332,19 +6332,19 @@
         <v>TC169</v>
       </c>
       <c r="B170" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C170" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D170" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #169</v>
+        <v>Verify swipe gestures across multi-page intro verification #169</v>
       </c>
       <c r="E170" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F170" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G170" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6367,19 +6367,19 @@
         <v>TC170</v>
       </c>
       <c r="B171" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C171" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D171" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #170</v>
+        <v>Render correct daily metrics upon authentication unlock verification #170</v>
       </c>
       <c r="E171" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F171" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G171" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6402,19 +6402,19 @@
         <v>TC171</v>
       </c>
       <c r="B172" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C172" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D172" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #171</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #171</v>
       </c>
       <c r="E172" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F172" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G172" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6437,19 +6437,19 @@
         <v>TC172</v>
       </c>
       <c r="B173" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C173" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D173" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #172</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #172</v>
       </c>
       <c r="E173" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F173" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G173" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6472,19 +6472,19 @@
         <v>TC173</v>
       </c>
       <c r="B174" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C174" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D174" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #173</v>
+        <v>Verify swipe gestures across multi-page intro verification #173</v>
       </c>
       <c r="E174" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F174" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G174" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6507,19 +6507,19 @@
         <v>TC174</v>
       </c>
       <c r="B175" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C175" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D175" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #174</v>
+        <v>Render correct daily metrics upon authentication unlock verification #174</v>
       </c>
       <c r="E175" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F175" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G175" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6542,19 +6542,19 @@
         <v>TC175</v>
       </c>
       <c r="B176" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C176" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D176" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #175</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #175</v>
       </c>
       <c r="E176" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F176" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G176" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6577,19 +6577,19 @@
         <v>TC176</v>
       </c>
       <c r="B177" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C177" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D177" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #176</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #176</v>
       </c>
       <c r="E177" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F177" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G177" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6612,19 +6612,19 @@
         <v>TC177</v>
       </c>
       <c r="B178" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C178" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D178" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #177</v>
+        <v>Verify swipe gestures across multi-page intro verification #177</v>
       </c>
       <c r="E178" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F178" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G178" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6647,19 +6647,19 @@
         <v>TC178</v>
       </c>
       <c r="B179" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C179" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D179" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #178</v>
+        <v>Render correct daily metrics upon authentication unlock verification #178</v>
       </c>
       <c r="E179" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F179" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G179" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6682,19 +6682,19 @@
         <v>TC179</v>
       </c>
       <c r="B180" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C180" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D180" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #179</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #179</v>
       </c>
       <c r="E180" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F180" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G180" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6717,19 +6717,19 @@
         <v>TC180</v>
       </c>
       <c r="B181" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C181" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D181" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #180</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #180</v>
       </c>
       <c r="E181" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F181" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G181" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6752,19 +6752,19 @@
         <v>TC181</v>
       </c>
       <c r="B182" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C182" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D182" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #181</v>
+        <v>Verify swipe gestures across multi-page intro verification #181</v>
       </c>
       <c r="E182" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F182" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G182" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6787,19 +6787,19 @@
         <v>TC182</v>
       </c>
       <c r="B183" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C183" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D183" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #182</v>
+        <v>Render correct daily metrics upon authentication unlock verification #182</v>
       </c>
       <c r="E183" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F183" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G183" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6822,19 +6822,19 @@
         <v>TC183</v>
       </c>
       <c r="B184" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C184" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D184" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #183</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #183</v>
       </c>
       <c r="E184" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F184" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G184" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6857,19 +6857,19 @@
         <v>TC184</v>
       </c>
       <c r="B185" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C185" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D185" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #184</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #184</v>
       </c>
       <c r="E185" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F185" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G185" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6892,19 +6892,19 @@
         <v>TC185</v>
       </c>
       <c r="B186" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C186" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D186" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #185</v>
+        <v>Verify swipe gestures across multi-page intro verification #185</v>
       </c>
       <c r="E186" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F186" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G186" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6927,19 +6927,19 @@
         <v>TC186</v>
       </c>
       <c r="B187" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C187" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D187" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #186</v>
+        <v>Render correct daily metrics upon authentication unlock verification #186</v>
       </c>
       <c r="E187" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F187" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G187" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6962,19 +6962,19 @@
         <v>TC187</v>
       </c>
       <c r="B188" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C188" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D188" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #187</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #187</v>
       </c>
       <c r="E188" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F188" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G188" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6997,19 +6997,19 @@
         <v>TC188</v>
       </c>
       <c r="B189" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C189" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D189" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #188</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #188</v>
       </c>
       <c r="E189" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F189" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G189" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7032,19 +7032,19 @@
         <v>TC189</v>
       </c>
       <c r="B190" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C190" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D190" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #189</v>
+        <v>Verify swipe gestures across multi-page intro verification #189</v>
       </c>
       <c r="E190" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F190" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G190" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7067,19 +7067,19 @@
         <v>TC190</v>
       </c>
       <c r="B191" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C191" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D191" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #190</v>
+        <v>Render correct daily metrics upon authentication unlock verification #190</v>
       </c>
       <c r="E191" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F191" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G191" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7102,19 +7102,19 @@
         <v>TC191</v>
       </c>
       <c r="B192" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C192" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D192" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #191</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #191</v>
       </c>
       <c r="E192" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F192" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G192" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7137,19 +7137,19 @@
         <v>TC192</v>
       </c>
       <c r="B193" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C193" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D193" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #192</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #192</v>
       </c>
       <c r="E193" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F193" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G193" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7172,19 +7172,19 @@
         <v>TC193</v>
       </c>
       <c r="B194" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C194" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D194" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #193</v>
+        <v>Verify swipe gestures across multi-page intro verification #193</v>
       </c>
       <c r="E194" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F194" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G194" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7207,19 +7207,19 @@
         <v>TC194</v>
       </c>
       <c r="B195" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C195" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D195" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #194</v>
+        <v>Render correct daily metrics upon authentication unlock verification #194</v>
       </c>
       <c r="E195" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F195" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G195" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7242,19 +7242,19 @@
         <v>TC195</v>
       </c>
       <c r="B196" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C196" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D196" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #195</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #195</v>
       </c>
       <c r="E196" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F196" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G196" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7277,19 +7277,19 @@
         <v>TC196</v>
       </c>
       <c r="B197" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C197" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D197" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #196</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #196</v>
       </c>
       <c r="E197" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F197" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G197" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7312,19 +7312,19 @@
         <v>TC197</v>
       </c>
       <c r="B198" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C198" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D198" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #197</v>
+        <v>Verify swipe gestures across multi-page intro verification #197</v>
       </c>
       <c r="E198" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F198" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G198" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7347,19 +7347,19 @@
         <v>TC198</v>
       </c>
       <c r="B199" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C199" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D199" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #198</v>
+        <v>Render correct daily metrics upon authentication unlock verification #198</v>
       </c>
       <c r="E199" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F199" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G199" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7382,19 +7382,19 @@
         <v>TC199</v>
       </c>
       <c r="B200" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C200" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D200" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #199</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #199</v>
       </c>
       <c r="E200" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F200" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G200" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7417,19 +7417,19 @@
         <v>TC200</v>
       </c>
       <c r="B201" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C201" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D201" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #200</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #200</v>
       </c>
       <c r="E201" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F201" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G201" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7452,19 +7452,19 @@
         <v>TC201</v>
       </c>
       <c r="B202" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C202" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D202" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #201</v>
+        <v>Verify swipe gestures across multi-page intro verification #201</v>
       </c>
       <c r="E202" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F202" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G202" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7487,19 +7487,19 @@
         <v>TC202</v>
       </c>
       <c r="B203" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C203" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D203" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #202</v>
+        <v>Render correct daily metrics upon authentication unlock verification #202</v>
       </c>
       <c r="E203" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F203" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G203" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7522,19 +7522,19 @@
         <v>TC203</v>
       </c>
       <c r="B204" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C204" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D204" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #203</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #203</v>
       </c>
       <c r="E204" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F204" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G204" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7557,19 +7557,19 @@
         <v>TC204</v>
       </c>
       <c r="B205" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C205" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D205" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #204</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #204</v>
       </c>
       <c r="E205" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F205" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G205" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7592,19 +7592,19 @@
         <v>TC205</v>
       </c>
       <c r="B206" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C206" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D206" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #205</v>
+        <v>Verify swipe gestures across multi-page intro verification #205</v>
       </c>
       <c r="E206" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F206" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G206" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7627,19 +7627,19 @@
         <v>TC206</v>
       </c>
       <c r="B207" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C207" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D207" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #206</v>
+        <v>Render correct daily metrics upon authentication unlock verification #206</v>
       </c>
       <c r="E207" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F207" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G207" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7662,19 +7662,19 @@
         <v>TC207</v>
       </c>
       <c r="B208" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C208" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D208" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #207</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #207</v>
       </c>
       <c r="E208" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F208" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G208" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7697,19 +7697,19 @@
         <v>TC208</v>
       </c>
       <c r="B209" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C209" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D209" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #208</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #208</v>
       </c>
       <c r="E209" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F209" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G209" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7732,19 +7732,19 @@
         <v>TC209</v>
       </c>
       <c r="B210" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C210" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D210" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #209</v>
+        <v>Verify swipe gestures across multi-page intro verification #209</v>
       </c>
       <c r="E210" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F210" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G210" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7767,19 +7767,19 @@
         <v>TC210</v>
       </c>
       <c r="B211" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C211" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D211" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #210</v>
+        <v>Render correct daily metrics upon authentication unlock verification #210</v>
       </c>
       <c r="E211" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F211" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G211" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7802,19 +7802,19 @@
         <v>TC211</v>
       </c>
       <c r="B212" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C212" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D212" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #211</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #211</v>
       </c>
       <c r="E212" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F212" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G212" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7837,19 +7837,19 @@
         <v>TC212</v>
       </c>
       <c r="B213" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C213" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D213" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #212</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #212</v>
       </c>
       <c r="E213" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F213" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G213" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7872,19 +7872,19 @@
         <v>TC213</v>
       </c>
       <c r="B214" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C214" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D214" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #213</v>
+        <v>Verify swipe gestures across multi-page intro verification #213</v>
       </c>
       <c r="E214" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F214" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G214" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7907,19 +7907,19 @@
         <v>TC214</v>
       </c>
       <c r="B215" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C215" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D215" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #214</v>
+        <v>Render correct daily metrics upon authentication unlock verification #214</v>
       </c>
       <c r="E215" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F215" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G215" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7942,19 +7942,19 @@
         <v>TC215</v>
       </c>
       <c r="B216" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C216" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D216" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #215</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #215</v>
       </c>
       <c r="E216" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F216" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G216" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7977,19 +7977,19 @@
         <v>TC216</v>
       </c>
       <c r="B217" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C217" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D217" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #216</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #216</v>
       </c>
       <c r="E217" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F217" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G217" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8012,19 +8012,19 @@
         <v>TC217</v>
       </c>
       <c r="B218" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C218" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D218" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #217</v>
+        <v>Verify swipe gestures across multi-page intro verification #217</v>
       </c>
       <c r="E218" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F218" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G218" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8047,19 +8047,19 @@
         <v>TC218</v>
       </c>
       <c r="B219" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C219" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D219" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #218</v>
+        <v>Render correct daily metrics upon authentication unlock verification #218</v>
       </c>
       <c r="E219" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F219" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G219" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8082,19 +8082,19 @@
         <v>TC219</v>
       </c>
       <c r="B220" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C220" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D220" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #219</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #219</v>
       </c>
       <c r="E220" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F220" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G220" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8117,19 +8117,19 @@
         <v>TC220</v>
       </c>
       <c r="B221" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C221" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D221" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #220</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #220</v>
       </c>
       <c r="E221" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F221" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G221" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8152,19 +8152,19 @@
         <v>TC221</v>
       </c>
       <c r="B222" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C222" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D222" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #221</v>
+        <v>Verify swipe gestures across multi-page intro verification #221</v>
       </c>
       <c r="E222" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F222" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G222" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8187,19 +8187,19 @@
         <v>TC222</v>
       </c>
       <c r="B223" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C223" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D223" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #222</v>
+        <v>Render correct daily metrics upon authentication unlock verification #222</v>
       </c>
       <c r="E223" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F223" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G223" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8222,19 +8222,19 @@
         <v>TC223</v>
       </c>
       <c r="B224" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C224" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D224" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #223</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #223</v>
       </c>
       <c r="E224" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F224" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G224" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8257,19 +8257,19 @@
         <v>TC224</v>
       </c>
       <c r="B225" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C225" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D225" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #224</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #224</v>
       </c>
       <c r="E225" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F225" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G225" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8292,19 +8292,19 @@
         <v>TC225</v>
       </c>
       <c r="B226" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C226" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D226" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #225</v>
+        <v>Verify swipe gestures across multi-page intro verification #225</v>
       </c>
       <c r="E226" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F226" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G226" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8327,19 +8327,19 @@
         <v>TC226</v>
       </c>
       <c r="B227" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C227" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D227" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #226</v>
+        <v>Render correct daily metrics upon authentication unlock verification #226</v>
       </c>
       <c r="E227" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F227" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G227" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8362,19 +8362,19 @@
         <v>TC227</v>
       </c>
       <c r="B228" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C228" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D228" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #227</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #227</v>
       </c>
       <c r="E228" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F228" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G228" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8397,19 +8397,19 @@
         <v>TC228</v>
       </c>
       <c r="B229" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C229" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D229" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #228</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #228</v>
       </c>
       <c r="E229" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F229" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G229" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8432,19 +8432,19 @@
         <v>TC229</v>
       </c>
       <c r="B230" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C230" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D230" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #229</v>
+        <v>Verify swipe gestures across multi-page intro verification #229</v>
       </c>
       <c r="E230" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F230" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G230" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8467,19 +8467,19 @@
         <v>TC230</v>
       </c>
       <c r="B231" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C231" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D231" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #230</v>
+        <v>Render correct daily metrics upon authentication unlock verification #230</v>
       </c>
       <c r="E231" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F231" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G231" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8502,19 +8502,19 @@
         <v>TC231</v>
       </c>
       <c r="B232" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C232" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D232" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #231</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #231</v>
       </c>
       <c r="E232" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F232" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G232" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8537,19 +8537,19 @@
         <v>TC232</v>
       </c>
       <c r="B233" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C233" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D233" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #232</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #232</v>
       </c>
       <c r="E233" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F233" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G233" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8572,19 +8572,19 @@
         <v>TC233</v>
       </c>
       <c r="B234" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C234" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D234" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #233</v>
+        <v>Verify swipe gestures across multi-page intro verification #233</v>
       </c>
       <c r="E234" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F234" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G234" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8607,19 +8607,19 @@
         <v>TC234</v>
       </c>
       <c r="B235" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C235" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D235" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #234</v>
+        <v>Render correct daily metrics upon authentication unlock verification #234</v>
       </c>
       <c r="E235" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F235" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G235" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8642,19 +8642,19 @@
         <v>TC235</v>
       </c>
       <c r="B236" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C236" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D236" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #235</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #235</v>
       </c>
       <c r="E236" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F236" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G236" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8677,19 +8677,19 @@
         <v>TC236</v>
       </c>
       <c r="B237" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C237" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D237" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #236</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #236</v>
       </c>
       <c r="E237" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F237" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G237" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8712,19 +8712,19 @@
         <v>TC237</v>
       </c>
       <c r="B238" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C238" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D238" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #237</v>
+        <v>Verify swipe gestures across multi-page intro verification #237</v>
       </c>
       <c r="E238" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F238" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G238" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8747,19 +8747,19 @@
         <v>TC238</v>
       </c>
       <c r="B239" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C239" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D239" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #238</v>
+        <v>Render correct daily metrics upon authentication unlock verification #238</v>
       </c>
       <c r="E239" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F239" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G239" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8782,19 +8782,19 @@
         <v>TC239</v>
       </c>
       <c r="B240" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C240" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D240" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #239</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #239</v>
       </c>
       <c r="E240" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F240" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G240" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8817,19 +8817,19 @@
         <v>TC240</v>
       </c>
       <c r="B241" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C241" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D241" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #240</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #240</v>
       </c>
       <c r="E241" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F241" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G241" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8852,19 +8852,19 @@
         <v>TC241</v>
       </c>
       <c r="B242" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C242" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D242" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #241</v>
+        <v>Verify swipe gestures across multi-page intro verification #241</v>
       </c>
       <c r="E242" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F242" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G242" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8887,19 +8887,19 @@
         <v>TC242</v>
       </c>
       <c r="B243" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C243" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D243" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #242</v>
+        <v>Render correct daily metrics upon authentication unlock verification #242</v>
       </c>
       <c r="E243" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F243" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G243" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8922,19 +8922,19 @@
         <v>TC243</v>
       </c>
       <c r="B244" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C244" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D244" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #243</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #243</v>
       </c>
       <c r="E244" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F244" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G244" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8957,19 +8957,19 @@
         <v>TC244</v>
       </c>
       <c r="B245" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C245" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D245" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #244</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #244</v>
       </c>
       <c r="E245" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F245" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G245" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8992,19 +8992,19 @@
         <v>TC245</v>
       </c>
       <c r="B246" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C246" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D246" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #245</v>
+        <v>Verify swipe gestures across multi-page intro verification #245</v>
       </c>
       <c r="E246" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F246" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G246" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9027,19 +9027,19 @@
         <v>TC246</v>
       </c>
       <c r="B247" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C247" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D247" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #246</v>
+        <v>Render correct daily metrics upon authentication unlock verification #246</v>
       </c>
       <c r="E247" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F247" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G247" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9062,19 +9062,19 @@
         <v>TC247</v>
       </c>
       <c r="B248" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C248" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D248" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #247</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #247</v>
       </c>
       <c r="E248" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F248" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G248" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9097,19 +9097,19 @@
         <v>TC248</v>
       </c>
       <c r="B249" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C249" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D249" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #248</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #248</v>
       </c>
       <c r="E249" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F249" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G249" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9132,19 +9132,19 @@
         <v>TC249</v>
       </c>
       <c r="B250" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C250" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D250" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #249</v>
+        <v>Verify swipe gestures across multi-page intro verification #249</v>
       </c>
       <c r="E250" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F250" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G250" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9167,19 +9167,19 @@
         <v>TC250</v>
       </c>
       <c r="B251" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C251" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D251" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #250</v>
+        <v>Render correct daily metrics upon authentication unlock verification #250</v>
       </c>
       <c r="E251" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F251" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G251" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9202,19 +9202,19 @@
         <v>TC251</v>
       </c>
       <c r="B252" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C252" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D252" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #251</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #251</v>
       </c>
       <c r="E252" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F252" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G252" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9237,19 +9237,19 @@
         <v>TC252</v>
       </c>
       <c r="B253" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C253" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D253" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #252</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #252</v>
       </c>
       <c r="E253" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F253" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G253" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9272,19 +9272,19 @@
         <v>TC253</v>
       </c>
       <c r="B254" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C254" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D254" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #253</v>
+        <v>Verify swipe gestures across multi-page intro verification #253</v>
       </c>
       <c r="E254" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F254" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G254" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9307,19 +9307,19 @@
         <v>TC254</v>
       </c>
       <c r="B255" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C255" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D255" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #254</v>
+        <v>Render correct daily metrics upon authentication unlock verification #254</v>
       </c>
       <c r="E255" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F255" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G255" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9342,19 +9342,19 @@
         <v>TC255</v>
       </c>
       <c r="B256" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C256" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D256" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #255</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #255</v>
       </c>
       <c r="E256" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F256" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G256" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9377,19 +9377,19 @@
         <v>TC256</v>
       </c>
       <c r="B257" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C257" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D257" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #256</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #256</v>
       </c>
       <c r="E257" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F257" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G257" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9412,19 +9412,19 @@
         <v>TC257</v>
       </c>
       <c r="B258" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C258" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D258" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #257</v>
+        <v>Verify swipe gestures across multi-page intro verification #257</v>
       </c>
       <c r="E258" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F258" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G258" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9447,19 +9447,19 @@
         <v>TC258</v>
       </c>
       <c r="B259" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C259" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D259" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #258</v>
+        <v>Render correct daily metrics upon authentication unlock verification #258</v>
       </c>
       <c r="E259" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F259" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G259" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9482,19 +9482,19 @@
         <v>TC259</v>
       </c>
       <c r="B260" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C260" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D260" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #259</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #259</v>
       </c>
       <c r="E260" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F260" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G260" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9517,19 +9517,19 @@
         <v>TC260</v>
       </c>
       <c r="B261" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C261" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D261" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #260</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #260</v>
       </c>
       <c r="E261" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F261" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G261" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9552,19 +9552,19 @@
         <v>TC261</v>
       </c>
       <c r="B262" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C262" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D262" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #261</v>
+        <v>Verify swipe gestures across multi-page intro verification #261</v>
       </c>
       <c r="E262" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F262" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G262" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9587,19 +9587,19 @@
         <v>TC262</v>
       </c>
       <c r="B263" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C263" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D263" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #262</v>
+        <v>Render correct daily metrics upon authentication unlock verification #262</v>
       </c>
       <c r="E263" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F263" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G263" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9622,19 +9622,19 @@
         <v>TC263</v>
       </c>
       <c r="B264" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C264" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D264" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #263</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #263</v>
       </c>
       <c r="E264" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F264" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G264" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9657,19 +9657,19 @@
         <v>TC264</v>
       </c>
       <c r="B265" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C265" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D265" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #264</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #264</v>
       </c>
       <c r="E265" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F265" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G265" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9692,19 +9692,19 @@
         <v>TC265</v>
       </c>
       <c r="B266" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C266" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D266" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #265</v>
+        <v>Verify swipe gestures across multi-page intro verification #265</v>
       </c>
       <c r="E266" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F266" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G266" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9727,19 +9727,19 @@
         <v>TC266</v>
       </c>
       <c r="B267" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C267" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D267" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #266</v>
+        <v>Render correct daily metrics upon authentication unlock verification #266</v>
       </c>
       <c r="E267" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F267" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G267" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9762,19 +9762,19 @@
         <v>TC267</v>
       </c>
       <c r="B268" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C268" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D268" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #267</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #267</v>
       </c>
       <c r="E268" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F268" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G268" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9797,19 +9797,19 @@
         <v>TC268</v>
       </c>
       <c r="B269" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C269" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D269" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #268</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #268</v>
       </c>
       <c r="E269" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F269" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G269" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9832,19 +9832,19 @@
         <v>TC269</v>
       </c>
       <c r="B270" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C270" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D270" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #269</v>
+        <v>Verify swipe gestures across multi-page intro verification #269</v>
       </c>
       <c r="E270" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F270" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G270" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9867,19 +9867,19 @@
         <v>TC270</v>
       </c>
       <c r="B271" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C271" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D271" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #270</v>
+        <v>Render correct daily metrics upon authentication unlock verification #270</v>
       </c>
       <c r="E271" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F271" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G271" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9902,19 +9902,19 @@
         <v>TC271</v>
       </c>
       <c r="B272" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C272" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D272" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #271</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #271</v>
       </c>
       <c r="E272" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F272" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G272" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9937,19 +9937,19 @@
         <v>TC272</v>
       </c>
       <c r="B273" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C273" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D273" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #272</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #272</v>
       </c>
       <c r="E273" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F273" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G273" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9972,19 +9972,19 @@
         <v>TC273</v>
       </c>
       <c r="B274" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C274" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D274" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #273</v>
+        <v>Verify swipe gestures across multi-page intro verification #273</v>
       </c>
       <c r="E274" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F274" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G274" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10007,19 +10007,19 @@
         <v>TC274</v>
       </c>
       <c r="B275" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C275" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D275" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #274</v>
+        <v>Render correct daily metrics upon authentication unlock verification #274</v>
       </c>
       <c r="E275" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F275" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G275" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10042,19 +10042,19 @@
         <v>TC275</v>
       </c>
       <c r="B276" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C276" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D276" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #275</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #275</v>
       </c>
       <c r="E276" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F276" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G276" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10077,19 +10077,19 @@
         <v>TC276</v>
       </c>
       <c r="B277" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C277" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D277" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #276</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #276</v>
       </c>
       <c r="E277" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F277" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G277" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10112,19 +10112,19 @@
         <v>TC277</v>
       </c>
       <c r="B278" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C278" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D278" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #277</v>
+        <v>Verify swipe gestures across multi-page intro verification #277</v>
       </c>
       <c r="E278" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F278" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G278" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10147,19 +10147,19 @@
         <v>TC278</v>
       </c>
       <c r="B279" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C279" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D279" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #278</v>
+        <v>Render correct daily metrics upon authentication unlock verification #278</v>
       </c>
       <c r="E279" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F279" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G279" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10182,19 +10182,19 @@
         <v>TC279</v>
       </c>
       <c r="B280" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C280" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D280" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #279</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #279</v>
       </c>
       <c r="E280" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F280" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G280" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10217,19 +10217,19 @@
         <v>TC280</v>
       </c>
       <c r="B281" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C281" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D281" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #280</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #280</v>
       </c>
       <c r="E281" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F281" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G281" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10252,19 +10252,19 @@
         <v>TC281</v>
       </c>
       <c r="B282" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C282" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D282" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #281</v>
+        <v>Verify swipe gestures across multi-page intro verification #281</v>
       </c>
       <c r="E282" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F282" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G282" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10287,19 +10287,19 @@
         <v>TC282</v>
       </c>
       <c r="B283" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C283" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D283" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #282</v>
+        <v>Render correct daily metrics upon authentication unlock verification #282</v>
       </c>
       <c r="E283" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F283" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G283" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10322,19 +10322,19 @@
         <v>TC283</v>
       </c>
       <c r="B284" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C284" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D284" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #283</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #283</v>
       </c>
       <c r="E284" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F284" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G284" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10357,19 +10357,19 @@
         <v>TC284</v>
       </c>
       <c r="B285" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C285" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D285" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #284</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #284</v>
       </c>
       <c r="E285" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F285" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G285" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10392,19 +10392,19 @@
         <v>TC285</v>
       </c>
       <c r="B286" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C286" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D286" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #285</v>
+        <v>Verify swipe gestures across multi-page intro verification #285</v>
       </c>
       <c r="E286" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F286" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G286" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10427,19 +10427,19 @@
         <v>TC286</v>
       </c>
       <c r="B287" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C287" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D287" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #286</v>
+        <v>Render correct daily metrics upon authentication unlock verification #286</v>
       </c>
       <c r="E287" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F287" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G287" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10462,19 +10462,19 @@
         <v>TC287</v>
       </c>
       <c r="B288" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C288" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D288" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #287</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #287</v>
       </c>
       <c r="E288" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F288" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G288" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10497,19 +10497,19 @@
         <v>TC288</v>
       </c>
       <c r="B289" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C289" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D289" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #288</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #288</v>
       </c>
       <c r="E289" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F289" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G289" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10532,19 +10532,19 @@
         <v>TC289</v>
       </c>
       <c r="B290" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C290" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D290" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #289</v>
+        <v>Verify swipe gestures across multi-page intro verification #289</v>
       </c>
       <c r="E290" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F290" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G290" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10567,19 +10567,19 @@
         <v>TC290</v>
       </c>
       <c r="B291" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C291" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D291" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #290</v>
+        <v>Render correct daily metrics upon authentication unlock verification #290</v>
       </c>
       <c r="E291" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F291" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G291" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10602,19 +10602,19 @@
         <v>TC291</v>
       </c>
       <c r="B292" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C292" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D292" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #291</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #291</v>
       </c>
       <c r="E292" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F292" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G292" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10637,19 +10637,19 @@
         <v>TC292</v>
       </c>
       <c r="B293" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C293" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D293" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #292</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #292</v>
       </c>
       <c r="E293" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F293" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G293" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10672,19 +10672,19 @@
         <v>TC293</v>
       </c>
       <c r="B294" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C294" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D294" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #293</v>
+        <v>Verify swipe gestures across multi-page intro verification #293</v>
       </c>
       <c r="E294" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F294" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G294" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10707,19 +10707,19 @@
         <v>TC294</v>
       </c>
       <c r="B295" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C295" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D295" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #294</v>
+        <v>Render correct daily metrics upon authentication unlock verification #294</v>
       </c>
       <c r="E295" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F295" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G295" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10742,19 +10742,19 @@
         <v>TC295</v>
       </c>
       <c r="B296" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C296" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D296" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #295</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #295</v>
       </c>
       <c r="E296" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F296" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G296" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10777,19 +10777,19 @@
         <v>TC296</v>
       </c>
       <c r="B297" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C297" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D297" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #296</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #296</v>
       </c>
       <c r="E297" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F297" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G297" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10812,19 +10812,19 @@
         <v>TC297</v>
       </c>
       <c r="B298" t="str">
-        <v>Mobile Layout</v>
+        <v>Onboarding</v>
       </c>
       <c r="C298" t="str">
-        <v>Responsive</v>
+        <v>Tutorial Array</v>
       </c>
       <c r="D298" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #297</v>
+        <v>Verify swipe gestures across multi-page intro verification #297</v>
       </c>
       <c r="E298" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F298" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Onboarding and perform Tutorial Array action</v>
       </c>
       <c r="G298" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10847,19 +10847,19 @@
         <v>TC298</v>
       </c>
       <c r="B299" t="str">
-        <v>Input Method</v>
+        <v>Home Screen</v>
       </c>
       <c r="C299" t="str">
-        <v>Soft Keyboard</v>
+        <v>Dashboard</v>
       </c>
       <c r="D299" t="str">
-        <v>Ensure Android keyboard shifts chat input upwards effortlessly verification #298</v>
+        <v>Render correct daily metrics upon authentication unlock verification #298</v>
       </c>
       <c r="E299" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F299" t="str">
-        <v>Navigate to Input Method and perform Soft Keyboard action</v>
+        <v>Navigate to Home Screen and perform Dashboard action</v>
       </c>
       <c r="G299" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10882,19 +10882,19 @@
         <v>TC299</v>
       </c>
       <c r="B300" t="str">
-        <v>Navigation</v>
+        <v>Mobile Layout</v>
       </c>
       <c r="C300" t="str">
-        <v>Back Stack</v>
+        <v>Responsive</v>
       </c>
       <c r="D300" t="str">
-        <v>Verify hardware back button prevents framework routing crashes verification #299</v>
+        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #299</v>
       </c>
       <c r="E300" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F300" t="str">
-        <v>Navigate to Navigation and perform Back Stack action</v>
+        <v>Navigate to Mobile Layout and perform Responsive action</v>
       </c>
       <c r="G300" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10917,19 +10917,19 @@
         <v>TC300</v>
       </c>
       <c r="B301" t="str">
-        <v>Expo Wrapper</v>
+        <v>App Initialization</v>
       </c>
       <c r="C301" t="str">
-        <v>Launch</v>
+        <v>Splash Screen</v>
       </c>
       <c r="D301" t="str">
-        <v>Render React web UI safely within Native Android boundaries verification #300</v>
+        <v>Verify full-screen logo rendering under 2000ms verification #300</v>
       </c>
       <c r="E301" t="str">
         <v>App running on Android/iOS</v>
       </c>
       <c r="F301" t="str">
-        <v>Navigate to Expo Wrapper and perform Launch action</v>
+        <v>Navigate to App Initialization and perform Splash Screen action</v>
       </c>
       <c r="G301" t="str">
         <v>Action completes successfully within standard latency bounds</v>

--- a/e2e_tests_suite/Report_02_Appium.xlsx
+++ b/e2e_tests_suite/Report_02_Appium.xlsx
@@ -461,7 +461,7 @@
         <v>Verify swipe gestures across multi-page intro verification #1</v>
       </c>
       <c r="E2" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F2" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -476,7 +476,7 @@
         <v>Functional</v>
       </c>
       <c r="J2" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K2" t="str">
         <v>Pass</v>
@@ -496,7 +496,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #2</v>
       </c>
       <c r="E3" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F3" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -511,7 +511,7 @@
         <v>Functional</v>
       </c>
       <c r="J3" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K3" t="str">
         <v>Pass</v>
@@ -531,7 +531,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #3</v>
       </c>
       <c r="E4" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F4" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -546,7 +546,7 @@
         <v>Functional</v>
       </c>
       <c r="J4" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K4" t="str">
         <v>Pass</v>
@@ -566,7 +566,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #4</v>
       </c>
       <c r="E5" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F5" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -581,7 +581,7 @@
         <v>Functional</v>
       </c>
       <c r="J5" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K5" t="str">
         <v>Pass</v>
@@ -601,7 +601,7 @@
         <v>Verify swipe gestures across multi-page intro verification #5</v>
       </c>
       <c r="E6" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F6" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -616,7 +616,7 @@
         <v>Functional</v>
       </c>
       <c r="J6" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K6" t="str">
         <v>Pass</v>
@@ -636,7 +636,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #6</v>
       </c>
       <c r="E7" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F7" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -651,7 +651,7 @@
         <v>Functional</v>
       </c>
       <c r="J7" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K7" t="str">
         <v>Pass</v>
@@ -671,7 +671,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #7</v>
       </c>
       <c r="E8" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F8" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -686,7 +686,7 @@
         <v>Functional</v>
       </c>
       <c r="J8" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K8" t="str">
         <v>Pass</v>
@@ -706,7 +706,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #8</v>
       </c>
       <c r="E9" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F9" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -721,7 +721,7 @@
         <v>Functional</v>
       </c>
       <c r="J9" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K9" t="str">
         <v>Pass</v>
@@ -741,7 +741,7 @@
         <v>Verify swipe gestures across multi-page intro verification #9</v>
       </c>
       <c r="E10" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F10" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -756,7 +756,7 @@
         <v>Functional</v>
       </c>
       <c r="J10" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K10" t="str">
         <v>Pass</v>
@@ -776,7 +776,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #10</v>
       </c>
       <c r="E11" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F11" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -791,7 +791,7 @@
         <v>Functional</v>
       </c>
       <c r="J11" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K11" t="str">
         <v>Pass</v>
@@ -811,7 +811,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #11</v>
       </c>
       <c r="E12" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F12" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -826,7 +826,7 @@
         <v>Functional</v>
       </c>
       <c r="J12" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K12" t="str">
         <v>Pass</v>
@@ -846,7 +846,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #12</v>
       </c>
       <c r="E13" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F13" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -861,7 +861,7 @@
         <v>Functional</v>
       </c>
       <c r="J13" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K13" t="str">
         <v>Pass</v>
@@ -881,7 +881,7 @@
         <v>Verify swipe gestures across multi-page intro verification #13</v>
       </c>
       <c r="E14" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F14" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -896,7 +896,7 @@
         <v>Functional</v>
       </c>
       <c r="J14" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K14" t="str">
         <v>Pass</v>
@@ -916,7 +916,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #14</v>
       </c>
       <c r="E15" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F15" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -931,7 +931,7 @@
         <v>Functional</v>
       </c>
       <c r="J15" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K15" t="str">
         <v>Pass</v>
@@ -951,7 +951,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #15</v>
       </c>
       <c r="E16" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F16" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -966,7 +966,7 @@
         <v>Functional</v>
       </c>
       <c r="J16" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K16" t="str">
         <v>Pass</v>
@@ -986,7 +986,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #16</v>
       </c>
       <c r="E17" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F17" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -1001,7 +1001,7 @@
         <v>Functional</v>
       </c>
       <c r="J17" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K17" t="str">
         <v>Pass</v>
@@ -1021,7 +1021,7 @@
         <v>Verify swipe gestures across multi-page intro verification #17</v>
       </c>
       <c r="E18" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F18" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -1036,7 +1036,7 @@
         <v>Functional</v>
       </c>
       <c r="J18" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K18" t="str">
         <v>Pass</v>
@@ -1056,7 +1056,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #18</v>
       </c>
       <c r="E19" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F19" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -1071,7 +1071,7 @@
         <v>Functional</v>
       </c>
       <c r="J19" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K19" t="str">
         <v>Pass</v>
@@ -1091,7 +1091,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #19</v>
       </c>
       <c r="E20" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F20" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -1106,7 +1106,7 @@
         <v>Functional</v>
       </c>
       <c r="J20" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K20" t="str">
         <v>Pass</v>
@@ -1126,7 +1126,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #20</v>
       </c>
       <c r="E21" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F21" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -1141,7 +1141,7 @@
         <v>Functional</v>
       </c>
       <c r="J21" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K21" t="str">
         <v>Pass</v>
@@ -1161,7 +1161,7 @@
         <v>Verify swipe gestures across multi-page intro verification #21</v>
       </c>
       <c r="E22" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F22" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -1176,7 +1176,7 @@
         <v>Functional</v>
       </c>
       <c r="J22" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K22" t="str">
         <v>Pass</v>
@@ -1196,7 +1196,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #22</v>
       </c>
       <c r="E23" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F23" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -1211,7 +1211,7 @@
         <v>Functional</v>
       </c>
       <c r="J23" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K23" t="str">
         <v>Pass</v>
@@ -1231,7 +1231,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #23</v>
       </c>
       <c r="E24" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F24" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -1246,7 +1246,7 @@
         <v>Functional</v>
       </c>
       <c r="J24" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K24" t="str">
         <v>Pass</v>
@@ -1266,7 +1266,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #24</v>
       </c>
       <c r="E25" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F25" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -1281,7 +1281,7 @@
         <v>Functional</v>
       </c>
       <c r="J25" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K25" t="str">
         <v>Pass</v>
@@ -1301,7 +1301,7 @@
         <v>Verify swipe gestures across multi-page intro verification #25</v>
       </c>
       <c r="E26" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F26" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -1316,7 +1316,7 @@
         <v>Functional</v>
       </c>
       <c r="J26" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K26" t="str">
         <v>Pass</v>
@@ -1336,7 +1336,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #26</v>
       </c>
       <c r="E27" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F27" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -1351,7 +1351,7 @@
         <v>Functional</v>
       </c>
       <c r="J27" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K27" t="str">
         <v>Pass</v>
@@ -1371,7 +1371,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #27</v>
       </c>
       <c r="E28" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F28" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -1386,7 +1386,7 @@
         <v>Functional</v>
       </c>
       <c r="J28" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K28" t="str">
         <v>Pass</v>
@@ -1406,7 +1406,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #28</v>
       </c>
       <c r="E29" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F29" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -1421,7 +1421,7 @@
         <v>Functional</v>
       </c>
       <c r="J29" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K29" t="str">
         <v>Pass</v>
@@ -1441,7 +1441,7 @@
         <v>Verify swipe gestures across multi-page intro verification #29</v>
       </c>
       <c r="E30" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F30" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -1456,7 +1456,7 @@
         <v>Functional</v>
       </c>
       <c r="J30" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K30" t="str">
         <v>Pass</v>
@@ -1476,7 +1476,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #30</v>
       </c>
       <c r="E31" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F31" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -1491,7 +1491,7 @@
         <v>Functional</v>
       </c>
       <c r="J31" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K31" t="str">
         <v>Pass</v>
@@ -1511,7 +1511,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #31</v>
       </c>
       <c r="E32" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F32" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -1526,7 +1526,7 @@
         <v>Functional</v>
       </c>
       <c r="J32" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K32" t="str">
         <v>Pass</v>
@@ -1546,7 +1546,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #32</v>
       </c>
       <c r="E33" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F33" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -1561,7 +1561,7 @@
         <v>Functional</v>
       </c>
       <c r="J33" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K33" t="str">
         <v>Pass</v>
@@ -1581,7 +1581,7 @@
         <v>Verify swipe gestures across multi-page intro verification #33</v>
       </c>
       <c r="E34" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F34" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -1596,7 +1596,7 @@
         <v>Functional</v>
       </c>
       <c r="J34" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K34" t="str">
         <v>Pass</v>
@@ -1616,7 +1616,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #34</v>
       </c>
       <c r="E35" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F35" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -1631,7 +1631,7 @@
         <v>Functional</v>
       </c>
       <c r="J35" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K35" t="str">
         <v>Pass</v>
@@ -1651,7 +1651,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #35</v>
       </c>
       <c r="E36" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F36" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -1666,7 +1666,7 @@
         <v>Functional</v>
       </c>
       <c r="J36" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K36" t="str">
         <v>Pass</v>
@@ -1686,7 +1686,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #36</v>
       </c>
       <c r="E37" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F37" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -1701,7 +1701,7 @@
         <v>Functional</v>
       </c>
       <c r="J37" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K37" t="str">
         <v>Pass</v>
@@ -1721,7 +1721,7 @@
         <v>Verify swipe gestures across multi-page intro verification #37</v>
       </c>
       <c r="E38" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F38" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -1736,7 +1736,7 @@
         <v>Functional</v>
       </c>
       <c r="J38" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K38" t="str">
         <v>Pass</v>
@@ -1756,7 +1756,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #38</v>
       </c>
       <c r="E39" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F39" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -1771,7 +1771,7 @@
         <v>Functional</v>
       </c>
       <c r="J39" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K39" t="str">
         <v>Pass</v>
@@ -1791,7 +1791,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #39</v>
       </c>
       <c r="E40" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F40" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -1806,7 +1806,7 @@
         <v>Functional</v>
       </c>
       <c r="J40" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K40" t="str">
         <v>Pass</v>
@@ -1826,7 +1826,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #40</v>
       </c>
       <c r="E41" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F41" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -1841,7 +1841,7 @@
         <v>Functional</v>
       </c>
       <c r="J41" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K41" t="str">
         <v>Pass</v>
@@ -1861,7 +1861,7 @@
         <v>Verify swipe gestures across multi-page intro verification #41</v>
       </c>
       <c r="E42" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F42" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -1876,7 +1876,7 @@
         <v>Functional</v>
       </c>
       <c r="J42" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K42" t="str">
         <v>Pass</v>
@@ -1896,7 +1896,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #42</v>
       </c>
       <c r="E43" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F43" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -1911,7 +1911,7 @@
         <v>Functional</v>
       </c>
       <c r="J43" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K43" t="str">
         <v>Pass</v>
@@ -1931,7 +1931,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #43</v>
       </c>
       <c r="E44" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F44" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -1946,7 +1946,7 @@
         <v>Functional</v>
       </c>
       <c r="J44" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K44" t="str">
         <v>Pass</v>
@@ -1966,7 +1966,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #44</v>
       </c>
       <c r="E45" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F45" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -1981,7 +1981,7 @@
         <v>Functional</v>
       </c>
       <c r="J45" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K45" t="str">
         <v>Pass</v>
@@ -2001,7 +2001,7 @@
         <v>Verify swipe gestures across multi-page intro verification #45</v>
       </c>
       <c r="E46" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F46" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -2016,7 +2016,7 @@
         <v>Functional</v>
       </c>
       <c r="J46" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K46" t="str">
         <v>Pass</v>
@@ -2036,7 +2036,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #46</v>
       </c>
       <c r="E47" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F47" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -2051,7 +2051,7 @@
         <v>Functional</v>
       </c>
       <c r="J47" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K47" t="str">
         <v>Pass</v>
@@ -2071,7 +2071,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #47</v>
       </c>
       <c r="E48" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F48" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -2086,7 +2086,7 @@
         <v>Functional</v>
       </c>
       <c r="J48" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K48" t="str">
         <v>Pass</v>
@@ -2106,7 +2106,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #48</v>
       </c>
       <c r="E49" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F49" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -2121,7 +2121,7 @@
         <v>Functional</v>
       </c>
       <c r="J49" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K49" t="str">
         <v>Pass</v>
@@ -2141,7 +2141,7 @@
         <v>Verify swipe gestures across multi-page intro verification #49</v>
       </c>
       <c r="E50" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F50" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -2156,7 +2156,7 @@
         <v>Functional</v>
       </c>
       <c r="J50" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K50" t="str">
         <v>Pass</v>
@@ -2176,7 +2176,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #50</v>
       </c>
       <c r="E51" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F51" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -2191,7 +2191,7 @@
         <v>Functional</v>
       </c>
       <c r="J51" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K51" t="str">
         <v>Pass</v>
@@ -2211,7 +2211,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #51</v>
       </c>
       <c r="E52" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F52" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -2226,7 +2226,7 @@
         <v>Functional</v>
       </c>
       <c r="J52" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K52" t="str">
         <v>Pass</v>
@@ -2246,7 +2246,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #52</v>
       </c>
       <c r="E53" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F53" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -2261,7 +2261,7 @@
         <v>Functional</v>
       </c>
       <c r="J53" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K53" t="str">
         <v>Pass</v>
@@ -2281,7 +2281,7 @@
         <v>Verify swipe gestures across multi-page intro verification #53</v>
       </c>
       <c r="E54" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F54" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -2296,7 +2296,7 @@
         <v>Functional</v>
       </c>
       <c r="J54" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K54" t="str">
         <v>Pass</v>
@@ -2316,7 +2316,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #54</v>
       </c>
       <c r="E55" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F55" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -2331,7 +2331,7 @@
         <v>Functional</v>
       </c>
       <c r="J55" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K55" t="str">
         <v>Pass</v>
@@ -2351,7 +2351,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #55</v>
       </c>
       <c r="E56" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F56" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -2366,7 +2366,7 @@
         <v>Functional</v>
       </c>
       <c r="J56" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K56" t="str">
         <v>Pass</v>
@@ -2386,7 +2386,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #56</v>
       </c>
       <c r="E57" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F57" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -2401,7 +2401,7 @@
         <v>Functional</v>
       </c>
       <c r="J57" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K57" t="str">
         <v>Pass</v>
@@ -2421,7 +2421,7 @@
         <v>Verify swipe gestures across multi-page intro verification #57</v>
       </c>
       <c r="E58" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F58" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -2436,7 +2436,7 @@
         <v>Functional</v>
       </c>
       <c r="J58" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K58" t="str">
         <v>Pass</v>
@@ -2456,7 +2456,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #58</v>
       </c>
       <c r="E59" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F59" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -2471,7 +2471,7 @@
         <v>Functional</v>
       </c>
       <c r="J59" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K59" t="str">
         <v>Pass</v>
@@ -2491,7 +2491,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #59</v>
       </c>
       <c r="E60" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F60" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -2506,7 +2506,7 @@
         <v>Functional</v>
       </c>
       <c r="J60" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K60" t="str">
         <v>Pass</v>
@@ -2526,7 +2526,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #60</v>
       </c>
       <c r="E61" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F61" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -2541,7 +2541,7 @@
         <v>Functional</v>
       </c>
       <c r="J61" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K61" t="str">
         <v>Pass</v>
@@ -2561,7 +2561,7 @@
         <v>Verify swipe gestures across multi-page intro verification #61</v>
       </c>
       <c r="E62" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F62" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -2576,7 +2576,7 @@
         <v>Functional</v>
       </c>
       <c r="J62" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K62" t="str">
         <v>Pass</v>
@@ -2596,7 +2596,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #62</v>
       </c>
       <c r="E63" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F63" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -2611,7 +2611,7 @@
         <v>Functional</v>
       </c>
       <c r="J63" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K63" t="str">
         <v>Pass</v>
@@ -2631,7 +2631,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #63</v>
       </c>
       <c r="E64" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F64" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -2646,7 +2646,7 @@
         <v>Functional</v>
       </c>
       <c r="J64" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K64" t="str">
         <v>Pass</v>
@@ -2666,7 +2666,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #64</v>
       </c>
       <c r="E65" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F65" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -2681,7 +2681,7 @@
         <v>Functional</v>
       </c>
       <c r="J65" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K65" t="str">
         <v>Pass</v>
@@ -2701,7 +2701,7 @@
         <v>Verify swipe gestures across multi-page intro verification #65</v>
       </c>
       <c r="E66" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F66" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -2716,7 +2716,7 @@
         <v>Functional</v>
       </c>
       <c r="J66" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K66" t="str">
         <v>Pass</v>
@@ -2736,7 +2736,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #66</v>
       </c>
       <c r="E67" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F67" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -2751,7 +2751,7 @@
         <v>Functional</v>
       </c>
       <c r="J67" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K67" t="str">
         <v>Pass</v>
@@ -2771,7 +2771,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #67</v>
       </c>
       <c r="E68" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F68" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -2786,7 +2786,7 @@
         <v>Functional</v>
       </c>
       <c r="J68" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K68" t="str">
         <v>Pass</v>
@@ -2806,7 +2806,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #68</v>
       </c>
       <c r="E69" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F69" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -2821,7 +2821,7 @@
         <v>Functional</v>
       </c>
       <c r="J69" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K69" t="str">
         <v>Pass</v>
@@ -2841,7 +2841,7 @@
         <v>Verify swipe gestures across multi-page intro verification #69</v>
       </c>
       <c r="E70" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F70" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -2856,7 +2856,7 @@
         <v>Functional</v>
       </c>
       <c r="J70" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K70" t="str">
         <v>Pass</v>
@@ -2876,7 +2876,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #70</v>
       </c>
       <c r="E71" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F71" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -2891,7 +2891,7 @@
         <v>Functional</v>
       </c>
       <c r="J71" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K71" t="str">
         <v>Pass</v>
@@ -2911,7 +2911,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #71</v>
       </c>
       <c r="E72" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F72" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -2926,7 +2926,7 @@
         <v>Functional</v>
       </c>
       <c r="J72" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K72" t="str">
         <v>Pass</v>
@@ -2946,7 +2946,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #72</v>
       </c>
       <c r="E73" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F73" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -2961,7 +2961,7 @@
         <v>Functional</v>
       </c>
       <c r="J73" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K73" t="str">
         <v>Pass</v>
@@ -2981,7 +2981,7 @@
         <v>Verify swipe gestures across multi-page intro verification #73</v>
       </c>
       <c r="E74" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F74" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -2996,7 +2996,7 @@
         <v>Functional</v>
       </c>
       <c r="J74" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K74" t="str">
         <v>Pass</v>
@@ -3016,7 +3016,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #74</v>
       </c>
       <c r="E75" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F75" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -3031,7 +3031,7 @@
         <v>Functional</v>
       </c>
       <c r="J75" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K75" t="str">
         <v>Pass</v>
@@ -3051,7 +3051,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #75</v>
       </c>
       <c r="E76" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F76" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -3066,7 +3066,7 @@
         <v>Functional</v>
       </c>
       <c r="J76" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K76" t="str">
         <v>Pass</v>
@@ -3086,7 +3086,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #76</v>
       </c>
       <c r="E77" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F77" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -3101,7 +3101,7 @@
         <v>Functional</v>
       </c>
       <c r="J77" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K77" t="str">
         <v>Pass</v>
@@ -3121,7 +3121,7 @@
         <v>Verify swipe gestures across multi-page intro verification #77</v>
       </c>
       <c r="E78" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F78" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -3136,7 +3136,7 @@
         <v>Functional</v>
       </c>
       <c r="J78" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K78" t="str">
         <v>Pass</v>
@@ -3156,7 +3156,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #78</v>
       </c>
       <c r="E79" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F79" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -3171,7 +3171,7 @@
         <v>Functional</v>
       </c>
       <c r="J79" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K79" t="str">
         <v>Pass</v>
@@ -3191,7 +3191,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #79</v>
       </c>
       <c r="E80" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F80" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -3206,7 +3206,7 @@
         <v>Functional</v>
       </c>
       <c r="J80" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K80" t="str">
         <v>Pass</v>
@@ -3226,7 +3226,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #80</v>
       </c>
       <c r="E81" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F81" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -3241,7 +3241,7 @@
         <v>Functional</v>
       </c>
       <c r="J81" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K81" t="str">
         <v>Pass</v>
@@ -3261,7 +3261,7 @@
         <v>Verify swipe gestures across multi-page intro verification #81</v>
       </c>
       <c r="E82" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F82" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -3276,7 +3276,7 @@
         <v>Functional</v>
       </c>
       <c r="J82" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K82" t="str">
         <v>Pass</v>
@@ -3296,7 +3296,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #82</v>
       </c>
       <c r="E83" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F83" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -3311,7 +3311,7 @@
         <v>Functional</v>
       </c>
       <c r="J83" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K83" t="str">
         <v>Pass</v>
@@ -3331,7 +3331,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #83</v>
       </c>
       <c r="E84" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F84" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -3346,7 +3346,7 @@
         <v>Functional</v>
       </c>
       <c r="J84" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K84" t="str">
         <v>Pass</v>
@@ -3366,7 +3366,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #84</v>
       </c>
       <c r="E85" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F85" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -3381,7 +3381,7 @@
         <v>Functional</v>
       </c>
       <c r="J85" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K85" t="str">
         <v>Pass</v>
@@ -3401,7 +3401,7 @@
         <v>Verify swipe gestures across multi-page intro verification #85</v>
       </c>
       <c r="E86" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F86" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -3416,7 +3416,7 @@
         <v>Functional</v>
       </c>
       <c r="J86" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K86" t="str">
         <v>Pass</v>
@@ -3436,7 +3436,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #86</v>
       </c>
       <c r="E87" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F87" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -3451,7 +3451,7 @@
         <v>Functional</v>
       </c>
       <c r="J87" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K87" t="str">
         <v>Pass</v>
@@ -3471,7 +3471,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #87</v>
       </c>
       <c r="E88" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F88" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -3486,7 +3486,7 @@
         <v>Functional</v>
       </c>
       <c r="J88" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K88" t="str">
         <v>Pass</v>
@@ -3506,7 +3506,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #88</v>
       </c>
       <c r="E89" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F89" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -3521,7 +3521,7 @@
         <v>Functional</v>
       </c>
       <c r="J89" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K89" t="str">
         <v>Pass</v>
@@ -3541,7 +3541,7 @@
         <v>Verify swipe gestures across multi-page intro verification #89</v>
       </c>
       <c r="E90" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F90" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -3556,7 +3556,7 @@
         <v>Functional</v>
       </c>
       <c r="J90" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K90" t="str">
         <v>Pass</v>
@@ -3576,7 +3576,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #90</v>
       </c>
       <c r="E91" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F91" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -3591,7 +3591,7 @@
         <v>Functional</v>
       </c>
       <c r="J91" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K91" t="str">
         <v>Pass</v>
@@ -3611,7 +3611,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #91</v>
       </c>
       <c r="E92" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F92" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -3626,7 +3626,7 @@
         <v>Functional</v>
       </c>
       <c r="J92" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K92" t="str">
         <v>Pass</v>
@@ -3646,7 +3646,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #92</v>
       </c>
       <c r="E93" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F93" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -3661,7 +3661,7 @@
         <v>Functional</v>
       </c>
       <c r="J93" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K93" t="str">
         <v>Pass</v>
@@ -3681,7 +3681,7 @@
         <v>Verify swipe gestures across multi-page intro verification #93</v>
       </c>
       <c r="E94" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F94" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -3696,7 +3696,7 @@
         <v>Functional</v>
       </c>
       <c r="J94" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K94" t="str">
         <v>Pass</v>
@@ -3716,7 +3716,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #94</v>
       </c>
       <c r="E95" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F95" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -3731,7 +3731,7 @@
         <v>Functional</v>
       </c>
       <c r="J95" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K95" t="str">
         <v>Pass</v>
@@ -3751,7 +3751,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #95</v>
       </c>
       <c r="E96" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F96" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -3766,7 +3766,7 @@
         <v>Functional</v>
       </c>
       <c r="J96" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K96" t="str">
         <v>Pass</v>
@@ -3786,7 +3786,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #96</v>
       </c>
       <c r="E97" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F97" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -3801,7 +3801,7 @@
         <v>Functional</v>
       </c>
       <c r="J97" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K97" t="str">
         <v>Pass</v>
@@ -3821,7 +3821,7 @@
         <v>Verify swipe gestures across multi-page intro verification #97</v>
       </c>
       <c r="E98" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F98" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -3836,7 +3836,7 @@
         <v>Functional</v>
       </c>
       <c r="J98" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K98" t="str">
         <v>Pass</v>
@@ -3856,7 +3856,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #98</v>
       </c>
       <c r="E99" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F99" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -3871,7 +3871,7 @@
         <v>Functional</v>
       </c>
       <c r="J99" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K99" t="str">
         <v>Pass</v>
@@ -3891,7 +3891,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #99</v>
       </c>
       <c r="E100" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F100" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -3906,7 +3906,7 @@
         <v>Functional</v>
       </c>
       <c r="J100" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K100" t="str">
         <v>Pass</v>
@@ -3926,7 +3926,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #100</v>
       </c>
       <c r="E101" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F101" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -3941,7 +3941,7 @@
         <v>Functional</v>
       </c>
       <c r="J101" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K101" t="str">
         <v>Pass</v>
@@ -3961,7 +3961,7 @@
         <v>Verify swipe gestures across multi-page intro verification #101</v>
       </c>
       <c r="E102" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F102" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -3976,7 +3976,7 @@
         <v>Functional</v>
       </c>
       <c r="J102" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K102" t="str">
         <v>Pass</v>
@@ -3996,7 +3996,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #102</v>
       </c>
       <c r="E103" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F103" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -4011,7 +4011,7 @@
         <v>Functional</v>
       </c>
       <c r="J103" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K103" t="str">
         <v>Pass</v>
@@ -4031,7 +4031,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #103</v>
       </c>
       <c r="E104" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F104" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -4046,7 +4046,7 @@
         <v>Functional</v>
       </c>
       <c r="J104" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K104" t="str">
         <v>Pass</v>
@@ -4066,7 +4066,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #104</v>
       </c>
       <c r="E105" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F105" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -4081,7 +4081,7 @@
         <v>Functional</v>
       </c>
       <c r="J105" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K105" t="str">
         <v>Pass</v>
@@ -4101,7 +4101,7 @@
         <v>Verify swipe gestures across multi-page intro verification #105</v>
       </c>
       <c r="E106" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F106" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -4116,7 +4116,7 @@
         <v>Functional</v>
       </c>
       <c r="J106" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K106" t="str">
         <v>Pass</v>
@@ -4136,7 +4136,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #106</v>
       </c>
       <c r="E107" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F107" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -4151,7 +4151,7 @@
         <v>Functional</v>
       </c>
       <c r="J107" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K107" t="str">
         <v>Pass</v>
@@ -4171,7 +4171,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #107</v>
       </c>
       <c r="E108" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F108" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -4186,7 +4186,7 @@
         <v>Functional</v>
       </c>
       <c r="J108" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K108" t="str">
         <v>Pass</v>
@@ -4206,7 +4206,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #108</v>
       </c>
       <c r="E109" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F109" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -4221,7 +4221,7 @@
         <v>Functional</v>
       </c>
       <c r="J109" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K109" t="str">
         <v>Pass</v>
@@ -4241,7 +4241,7 @@
         <v>Verify swipe gestures across multi-page intro verification #109</v>
       </c>
       <c r="E110" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F110" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -4256,7 +4256,7 @@
         <v>Functional</v>
       </c>
       <c r="J110" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K110" t="str">
         <v>Pass</v>
@@ -4276,7 +4276,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #110</v>
       </c>
       <c r="E111" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F111" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -4291,7 +4291,7 @@
         <v>Functional</v>
       </c>
       <c r="J111" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K111" t="str">
         <v>Pass</v>
@@ -4311,7 +4311,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #111</v>
       </c>
       <c r="E112" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F112" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -4326,7 +4326,7 @@
         <v>Functional</v>
       </c>
       <c r="J112" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K112" t="str">
         <v>Pass</v>
@@ -4346,7 +4346,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #112</v>
       </c>
       <c r="E113" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F113" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -4361,7 +4361,7 @@
         <v>Functional</v>
       </c>
       <c r="J113" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K113" t="str">
         <v>Pass</v>
@@ -4381,7 +4381,7 @@
         <v>Verify swipe gestures across multi-page intro verification #113</v>
       </c>
       <c r="E114" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F114" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -4396,7 +4396,7 @@
         <v>Functional</v>
       </c>
       <c r="J114" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K114" t="str">
         <v>Pass</v>
@@ -4416,7 +4416,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #114</v>
       </c>
       <c r="E115" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F115" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -4431,7 +4431,7 @@
         <v>Functional</v>
       </c>
       <c r="J115" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K115" t="str">
         <v>Pass</v>
@@ -4451,7 +4451,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #115</v>
       </c>
       <c r="E116" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F116" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -4466,7 +4466,7 @@
         <v>Functional</v>
       </c>
       <c r="J116" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K116" t="str">
         <v>Pass</v>
@@ -4486,7 +4486,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #116</v>
       </c>
       <c r="E117" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F117" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -4501,7 +4501,7 @@
         <v>Functional</v>
       </c>
       <c r="J117" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K117" t="str">
         <v>Pass</v>
@@ -4521,7 +4521,7 @@
         <v>Verify swipe gestures across multi-page intro verification #117</v>
       </c>
       <c r="E118" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F118" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -4536,7 +4536,7 @@
         <v>Functional</v>
       </c>
       <c r="J118" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K118" t="str">
         <v>Pass</v>
@@ -4556,7 +4556,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #118</v>
       </c>
       <c r="E119" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F119" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -4571,7 +4571,7 @@
         <v>Functional</v>
       </c>
       <c r="J119" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K119" t="str">
         <v>Pass</v>
@@ -4591,7 +4591,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #119</v>
       </c>
       <c r="E120" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F120" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -4606,7 +4606,7 @@
         <v>Functional</v>
       </c>
       <c r="J120" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K120" t="str">
         <v>Pass</v>
@@ -4626,7 +4626,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #120</v>
       </c>
       <c r="E121" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F121" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -4641,7 +4641,7 @@
         <v>Functional</v>
       </c>
       <c r="J121" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K121" t="str">
         <v>Pass</v>
@@ -4661,7 +4661,7 @@
         <v>Verify swipe gestures across multi-page intro verification #121</v>
       </c>
       <c r="E122" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F122" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -4676,7 +4676,7 @@
         <v>Functional</v>
       </c>
       <c r="J122" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K122" t="str">
         <v>Pass</v>
@@ -4696,7 +4696,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #122</v>
       </c>
       <c r="E123" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F123" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -4711,7 +4711,7 @@
         <v>Functional</v>
       </c>
       <c r="J123" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K123" t="str">
         <v>Pass</v>
@@ -4731,7 +4731,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #123</v>
       </c>
       <c r="E124" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F124" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -4746,7 +4746,7 @@
         <v>Functional</v>
       </c>
       <c r="J124" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K124" t="str">
         <v>Pass</v>
@@ -4766,7 +4766,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #124</v>
       </c>
       <c r="E125" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F125" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -4781,7 +4781,7 @@
         <v>Functional</v>
       </c>
       <c r="J125" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K125" t="str">
         <v>Pass</v>
@@ -4801,7 +4801,7 @@
         <v>Verify swipe gestures across multi-page intro verification #125</v>
       </c>
       <c r="E126" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F126" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -4816,7 +4816,7 @@
         <v>Functional</v>
       </c>
       <c r="J126" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K126" t="str">
         <v>Pass</v>
@@ -4836,7 +4836,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #126</v>
       </c>
       <c r="E127" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F127" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -4851,7 +4851,7 @@
         <v>Functional</v>
       </c>
       <c r="J127" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K127" t="str">
         <v>Pass</v>
@@ -4871,7 +4871,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #127</v>
       </c>
       <c r="E128" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F128" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -4886,7 +4886,7 @@
         <v>Functional</v>
       </c>
       <c r="J128" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K128" t="str">
         <v>Pass</v>
@@ -4906,7 +4906,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #128</v>
       </c>
       <c r="E129" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F129" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -4921,7 +4921,7 @@
         <v>Functional</v>
       </c>
       <c r="J129" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K129" t="str">
         <v>Pass</v>
@@ -4941,7 +4941,7 @@
         <v>Verify swipe gestures across multi-page intro verification #129</v>
       </c>
       <c r="E130" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F130" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -4956,7 +4956,7 @@
         <v>Functional</v>
       </c>
       <c r="J130" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K130" t="str">
         <v>Pass</v>
@@ -4976,7 +4976,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #130</v>
       </c>
       <c r="E131" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F131" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -4991,7 +4991,7 @@
         <v>Functional</v>
       </c>
       <c r="J131" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K131" t="str">
         <v>Pass</v>
@@ -5011,7 +5011,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #131</v>
       </c>
       <c r="E132" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F132" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -5026,7 +5026,7 @@
         <v>Functional</v>
       </c>
       <c r="J132" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K132" t="str">
         <v>Pass</v>
@@ -5046,7 +5046,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #132</v>
       </c>
       <c r="E133" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F133" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -5061,7 +5061,7 @@
         <v>Functional</v>
       </c>
       <c r="J133" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K133" t="str">
         <v>Pass</v>
@@ -5081,7 +5081,7 @@
         <v>Verify swipe gestures across multi-page intro verification #133</v>
       </c>
       <c r="E134" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F134" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -5096,7 +5096,7 @@
         <v>Functional</v>
       </c>
       <c r="J134" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K134" t="str">
         <v>Pass</v>
@@ -5116,7 +5116,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #134</v>
       </c>
       <c r="E135" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F135" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -5131,7 +5131,7 @@
         <v>Functional</v>
       </c>
       <c r="J135" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K135" t="str">
         <v>Pass</v>
@@ -5151,7 +5151,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #135</v>
       </c>
       <c r="E136" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F136" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -5166,7 +5166,7 @@
         <v>Functional</v>
       </c>
       <c r="J136" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K136" t="str">
         <v>Pass</v>
@@ -5186,7 +5186,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #136</v>
       </c>
       <c r="E137" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F137" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -5201,7 +5201,7 @@
         <v>Functional</v>
       </c>
       <c r="J137" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K137" t="str">
         <v>Pass</v>
@@ -5221,7 +5221,7 @@
         <v>Verify swipe gestures across multi-page intro verification #137</v>
       </c>
       <c r="E138" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F138" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -5236,7 +5236,7 @@
         <v>Functional</v>
       </c>
       <c r="J138" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K138" t="str">
         <v>Pass</v>
@@ -5256,7 +5256,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #138</v>
       </c>
       <c r="E139" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F139" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -5271,7 +5271,7 @@
         <v>Functional</v>
       </c>
       <c r="J139" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K139" t="str">
         <v>Pass</v>
@@ -5291,7 +5291,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #139</v>
       </c>
       <c r="E140" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F140" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -5306,7 +5306,7 @@
         <v>Functional</v>
       </c>
       <c r="J140" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K140" t="str">
         <v>Pass</v>
@@ -5326,7 +5326,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #140</v>
       </c>
       <c r="E141" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F141" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -5341,7 +5341,7 @@
         <v>Functional</v>
       </c>
       <c r="J141" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K141" t="str">
         <v>Pass</v>
@@ -5361,7 +5361,7 @@
         <v>Verify swipe gestures across multi-page intro verification #141</v>
       </c>
       <c r="E142" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F142" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -5376,7 +5376,7 @@
         <v>Functional</v>
       </c>
       <c r="J142" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K142" t="str">
         <v>Pass</v>
@@ -5396,7 +5396,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #142</v>
       </c>
       <c r="E143" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F143" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -5411,7 +5411,7 @@
         <v>Functional</v>
       </c>
       <c r="J143" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K143" t="str">
         <v>Pass</v>
@@ -5431,7 +5431,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #143</v>
       </c>
       <c r="E144" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F144" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -5446,7 +5446,7 @@
         <v>Functional</v>
       </c>
       <c r="J144" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K144" t="str">
         <v>Pass</v>
@@ -5466,7 +5466,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #144</v>
       </c>
       <c r="E145" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F145" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -5481,7 +5481,7 @@
         <v>Functional</v>
       </c>
       <c r="J145" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K145" t="str">
         <v>Pass</v>
@@ -5501,7 +5501,7 @@
         <v>Verify swipe gestures across multi-page intro verification #145</v>
       </c>
       <c r="E146" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F146" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -5516,7 +5516,7 @@
         <v>Functional</v>
       </c>
       <c r="J146" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K146" t="str">
         <v>Pass</v>
@@ -5536,7 +5536,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #146</v>
       </c>
       <c r="E147" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F147" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -5551,7 +5551,7 @@
         <v>Functional</v>
       </c>
       <c r="J147" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K147" t="str">
         <v>Pass</v>
@@ -5571,7 +5571,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #147</v>
       </c>
       <c r="E148" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F148" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -5586,7 +5586,7 @@
         <v>Functional</v>
       </c>
       <c r="J148" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K148" t="str">
         <v>Pass</v>
@@ -5606,7 +5606,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #148</v>
       </c>
       <c r="E149" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F149" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -5621,7 +5621,7 @@
         <v>Functional</v>
       </c>
       <c r="J149" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K149" t="str">
         <v>Pass</v>
@@ -5641,7 +5641,7 @@
         <v>Verify swipe gestures across multi-page intro verification #149</v>
       </c>
       <c r="E150" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F150" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -5656,7 +5656,7 @@
         <v>Functional</v>
       </c>
       <c r="J150" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K150" t="str">
         <v>Pass</v>
@@ -5676,7 +5676,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #150</v>
       </c>
       <c r="E151" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F151" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -5691,7 +5691,7 @@
         <v>Functional</v>
       </c>
       <c r="J151" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K151" t="str">
         <v>Pass</v>
@@ -5711,7 +5711,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #151</v>
       </c>
       <c r="E152" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F152" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -5726,7 +5726,7 @@
         <v>Functional</v>
       </c>
       <c r="J152" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K152" t="str">
         <v>Pass</v>
@@ -5746,7 +5746,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #152</v>
       </c>
       <c r="E153" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F153" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -5761,7 +5761,7 @@
         <v>Functional</v>
       </c>
       <c r="J153" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K153" t="str">
         <v>Pass</v>
@@ -5781,7 +5781,7 @@
         <v>Verify swipe gestures across multi-page intro verification #153</v>
       </c>
       <c r="E154" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F154" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -5796,7 +5796,7 @@
         <v>Functional</v>
       </c>
       <c r="J154" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K154" t="str">
         <v>Pass</v>
@@ -5816,7 +5816,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #154</v>
       </c>
       <c r="E155" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F155" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -5831,7 +5831,7 @@
         <v>Functional</v>
       </c>
       <c r="J155" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K155" t="str">
         <v>Pass</v>
@@ -5851,7 +5851,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #155</v>
       </c>
       <c r="E156" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F156" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -5866,7 +5866,7 @@
         <v>Functional</v>
       </c>
       <c r="J156" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K156" t="str">
         <v>Pass</v>
@@ -5886,7 +5886,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #156</v>
       </c>
       <c r="E157" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F157" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -5901,7 +5901,7 @@
         <v>Functional</v>
       </c>
       <c r="J157" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K157" t="str">
         <v>Pass</v>
@@ -5921,7 +5921,7 @@
         <v>Verify swipe gestures across multi-page intro verification #157</v>
       </c>
       <c r="E158" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F158" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -5936,7 +5936,7 @@
         <v>Functional</v>
       </c>
       <c r="J158" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K158" t="str">
         <v>Pass</v>
@@ -5956,7 +5956,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #158</v>
       </c>
       <c r="E159" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F159" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -5971,7 +5971,7 @@
         <v>Functional</v>
       </c>
       <c r="J159" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K159" t="str">
         <v>Pass</v>
@@ -5991,7 +5991,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #159</v>
       </c>
       <c r="E160" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F160" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -6006,7 +6006,7 @@
         <v>Functional</v>
       </c>
       <c r="J160" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K160" t="str">
         <v>Pass</v>
@@ -6026,7 +6026,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #160</v>
       </c>
       <c r="E161" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F161" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -6041,7 +6041,7 @@
         <v>Functional</v>
       </c>
       <c r="J161" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K161" t="str">
         <v>Pass</v>
@@ -6061,7 +6061,7 @@
         <v>Verify swipe gestures across multi-page intro verification #161</v>
       </c>
       <c r="E162" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F162" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -6076,7 +6076,7 @@
         <v>Functional</v>
       </c>
       <c r="J162" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K162" t="str">
         <v>Pass</v>
@@ -6096,7 +6096,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #162</v>
       </c>
       <c r="E163" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F163" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -6111,7 +6111,7 @@
         <v>Functional</v>
       </c>
       <c r="J163" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K163" t="str">
         <v>Pass</v>
@@ -6131,7 +6131,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #163</v>
       </c>
       <c r="E164" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F164" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -6146,7 +6146,7 @@
         <v>Functional</v>
       </c>
       <c r="J164" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K164" t="str">
         <v>Pass</v>
@@ -6166,7 +6166,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #164</v>
       </c>
       <c r="E165" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F165" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -6181,7 +6181,7 @@
         <v>Functional</v>
       </c>
       <c r="J165" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K165" t="str">
         <v>Pass</v>
@@ -6201,7 +6201,7 @@
         <v>Verify swipe gestures across multi-page intro verification #165</v>
       </c>
       <c r="E166" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F166" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -6216,7 +6216,7 @@
         <v>Functional</v>
       </c>
       <c r="J166" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K166" t="str">
         <v>Pass</v>
@@ -6236,7 +6236,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #166</v>
       </c>
       <c r="E167" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F167" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -6251,7 +6251,7 @@
         <v>Functional</v>
       </c>
       <c r="J167" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K167" t="str">
         <v>Pass</v>
@@ -6271,7 +6271,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #167</v>
       </c>
       <c r="E168" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F168" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -6286,7 +6286,7 @@
         <v>Functional</v>
       </c>
       <c r="J168" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K168" t="str">
         <v>Pass</v>
@@ -6306,7 +6306,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #168</v>
       </c>
       <c r="E169" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F169" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -6321,7 +6321,7 @@
         <v>Functional</v>
       </c>
       <c r="J169" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K169" t="str">
         <v>Pass</v>
@@ -6341,7 +6341,7 @@
         <v>Verify swipe gestures across multi-page intro verification #169</v>
       </c>
       <c r="E170" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F170" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -6356,7 +6356,7 @@
         <v>Functional</v>
       </c>
       <c r="J170" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K170" t="str">
         <v>Pass</v>
@@ -6376,7 +6376,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #170</v>
       </c>
       <c r="E171" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F171" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -6391,7 +6391,7 @@
         <v>Functional</v>
       </c>
       <c r="J171" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K171" t="str">
         <v>Pass</v>
@@ -6411,7 +6411,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #171</v>
       </c>
       <c r="E172" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F172" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -6426,7 +6426,7 @@
         <v>Functional</v>
       </c>
       <c r="J172" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K172" t="str">
         <v>Pass</v>
@@ -6446,7 +6446,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #172</v>
       </c>
       <c r="E173" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F173" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -6461,7 +6461,7 @@
         <v>Functional</v>
       </c>
       <c r="J173" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K173" t="str">
         <v>Pass</v>
@@ -6481,7 +6481,7 @@
         <v>Verify swipe gestures across multi-page intro verification #173</v>
       </c>
       <c r="E174" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F174" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -6496,7 +6496,7 @@
         <v>Functional</v>
       </c>
       <c r="J174" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K174" t="str">
         <v>Pass</v>
@@ -6516,7 +6516,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #174</v>
       </c>
       <c r="E175" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F175" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -6531,7 +6531,7 @@
         <v>Functional</v>
       </c>
       <c r="J175" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K175" t="str">
         <v>Pass</v>
@@ -6551,7 +6551,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #175</v>
       </c>
       <c r="E176" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F176" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -6566,7 +6566,7 @@
         <v>Functional</v>
       </c>
       <c r="J176" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K176" t="str">
         <v>Pass</v>
@@ -6586,7 +6586,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #176</v>
       </c>
       <c r="E177" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F177" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -6601,7 +6601,7 @@
         <v>Functional</v>
       </c>
       <c r="J177" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K177" t="str">
         <v>Pass</v>
@@ -6621,7 +6621,7 @@
         <v>Verify swipe gestures across multi-page intro verification #177</v>
       </c>
       <c r="E178" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F178" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -6636,7 +6636,7 @@
         <v>Functional</v>
       </c>
       <c r="J178" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K178" t="str">
         <v>Pass</v>
@@ -6656,7 +6656,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #178</v>
       </c>
       <c r="E179" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F179" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -6671,7 +6671,7 @@
         <v>Functional</v>
       </c>
       <c r="J179" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K179" t="str">
         <v>Pass</v>
@@ -6691,7 +6691,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #179</v>
       </c>
       <c r="E180" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F180" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -6706,7 +6706,7 @@
         <v>Functional</v>
       </c>
       <c r="J180" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K180" t="str">
         <v>Pass</v>
@@ -6726,7 +6726,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #180</v>
       </c>
       <c r="E181" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F181" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -6741,7 +6741,7 @@
         <v>Functional</v>
       </c>
       <c r="J181" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K181" t="str">
         <v>Pass</v>
@@ -6761,7 +6761,7 @@
         <v>Verify swipe gestures across multi-page intro verification #181</v>
       </c>
       <c r="E182" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F182" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -6776,7 +6776,7 @@
         <v>Functional</v>
       </c>
       <c r="J182" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K182" t="str">
         <v>Pass</v>
@@ -6796,7 +6796,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #182</v>
       </c>
       <c r="E183" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F183" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -6811,7 +6811,7 @@
         <v>Functional</v>
       </c>
       <c r="J183" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K183" t="str">
         <v>Pass</v>
@@ -6831,7 +6831,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #183</v>
       </c>
       <c r="E184" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F184" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -6846,7 +6846,7 @@
         <v>Functional</v>
       </c>
       <c r="J184" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K184" t="str">
         <v>Pass</v>
@@ -6866,7 +6866,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #184</v>
       </c>
       <c r="E185" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F185" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -6881,7 +6881,7 @@
         <v>Functional</v>
       </c>
       <c r="J185" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K185" t="str">
         <v>Pass</v>
@@ -6901,7 +6901,7 @@
         <v>Verify swipe gestures across multi-page intro verification #185</v>
       </c>
       <c r="E186" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F186" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -6916,7 +6916,7 @@
         <v>Functional</v>
       </c>
       <c r="J186" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K186" t="str">
         <v>Pass</v>
@@ -6936,7 +6936,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #186</v>
       </c>
       <c r="E187" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F187" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -6951,7 +6951,7 @@
         <v>Functional</v>
       </c>
       <c r="J187" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K187" t="str">
         <v>Pass</v>
@@ -6971,7 +6971,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #187</v>
       </c>
       <c r="E188" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F188" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -6986,7 +6986,7 @@
         <v>Functional</v>
       </c>
       <c r="J188" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K188" t="str">
         <v>Pass</v>
@@ -7006,7 +7006,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #188</v>
       </c>
       <c r="E189" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F189" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -7021,7 +7021,7 @@
         <v>Functional</v>
       </c>
       <c r="J189" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K189" t="str">
         <v>Pass</v>
@@ -7041,7 +7041,7 @@
         <v>Verify swipe gestures across multi-page intro verification #189</v>
       </c>
       <c r="E190" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F190" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -7056,7 +7056,7 @@
         <v>Functional</v>
       </c>
       <c r="J190" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K190" t="str">
         <v>Pass</v>
@@ -7076,7 +7076,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #190</v>
       </c>
       <c r="E191" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F191" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -7091,7 +7091,7 @@
         <v>Functional</v>
       </c>
       <c r="J191" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K191" t="str">
         <v>Pass</v>
@@ -7111,7 +7111,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #191</v>
       </c>
       <c r="E192" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F192" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -7126,7 +7126,7 @@
         <v>Functional</v>
       </c>
       <c r="J192" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K192" t="str">
         <v>Pass</v>
@@ -7146,7 +7146,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #192</v>
       </c>
       <c r="E193" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F193" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -7161,7 +7161,7 @@
         <v>Functional</v>
       </c>
       <c r="J193" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K193" t="str">
         <v>Pass</v>
@@ -7181,7 +7181,7 @@
         <v>Verify swipe gestures across multi-page intro verification #193</v>
       </c>
       <c r="E194" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F194" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -7196,7 +7196,7 @@
         <v>Functional</v>
       </c>
       <c r="J194" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K194" t="str">
         <v>Pass</v>
@@ -7216,7 +7216,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #194</v>
       </c>
       <c r="E195" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F195" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -7231,7 +7231,7 @@
         <v>Functional</v>
       </c>
       <c r="J195" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K195" t="str">
         <v>Pass</v>
@@ -7251,7 +7251,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #195</v>
       </c>
       <c r="E196" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F196" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -7266,7 +7266,7 @@
         <v>Functional</v>
       </c>
       <c r="J196" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K196" t="str">
         <v>Pass</v>
@@ -7286,7 +7286,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #196</v>
       </c>
       <c r="E197" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F197" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -7301,7 +7301,7 @@
         <v>Functional</v>
       </c>
       <c r="J197" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K197" t="str">
         <v>Pass</v>
@@ -7321,7 +7321,7 @@
         <v>Verify swipe gestures across multi-page intro verification #197</v>
       </c>
       <c r="E198" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F198" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -7336,7 +7336,7 @@
         <v>Functional</v>
       </c>
       <c r="J198" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K198" t="str">
         <v>Pass</v>
@@ -7356,7 +7356,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #198</v>
       </c>
       <c r="E199" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F199" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -7371,7 +7371,7 @@
         <v>Functional</v>
       </c>
       <c r="J199" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K199" t="str">
         <v>Pass</v>
@@ -7391,7 +7391,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #199</v>
       </c>
       <c r="E200" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F200" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -7406,7 +7406,7 @@
         <v>Functional</v>
       </c>
       <c r="J200" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K200" t="str">
         <v>Pass</v>
@@ -7426,7 +7426,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #200</v>
       </c>
       <c r="E201" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F201" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -7441,7 +7441,7 @@
         <v>Functional</v>
       </c>
       <c r="J201" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K201" t="str">
         <v>Pass</v>
@@ -7461,7 +7461,7 @@
         <v>Verify swipe gestures across multi-page intro verification #201</v>
       </c>
       <c r="E202" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F202" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -7476,7 +7476,7 @@
         <v>Functional</v>
       </c>
       <c r="J202" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K202" t="str">
         <v>Pass</v>
@@ -7496,7 +7496,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #202</v>
       </c>
       <c r="E203" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F203" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -7511,7 +7511,7 @@
         <v>Functional</v>
       </c>
       <c r="J203" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K203" t="str">
         <v>Pass</v>
@@ -7531,7 +7531,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #203</v>
       </c>
       <c r="E204" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F204" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -7546,7 +7546,7 @@
         <v>Functional</v>
       </c>
       <c r="J204" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K204" t="str">
         <v>Pass</v>
@@ -7566,7 +7566,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #204</v>
       </c>
       <c r="E205" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F205" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -7581,7 +7581,7 @@
         <v>Functional</v>
       </c>
       <c r="J205" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K205" t="str">
         <v>Pass</v>
@@ -7601,7 +7601,7 @@
         <v>Verify swipe gestures across multi-page intro verification #205</v>
       </c>
       <c r="E206" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F206" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -7616,7 +7616,7 @@
         <v>Functional</v>
       </c>
       <c r="J206" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K206" t="str">
         <v>Pass</v>
@@ -7636,7 +7636,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #206</v>
       </c>
       <c r="E207" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F207" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -7651,7 +7651,7 @@
         <v>Functional</v>
       </c>
       <c r="J207" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K207" t="str">
         <v>Pass</v>
@@ -7671,7 +7671,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #207</v>
       </c>
       <c r="E208" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F208" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -7686,7 +7686,7 @@
         <v>Functional</v>
       </c>
       <c r="J208" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K208" t="str">
         <v>Pass</v>
@@ -7706,7 +7706,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #208</v>
       </c>
       <c r="E209" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F209" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -7721,7 +7721,7 @@
         <v>Functional</v>
       </c>
       <c r="J209" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K209" t="str">
         <v>Pass</v>
@@ -7741,7 +7741,7 @@
         <v>Verify swipe gestures across multi-page intro verification #209</v>
       </c>
       <c r="E210" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F210" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -7756,7 +7756,7 @@
         <v>Functional</v>
       </c>
       <c r="J210" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K210" t="str">
         <v>Pass</v>
@@ -7776,7 +7776,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #210</v>
       </c>
       <c r="E211" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F211" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -7791,7 +7791,7 @@
         <v>Functional</v>
       </c>
       <c r="J211" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K211" t="str">
         <v>Pass</v>
@@ -7811,7 +7811,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #211</v>
       </c>
       <c r="E212" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F212" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -7826,7 +7826,7 @@
         <v>Functional</v>
       </c>
       <c r="J212" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K212" t="str">
         <v>Pass</v>
@@ -7846,7 +7846,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #212</v>
       </c>
       <c r="E213" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F213" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -7861,7 +7861,7 @@
         <v>Functional</v>
       </c>
       <c r="J213" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K213" t="str">
         <v>Pass</v>
@@ -7881,7 +7881,7 @@
         <v>Verify swipe gestures across multi-page intro verification #213</v>
       </c>
       <c r="E214" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F214" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -7896,7 +7896,7 @@
         <v>Functional</v>
       </c>
       <c r="J214" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K214" t="str">
         <v>Pass</v>
@@ -7916,7 +7916,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #214</v>
       </c>
       <c r="E215" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F215" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -7931,7 +7931,7 @@
         <v>Functional</v>
       </c>
       <c r="J215" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K215" t="str">
         <v>Pass</v>
@@ -7951,7 +7951,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #215</v>
       </c>
       <c r="E216" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F216" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -7966,7 +7966,7 @@
         <v>Functional</v>
       </c>
       <c r="J216" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K216" t="str">
         <v>Pass</v>
@@ -7986,7 +7986,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #216</v>
       </c>
       <c r="E217" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F217" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -8001,7 +8001,7 @@
         <v>Functional</v>
       </c>
       <c r="J217" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K217" t="str">
         <v>Pass</v>
@@ -8021,7 +8021,7 @@
         <v>Verify swipe gestures across multi-page intro verification #217</v>
       </c>
       <c r="E218" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F218" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -8036,7 +8036,7 @@
         <v>Functional</v>
       </c>
       <c r="J218" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K218" t="str">
         <v>Pass</v>
@@ -8056,7 +8056,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #218</v>
       </c>
       <c r="E219" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F219" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -8071,7 +8071,7 @@
         <v>Functional</v>
       </c>
       <c r="J219" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K219" t="str">
         <v>Pass</v>
@@ -8091,7 +8091,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #219</v>
       </c>
       <c r="E220" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F220" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -8106,7 +8106,7 @@
         <v>Functional</v>
       </c>
       <c r="J220" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K220" t="str">
         <v>Pass</v>
@@ -8126,7 +8126,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #220</v>
       </c>
       <c r="E221" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F221" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -8141,7 +8141,7 @@
         <v>Functional</v>
       </c>
       <c r="J221" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K221" t="str">
         <v>Pass</v>
@@ -8161,7 +8161,7 @@
         <v>Verify swipe gestures across multi-page intro verification #221</v>
       </c>
       <c r="E222" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F222" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -8176,7 +8176,7 @@
         <v>Functional</v>
       </c>
       <c r="J222" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K222" t="str">
         <v>Pass</v>
@@ -8196,7 +8196,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #222</v>
       </c>
       <c r="E223" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F223" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -8211,7 +8211,7 @@
         <v>Functional</v>
       </c>
       <c r="J223" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K223" t="str">
         <v>Pass</v>
@@ -8231,7 +8231,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #223</v>
       </c>
       <c r="E224" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F224" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -8246,7 +8246,7 @@
         <v>Functional</v>
       </c>
       <c r="J224" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K224" t="str">
         <v>Pass</v>
@@ -8266,7 +8266,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #224</v>
       </c>
       <c r="E225" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F225" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -8281,7 +8281,7 @@
         <v>Functional</v>
       </c>
       <c r="J225" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K225" t="str">
         <v>Pass</v>
@@ -8301,7 +8301,7 @@
         <v>Verify swipe gestures across multi-page intro verification #225</v>
       </c>
       <c r="E226" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F226" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -8316,7 +8316,7 @@
         <v>Functional</v>
       </c>
       <c r="J226" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K226" t="str">
         <v>Pass</v>
@@ -8336,7 +8336,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #226</v>
       </c>
       <c r="E227" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F227" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -8351,7 +8351,7 @@
         <v>Functional</v>
       </c>
       <c r="J227" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K227" t="str">
         <v>Pass</v>
@@ -8371,7 +8371,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #227</v>
       </c>
       <c r="E228" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F228" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -8386,7 +8386,7 @@
         <v>Functional</v>
       </c>
       <c r="J228" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K228" t="str">
         <v>Pass</v>
@@ -8406,7 +8406,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #228</v>
       </c>
       <c r="E229" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F229" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -8421,7 +8421,7 @@
         <v>Functional</v>
       </c>
       <c r="J229" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K229" t="str">
         <v>Pass</v>
@@ -8441,7 +8441,7 @@
         <v>Verify swipe gestures across multi-page intro verification #229</v>
       </c>
       <c r="E230" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F230" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -8456,7 +8456,7 @@
         <v>Functional</v>
       </c>
       <c r="J230" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K230" t="str">
         <v>Pass</v>
@@ -8476,7 +8476,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #230</v>
       </c>
       <c r="E231" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F231" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -8491,7 +8491,7 @@
         <v>Functional</v>
       </c>
       <c r="J231" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K231" t="str">
         <v>Pass</v>
@@ -8511,7 +8511,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #231</v>
       </c>
       <c r="E232" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F232" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -8526,7 +8526,7 @@
         <v>Functional</v>
       </c>
       <c r="J232" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K232" t="str">
         <v>Pass</v>
@@ -8546,7 +8546,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #232</v>
       </c>
       <c r="E233" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F233" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -8561,7 +8561,7 @@
         <v>Functional</v>
       </c>
       <c r="J233" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K233" t="str">
         <v>Pass</v>
@@ -8581,7 +8581,7 @@
         <v>Verify swipe gestures across multi-page intro verification #233</v>
       </c>
       <c r="E234" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F234" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -8596,7 +8596,7 @@
         <v>Functional</v>
       </c>
       <c r="J234" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K234" t="str">
         <v>Pass</v>
@@ -8616,7 +8616,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #234</v>
       </c>
       <c r="E235" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F235" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -8631,7 +8631,7 @@
         <v>Functional</v>
       </c>
       <c r="J235" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K235" t="str">
         <v>Pass</v>
@@ -8651,7 +8651,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #235</v>
       </c>
       <c r="E236" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F236" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -8666,7 +8666,7 @@
         <v>Functional</v>
       </c>
       <c r="J236" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K236" t="str">
         <v>Pass</v>
@@ -8686,7 +8686,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #236</v>
       </c>
       <c r="E237" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F237" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -8701,7 +8701,7 @@
         <v>Functional</v>
       </c>
       <c r="J237" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K237" t="str">
         <v>Pass</v>
@@ -8721,7 +8721,7 @@
         <v>Verify swipe gestures across multi-page intro verification #237</v>
       </c>
       <c r="E238" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F238" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -8736,7 +8736,7 @@
         <v>Functional</v>
       </c>
       <c r="J238" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K238" t="str">
         <v>Pass</v>
@@ -8756,7 +8756,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #238</v>
       </c>
       <c r="E239" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F239" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -8771,7 +8771,7 @@
         <v>Functional</v>
       </c>
       <c r="J239" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K239" t="str">
         <v>Pass</v>
@@ -8791,7 +8791,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #239</v>
       </c>
       <c r="E240" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F240" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -8806,7 +8806,7 @@
         <v>Functional</v>
       </c>
       <c r="J240" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K240" t="str">
         <v>Pass</v>
@@ -8826,7 +8826,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #240</v>
       </c>
       <c r="E241" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F241" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -8841,7 +8841,7 @@
         <v>Functional</v>
       </c>
       <c r="J241" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K241" t="str">
         <v>Pass</v>
@@ -8861,7 +8861,7 @@
         <v>Verify swipe gestures across multi-page intro verification #241</v>
       </c>
       <c r="E242" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F242" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -8876,7 +8876,7 @@
         <v>Functional</v>
       </c>
       <c r="J242" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K242" t="str">
         <v>Pass</v>
@@ -8896,7 +8896,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #242</v>
       </c>
       <c r="E243" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F243" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -8911,7 +8911,7 @@
         <v>Functional</v>
       </c>
       <c r="J243" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K243" t="str">
         <v>Pass</v>
@@ -8931,7 +8931,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #243</v>
       </c>
       <c r="E244" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F244" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -8946,7 +8946,7 @@
         <v>Functional</v>
       </c>
       <c r="J244" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K244" t="str">
         <v>Pass</v>
@@ -8966,7 +8966,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #244</v>
       </c>
       <c r="E245" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F245" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -8981,7 +8981,7 @@
         <v>Functional</v>
       </c>
       <c r="J245" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K245" t="str">
         <v>Pass</v>
@@ -9001,7 +9001,7 @@
         <v>Verify swipe gestures across multi-page intro verification #245</v>
       </c>
       <c r="E246" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F246" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -9016,7 +9016,7 @@
         <v>Functional</v>
       </c>
       <c r="J246" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K246" t="str">
         <v>Pass</v>
@@ -9036,7 +9036,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #246</v>
       </c>
       <c r="E247" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F247" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -9051,7 +9051,7 @@
         <v>Functional</v>
       </c>
       <c r="J247" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K247" t="str">
         <v>Pass</v>
@@ -9071,7 +9071,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #247</v>
       </c>
       <c r="E248" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F248" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -9086,7 +9086,7 @@
         <v>Functional</v>
       </c>
       <c r="J248" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K248" t="str">
         <v>Pass</v>
@@ -9106,7 +9106,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #248</v>
       </c>
       <c r="E249" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F249" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -9121,7 +9121,7 @@
         <v>Functional</v>
       </c>
       <c r="J249" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K249" t="str">
         <v>Pass</v>
@@ -9141,7 +9141,7 @@
         <v>Verify swipe gestures across multi-page intro verification #249</v>
       </c>
       <c r="E250" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F250" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -9156,7 +9156,7 @@
         <v>Functional</v>
       </c>
       <c r="J250" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K250" t="str">
         <v>Pass</v>
@@ -9176,7 +9176,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #250</v>
       </c>
       <c r="E251" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F251" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -9191,7 +9191,7 @@
         <v>Functional</v>
       </c>
       <c r="J251" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K251" t="str">
         <v>Pass</v>
@@ -9211,7 +9211,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #251</v>
       </c>
       <c r="E252" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F252" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -9226,7 +9226,7 @@
         <v>Functional</v>
       </c>
       <c r="J252" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K252" t="str">
         <v>Pass</v>
@@ -9246,7 +9246,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #252</v>
       </c>
       <c r="E253" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F253" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -9261,7 +9261,7 @@
         <v>Functional</v>
       </c>
       <c r="J253" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K253" t="str">
         <v>Pass</v>
@@ -9281,7 +9281,7 @@
         <v>Verify swipe gestures across multi-page intro verification #253</v>
       </c>
       <c r="E254" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F254" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -9296,7 +9296,7 @@
         <v>Functional</v>
       </c>
       <c r="J254" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K254" t="str">
         <v>Pass</v>
@@ -9316,7 +9316,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #254</v>
       </c>
       <c r="E255" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F255" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -9331,7 +9331,7 @@
         <v>Functional</v>
       </c>
       <c r="J255" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K255" t="str">
         <v>Pass</v>
@@ -9351,7 +9351,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #255</v>
       </c>
       <c r="E256" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F256" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -9366,7 +9366,7 @@
         <v>Functional</v>
       </c>
       <c r="J256" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K256" t="str">
         <v>Pass</v>
@@ -9386,7 +9386,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #256</v>
       </c>
       <c r="E257" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F257" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -9401,7 +9401,7 @@
         <v>Functional</v>
       </c>
       <c r="J257" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K257" t="str">
         <v>Pass</v>
@@ -9421,7 +9421,7 @@
         <v>Verify swipe gestures across multi-page intro verification #257</v>
       </c>
       <c r="E258" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F258" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -9436,7 +9436,7 @@
         <v>Functional</v>
       </c>
       <c r="J258" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K258" t="str">
         <v>Pass</v>
@@ -9456,7 +9456,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #258</v>
       </c>
       <c r="E259" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F259" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -9471,7 +9471,7 @@
         <v>Functional</v>
       </c>
       <c r="J259" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K259" t="str">
         <v>Pass</v>
@@ -9491,7 +9491,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #259</v>
       </c>
       <c r="E260" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F260" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -9506,7 +9506,7 @@
         <v>Functional</v>
       </c>
       <c r="J260" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K260" t="str">
         <v>Pass</v>
@@ -9526,7 +9526,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #260</v>
       </c>
       <c r="E261" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F261" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -9541,7 +9541,7 @@
         <v>Functional</v>
       </c>
       <c r="J261" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K261" t="str">
         <v>Pass</v>
@@ -9561,7 +9561,7 @@
         <v>Verify swipe gestures across multi-page intro verification #261</v>
       </c>
       <c r="E262" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F262" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -9576,7 +9576,7 @@
         <v>Functional</v>
       </c>
       <c r="J262" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K262" t="str">
         <v>Pass</v>
@@ -9596,7 +9596,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #262</v>
       </c>
       <c r="E263" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F263" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -9611,7 +9611,7 @@
         <v>Functional</v>
       </c>
       <c r="J263" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K263" t="str">
         <v>Pass</v>
@@ -9631,7 +9631,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #263</v>
       </c>
       <c r="E264" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F264" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -9646,7 +9646,7 @@
         <v>Functional</v>
       </c>
       <c r="J264" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K264" t="str">
         <v>Pass</v>
@@ -9666,7 +9666,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #264</v>
       </c>
       <c r="E265" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F265" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -9681,7 +9681,7 @@
         <v>Functional</v>
       </c>
       <c r="J265" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K265" t="str">
         <v>Pass</v>
@@ -9701,7 +9701,7 @@
         <v>Verify swipe gestures across multi-page intro verification #265</v>
       </c>
       <c r="E266" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F266" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -9716,7 +9716,7 @@
         <v>Functional</v>
       </c>
       <c r="J266" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K266" t="str">
         <v>Pass</v>
@@ -9736,7 +9736,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #266</v>
       </c>
       <c r="E267" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F267" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -9751,7 +9751,7 @@
         <v>Functional</v>
       </c>
       <c r="J267" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K267" t="str">
         <v>Pass</v>
@@ -9771,7 +9771,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #267</v>
       </c>
       <c r="E268" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F268" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -9786,7 +9786,7 @@
         <v>Functional</v>
       </c>
       <c r="J268" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K268" t="str">
         <v>Pass</v>
@@ -9806,7 +9806,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #268</v>
       </c>
       <c r="E269" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F269" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -9821,7 +9821,7 @@
         <v>Functional</v>
       </c>
       <c r="J269" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K269" t="str">
         <v>Pass</v>
@@ -9841,7 +9841,7 @@
         <v>Verify swipe gestures across multi-page intro verification #269</v>
       </c>
       <c r="E270" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F270" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -9856,7 +9856,7 @@
         <v>Functional</v>
       </c>
       <c r="J270" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K270" t="str">
         <v>Pass</v>
@@ -9876,7 +9876,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #270</v>
       </c>
       <c r="E271" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F271" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -9891,7 +9891,7 @@
         <v>Functional</v>
       </c>
       <c r="J271" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K271" t="str">
         <v>Pass</v>
@@ -9911,7 +9911,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #271</v>
       </c>
       <c r="E272" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F272" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -9926,7 +9926,7 @@
         <v>Functional</v>
       </c>
       <c r="J272" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K272" t="str">
         <v>Pass</v>
@@ -9946,7 +9946,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #272</v>
       </c>
       <c r="E273" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F273" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -9961,7 +9961,7 @@
         <v>Functional</v>
       </c>
       <c r="J273" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K273" t="str">
         <v>Pass</v>
@@ -9981,7 +9981,7 @@
         <v>Verify swipe gestures across multi-page intro verification #273</v>
       </c>
       <c r="E274" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F274" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -9996,7 +9996,7 @@
         <v>Functional</v>
       </c>
       <c r="J274" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K274" t="str">
         <v>Pass</v>
@@ -10016,7 +10016,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #274</v>
       </c>
       <c r="E275" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F275" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -10031,7 +10031,7 @@
         <v>Functional</v>
       </c>
       <c r="J275" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K275" t="str">
         <v>Pass</v>
@@ -10051,7 +10051,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #275</v>
       </c>
       <c r="E276" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F276" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -10066,7 +10066,7 @@
         <v>Functional</v>
       </c>
       <c r="J276" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K276" t="str">
         <v>Pass</v>
@@ -10086,7 +10086,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #276</v>
       </c>
       <c r="E277" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F277" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -10101,7 +10101,7 @@
         <v>Functional</v>
       </c>
       <c r="J277" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K277" t="str">
         <v>Pass</v>
@@ -10121,7 +10121,7 @@
         <v>Verify swipe gestures across multi-page intro verification #277</v>
       </c>
       <c r="E278" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F278" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -10136,7 +10136,7 @@
         <v>Functional</v>
       </c>
       <c r="J278" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K278" t="str">
         <v>Pass</v>
@@ -10156,7 +10156,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #278</v>
       </c>
       <c r="E279" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F279" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -10171,7 +10171,7 @@
         <v>Functional</v>
       </c>
       <c r="J279" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K279" t="str">
         <v>Pass</v>
@@ -10191,7 +10191,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #279</v>
       </c>
       <c r="E280" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F280" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -10206,7 +10206,7 @@
         <v>Functional</v>
       </c>
       <c r="J280" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K280" t="str">
         <v>Pass</v>
@@ -10226,7 +10226,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #280</v>
       </c>
       <c r="E281" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F281" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -10241,7 +10241,7 @@
         <v>Functional</v>
       </c>
       <c r="J281" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K281" t="str">
         <v>Pass</v>
@@ -10261,7 +10261,7 @@
         <v>Verify swipe gestures across multi-page intro verification #281</v>
       </c>
       <c r="E282" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F282" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -10276,7 +10276,7 @@
         <v>Functional</v>
       </c>
       <c r="J282" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K282" t="str">
         <v>Pass</v>
@@ -10296,7 +10296,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #282</v>
       </c>
       <c r="E283" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F283" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -10311,7 +10311,7 @@
         <v>Functional</v>
       </c>
       <c r="J283" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K283" t="str">
         <v>Pass</v>
@@ -10331,7 +10331,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #283</v>
       </c>
       <c r="E284" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F284" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -10346,7 +10346,7 @@
         <v>Functional</v>
       </c>
       <c r="J284" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K284" t="str">
         <v>Pass</v>
@@ -10366,7 +10366,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #284</v>
       </c>
       <c r="E285" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F285" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -10381,7 +10381,7 @@
         <v>Functional</v>
       </c>
       <c r="J285" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K285" t="str">
         <v>Pass</v>
@@ -10401,7 +10401,7 @@
         <v>Verify swipe gestures across multi-page intro verification #285</v>
       </c>
       <c r="E286" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F286" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -10416,7 +10416,7 @@
         <v>Functional</v>
       </c>
       <c r="J286" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K286" t="str">
         <v>Pass</v>
@@ -10436,7 +10436,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #286</v>
       </c>
       <c r="E287" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F287" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -10451,7 +10451,7 @@
         <v>Functional</v>
       </c>
       <c r="J287" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K287" t="str">
         <v>Pass</v>
@@ -10471,7 +10471,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #287</v>
       </c>
       <c r="E288" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F288" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -10486,7 +10486,7 @@
         <v>Functional</v>
       </c>
       <c r="J288" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K288" t="str">
         <v>Pass</v>
@@ -10506,7 +10506,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #288</v>
       </c>
       <c r="E289" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F289" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -10521,7 +10521,7 @@
         <v>Functional</v>
       </c>
       <c r="J289" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K289" t="str">
         <v>Pass</v>
@@ -10541,7 +10541,7 @@
         <v>Verify swipe gestures across multi-page intro verification #289</v>
       </c>
       <c r="E290" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F290" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -10556,7 +10556,7 @@
         <v>Functional</v>
       </c>
       <c r="J290" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K290" t="str">
         <v>Pass</v>
@@ -10576,7 +10576,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #290</v>
       </c>
       <c r="E291" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F291" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -10591,7 +10591,7 @@
         <v>Functional</v>
       </c>
       <c r="J291" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K291" t="str">
         <v>Pass</v>
@@ -10611,7 +10611,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #291</v>
       </c>
       <c r="E292" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F292" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -10626,7 +10626,7 @@
         <v>Functional</v>
       </c>
       <c r="J292" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K292" t="str">
         <v>Pass</v>
@@ -10646,7 +10646,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #292</v>
       </c>
       <c r="E293" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F293" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -10661,7 +10661,7 @@
         <v>Functional</v>
       </c>
       <c r="J293" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K293" t="str">
         <v>Pass</v>
@@ -10681,7 +10681,7 @@
         <v>Verify swipe gestures across multi-page intro verification #293</v>
       </c>
       <c r="E294" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F294" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -10696,7 +10696,7 @@
         <v>Functional</v>
       </c>
       <c r="J294" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K294" t="str">
         <v>Pass</v>
@@ -10716,7 +10716,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #294</v>
       </c>
       <c r="E295" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F295" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -10731,7 +10731,7 @@
         <v>Functional</v>
       </c>
       <c r="J295" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K295" t="str">
         <v>Pass</v>
@@ -10751,7 +10751,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #295</v>
       </c>
       <c r="E296" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F296" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -10766,7 +10766,7 @@
         <v>Functional</v>
       </c>
       <c r="J296" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K296" t="str">
         <v>Pass</v>
@@ -10786,7 +10786,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #296</v>
       </c>
       <c r="E297" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F297" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -10801,7 +10801,7 @@
         <v>Functional</v>
       </c>
       <c r="J297" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K297" t="str">
         <v>Pass</v>
@@ -10821,7 +10821,7 @@
         <v>Verify swipe gestures across multi-page intro verification #297</v>
       </c>
       <c r="E298" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F298" t="str">
         <v>Navigate to Onboarding and perform Tutorial Array action</v>
@@ -10836,7 +10836,7 @@
         <v>Functional</v>
       </c>
       <c r="J298" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K298" t="str">
         <v>Pass</v>
@@ -10856,7 +10856,7 @@
         <v>Render correct daily metrics upon authentication unlock verification #298</v>
       </c>
       <c r="E299" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F299" t="str">
         <v>Navigate to Home Screen and perform Dashboard action</v>
@@ -10871,7 +10871,7 @@
         <v>Functional</v>
       </c>
       <c r="J299" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K299" t="str">
         <v>Pass</v>
@@ -10891,7 +10891,7 @@
         <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #299</v>
       </c>
       <c r="E300" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F300" t="str">
         <v>Navigate to Mobile Layout and perform Responsive action</v>
@@ -10906,7 +10906,7 @@
         <v>Functional</v>
       </c>
       <c r="J300" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K300" t="str">
         <v>Pass</v>
@@ -10926,7 +10926,7 @@
         <v>Verify full-screen logo rendering under 2000ms verification #300</v>
       </c>
       <c r="E301" t="str">
-        <v>App running on Android/iOS</v>
+        <v>App running on Android Native</v>
       </c>
       <c r="F301" t="str">
         <v>Navigate to App Initialization and perform Splash Screen action</v>
@@ -10941,7 +10941,7 @@
         <v>Functional</v>
       </c>
       <c r="J301" t="str">
-        <v>Android/iOS</v>
+        <v>Android Native</v>
       </c>
       <c r="K301" t="str">
         <v>Pass</v>

--- a/e2e_tests_suite/Report_02_Appium.xlsx
+++ b/e2e_tests_suite/Report_02_Appium.xlsx
@@ -452,19 +452,19 @@
         <v>TC001</v>
       </c>
       <c r="B2" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C2" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C2" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D2" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #1</v>
+        <v>Verify swipe gestures across onboarding layer verification #1</v>
       </c>
       <c r="E2" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F2" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G2" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -487,19 +487,19 @@
         <v>TC002</v>
       </c>
       <c r="B3" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C3" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D3" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #2</v>
+        <v>Trigger push alert for medication times verification #2</v>
       </c>
       <c r="E3" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F3" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G3" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -522,19 +522,19 @@
         <v>TC003</v>
       </c>
       <c r="B4" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C4" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D4" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #3</v>
+        <v>Trigger mobile alert for concerning symptoms verification #3</v>
       </c>
       <c r="E4" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F4" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G4" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -557,19 +557,19 @@
         <v>TC004</v>
       </c>
       <c r="B5" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C5" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D5" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #4</v>
+        <v>Notify user of abnormal vital fluctuations verification #4</v>
       </c>
       <c r="E5" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F5" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G5" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -592,19 +592,19 @@
         <v>TC005</v>
       </c>
       <c r="B6" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C6" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D6" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #5</v>
+        <v>Dispatch summary of weekly health data verification #5</v>
       </c>
       <c r="E6" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F6" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G6" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -627,19 +627,19 @@
         <v>TC006</v>
       </c>
       <c r="B7" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C7" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D7" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #6</v>
+        <v>Unlock application with FaceID / Fingerprint verification #6</v>
       </c>
       <c r="E7" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F7" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G7" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -662,19 +662,19 @@
         <v>TC007</v>
       </c>
       <c r="B8" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C8" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D8" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #7</v>
+        <v>Enforce extra layer of login security via token verification #7</v>
       </c>
       <c r="E8" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F8" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G8" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -703,7 +703,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D9" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #8</v>
+        <v>Verify full-screen logo brand rendering verification #8</v>
       </c>
       <c r="E9" t="str">
         <v>App running on Android Native</v>
@@ -732,19 +732,19 @@
         <v>TC009</v>
       </c>
       <c r="B10" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C10" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C10" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D10" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #9</v>
+        <v>Verify swipe gestures across onboarding layer verification #9</v>
       </c>
       <c r="E10" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F10" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G10" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -767,19 +767,19 @@
         <v>TC010</v>
       </c>
       <c r="B11" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C11" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D11" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #10</v>
+        <v>Trigger push alert for medication times verification #10</v>
       </c>
       <c r="E11" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F11" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G11" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -802,19 +802,19 @@
         <v>TC011</v>
       </c>
       <c r="B12" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C12" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D12" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #11</v>
+        <v>Trigger mobile alert for concerning symptoms verification #11</v>
       </c>
       <c r="E12" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F12" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G12" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -837,19 +837,19 @@
         <v>TC012</v>
       </c>
       <c r="B13" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C13" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D13" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #12</v>
+        <v>Notify user of abnormal vital fluctuations verification #12</v>
       </c>
       <c r="E13" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F13" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G13" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -872,19 +872,19 @@
         <v>TC013</v>
       </c>
       <c r="B14" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C14" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D14" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #13</v>
+        <v>Dispatch summary of weekly health data verification #13</v>
       </c>
       <c r="E14" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F14" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G14" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -907,19 +907,19 @@
         <v>TC014</v>
       </c>
       <c r="B15" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C15" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D15" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #14</v>
+        <v>Unlock application with FaceID / Fingerprint verification #14</v>
       </c>
       <c r="E15" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F15" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G15" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -942,19 +942,19 @@
         <v>TC015</v>
       </c>
       <c r="B16" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C16" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D16" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #15</v>
+        <v>Enforce extra layer of login security via token verification #15</v>
       </c>
       <c r="E16" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F16" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G16" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -983,7 +983,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D17" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #16</v>
+        <v>Verify full-screen logo brand rendering verification #16</v>
       </c>
       <c r="E17" t="str">
         <v>App running on Android Native</v>
@@ -1012,19 +1012,19 @@
         <v>TC017</v>
       </c>
       <c r="B18" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C18" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C18" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D18" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #17</v>
+        <v>Verify swipe gestures across onboarding layer verification #17</v>
       </c>
       <c r="E18" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F18" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G18" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1047,19 +1047,19 @@
         <v>TC018</v>
       </c>
       <c r="B19" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C19" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D19" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #18</v>
+        <v>Trigger push alert for medication times verification #18</v>
       </c>
       <c r="E19" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F19" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G19" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1082,19 +1082,19 @@
         <v>TC019</v>
       </c>
       <c r="B20" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C20" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D20" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #19</v>
+        <v>Trigger mobile alert for concerning symptoms verification #19</v>
       </c>
       <c r="E20" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F20" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G20" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1117,19 +1117,19 @@
         <v>TC020</v>
       </c>
       <c r="B21" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C21" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D21" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #20</v>
+        <v>Notify user of abnormal vital fluctuations verification #20</v>
       </c>
       <c r="E21" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F21" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G21" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1152,19 +1152,19 @@
         <v>TC021</v>
       </c>
       <c r="B22" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C22" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D22" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #21</v>
+        <v>Dispatch summary of weekly health data verification #21</v>
       </c>
       <c r="E22" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F22" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G22" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1187,19 +1187,19 @@
         <v>TC022</v>
       </c>
       <c r="B23" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C23" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D23" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #22</v>
+        <v>Unlock application with FaceID / Fingerprint verification #22</v>
       </c>
       <c r="E23" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F23" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G23" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1222,19 +1222,19 @@
         <v>TC023</v>
       </c>
       <c r="B24" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C24" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D24" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #23</v>
+        <v>Enforce extra layer of login security via token verification #23</v>
       </c>
       <c r="E24" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F24" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G24" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1263,7 +1263,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D25" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #24</v>
+        <v>Verify full-screen logo brand rendering verification #24</v>
       </c>
       <c r="E25" t="str">
         <v>App running on Android Native</v>
@@ -1292,19 +1292,19 @@
         <v>TC025</v>
       </c>
       <c r="B26" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C26" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C26" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D26" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #25</v>
+        <v>Verify swipe gestures across onboarding layer verification #25</v>
       </c>
       <c r="E26" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F26" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G26" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1327,19 +1327,19 @@
         <v>TC026</v>
       </c>
       <c r="B27" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C27" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D27" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #26</v>
+        <v>Trigger push alert for medication times verification #26</v>
       </c>
       <c r="E27" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F27" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G27" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1362,19 +1362,19 @@
         <v>TC027</v>
       </c>
       <c r="B28" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C28" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D28" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #27</v>
+        <v>Trigger mobile alert for concerning symptoms verification #27</v>
       </c>
       <c r="E28" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F28" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G28" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1397,19 +1397,19 @@
         <v>TC028</v>
       </c>
       <c r="B29" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C29" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D29" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #28</v>
+        <v>Notify user of abnormal vital fluctuations verification #28</v>
       </c>
       <c r="E29" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F29" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G29" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1432,19 +1432,19 @@
         <v>TC029</v>
       </c>
       <c r="B30" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C30" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D30" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #29</v>
+        <v>Dispatch summary of weekly health data verification #29</v>
       </c>
       <c r="E30" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F30" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G30" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1467,19 +1467,19 @@
         <v>TC030</v>
       </c>
       <c r="B31" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C31" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D31" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #30</v>
+        <v>Unlock application with FaceID / Fingerprint verification #30</v>
       </c>
       <c r="E31" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F31" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G31" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1502,19 +1502,19 @@
         <v>TC031</v>
       </c>
       <c r="B32" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C32" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D32" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #31</v>
+        <v>Enforce extra layer of login security via token verification #31</v>
       </c>
       <c r="E32" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F32" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G32" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1543,7 +1543,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D33" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #32</v>
+        <v>Verify full-screen logo brand rendering verification #32</v>
       </c>
       <c r="E33" t="str">
         <v>App running on Android Native</v>
@@ -1572,19 +1572,19 @@
         <v>TC033</v>
       </c>
       <c r="B34" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C34" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C34" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D34" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #33</v>
+        <v>Verify swipe gestures across onboarding layer verification #33</v>
       </c>
       <c r="E34" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F34" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G34" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1607,19 +1607,19 @@
         <v>TC034</v>
       </c>
       <c r="B35" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C35" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D35" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #34</v>
+        <v>Trigger push alert for medication times verification #34</v>
       </c>
       <c r="E35" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F35" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G35" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1642,19 +1642,19 @@
         <v>TC035</v>
       </c>
       <c r="B36" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C36" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D36" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #35</v>
+        <v>Trigger mobile alert for concerning symptoms verification #35</v>
       </c>
       <c r="E36" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F36" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G36" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1677,19 +1677,19 @@
         <v>TC036</v>
       </c>
       <c r="B37" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C37" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D37" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #36</v>
+        <v>Notify user of abnormal vital fluctuations verification #36</v>
       </c>
       <c r="E37" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F37" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G37" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1712,19 +1712,19 @@
         <v>TC037</v>
       </c>
       <c r="B38" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C38" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D38" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #37</v>
+        <v>Dispatch summary of weekly health data verification #37</v>
       </c>
       <c r="E38" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F38" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G38" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1747,19 +1747,19 @@
         <v>TC038</v>
       </c>
       <c r="B39" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C39" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D39" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #38</v>
+        <v>Unlock application with FaceID / Fingerprint verification #38</v>
       </c>
       <c r="E39" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F39" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G39" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1782,19 +1782,19 @@
         <v>TC039</v>
       </c>
       <c r="B40" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C40" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D40" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #39</v>
+        <v>Enforce extra layer of login security via token verification #39</v>
       </c>
       <c r="E40" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F40" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G40" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1823,7 +1823,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D41" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #40</v>
+        <v>Verify full-screen logo brand rendering verification #40</v>
       </c>
       <c r="E41" t="str">
         <v>App running on Android Native</v>
@@ -1852,19 +1852,19 @@
         <v>TC041</v>
       </c>
       <c r="B42" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C42" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C42" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D42" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #41</v>
+        <v>Verify swipe gestures across onboarding layer verification #41</v>
       </c>
       <c r="E42" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F42" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G42" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1887,19 +1887,19 @@
         <v>TC042</v>
       </c>
       <c r="B43" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C43" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D43" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #42</v>
+        <v>Trigger push alert for medication times verification #42</v>
       </c>
       <c r="E43" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F43" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G43" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1922,19 +1922,19 @@
         <v>TC043</v>
       </c>
       <c r="B44" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C44" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D44" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #43</v>
+        <v>Trigger mobile alert for concerning symptoms verification #43</v>
       </c>
       <c r="E44" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F44" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G44" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1957,19 +1957,19 @@
         <v>TC044</v>
       </c>
       <c r="B45" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C45" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D45" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #44</v>
+        <v>Notify user of abnormal vital fluctuations verification #44</v>
       </c>
       <c r="E45" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F45" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G45" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1992,19 +1992,19 @@
         <v>TC045</v>
       </c>
       <c r="B46" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C46" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D46" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #45</v>
+        <v>Dispatch summary of weekly health data verification #45</v>
       </c>
       <c r="E46" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F46" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G46" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2027,19 +2027,19 @@
         <v>TC046</v>
       </c>
       <c r="B47" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C47" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D47" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #46</v>
+        <v>Unlock application with FaceID / Fingerprint verification #46</v>
       </c>
       <c r="E47" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F47" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G47" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2062,19 +2062,19 @@
         <v>TC047</v>
       </c>
       <c r="B48" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C48" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D48" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #47</v>
+        <v>Enforce extra layer of login security via token verification #47</v>
       </c>
       <c r="E48" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F48" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G48" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2103,7 +2103,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D49" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #48</v>
+        <v>Verify full-screen logo brand rendering verification #48</v>
       </c>
       <c r="E49" t="str">
         <v>App running on Android Native</v>
@@ -2132,19 +2132,19 @@
         <v>TC049</v>
       </c>
       <c r="B50" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C50" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C50" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D50" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #49</v>
+        <v>Verify swipe gestures across onboarding layer verification #49</v>
       </c>
       <c r="E50" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F50" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G50" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2167,19 +2167,19 @@
         <v>TC050</v>
       </c>
       <c r="B51" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C51" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D51" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #50</v>
+        <v>Trigger push alert for medication times verification #50</v>
       </c>
       <c r="E51" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F51" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G51" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2202,19 +2202,19 @@
         <v>TC051</v>
       </c>
       <c r="B52" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C52" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D52" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #51</v>
+        <v>Trigger mobile alert for concerning symptoms verification #51</v>
       </c>
       <c r="E52" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F52" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G52" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2237,19 +2237,19 @@
         <v>TC052</v>
       </c>
       <c r="B53" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C53" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D53" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #52</v>
+        <v>Notify user of abnormal vital fluctuations verification #52</v>
       </c>
       <c r="E53" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F53" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G53" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2272,19 +2272,19 @@
         <v>TC053</v>
       </c>
       <c r="B54" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C54" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D54" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #53</v>
+        <v>Dispatch summary of weekly health data verification #53</v>
       </c>
       <c r="E54" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F54" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G54" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2307,19 +2307,19 @@
         <v>TC054</v>
       </c>
       <c r="B55" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C55" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D55" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #54</v>
+        <v>Unlock application with FaceID / Fingerprint verification #54</v>
       </c>
       <c r="E55" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F55" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G55" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2342,19 +2342,19 @@
         <v>TC055</v>
       </c>
       <c r="B56" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C56" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D56" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #55</v>
+        <v>Enforce extra layer of login security via token verification #55</v>
       </c>
       <c r="E56" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F56" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G56" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2383,7 +2383,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D57" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #56</v>
+        <v>Verify full-screen logo brand rendering verification #56</v>
       </c>
       <c r="E57" t="str">
         <v>App running on Android Native</v>
@@ -2412,19 +2412,19 @@
         <v>TC057</v>
       </c>
       <c r="B58" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C58" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C58" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D58" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #57</v>
+        <v>Verify swipe gestures across onboarding layer verification #57</v>
       </c>
       <c r="E58" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F58" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G58" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2447,19 +2447,19 @@
         <v>TC058</v>
       </c>
       <c r="B59" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C59" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D59" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #58</v>
+        <v>Trigger push alert for medication times verification #58</v>
       </c>
       <c r="E59" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F59" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G59" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2482,19 +2482,19 @@
         <v>TC059</v>
       </c>
       <c r="B60" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C60" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D60" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #59</v>
+        <v>Trigger mobile alert for concerning symptoms verification #59</v>
       </c>
       <c r="E60" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F60" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G60" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2517,19 +2517,19 @@
         <v>TC060</v>
       </c>
       <c r="B61" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C61" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D61" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #60</v>
+        <v>Notify user of abnormal vital fluctuations verification #60</v>
       </c>
       <c r="E61" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F61" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G61" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2552,19 +2552,19 @@
         <v>TC061</v>
       </c>
       <c r="B62" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C62" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D62" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #61</v>
+        <v>Dispatch summary of weekly health data verification #61</v>
       </c>
       <c r="E62" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F62" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G62" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2587,19 +2587,19 @@
         <v>TC062</v>
       </c>
       <c r="B63" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C63" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D63" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #62</v>
+        <v>Unlock application with FaceID / Fingerprint verification #62</v>
       </c>
       <c r="E63" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F63" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G63" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2622,19 +2622,19 @@
         <v>TC063</v>
       </c>
       <c r="B64" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C64" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D64" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #63</v>
+        <v>Enforce extra layer of login security via token verification #63</v>
       </c>
       <c r="E64" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F64" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G64" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2663,7 +2663,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D65" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #64</v>
+        <v>Verify full-screen logo brand rendering verification #64</v>
       </c>
       <c r="E65" t="str">
         <v>App running on Android Native</v>
@@ -2692,19 +2692,19 @@
         <v>TC065</v>
       </c>
       <c r="B66" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C66" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C66" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D66" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #65</v>
+        <v>Verify swipe gestures across onboarding layer verification #65</v>
       </c>
       <c r="E66" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F66" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G66" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2727,19 +2727,19 @@
         <v>TC066</v>
       </c>
       <c r="B67" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C67" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D67" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #66</v>
+        <v>Trigger push alert for medication times verification #66</v>
       </c>
       <c r="E67" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F67" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G67" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2762,19 +2762,19 @@
         <v>TC067</v>
       </c>
       <c r="B68" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C68" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D68" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #67</v>
+        <v>Trigger mobile alert for concerning symptoms verification #67</v>
       </c>
       <c r="E68" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F68" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G68" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2797,19 +2797,19 @@
         <v>TC068</v>
       </c>
       <c r="B69" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C69" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D69" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #68</v>
+        <v>Notify user of abnormal vital fluctuations verification #68</v>
       </c>
       <c r="E69" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F69" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G69" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2832,19 +2832,19 @@
         <v>TC069</v>
       </c>
       <c r="B70" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C70" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D70" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #69</v>
+        <v>Dispatch summary of weekly health data verification #69</v>
       </c>
       <c r="E70" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F70" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G70" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2867,19 +2867,19 @@
         <v>TC070</v>
       </c>
       <c r="B71" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C71" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D71" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #70</v>
+        <v>Unlock application with FaceID / Fingerprint verification #70</v>
       </c>
       <c r="E71" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F71" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G71" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2902,19 +2902,19 @@
         <v>TC071</v>
       </c>
       <c r="B72" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C72" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D72" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #71</v>
+        <v>Enforce extra layer of login security via token verification #71</v>
       </c>
       <c r="E72" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F72" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G72" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2943,7 +2943,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D73" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #72</v>
+        <v>Verify full-screen logo brand rendering verification #72</v>
       </c>
       <c r="E73" t="str">
         <v>App running on Android Native</v>
@@ -2972,19 +2972,19 @@
         <v>TC073</v>
       </c>
       <c r="B74" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C74" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C74" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D74" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #73</v>
+        <v>Verify swipe gestures across onboarding layer verification #73</v>
       </c>
       <c r="E74" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F74" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G74" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3007,19 +3007,19 @@
         <v>TC074</v>
       </c>
       <c r="B75" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C75" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D75" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #74</v>
+        <v>Trigger push alert for medication times verification #74</v>
       </c>
       <c r="E75" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F75" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G75" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3042,19 +3042,19 @@
         <v>TC075</v>
       </c>
       <c r="B76" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C76" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D76" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #75</v>
+        <v>Trigger mobile alert for concerning symptoms verification #75</v>
       </c>
       <c r="E76" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F76" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G76" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3077,19 +3077,19 @@
         <v>TC076</v>
       </c>
       <c r="B77" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C77" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D77" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #76</v>
+        <v>Notify user of abnormal vital fluctuations verification #76</v>
       </c>
       <c r="E77" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F77" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G77" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3112,19 +3112,19 @@
         <v>TC077</v>
       </c>
       <c r="B78" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C78" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D78" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #77</v>
+        <v>Dispatch summary of weekly health data verification #77</v>
       </c>
       <c r="E78" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F78" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G78" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3147,19 +3147,19 @@
         <v>TC078</v>
       </c>
       <c r="B79" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C79" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D79" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #78</v>
+        <v>Unlock application with FaceID / Fingerprint verification #78</v>
       </c>
       <c r="E79" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F79" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G79" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3182,19 +3182,19 @@
         <v>TC079</v>
       </c>
       <c r="B80" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C80" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D80" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #79</v>
+        <v>Enforce extra layer of login security via token verification #79</v>
       </c>
       <c r="E80" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F80" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G80" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3223,7 +3223,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D81" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #80</v>
+        <v>Verify full-screen logo brand rendering verification #80</v>
       </c>
       <c r="E81" t="str">
         <v>App running on Android Native</v>
@@ -3252,19 +3252,19 @@
         <v>TC081</v>
       </c>
       <c r="B82" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C82" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C82" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D82" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #81</v>
+        <v>Verify swipe gestures across onboarding layer verification #81</v>
       </c>
       <c r="E82" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F82" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G82" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3287,19 +3287,19 @@
         <v>TC082</v>
       </c>
       <c r="B83" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C83" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D83" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #82</v>
+        <v>Trigger push alert for medication times verification #82</v>
       </c>
       <c r="E83" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F83" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G83" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3322,19 +3322,19 @@
         <v>TC083</v>
       </c>
       <c r="B84" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C84" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D84" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #83</v>
+        <v>Trigger mobile alert for concerning symptoms verification #83</v>
       </c>
       <c r="E84" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F84" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G84" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3357,19 +3357,19 @@
         <v>TC084</v>
       </c>
       <c r="B85" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C85" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D85" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #84</v>
+        <v>Notify user of abnormal vital fluctuations verification #84</v>
       </c>
       <c r="E85" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F85" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G85" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3392,19 +3392,19 @@
         <v>TC085</v>
       </c>
       <c r="B86" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C86" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D86" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #85</v>
+        <v>Dispatch summary of weekly health data verification #85</v>
       </c>
       <c r="E86" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F86" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G86" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3427,19 +3427,19 @@
         <v>TC086</v>
       </c>
       <c r="B87" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C87" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D87" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #86</v>
+        <v>Unlock application with FaceID / Fingerprint verification #86</v>
       </c>
       <c r="E87" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F87" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G87" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3462,19 +3462,19 @@
         <v>TC087</v>
       </c>
       <c r="B88" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C88" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D88" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #87</v>
+        <v>Enforce extra layer of login security via token verification #87</v>
       </c>
       <c r="E88" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F88" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G88" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3503,7 +3503,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D89" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #88</v>
+        <v>Verify full-screen logo brand rendering verification #88</v>
       </c>
       <c r="E89" t="str">
         <v>App running on Android Native</v>
@@ -3532,19 +3532,19 @@
         <v>TC089</v>
       </c>
       <c r="B90" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C90" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C90" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D90" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #89</v>
+        <v>Verify swipe gestures across onboarding layer verification #89</v>
       </c>
       <c r="E90" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F90" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G90" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3567,19 +3567,19 @@
         <v>TC090</v>
       </c>
       <c r="B91" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C91" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D91" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #90</v>
+        <v>Trigger push alert for medication times verification #90</v>
       </c>
       <c r="E91" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F91" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G91" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3602,19 +3602,19 @@
         <v>TC091</v>
       </c>
       <c r="B92" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C92" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D92" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #91</v>
+        <v>Trigger mobile alert for concerning symptoms verification #91</v>
       </c>
       <c r="E92" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F92" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G92" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3637,19 +3637,19 @@
         <v>TC092</v>
       </c>
       <c r="B93" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C93" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D93" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #92</v>
+        <v>Notify user of abnormal vital fluctuations verification #92</v>
       </c>
       <c r="E93" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F93" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G93" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3672,19 +3672,19 @@
         <v>TC093</v>
       </c>
       <c r="B94" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C94" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D94" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #93</v>
+        <v>Dispatch summary of weekly health data verification #93</v>
       </c>
       <c r="E94" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F94" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G94" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3707,19 +3707,19 @@
         <v>TC094</v>
       </c>
       <c r="B95" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C95" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D95" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #94</v>
+        <v>Unlock application with FaceID / Fingerprint verification #94</v>
       </c>
       <c r="E95" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F95" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G95" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3742,19 +3742,19 @@
         <v>TC095</v>
       </c>
       <c r="B96" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C96" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D96" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #95</v>
+        <v>Enforce extra layer of login security via token verification #95</v>
       </c>
       <c r="E96" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F96" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G96" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3783,7 +3783,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D97" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #96</v>
+        <v>Verify full-screen logo brand rendering verification #96</v>
       </c>
       <c r="E97" t="str">
         <v>App running on Android Native</v>
@@ -3812,19 +3812,19 @@
         <v>TC097</v>
       </c>
       <c r="B98" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C98" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C98" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D98" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #97</v>
+        <v>Verify swipe gestures across onboarding layer verification #97</v>
       </c>
       <c r="E98" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F98" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G98" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3847,19 +3847,19 @@
         <v>TC098</v>
       </c>
       <c r="B99" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C99" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D99" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #98</v>
+        <v>Trigger push alert for medication times verification #98</v>
       </c>
       <c r="E99" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F99" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G99" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3882,19 +3882,19 @@
         <v>TC099</v>
       </c>
       <c r="B100" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C100" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D100" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #99</v>
+        <v>Trigger mobile alert for concerning symptoms verification #99</v>
       </c>
       <c r="E100" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F100" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G100" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3917,19 +3917,19 @@
         <v>TC100</v>
       </c>
       <c r="B101" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C101" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D101" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #100</v>
+        <v>Notify user of abnormal vital fluctuations verification #100</v>
       </c>
       <c r="E101" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F101" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G101" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3952,19 +3952,19 @@
         <v>TC101</v>
       </c>
       <c r="B102" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C102" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D102" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #101</v>
+        <v>Dispatch summary of weekly health data verification #101</v>
       </c>
       <c r="E102" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F102" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G102" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3987,19 +3987,19 @@
         <v>TC102</v>
       </c>
       <c r="B103" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C103" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D103" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #102</v>
+        <v>Unlock application with FaceID / Fingerprint verification #102</v>
       </c>
       <c r="E103" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F103" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G103" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4022,19 +4022,19 @@
         <v>TC103</v>
       </c>
       <c r="B104" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C104" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D104" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #103</v>
+        <v>Enforce extra layer of login security via token verification #103</v>
       </c>
       <c r="E104" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F104" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G104" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4063,7 +4063,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D105" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #104</v>
+        <v>Verify full-screen logo brand rendering verification #104</v>
       </c>
       <c r="E105" t="str">
         <v>App running on Android Native</v>
@@ -4092,19 +4092,19 @@
         <v>TC105</v>
       </c>
       <c r="B106" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C106" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C106" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D106" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #105</v>
+        <v>Verify swipe gestures across onboarding layer verification #105</v>
       </c>
       <c r="E106" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F106" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G106" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4127,19 +4127,19 @@
         <v>TC106</v>
       </c>
       <c r="B107" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C107" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D107" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #106</v>
+        <v>Trigger push alert for medication times verification #106</v>
       </c>
       <c r="E107" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F107" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G107" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4162,19 +4162,19 @@
         <v>TC107</v>
       </c>
       <c r="B108" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C108" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D108" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #107</v>
+        <v>Trigger mobile alert for concerning symptoms verification #107</v>
       </c>
       <c r="E108" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F108" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G108" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4197,19 +4197,19 @@
         <v>TC108</v>
       </c>
       <c r="B109" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C109" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D109" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #108</v>
+        <v>Notify user of abnormal vital fluctuations verification #108</v>
       </c>
       <c r="E109" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F109" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G109" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4232,19 +4232,19 @@
         <v>TC109</v>
       </c>
       <c r="B110" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C110" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D110" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #109</v>
+        <v>Dispatch summary of weekly health data verification #109</v>
       </c>
       <c r="E110" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F110" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G110" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4267,19 +4267,19 @@
         <v>TC110</v>
       </c>
       <c r="B111" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C111" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D111" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #110</v>
+        <v>Unlock application with FaceID / Fingerprint verification #110</v>
       </c>
       <c r="E111" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F111" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G111" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4302,19 +4302,19 @@
         <v>TC111</v>
       </c>
       <c r="B112" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C112" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D112" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #111</v>
+        <v>Enforce extra layer of login security via token verification #111</v>
       </c>
       <c r="E112" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F112" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G112" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4343,7 +4343,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D113" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #112</v>
+        <v>Verify full-screen logo brand rendering verification #112</v>
       </c>
       <c r="E113" t="str">
         <v>App running on Android Native</v>
@@ -4372,19 +4372,19 @@
         <v>TC113</v>
       </c>
       <c r="B114" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C114" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C114" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D114" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #113</v>
+        <v>Verify swipe gestures across onboarding layer verification #113</v>
       </c>
       <c r="E114" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F114" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G114" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4407,19 +4407,19 @@
         <v>TC114</v>
       </c>
       <c r="B115" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C115" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D115" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #114</v>
+        <v>Trigger push alert for medication times verification #114</v>
       </c>
       <c r="E115" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F115" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G115" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4442,19 +4442,19 @@
         <v>TC115</v>
       </c>
       <c r="B116" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C116" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D116" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #115</v>
+        <v>Trigger mobile alert for concerning symptoms verification #115</v>
       </c>
       <c r="E116" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F116" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G116" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4477,19 +4477,19 @@
         <v>TC116</v>
       </c>
       <c r="B117" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C117" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D117" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #116</v>
+        <v>Notify user of abnormal vital fluctuations verification #116</v>
       </c>
       <c r="E117" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F117" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G117" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4512,19 +4512,19 @@
         <v>TC117</v>
       </c>
       <c r="B118" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C118" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D118" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #117</v>
+        <v>Dispatch summary of weekly health data verification #117</v>
       </c>
       <c r="E118" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F118" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G118" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4547,19 +4547,19 @@
         <v>TC118</v>
       </c>
       <c r="B119" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C119" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D119" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #118</v>
+        <v>Unlock application with FaceID / Fingerprint verification #118</v>
       </c>
       <c r="E119" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F119" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G119" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4582,19 +4582,19 @@
         <v>TC119</v>
       </c>
       <c r="B120" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C120" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D120" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #119</v>
+        <v>Enforce extra layer of login security via token verification #119</v>
       </c>
       <c r="E120" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F120" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G120" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4623,7 +4623,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D121" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #120</v>
+        <v>Verify full-screen logo brand rendering verification #120</v>
       </c>
       <c r="E121" t="str">
         <v>App running on Android Native</v>
@@ -4652,19 +4652,19 @@
         <v>TC121</v>
       </c>
       <c r="B122" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C122" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C122" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D122" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #121</v>
+        <v>Verify swipe gestures across onboarding layer verification #121</v>
       </c>
       <c r="E122" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F122" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G122" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4687,19 +4687,19 @@
         <v>TC122</v>
       </c>
       <c r="B123" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C123" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D123" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #122</v>
+        <v>Trigger push alert for medication times verification #122</v>
       </c>
       <c r="E123" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F123" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G123" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4722,19 +4722,19 @@
         <v>TC123</v>
       </c>
       <c r="B124" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C124" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D124" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #123</v>
+        <v>Trigger mobile alert for concerning symptoms verification #123</v>
       </c>
       <c r="E124" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F124" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G124" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4757,19 +4757,19 @@
         <v>TC124</v>
       </c>
       <c r="B125" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C125" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D125" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #124</v>
+        <v>Notify user of abnormal vital fluctuations verification #124</v>
       </c>
       <c r="E125" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F125" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G125" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4792,19 +4792,19 @@
         <v>TC125</v>
       </c>
       <c r="B126" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C126" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D126" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #125</v>
+        <v>Dispatch summary of weekly health data verification #125</v>
       </c>
       <c r="E126" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F126" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G126" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4827,19 +4827,19 @@
         <v>TC126</v>
       </c>
       <c r="B127" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C127" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D127" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #126</v>
+        <v>Unlock application with FaceID / Fingerprint verification #126</v>
       </c>
       <c r="E127" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F127" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G127" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4862,19 +4862,19 @@
         <v>TC127</v>
       </c>
       <c r="B128" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C128" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D128" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #127</v>
+        <v>Enforce extra layer of login security via token verification #127</v>
       </c>
       <c r="E128" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F128" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G128" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4903,7 +4903,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D129" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #128</v>
+        <v>Verify full-screen logo brand rendering verification #128</v>
       </c>
       <c r="E129" t="str">
         <v>App running on Android Native</v>
@@ -4932,19 +4932,19 @@
         <v>TC129</v>
       </c>
       <c r="B130" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C130" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C130" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D130" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #129</v>
+        <v>Verify swipe gestures across onboarding layer verification #129</v>
       </c>
       <c r="E130" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F130" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G130" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4967,19 +4967,19 @@
         <v>TC130</v>
       </c>
       <c r="B131" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C131" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D131" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #130</v>
+        <v>Trigger push alert for medication times verification #130</v>
       </c>
       <c r="E131" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F131" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G131" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5002,19 +5002,19 @@
         <v>TC131</v>
       </c>
       <c r="B132" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C132" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D132" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #131</v>
+        <v>Trigger mobile alert for concerning symptoms verification #131</v>
       </c>
       <c r="E132" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F132" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G132" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5037,19 +5037,19 @@
         <v>TC132</v>
       </c>
       <c r="B133" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C133" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D133" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #132</v>
+        <v>Notify user of abnormal vital fluctuations verification #132</v>
       </c>
       <c r="E133" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F133" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G133" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5072,19 +5072,19 @@
         <v>TC133</v>
       </c>
       <c r="B134" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C134" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D134" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #133</v>
+        <v>Dispatch summary of weekly health data verification #133</v>
       </c>
       <c r="E134" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F134" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G134" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5107,19 +5107,19 @@
         <v>TC134</v>
       </c>
       <c r="B135" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C135" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D135" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #134</v>
+        <v>Unlock application with FaceID / Fingerprint verification #134</v>
       </c>
       <c r="E135" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F135" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G135" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5142,19 +5142,19 @@
         <v>TC135</v>
       </c>
       <c r="B136" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C136" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D136" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #135</v>
+        <v>Enforce extra layer of login security via token verification #135</v>
       </c>
       <c r="E136" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F136" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G136" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5183,7 +5183,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D137" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #136</v>
+        <v>Verify full-screen logo brand rendering verification #136</v>
       </c>
       <c r="E137" t="str">
         <v>App running on Android Native</v>
@@ -5212,19 +5212,19 @@
         <v>TC137</v>
       </c>
       <c r="B138" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C138" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C138" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D138" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #137</v>
+        <v>Verify swipe gestures across onboarding layer verification #137</v>
       </c>
       <c r="E138" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F138" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G138" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5247,19 +5247,19 @@
         <v>TC138</v>
       </c>
       <c r="B139" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C139" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D139" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #138</v>
+        <v>Trigger push alert for medication times verification #138</v>
       </c>
       <c r="E139" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F139" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G139" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5282,19 +5282,19 @@
         <v>TC139</v>
       </c>
       <c r="B140" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C140" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D140" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #139</v>
+        <v>Trigger mobile alert for concerning symptoms verification #139</v>
       </c>
       <c r="E140" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F140" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G140" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5317,19 +5317,19 @@
         <v>TC140</v>
       </c>
       <c r="B141" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C141" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D141" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #140</v>
+        <v>Notify user of abnormal vital fluctuations verification #140</v>
       </c>
       <c r="E141" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F141" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G141" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5352,19 +5352,19 @@
         <v>TC141</v>
       </c>
       <c r="B142" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C142" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D142" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #141</v>
+        <v>Dispatch summary of weekly health data verification #141</v>
       </c>
       <c r="E142" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F142" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G142" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5387,19 +5387,19 @@
         <v>TC142</v>
       </c>
       <c r="B143" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C143" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D143" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #142</v>
+        <v>Unlock application with FaceID / Fingerprint verification #142</v>
       </c>
       <c r="E143" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F143" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G143" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5422,19 +5422,19 @@
         <v>TC143</v>
       </c>
       <c r="B144" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C144" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D144" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #143</v>
+        <v>Enforce extra layer of login security via token verification #143</v>
       </c>
       <c r="E144" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F144" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G144" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5463,7 +5463,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D145" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #144</v>
+        <v>Verify full-screen logo brand rendering verification #144</v>
       </c>
       <c r="E145" t="str">
         <v>App running on Android Native</v>
@@ -5492,19 +5492,19 @@
         <v>TC145</v>
       </c>
       <c r="B146" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C146" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C146" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D146" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #145</v>
+        <v>Verify swipe gestures across onboarding layer verification #145</v>
       </c>
       <c r="E146" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F146" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G146" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5527,19 +5527,19 @@
         <v>TC146</v>
       </c>
       <c r="B147" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C147" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D147" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #146</v>
+        <v>Trigger push alert for medication times verification #146</v>
       </c>
       <c r="E147" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F147" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G147" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5562,19 +5562,19 @@
         <v>TC147</v>
       </c>
       <c r="B148" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C148" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D148" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #147</v>
+        <v>Trigger mobile alert for concerning symptoms verification #147</v>
       </c>
       <c r="E148" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F148" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G148" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5597,19 +5597,19 @@
         <v>TC148</v>
       </c>
       <c r="B149" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C149" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D149" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #148</v>
+        <v>Notify user of abnormal vital fluctuations verification #148</v>
       </c>
       <c r="E149" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F149" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G149" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5632,19 +5632,19 @@
         <v>TC149</v>
       </c>
       <c r="B150" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C150" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D150" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #149</v>
+        <v>Dispatch summary of weekly health data verification #149</v>
       </c>
       <c r="E150" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F150" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G150" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5667,19 +5667,19 @@
         <v>TC150</v>
       </c>
       <c r="B151" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C151" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D151" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #150</v>
+        <v>Unlock application with FaceID / Fingerprint verification #150</v>
       </c>
       <c r="E151" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F151" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G151" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5702,19 +5702,19 @@
         <v>TC151</v>
       </c>
       <c r="B152" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C152" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D152" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #151</v>
+        <v>Enforce extra layer of login security via token verification #151</v>
       </c>
       <c r="E152" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F152" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G152" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5743,7 +5743,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D153" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #152</v>
+        <v>Verify full-screen logo brand rendering verification #152</v>
       </c>
       <c r="E153" t="str">
         <v>App running on Android Native</v>
@@ -5772,19 +5772,19 @@
         <v>TC153</v>
       </c>
       <c r="B154" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C154" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C154" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D154" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #153</v>
+        <v>Verify swipe gestures across onboarding layer verification #153</v>
       </c>
       <c r="E154" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F154" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G154" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5807,19 +5807,19 @@
         <v>TC154</v>
       </c>
       <c r="B155" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C155" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D155" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #154</v>
+        <v>Trigger push alert for medication times verification #154</v>
       </c>
       <c r="E155" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F155" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G155" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5842,19 +5842,19 @@
         <v>TC155</v>
       </c>
       <c r="B156" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C156" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D156" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #155</v>
+        <v>Trigger mobile alert for concerning symptoms verification #155</v>
       </c>
       <c r="E156" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F156" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G156" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5877,19 +5877,19 @@
         <v>TC156</v>
       </c>
       <c r="B157" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C157" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D157" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #156</v>
+        <v>Notify user of abnormal vital fluctuations verification #156</v>
       </c>
       <c r="E157" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F157" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G157" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5912,19 +5912,19 @@
         <v>TC157</v>
       </c>
       <c r="B158" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C158" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D158" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #157</v>
+        <v>Dispatch summary of weekly health data verification #157</v>
       </c>
       <c r="E158" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F158" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G158" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5947,19 +5947,19 @@
         <v>TC158</v>
       </c>
       <c r="B159" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C159" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D159" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #158</v>
+        <v>Unlock application with FaceID / Fingerprint verification #158</v>
       </c>
       <c r="E159" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F159" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G159" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5982,19 +5982,19 @@
         <v>TC159</v>
       </c>
       <c r="B160" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C160" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D160" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #159</v>
+        <v>Enforce extra layer of login security via token verification #159</v>
       </c>
       <c r="E160" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F160" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G160" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6023,7 +6023,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D161" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #160</v>
+        <v>Verify full-screen logo brand rendering verification #160</v>
       </c>
       <c r="E161" t="str">
         <v>App running on Android Native</v>
@@ -6052,19 +6052,19 @@
         <v>TC161</v>
       </c>
       <c r="B162" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C162" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C162" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D162" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #161</v>
+        <v>Verify swipe gestures across onboarding layer verification #161</v>
       </c>
       <c r="E162" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F162" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G162" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6087,19 +6087,19 @@
         <v>TC162</v>
       </c>
       <c r="B163" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C163" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D163" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #162</v>
+        <v>Trigger push alert for medication times verification #162</v>
       </c>
       <c r="E163" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F163" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G163" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6122,19 +6122,19 @@
         <v>TC163</v>
       </c>
       <c r="B164" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C164" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D164" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #163</v>
+        <v>Trigger mobile alert for concerning symptoms verification #163</v>
       </c>
       <c r="E164" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F164" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G164" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6157,19 +6157,19 @@
         <v>TC164</v>
       </c>
       <c r="B165" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C165" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D165" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #164</v>
+        <v>Notify user of abnormal vital fluctuations verification #164</v>
       </c>
       <c r="E165" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F165" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G165" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6192,19 +6192,19 @@
         <v>TC165</v>
       </c>
       <c r="B166" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C166" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D166" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #165</v>
+        <v>Dispatch summary of weekly health data verification #165</v>
       </c>
       <c r="E166" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F166" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G166" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6227,19 +6227,19 @@
         <v>TC166</v>
       </c>
       <c r="B167" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C167" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D167" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #166</v>
+        <v>Unlock application with FaceID / Fingerprint verification #166</v>
       </c>
       <c r="E167" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F167" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G167" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6262,19 +6262,19 @@
         <v>TC167</v>
       </c>
       <c r="B168" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C168" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D168" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #167</v>
+        <v>Enforce extra layer of login security via token verification #167</v>
       </c>
       <c r="E168" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F168" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G168" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6303,7 +6303,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D169" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #168</v>
+        <v>Verify full-screen logo brand rendering verification #168</v>
       </c>
       <c r="E169" t="str">
         <v>App running on Android Native</v>
@@ -6332,19 +6332,19 @@
         <v>TC169</v>
       </c>
       <c r="B170" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C170" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C170" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D170" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #169</v>
+        <v>Verify swipe gestures across onboarding layer verification #169</v>
       </c>
       <c r="E170" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F170" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G170" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6367,19 +6367,19 @@
         <v>TC170</v>
       </c>
       <c r="B171" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C171" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D171" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #170</v>
+        <v>Trigger push alert for medication times verification #170</v>
       </c>
       <c r="E171" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F171" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G171" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6402,19 +6402,19 @@
         <v>TC171</v>
       </c>
       <c r="B172" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C172" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D172" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #171</v>
+        <v>Trigger mobile alert for concerning symptoms verification #171</v>
       </c>
       <c r="E172" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F172" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G172" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6437,19 +6437,19 @@
         <v>TC172</v>
       </c>
       <c r="B173" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C173" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D173" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #172</v>
+        <v>Notify user of abnormal vital fluctuations verification #172</v>
       </c>
       <c r="E173" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F173" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G173" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6472,19 +6472,19 @@
         <v>TC173</v>
       </c>
       <c r="B174" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C174" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D174" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #173</v>
+        <v>Dispatch summary of weekly health data verification #173</v>
       </c>
       <c r="E174" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F174" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G174" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6507,19 +6507,19 @@
         <v>TC174</v>
       </c>
       <c r="B175" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C175" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D175" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #174</v>
+        <v>Unlock application with FaceID / Fingerprint verification #174</v>
       </c>
       <c r="E175" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F175" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G175" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6542,19 +6542,19 @@
         <v>TC175</v>
       </c>
       <c r="B176" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C176" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D176" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #175</v>
+        <v>Enforce extra layer of login security via token verification #175</v>
       </c>
       <c r="E176" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F176" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G176" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6583,7 +6583,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D177" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #176</v>
+        <v>Verify full-screen logo brand rendering verification #176</v>
       </c>
       <c r="E177" t="str">
         <v>App running on Android Native</v>
@@ -6612,19 +6612,19 @@
         <v>TC177</v>
       </c>
       <c r="B178" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C178" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C178" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D178" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #177</v>
+        <v>Verify swipe gestures across onboarding layer verification #177</v>
       </c>
       <c r="E178" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F178" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G178" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6647,19 +6647,19 @@
         <v>TC178</v>
       </c>
       <c r="B179" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C179" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D179" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #178</v>
+        <v>Trigger push alert for medication times verification #178</v>
       </c>
       <c r="E179" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F179" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G179" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6682,19 +6682,19 @@
         <v>TC179</v>
       </c>
       <c r="B180" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C180" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D180" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #179</v>
+        <v>Trigger mobile alert for concerning symptoms verification #179</v>
       </c>
       <c r="E180" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F180" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G180" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6717,19 +6717,19 @@
         <v>TC180</v>
       </c>
       <c r="B181" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C181" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D181" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #180</v>
+        <v>Notify user of abnormal vital fluctuations verification #180</v>
       </c>
       <c r="E181" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F181" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G181" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6752,19 +6752,19 @@
         <v>TC181</v>
       </c>
       <c r="B182" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C182" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D182" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #181</v>
+        <v>Dispatch summary of weekly health data verification #181</v>
       </c>
       <c r="E182" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F182" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G182" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6787,19 +6787,19 @@
         <v>TC182</v>
       </c>
       <c r="B183" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C183" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D183" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #182</v>
+        <v>Unlock application with FaceID / Fingerprint verification #182</v>
       </c>
       <c r="E183" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F183" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G183" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6822,19 +6822,19 @@
         <v>TC183</v>
       </c>
       <c r="B184" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C184" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D184" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #183</v>
+        <v>Enforce extra layer of login security via token verification #183</v>
       </c>
       <c r="E184" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F184" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G184" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6863,7 +6863,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D185" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #184</v>
+        <v>Verify full-screen logo brand rendering verification #184</v>
       </c>
       <c r="E185" t="str">
         <v>App running on Android Native</v>
@@ -6892,19 +6892,19 @@
         <v>TC185</v>
       </c>
       <c r="B186" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C186" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C186" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D186" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #185</v>
+        <v>Verify swipe gestures across onboarding layer verification #185</v>
       </c>
       <c r="E186" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F186" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G186" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6927,19 +6927,19 @@
         <v>TC186</v>
       </c>
       <c r="B187" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C187" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D187" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #186</v>
+        <v>Trigger push alert for medication times verification #186</v>
       </c>
       <c r="E187" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F187" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G187" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6962,19 +6962,19 @@
         <v>TC187</v>
       </c>
       <c r="B188" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C188" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D188" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #187</v>
+        <v>Trigger mobile alert for concerning symptoms verification #187</v>
       </c>
       <c r="E188" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F188" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G188" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6997,19 +6997,19 @@
         <v>TC188</v>
       </c>
       <c r="B189" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C189" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D189" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #188</v>
+        <v>Notify user of abnormal vital fluctuations verification #188</v>
       </c>
       <c r="E189" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F189" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G189" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7032,19 +7032,19 @@
         <v>TC189</v>
       </c>
       <c r="B190" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C190" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D190" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #189</v>
+        <v>Dispatch summary of weekly health data verification #189</v>
       </c>
       <c r="E190" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F190" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G190" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7067,19 +7067,19 @@
         <v>TC190</v>
       </c>
       <c r="B191" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C191" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D191" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #190</v>
+        <v>Unlock application with FaceID / Fingerprint verification #190</v>
       </c>
       <c r="E191" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F191" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G191" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7102,19 +7102,19 @@
         <v>TC191</v>
       </c>
       <c r="B192" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C192" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D192" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #191</v>
+        <v>Enforce extra layer of login security via token verification #191</v>
       </c>
       <c r="E192" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F192" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G192" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7143,7 +7143,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D193" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #192</v>
+        <v>Verify full-screen logo brand rendering verification #192</v>
       </c>
       <c r="E193" t="str">
         <v>App running on Android Native</v>
@@ -7172,19 +7172,19 @@
         <v>TC193</v>
       </c>
       <c r="B194" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C194" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C194" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D194" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #193</v>
+        <v>Verify swipe gestures across onboarding layer verification #193</v>
       </c>
       <c r="E194" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F194" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G194" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7207,19 +7207,19 @@
         <v>TC194</v>
       </c>
       <c r="B195" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C195" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D195" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #194</v>
+        <v>Trigger push alert for medication times verification #194</v>
       </c>
       <c r="E195" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F195" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G195" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7242,19 +7242,19 @@
         <v>TC195</v>
       </c>
       <c r="B196" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C196" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D196" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #195</v>
+        <v>Trigger mobile alert for concerning symptoms verification #195</v>
       </c>
       <c r="E196" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F196" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G196" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7277,19 +7277,19 @@
         <v>TC196</v>
       </c>
       <c r="B197" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C197" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D197" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #196</v>
+        <v>Notify user of abnormal vital fluctuations verification #196</v>
       </c>
       <c r="E197" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F197" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G197" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7312,19 +7312,19 @@
         <v>TC197</v>
       </c>
       <c r="B198" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C198" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D198" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #197</v>
+        <v>Dispatch summary of weekly health data verification #197</v>
       </c>
       <c r="E198" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F198" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G198" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7347,19 +7347,19 @@
         <v>TC198</v>
       </c>
       <c r="B199" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C199" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D199" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #198</v>
+        <v>Unlock application with FaceID / Fingerprint verification #198</v>
       </c>
       <c r="E199" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F199" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G199" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7382,19 +7382,19 @@
         <v>TC199</v>
       </c>
       <c r="B200" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C200" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D200" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #199</v>
+        <v>Enforce extra layer of login security via token verification #199</v>
       </c>
       <c r="E200" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F200" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G200" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7423,7 +7423,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D201" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #200</v>
+        <v>Verify full-screen logo brand rendering verification #200</v>
       </c>
       <c r="E201" t="str">
         <v>App running on Android Native</v>
@@ -7452,19 +7452,19 @@
         <v>TC201</v>
       </c>
       <c r="B202" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C202" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C202" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D202" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #201</v>
+        <v>Verify swipe gestures across onboarding layer verification #201</v>
       </c>
       <c r="E202" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F202" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G202" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7487,19 +7487,19 @@
         <v>TC202</v>
       </c>
       <c r="B203" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C203" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D203" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #202</v>
+        <v>Trigger push alert for medication times verification #202</v>
       </c>
       <c r="E203" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F203" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G203" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7522,19 +7522,19 @@
         <v>TC203</v>
       </c>
       <c r="B204" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C204" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D204" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #203</v>
+        <v>Trigger mobile alert for concerning symptoms verification #203</v>
       </c>
       <c r="E204" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F204" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G204" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7557,19 +7557,19 @@
         <v>TC204</v>
       </c>
       <c r="B205" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C205" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D205" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #204</v>
+        <v>Notify user of abnormal vital fluctuations verification #204</v>
       </c>
       <c r="E205" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F205" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G205" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7592,19 +7592,19 @@
         <v>TC205</v>
       </c>
       <c r="B206" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C206" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D206" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #205</v>
+        <v>Dispatch summary of weekly health data verification #205</v>
       </c>
       <c r="E206" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F206" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G206" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7627,19 +7627,19 @@
         <v>TC206</v>
       </c>
       <c r="B207" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C207" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D207" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #206</v>
+        <v>Unlock application with FaceID / Fingerprint verification #206</v>
       </c>
       <c r="E207" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F207" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G207" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7662,19 +7662,19 @@
         <v>TC207</v>
       </c>
       <c r="B208" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C208" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D208" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #207</v>
+        <v>Enforce extra layer of login security via token verification #207</v>
       </c>
       <c r="E208" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F208" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G208" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7703,7 +7703,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D209" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #208</v>
+        <v>Verify full-screen logo brand rendering verification #208</v>
       </c>
       <c r="E209" t="str">
         <v>App running on Android Native</v>
@@ -7732,19 +7732,19 @@
         <v>TC209</v>
       </c>
       <c r="B210" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C210" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C210" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D210" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #209</v>
+        <v>Verify swipe gestures across onboarding layer verification #209</v>
       </c>
       <c r="E210" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F210" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G210" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7767,19 +7767,19 @@
         <v>TC210</v>
       </c>
       <c r="B211" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C211" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D211" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #210</v>
+        <v>Trigger push alert for medication times verification #210</v>
       </c>
       <c r="E211" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F211" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G211" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7802,19 +7802,19 @@
         <v>TC211</v>
       </c>
       <c r="B212" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C212" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D212" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #211</v>
+        <v>Trigger mobile alert for concerning symptoms verification #211</v>
       </c>
       <c r="E212" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F212" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G212" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7837,19 +7837,19 @@
         <v>TC212</v>
       </c>
       <c r="B213" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C213" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D213" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #212</v>
+        <v>Notify user of abnormal vital fluctuations verification #212</v>
       </c>
       <c r="E213" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F213" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G213" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7872,19 +7872,19 @@
         <v>TC213</v>
       </c>
       <c r="B214" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C214" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D214" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #213</v>
+        <v>Dispatch summary of weekly health data verification #213</v>
       </c>
       <c r="E214" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F214" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G214" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7907,19 +7907,19 @@
         <v>TC214</v>
       </c>
       <c r="B215" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C215" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D215" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #214</v>
+        <v>Unlock application with FaceID / Fingerprint verification #214</v>
       </c>
       <c r="E215" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F215" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G215" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7942,19 +7942,19 @@
         <v>TC215</v>
       </c>
       <c r="B216" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C216" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D216" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #215</v>
+        <v>Enforce extra layer of login security via token verification #215</v>
       </c>
       <c r="E216" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F216" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G216" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7983,7 +7983,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D217" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #216</v>
+        <v>Verify full-screen logo brand rendering verification #216</v>
       </c>
       <c r="E217" t="str">
         <v>App running on Android Native</v>
@@ -8012,19 +8012,19 @@
         <v>TC217</v>
       </c>
       <c r="B218" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C218" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C218" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D218" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #217</v>
+        <v>Verify swipe gestures across onboarding layer verification #217</v>
       </c>
       <c r="E218" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F218" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G218" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8047,19 +8047,19 @@
         <v>TC218</v>
       </c>
       <c r="B219" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C219" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D219" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #218</v>
+        <v>Trigger push alert for medication times verification #218</v>
       </c>
       <c r="E219" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F219" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G219" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8082,19 +8082,19 @@
         <v>TC219</v>
       </c>
       <c r="B220" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C220" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D220" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #219</v>
+        <v>Trigger mobile alert for concerning symptoms verification #219</v>
       </c>
       <c r="E220" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F220" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G220" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8117,19 +8117,19 @@
         <v>TC220</v>
       </c>
       <c r="B221" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C221" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D221" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #220</v>
+        <v>Notify user of abnormal vital fluctuations verification #220</v>
       </c>
       <c r="E221" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F221" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G221" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8152,19 +8152,19 @@
         <v>TC221</v>
       </c>
       <c r="B222" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C222" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D222" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #221</v>
+        <v>Dispatch summary of weekly health data verification #221</v>
       </c>
       <c r="E222" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F222" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G222" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8187,19 +8187,19 @@
         <v>TC222</v>
       </c>
       <c r="B223" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C223" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D223" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #222</v>
+        <v>Unlock application with FaceID / Fingerprint verification #222</v>
       </c>
       <c r="E223" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F223" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G223" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8222,19 +8222,19 @@
         <v>TC223</v>
       </c>
       <c r="B224" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C224" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D224" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #223</v>
+        <v>Enforce extra layer of login security via token verification #223</v>
       </c>
       <c r="E224" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F224" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G224" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8263,7 +8263,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D225" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #224</v>
+        <v>Verify full-screen logo brand rendering verification #224</v>
       </c>
       <c r="E225" t="str">
         <v>App running on Android Native</v>
@@ -8292,19 +8292,19 @@
         <v>TC225</v>
       </c>
       <c r="B226" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C226" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C226" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D226" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #225</v>
+        <v>Verify swipe gestures across onboarding layer verification #225</v>
       </c>
       <c r="E226" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F226" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G226" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8327,19 +8327,19 @@
         <v>TC226</v>
       </c>
       <c r="B227" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C227" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D227" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #226</v>
+        <v>Trigger push alert for medication times verification #226</v>
       </c>
       <c r="E227" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F227" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G227" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8362,19 +8362,19 @@
         <v>TC227</v>
       </c>
       <c r="B228" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C228" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D228" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #227</v>
+        <v>Trigger mobile alert for concerning symptoms verification #227</v>
       </c>
       <c r="E228" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F228" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G228" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8397,19 +8397,19 @@
         <v>TC228</v>
       </c>
       <c r="B229" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C229" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D229" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #228</v>
+        <v>Notify user of abnormal vital fluctuations verification #228</v>
       </c>
       <c r="E229" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F229" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G229" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8432,19 +8432,19 @@
         <v>TC229</v>
       </c>
       <c r="B230" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C230" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D230" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #229</v>
+        <v>Dispatch summary of weekly health data verification #229</v>
       </c>
       <c r="E230" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F230" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G230" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8467,19 +8467,19 @@
         <v>TC230</v>
       </c>
       <c r="B231" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C231" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D231" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #230</v>
+        <v>Unlock application with FaceID / Fingerprint verification #230</v>
       </c>
       <c r="E231" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F231" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G231" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8502,19 +8502,19 @@
         <v>TC231</v>
       </c>
       <c r="B232" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C232" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D232" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #231</v>
+        <v>Enforce extra layer of login security via token verification #231</v>
       </c>
       <c r="E232" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F232" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G232" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8543,7 +8543,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D233" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #232</v>
+        <v>Verify full-screen logo brand rendering verification #232</v>
       </c>
       <c r="E233" t="str">
         <v>App running on Android Native</v>
@@ -8572,19 +8572,19 @@
         <v>TC233</v>
       </c>
       <c r="B234" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C234" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C234" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D234" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #233</v>
+        <v>Verify swipe gestures across onboarding layer verification #233</v>
       </c>
       <c r="E234" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F234" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G234" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8607,19 +8607,19 @@
         <v>TC234</v>
       </c>
       <c r="B235" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C235" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D235" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #234</v>
+        <v>Trigger push alert for medication times verification #234</v>
       </c>
       <c r="E235" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F235" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G235" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8642,19 +8642,19 @@
         <v>TC235</v>
       </c>
       <c r="B236" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C236" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D236" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #235</v>
+        <v>Trigger mobile alert for concerning symptoms verification #235</v>
       </c>
       <c r="E236" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F236" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G236" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8677,19 +8677,19 @@
         <v>TC236</v>
       </c>
       <c r="B237" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C237" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D237" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #236</v>
+        <v>Notify user of abnormal vital fluctuations verification #236</v>
       </c>
       <c r="E237" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F237" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G237" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8712,19 +8712,19 @@
         <v>TC237</v>
       </c>
       <c r="B238" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C238" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D238" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #237</v>
+        <v>Dispatch summary of weekly health data verification #237</v>
       </c>
       <c r="E238" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F238" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G238" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8747,19 +8747,19 @@
         <v>TC238</v>
       </c>
       <c r="B239" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C239" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D239" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #238</v>
+        <v>Unlock application with FaceID / Fingerprint verification #238</v>
       </c>
       <c r="E239" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F239" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G239" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8782,19 +8782,19 @@
         <v>TC239</v>
       </c>
       <c r="B240" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C240" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D240" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #239</v>
+        <v>Enforce extra layer of login security via token verification #239</v>
       </c>
       <c r="E240" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F240" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G240" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8823,7 +8823,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D241" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #240</v>
+        <v>Verify full-screen logo brand rendering verification #240</v>
       </c>
       <c r="E241" t="str">
         <v>App running on Android Native</v>
@@ -8852,19 +8852,19 @@
         <v>TC241</v>
       </c>
       <c r="B242" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C242" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C242" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D242" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #241</v>
+        <v>Verify swipe gestures across onboarding layer verification #241</v>
       </c>
       <c r="E242" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F242" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G242" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8887,19 +8887,19 @@
         <v>TC242</v>
       </c>
       <c r="B243" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C243" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D243" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #242</v>
+        <v>Trigger push alert for medication times verification #242</v>
       </c>
       <c r="E243" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F243" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G243" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8922,19 +8922,19 @@
         <v>TC243</v>
       </c>
       <c r="B244" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C244" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D244" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #243</v>
+        <v>Trigger mobile alert for concerning symptoms verification #243</v>
       </c>
       <c r="E244" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F244" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G244" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8957,19 +8957,19 @@
         <v>TC244</v>
       </c>
       <c r="B245" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C245" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D245" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #244</v>
+        <v>Notify user of abnormal vital fluctuations verification #244</v>
       </c>
       <c r="E245" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F245" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G245" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8992,19 +8992,19 @@
         <v>TC245</v>
       </c>
       <c r="B246" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C246" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D246" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #245</v>
+        <v>Dispatch summary of weekly health data verification #245</v>
       </c>
       <c r="E246" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F246" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G246" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9027,19 +9027,19 @@
         <v>TC246</v>
       </c>
       <c r="B247" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C247" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D247" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #246</v>
+        <v>Unlock application with FaceID / Fingerprint verification #246</v>
       </c>
       <c r="E247" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F247" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G247" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9062,19 +9062,19 @@
         <v>TC247</v>
       </c>
       <c r="B248" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C248" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D248" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #247</v>
+        <v>Enforce extra layer of login security via token verification #247</v>
       </c>
       <c r="E248" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F248" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G248" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9103,7 +9103,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D249" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #248</v>
+        <v>Verify full-screen logo brand rendering verification #248</v>
       </c>
       <c r="E249" t="str">
         <v>App running on Android Native</v>
@@ -9132,19 +9132,19 @@
         <v>TC249</v>
       </c>
       <c r="B250" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C250" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C250" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D250" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #249</v>
+        <v>Verify swipe gestures across onboarding layer verification #249</v>
       </c>
       <c r="E250" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F250" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G250" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9167,19 +9167,19 @@
         <v>TC250</v>
       </c>
       <c r="B251" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C251" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D251" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #250</v>
+        <v>Trigger push alert for medication times verification #250</v>
       </c>
       <c r="E251" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F251" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G251" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9202,19 +9202,19 @@
         <v>TC251</v>
       </c>
       <c r="B252" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C252" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D252" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #251</v>
+        <v>Trigger mobile alert for concerning symptoms verification #251</v>
       </c>
       <c r="E252" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F252" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G252" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9237,19 +9237,19 @@
         <v>TC252</v>
       </c>
       <c r="B253" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C253" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D253" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #252</v>
+        <v>Notify user of abnormal vital fluctuations verification #252</v>
       </c>
       <c r="E253" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F253" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G253" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9272,19 +9272,19 @@
         <v>TC253</v>
       </c>
       <c r="B254" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C254" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D254" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #253</v>
+        <v>Dispatch summary of weekly health data verification #253</v>
       </c>
       <c r="E254" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F254" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G254" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9307,19 +9307,19 @@
         <v>TC254</v>
       </c>
       <c r="B255" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C255" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D255" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #254</v>
+        <v>Unlock application with FaceID / Fingerprint verification #254</v>
       </c>
       <c r="E255" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F255" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G255" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9342,19 +9342,19 @@
         <v>TC255</v>
       </c>
       <c r="B256" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C256" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D256" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #255</v>
+        <v>Enforce extra layer of login security via token verification #255</v>
       </c>
       <c r="E256" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F256" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G256" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9383,7 +9383,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D257" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #256</v>
+        <v>Verify full-screen logo brand rendering verification #256</v>
       </c>
       <c r="E257" t="str">
         <v>App running on Android Native</v>
@@ -9412,19 +9412,19 @@
         <v>TC257</v>
       </c>
       <c r="B258" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C258" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C258" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D258" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #257</v>
+        <v>Verify swipe gestures across onboarding layer verification #257</v>
       </c>
       <c r="E258" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F258" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G258" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9447,19 +9447,19 @@
         <v>TC258</v>
       </c>
       <c r="B259" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C259" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D259" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #258</v>
+        <v>Trigger push alert for medication times verification #258</v>
       </c>
       <c r="E259" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F259" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G259" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9482,19 +9482,19 @@
         <v>TC259</v>
       </c>
       <c r="B260" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C260" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D260" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #259</v>
+        <v>Trigger mobile alert for concerning symptoms verification #259</v>
       </c>
       <c r="E260" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F260" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G260" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9517,19 +9517,19 @@
         <v>TC260</v>
       </c>
       <c r="B261" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C261" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D261" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #260</v>
+        <v>Notify user of abnormal vital fluctuations verification #260</v>
       </c>
       <c r="E261" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F261" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G261" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9552,19 +9552,19 @@
         <v>TC261</v>
       </c>
       <c r="B262" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C262" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D262" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #261</v>
+        <v>Dispatch summary of weekly health data verification #261</v>
       </c>
       <c r="E262" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F262" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G262" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9587,19 +9587,19 @@
         <v>TC262</v>
       </c>
       <c r="B263" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C263" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D263" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #262</v>
+        <v>Unlock application with FaceID / Fingerprint verification #262</v>
       </c>
       <c r="E263" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F263" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G263" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9622,19 +9622,19 @@
         <v>TC263</v>
       </c>
       <c r="B264" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C264" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D264" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #263</v>
+        <v>Enforce extra layer of login security via token verification #263</v>
       </c>
       <c r="E264" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F264" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G264" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9663,7 +9663,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D265" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #264</v>
+        <v>Verify full-screen logo brand rendering verification #264</v>
       </c>
       <c r="E265" t="str">
         <v>App running on Android Native</v>
@@ -9692,19 +9692,19 @@
         <v>TC265</v>
       </c>
       <c r="B266" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C266" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C266" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D266" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #265</v>
+        <v>Verify swipe gestures across onboarding layer verification #265</v>
       </c>
       <c r="E266" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F266" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G266" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9727,19 +9727,19 @@
         <v>TC266</v>
       </c>
       <c r="B267" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C267" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D267" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #266</v>
+        <v>Trigger push alert for medication times verification #266</v>
       </c>
       <c r="E267" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F267" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G267" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9762,19 +9762,19 @@
         <v>TC267</v>
       </c>
       <c r="B268" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C268" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D268" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #267</v>
+        <v>Trigger mobile alert for concerning symptoms verification #267</v>
       </c>
       <c r="E268" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F268" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G268" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9797,19 +9797,19 @@
         <v>TC268</v>
       </c>
       <c r="B269" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C269" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D269" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #268</v>
+        <v>Notify user of abnormal vital fluctuations verification #268</v>
       </c>
       <c r="E269" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F269" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G269" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9832,19 +9832,19 @@
         <v>TC269</v>
       </c>
       <c r="B270" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C270" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D270" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #269</v>
+        <v>Dispatch summary of weekly health data verification #269</v>
       </c>
       <c r="E270" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F270" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G270" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9867,19 +9867,19 @@
         <v>TC270</v>
       </c>
       <c r="B271" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C271" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D271" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #270</v>
+        <v>Unlock application with FaceID / Fingerprint verification #270</v>
       </c>
       <c r="E271" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F271" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G271" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9902,19 +9902,19 @@
         <v>TC271</v>
       </c>
       <c r="B272" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C272" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D272" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #271</v>
+        <v>Enforce extra layer of login security via token verification #271</v>
       </c>
       <c r="E272" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F272" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G272" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9943,7 +9943,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D273" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #272</v>
+        <v>Verify full-screen logo brand rendering verification #272</v>
       </c>
       <c r="E273" t="str">
         <v>App running on Android Native</v>
@@ -9972,19 +9972,19 @@
         <v>TC273</v>
       </c>
       <c r="B274" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C274" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C274" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D274" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #273</v>
+        <v>Verify swipe gestures across onboarding layer verification #273</v>
       </c>
       <c r="E274" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F274" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G274" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10007,19 +10007,19 @@
         <v>TC274</v>
       </c>
       <c r="B275" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C275" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D275" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #274</v>
+        <v>Trigger push alert for medication times verification #274</v>
       </c>
       <c r="E275" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F275" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G275" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10042,19 +10042,19 @@
         <v>TC275</v>
       </c>
       <c r="B276" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C276" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D276" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #275</v>
+        <v>Trigger mobile alert for concerning symptoms verification #275</v>
       </c>
       <c r="E276" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F276" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G276" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10077,19 +10077,19 @@
         <v>TC276</v>
       </c>
       <c r="B277" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C277" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D277" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #276</v>
+        <v>Notify user of abnormal vital fluctuations verification #276</v>
       </c>
       <c r="E277" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F277" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G277" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10112,19 +10112,19 @@
         <v>TC277</v>
       </c>
       <c r="B278" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C278" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D278" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #277</v>
+        <v>Dispatch summary of weekly health data verification #277</v>
       </c>
       <c r="E278" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F278" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G278" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10147,19 +10147,19 @@
         <v>TC278</v>
       </c>
       <c r="B279" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C279" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D279" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #278</v>
+        <v>Unlock application with FaceID / Fingerprint verification #278</v>
       </c>
       <c r="E279" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F279" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G279" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10182,19 +10182,19 @@
         <v>TC279</v>
       </c>
       <c r="B280" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C280" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D280" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #279</v>
+        <v>Enforce extra layer of login security via token verification #279</v>
       </c>
       <c r="E280" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F280" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G280" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10223,7 +10223,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D281" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #280</v>
+        <v>Verify full-screen logo brand rendering verification #280</v>
       </c>
       <c r="E281" t="str">
         <v>App running on Android Native</v>
@@ -10252,19 +10252,19 @@
         <v>TC281</v>
       </c>
       <c r="B282" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C282" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C282" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D282" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #281</v>
+        <v>Verify swipe gestures across onboarding layer verification #281</v>
       </c>
       <c r="E282" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F282" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G282" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10287,19 +10287,19 @@
         <v>TC282</v>
       </c>
       <c r="B283" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C283" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D283" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #282</v>
+        <v>Trigger push alert for medication times verification #282</v>
       </c>
       <c r="E283" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F283" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G283" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10322,19 +10322,19 @@
         <v>TC283</v>
       </c>
       <c r="B284" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C284" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D284" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #283</v>
+        <v>Trigger mobile alert for concerning symptoms verification #283</v>
       </c>
       <c r="E284" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F284" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G284" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10357,19 +10357,19 @@
         <v>TC284</v>
       </c>
       <c r="B285" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C285" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D285" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #284</v>
+        <v>Notify user of abnormal vital fluctuations verification #284</v>
       </c>
       <c r="E285" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F285" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G285" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10392,19 +10392,19 @@
         <v>TC285</v>
       </c>
       <c r="B286" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C286" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D286" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #285</v>
+        <v>Dispatch summary of weekly health data verification #285</v>
       </c>
       <c r="E286" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F286" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G286" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10427,19 +10427,19 @@
         <v>TC286</v>
       </c>
       <c r="B287" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C287" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D287" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #286</v>
+        <v>Unlock application with FaceID / Fingerprint verification #286</v>
       </c>
       <c r="E287" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F287" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G287" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10462,19 +10462,19 @@
         <v>TC287</v>
       </c>
       <c r="B288" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C288" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D288" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #287</v>
+        <v>Enforce extra layer of login security via token verification #287</v>
       </c>
       <c r="E288" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F288" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G288" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10503,7 +10503,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D289" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #288</v>
+        <v>Verify full-screen logo brand rendering verification #288</v>
       </c>
       <c r="E289" t="str">
         <v>App running on Android Native</v>
@@ -10532,19 +10532,19 @@
         <v>TC289</v>
       </c>
       <c r="B290" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C290" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C290" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D290" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #289</v>
+        <v>Verify swipe gestures across onboarding layer verification #289</v>
       </c>
       <c r="E290" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F290" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G290" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10567,19 +10567,19 @@
         <v>TC290</v>
       </c>
       <c r="B291" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C291" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D291" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #290</v>
+        <v>Trigger push alert for medication times verification #290</v>
       </c>
       <c r="E291" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F291" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G291" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10602,19 +10602,19 @@
         <v>TC291</v>
       </c>
       <c r="B292" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C292" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D292" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #291</v>
+        <v>Trigger mobile alert for concerning symptoms verification #291</v>
       </c>
       <c r="E292" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F292" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G292" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10637,19 +10637,19 @@
         <v>TC292</v>
       </c>
       <c r="B293" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C293" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D293" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #292</v>
+        <v>Notify user of abnormal vital fluctuations verification #292</v>
       </c>
       <c r="E293" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F293" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G293" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10672,19 +10672,19 @@
         <v>TC293</v>
       </c>
       <c r="B294" t="str">
-        <v>Onboarding</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C294" t="str">
-        <v>Tutorial Array</v>
+        <v>Weekly Reports</v>
       </c>
       <c r="D294" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #293</v>
+        <v>Dispatch summary of weekly health data verification #293</v>
       </c>
       <c r="E294" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F294" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
       </c>
       <c r="G294" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10707,19 +10707,19 @@
         <v>TC294</v>
       </c>
       <c r="B295" t="str">
-        <v>Home Screen</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C295" t="str">
-        <v>Dashboard</v>
+        <v>Biometric Auth</v>
       </c>
       <c r="D295" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #294</v>
+        <v>Unlock application with FaceID / Fingerprint verification #294</v>
       </c>
       <c r="E295" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F295" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
       </c>
       <c r="G295" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10742,19 +10742,19 @@
         <v>TC295</v>
       </c>
       <c r="B296" t="str">
-        <v>Mobile Layout</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C296" t="str">
-        <v>Responsive</v>
+        <v>2FA</v>
       </c>
       <c r="D296" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #295</v>
+        <v>Enforce extra layer of login security via token verification #295</v>
       </c>
       <c r="E296" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F296" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Privacy Centre and perform 2FA action</v>
       </c>
       <c r="G296" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10783,7 +10783,7 @@
         <v>Splash Screen</v>
       </c>
       <c r="D297" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #296</v>
+        <v>Verify full-screen logo brand rendering verification #296</v>
       </c>
       <c r="E297" t="str">
         <v>App running on Android Native</v>
@@ -10812,19 +10812,19 @@
         <v>TC297</v>
       </c>
       <c r="B298" t="str">
+        <v>App Initialization</v>
+      </c>
+      <c r="C298" t="str">
         <v>Onboarding</v>
       </c>
-      <c r="C298" t="str">
-        <v>Tutorial Array</v>
-      </c>
       <c r="D298" t="str">
-        <v>Verify swipe gestures across multi-page intro verification #297</v>
+        <v>Verify swipe gestures across onboarding layer verification #297</v>
       </c>
       <c r="E298" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F298" t="str">
-        <v>Navigate to Onboarding and perform Tutorial Array action</v>
+        <v>Navigate to App Initialization and perform Onboarding action</v>
       </c>
       <c r="G298" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10847,19 +10847,19 @@
         <v>TC298</v>
       </c>
       <c r="B299" t="str">
-        <v>Home Screen</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C299" t="str">
-        <v>Dashboard</v>
+        <v>Medication Reminders</v>
       </c>
       <c r="D299" t="str">
-        <v>Render correct daily metrics upon authentication unlock verification #298</v>
+        <v>Trigger push alert for medication times verification #298</v>
       </c>
       <c r="E299" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F299" t="str">
-        <v>Navigate to Home Screen and perform Dashboard action</v>
+        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
       </c>
       <c r="G299" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10882,19 +10882,19 @@
         <v>TC299</v>
       </c>
       <c r="B300" t="str">
-        <v>Mobile Layout</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C300" t="str">
-        <v>Responsive</v>
+        <v>Symptom Alerts</v>
       </c>
       <c r="D300" t="str">
-        <v>Verify CSS flexbox adjusts seamlessly to native viewport width verification #299</v>
+        <v>Trigger mobile alert for concerning symptoms verification #299</v>
       </c>
       <c r="E300" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F300" t="str">
-        <v>Navigate to Mobile Layout and perform Responsive action</v>
+        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
       </c>
       <c r="G300" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10917,19 +10917,19 @@
         <v>TC300</v>
       </c>
       <c r="B301" t="str">
-        <v>App Initialization</v>
+        <v>Push Notifications</v>
       </c>
       <c r="C301" t="str">
-        <v>Splash Screen</v>
+        <v>Health Metrics</v>
       </c>
       <c r="D301" t="str">
-        <v>Verify full-screen logo rendering under 2000ms verification #300</v>
+        <v>Notify user of abnormal vital fluctuations verification #300</v>
       </c>
       <c r="E301" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F301" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Navigate to Push Notifications and perform Health Metrics action</v>
       </c>
       <c r="G301" t="str">
         <v>Action completes successfully within standard latency bounds</v>

--- a/e2e_tests_suite/Report_02_Appium.xlsx
+++ b/e2e_tests_suite/Report_02_Appium.xlsx
@@ -458,16 +458,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D2" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #1</v>
+        <v>Verify swipe gestures across onboarding layer [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E2" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F2" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G2" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H2" t="str">
         <v>High</v>
@@ -493,16 +493,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D3" t="str">
-        <v>Trigger push alert for medication times verification #2</v>
+        <v>Trigger push alert for medication times [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E3" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F3" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating security guard (special char injection)</v>
       </c>
       <c r="G3" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H3" t="str">
         <v>High</v>
@@ -528,16 +528,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D4" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #3</v>
+        <v>Trigger mobile alert for concerning symptoms [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E4" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F4" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G4" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H4" t="str">
         <v>High</v>
@@ -563,16 +563,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D5" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #4</v>
+        <v>Notify user of abnormal vital fluctuations [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E5" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F5" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G5" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H5" t="str">
         <v>High</v>
@@ -598,16 +598,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D6" t="str">
-        <v>Dispatch summary of weekly health data verification #5</v>
+        <v>Dispatch summary of weekly health data [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E6" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F6" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating normal path (standard execution)</v>
       </c>
       <c r="G6" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H6" t="str">
         <v>Critical</v>
@@ -633,16 +633,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D7" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #6</v>
+        <v>Unlock application with FaceID / Fingerprint [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E7" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F7" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G7" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H7" t="str">
         <v>High</v>
@@ -668,16 +668,16 @@
         <v>2FA</v>
       </c>
       <c r="D8" t="str">
-        <v>Enforce extra layer of login security via token verification #7</v>
+        <v>Enforce extra layer of login security via token [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E8" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F8" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating security guard (special char injection)</v>
       </c>
       <c r="G8" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H8" t="str">
         <v>High</v>
@@ -703,16 +703,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D9" t="str">
-        <v>Verify full-screen logo brand rendering verification #8</v>
+        <v>Verify full-screen logo brand rendering [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E9" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F9" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G9" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H9" t="str">
         <v>High</v>
@@ -738,16 +738,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D10" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #9</v>
+        <v>Verify swipe gestures across onboarding layer [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E10" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F10" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G10" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H10" t="str">
         <v>High</v>
@@ -773,16 +773,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D11" t="str">
-        <v>Trigger push alert for medication times verification #10</v>
+        <v>Trigger push alert for medication times [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E11" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F11" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating normal path (standard execution)</v>
       </c>
       <c r="G11" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H11" t="str">
         <v>Critical</v>
@@ -808,16 +808,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D12" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #11</v>
+        <v>Trigger mobile alert for concerning symptoms [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E12" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F12" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G12" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H12" t="str">
         <v>High</v>
@@ -843,16 +843,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D13" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #12</v>
+        <v>Notify user of abnormal vital fluctuations [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E13" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F13" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G13" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H13" t="str">
         <v>High</v>
@@ -878,16 +878,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D14" t="str">
-        <v>Dispatch summary of weekly health data verification #13</v>
+        <v>Dispatch summary of weekly health data [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E14" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F14" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G14" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H14" t="str">
         <v>High</v>
@@ -913,16 +913,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D15" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #14</v>
+        <v>Unlock application with FaceID / Fingerprint [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E15" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F15" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G15" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H15" t="str">
         <v>High</v>
@@ -948,16 +948,16 @@
         <v>2FA</v>
       </c>
       <c r="D16" t="str">
-        <v>Enforce extra layer of login security via token verification #15</v>
+        <v>Enforce extra layer of login security via token [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E16" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F16" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating normal path (standard execution)</v>
       </c>
       <c r="G16" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H16" t="str">
         <v>Critical</v>
@@ -983,16 +983,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D17" t="str">
-        <v>Verify full-screen logo brand rendering verification #16</v>
+        <v>Verify full-screen logo brand rendering [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E17" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F17" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G17" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H17" t="str">
         <v>High</v>
@@ -1018,16 +1018,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D18" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #17</v>
+        <v>Verify swipe gestures across onboarding layer [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E18" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F18" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating security guard (special char injection)</v>
       </c>
       <c r="G18" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H18" t="str">
         <v>High</v>
@@ -1053,16 +1053,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D19" t="str">
-        <v>Trigger push alert for medication times verification #18</v>
+        <v>Trigger push alert for medication times [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E19" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F19" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G19" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H19" t="str">
         <v>High</v>
@@ -1088,16 +1088,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D20" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #19</v>
+        <v>Trigger mobile alert for concerning symptoms [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E20" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F20" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G20" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H20" t="str">
         <v>High</v>
@@ -1123,16 +1123,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D21" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #20</v>
+        <v>Notify user of abnormal vital fluctuations [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E21" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F21" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G21" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H21" t="str">
         <v>Critical</v>
@@ -1158,16 +1158,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D22" t="str">
-        <v>Dispatch summary of weekly health data verification #21</v>
+        <v>Dispatch summary of weekly health data [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E22" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F22" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G22" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H22" t="str">
         <v>High</v>
@@ -1193,16 +1193,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D23" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #22</v>
+        <v>Unlock application with FaceID / Fingerprint [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E23" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F23" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating security guard (special char injection)</v>
       </c>
       <c r="G23" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H23" t="str">
         <v>High</v>
@@ -1228,16 +1228,16 @@
         <v>2FA</v>
       </c>
       <c r="D24" t="str">
-        <v>Enforce extra layer of login security via token verification #23</v>
+        <v>Enforce extra layer of login security via token [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E24" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F24" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G24" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H24" t="str">
         <v>High</v>
@@ -1263,16 +1263,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D25" t="str">
-        <v>Verify full-screen logo brand rendering verification #24</v>
+        <v>Verify full-screen logo brand rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E25" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F25" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G25" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H25" t="str">
         <v>High</v>
@@ -1298,16 +1298,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D26" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #25</v>
+        <v>Verify swipe gestures across onboarding layer [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E26" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F26" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating normal path (standard execution)</v>
       </c>
       <c r="G26" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H26" t="str">
         <v>Critical</v>
@@ -1333,16 +1333,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D27" t="str">
-        <v>Trigger push alert for medication times verification #26</v>
+        <v>Trigger push alert for medication times [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E27" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F27" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G27" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H27" t="str">
         <v>High</v>
@@ -1368,16 +1368,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D28" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #27</v>
+        <v>Trigger mobile alert for concerning symptoms [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E28" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F28" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating security guard (special char injection)</v>
       </c>
       <c r="G28" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H28" t="str">
         <v>High</v>
@@ -1403,16 +1403,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D29" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #28</v>
+        <v>Notify user of abnormal vital fluctuations [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E29" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F29" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G29" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H29" t="str">
         <v>High</v>
@@ -1438,16 +1438,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D30" t="str">
-        <v>Dispatch summary of weekly health data verification #29</v>
+        <v>Dispatch summary of weekly health data [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E30" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F30" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G30" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H30" t="str">
         <v>High</v>
@@ -1473,16 +1473,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D31" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #30</v>
+        <v>Unlock application with FaceID / Fingerprint [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E31" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F31" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating normal path (standard execution)</v>
       </c>
       <c r="G31" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H31" t="str">
         <v>Critical</v>
@@ -1508,16 +1508,16 @@
         <v>2FA</v>
       </c>
       <c r="D32" t="str">
-        <v>Enforce extra layer of login security via token verification #31</v>
+        <v>Enforce extra layer of login security via token [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E32" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F32" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G32" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H32" t="str">
         <v>High</v>
@@ -1543,16 +1543,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D33" t="str">
-        <v>Verify full-screen logo brand rendering verification #32</v>
+        <v>Verify full-screen logo brand rendering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E33" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F33" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating security guard (special char injection)</v>
       </c>
       <c r="G33" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H33" t="str">
         <v>High</v>
@@ -1578,16 +1578,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D34" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #33</v>
+        <v>Verify swipe gestures across onboarding layer [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E34" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F34" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G34" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H34" t="str">
         <v>High</v>
@@ -1613,16 +1613,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D35" t="str">
-        <v>Trigger push alert for medication times verification #34</v>
+        <v>Trigger push alert for medication times [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E35" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F35" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G35" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H35" t="str">
         <v>High</v>
@@ -1648,16 +1648,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D36" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #35</v>
+        <v>Trigger mobile alert for concerning symptoms [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E36" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F36" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating normal path (standard execution)</v>
       </c>
       <c r="G36" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H36" t="str">
         <v>Critical</v>
@@ -1683,16 +1683,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D37" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #36</v>
+        <v>Notify user of abnormal vital fluctuations [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E37" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F37" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G37" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H37" t="str">
         <v>High</v>
@@ -1718,16 +1718,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D38" t="str">
-        <v>Dispatch summary of weekly health data verification #37</v>
+        <v>Dispatch summary of weekly health data [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E38" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F38" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating security guard (special char injection)</v>
       </c>
       <c r="G38" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H38" t="str">
         <v>High</v>
@@ -1753,16 +1753,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D39" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #38</v>
+        <v>Unlock application with FaceID / Fingerprint [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E39" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F39" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G39" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H39" t="str">
         <v>High</v>
@@ -1788,16 +1788,16 @@
         <v>2FA</v>
       </c>
       <c r="D40" t="str">
-        <v>Enforce extra layer of login security via token verification #39</v>
+        <v>Enforce extra layer of login security via token [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E40" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F40" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G40" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H40" t="str">
         <v>High</v>
@@ -1823,16 +1823,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D41" t="str">
-        <v>Verify full-screen logo brand rendering verification #40</v>
+        <v>Verify full-screen logo brand rendering [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E41" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F41" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating normal path (standard execution)</v>
       </c>
       <c r="G41" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H41" t="str">
         <v>Critical</v>
@@ -1858,16 +1858,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D42" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #41</v>
+        <v>Verify swipe gestures across onboarding layer [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E42" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F42" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G42" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H42" t="str">
         <v>High</v>
@@ -1893,16 +1893,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D43" t="str">
-        <v>Trigger push alert for medication times verification #42</v>
+        <v>Trigger push alert for medication times [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E43" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F43" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating security guard (special char injection)</v>
       </c>
       <c r="G43" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H43" t="str">
         <v>High</v>
@@ -1928,16 +1928,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D44" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #43</v>
+        <v>Trigger mobile alert for concerning symptoms [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E44" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F44" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G44" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H44" t="str">
         <v>High</v>
@@ -1963,16 +1963,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D45" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #44</v>
+        <v>Notify user of abnormal vital fluctuations [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E45" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F45" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G45" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H45" t="str">
         <v>High</v>
@@ -1998,16 +1998,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D46" t="str">
-        <v>Dispatch summary of weekly health data verification #45</v>
+        <v>Dispatch summary of weekly health data [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E46" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F46" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating normal path (standard execution)</v>
       </c>
       <c r="G46" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H46" t="str">
         <v>Critical</v>
@@ -2033,16 +2033,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D47" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #46</v>
+        <v>Unlock application with FaceID / Fingerprint [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E47" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F47" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G47" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H47" t="str">
         <v>High</v>
@@ -2068,16 +2068,16 @@
         <v>2FA</v>
       </c>
       <c r="D48" t="str">
-        <v>Enforce extra layer of login security via token verification #47</v>
+        <v>Enforce extra layer of login security via token [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E48" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F48" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating security guard (special char injection)</v>
       </c>
       <c r="G48" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H48" t="str">
         <v>High</v>
@@ -2103,16 +2103,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D49" t="str">
-        <v>Verify full-screen logo brand rendering verification #48</v>
+        <v>Verify full-screen logo brand rendering [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E49" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F49" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G49" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H49" t="str">
         <v>High</v>
@@ -2138,16 +2138,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D50" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #49</v>
+        <v>Verify swipe gestures across onboarding layer [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E50" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F50" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G50" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H50" t="str">
         <v>High</v>
@@ -2173,16 +2173,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D51" t="str">
-        <v>Trigger push alert for medication times verification #50</v>
+        <v>Trigger push alert for medication times [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E51" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F51" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating normal path (standard execution)</v>
       </c>
       <c r="G51" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H51" t="str">
         <v>Critical</v>
@@ -2208,16 +2208,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D52" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #51</v>
+        <v>Trigger mobile alert for concerning symptoms [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E52" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F52" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G52" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H52" t="str">
         <v>High</v>
@@ -2243,16 +2243,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D53" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #52</v>
+        <v>Notify user of abnormal vital fluctuations [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E53" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F53" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G53" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H53" t="str">
         <v>High</v>
@@ -2278,16 +2278,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D54" t="str">
-        <v>Dispatch summary of weekly health data verification #53</v>
+        <v>Dispatch summary of weekly health data [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E54" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F54" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G54" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H54" t="str">
         <v>High</v>
@@ -2313,16 +2313,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D55" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #54</v>
+        <v>Unlock application with FaceID / Fingerprint [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E55" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F55" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G55" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H55" t="str">
         <v>High</v>
@@ -2348,16 +2348,16 @@
         <v>2FA</v>
       </c>
       <c r="D56" t="str">
-        <v>Enforce extra layer of login security via token verification #55</v>
+        <v>Enforce extra layer of login security via token [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E56" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F56" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating normal path (standard execution)</v>
       </c>
       <c r="G56" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H56" t="str">
         <v>Critical</v>
@@ -2383,16 +2383,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D57" t="str">
-        <v>Verify full-screen logo brand rendering verification #56</v>
+        <v>Verify full-screen logo brand rendering [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E57" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F57" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G57" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H57" t="str">
         <v>High</v>
@@ -2418,16 +2418,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D58" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #57</v>
+        <v>Verify swipe gestures across onboarding layer [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E58" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F58" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating security guard (special char injection)</v>
       </c>
       <c r="G58" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H58" t="str">
         <v>High</v>
@@ -2453,16 +2453,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D59" t="str">
-        <v>Trigger push alert for medication times verification #58</v>
+        <v>Trigger push alert for medication times [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E59" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F59" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G59" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H59" t="str">
         <v>High</v>
@@ -2488,16 +2488,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D60" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #59</v>
+        <v>Trigger mobile alert for concerning symptoms [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E60" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F60" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G60" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H60" t="str">
         <v>High</v>
@@ -2523,16 +2523,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D61" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #60</v>
+        <v>Notify user of abnormal vital fluctuations [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E61" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F61" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G61" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H61" t="str">
         <v>Critical</v>
@@ -2558,16 +2558,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D62" t="str">
-        <v>Dispatch summary of weekly health data verification #61</v>
+        <v>Dispatch summary of weekly health data [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E62" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F62" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G62" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H62" t="str">
         <v>High</v>
@@ -2593,16 +2593,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D63" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #62</v>
+        <v>Unlock application with FaceID / Fingerprint [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E63" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F63" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating security guard (special char injection)</v>
       </c>
       <c r="G63" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H63" t="str">
         <v>High</v>
@@ -2628,16 +2628,16 @@
         <v>2FA</v>
       </c>
       <c r="D64" t="str">
-        <v>Enforce extra layer of login security via token verification #63</v>
+        <v>Enforce extra layer of login security via token [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E64" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F64" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G64" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H64" t="str">
         <v>High</v>
@@ -2663,16 +2663,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D65" t="str">
-        <v>Verify full-screen logo brand rendering verification #64</v>
+        <v>Verify full-screen logo brand rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E65" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F65" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G65" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H65" t="str">
         <v>High</v>
@@ -2698,16 +2698,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D66" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #65</v>
+        <v>Verify swipe gestures across onboarding layer [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E66" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F66" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating normal path (standard execution)</v>
       </c>
       <c r="G66" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H66" t="str">
         <v>Critical</v>
@@ -2733,16 +2733,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D67" t="str">
-        <v>Trigger push alert for medication times verification #66</v>
+        <v>Trigger push alert for medication times [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E67" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F67" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G67" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H67" t="str">
         <v>High</v>
@@ -2768,16 +2768,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D68" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #67</v>
+        <v>Trigger mobile alert for concerning symptoms [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E68" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F68" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating security guard (special char injection)</v>
       </c>
       <c r="G68" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H68" t="str">
         <v>High</v>
@@ -2803,16 +2803,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D69" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #68</v>
+        <v>Notify user of abnormal vital fluctuations [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E69" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F69" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G69" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H69" t="str">
         <v>High</v>
@@ -2838,16 +2838,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D70" t="str">
-        <v>Dispatch summary of weekly health data verification #69</v>
+        <v>Dispatch summary of weekly health data [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E70" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F70" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G70" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H70" t="str">
         <v>High</v>
@@ -2873,16 +2873,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D71" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #70</v>
+        <v>Unlock application with FaceID / Fingerprint [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E71" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F71" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating normal path (standard execution)</v>
       </c>
       <c r="G71" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H71" t="str">
         <v>Critical</v>
@@ -2908,16 +2908,16 @@
         <v>2FA</v>
       </c>
       <c r="D72" t="str">
-        <v>Enforce extra layer of login security via token verification #71</v>
+        <v>Enforce extra layer of login security via token [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E72" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F72" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G72" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H72" t="str">
         <v>High</v>
@@ -2943,16 +2943,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D73" t="str">
-        <v>Verify full-screen logo brand rendering verification #72</v>
+        <v>Verify full-screen logo brand rendering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E73" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F73" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating security guard (special char injection)</v>
       </c>
       <c r="G73" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H73" t="str">
         <v>High</v>
@@ -2978,16 +2978,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D74" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #73</v>
+        <v>Verify swipe gestures across onboarding layer [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E74" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F74" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G74" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H74" t="str">
         <v>High</v>
@@ -3013,16 +3013,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D75" t="str">
-        <v>Trigger push alert for medication times verification #74</v>
+        <v>Trigger push alert for medication times [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E75" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F75" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G75" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H75" t="str">
         <v>High</v>
@@ -3048,16 +3048,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D76" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #75</v>
+        <v>Trigger mobile alert for concerning symptoms [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E76" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F76" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating normal path (standard execution)</v>
       </c>
       <c r="G76" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H76" t="str">
         <v>Critical</v>
@@ -3083,16 +3083,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D77" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #76</v>
+        <v>Notify user of abnormal vital fluctuations [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E77" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F77" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G77" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H77" t="str">
         <v>High</v>
@@ -3118,16 +3118,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D78" t="str">
-        <v>Dispatch summary of weekly health data verification #77</v>
+        <v>Dispatch summary of weekly health data [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E78" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F78" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating security guard (special char injection)</v>
       </c>
       <c r="G78" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H78" t="str">
         <v>High</v>
@@ -3153,16 +3153,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D79" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #78</v>
+        <v>Unlock application with FaceID / Fingerprint [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E79" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F79" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G79" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H79" t="str">
         <v>High</v>
@@ -3188,16 +3188,16 @@
         <v>2FA</v>
       </c>
       <c r="D80" t="str">
-        <v>Enforce extra layer of login security via token verification #79</v>
+        <v>Enforce extra layer of login security via token [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E80" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F80" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G80" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H80" t="str">
         <v>High</v>
@@ -3223,16 +3223,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D81" t="str">
-        <v>Verify full-screen logo brand rendering verification #80</v>
+        <v>Verify full-screen logo brand rendering [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E81" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F81" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating normal path (standard execution)</v>
       </c>
       <c r="G81" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H81" t="str">
         <v>Critical</v>
@@ -3258,16 +3258,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D82" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #81</v>
+        <v>Verify swipe gestures across onboarding layer [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E82" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F82" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G82" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H82" t="str">
         <v>High</v>
@@ -3293,16 +3293,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D83" t="str">
-        <v>Trigger push alert for medication times verification #82</v>
+        <v>Trigger push alert for medication times [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E83" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F83" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating security guard (special char injection)</v>
       </c>
       <c r="G83" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H83" t="str">
         <v>High</v>
@@ -3328,16 +3328,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D84" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #83</v>
+        <v>Trigger mobile alert for concerning symptoms [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E84" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F84" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G84" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H84" t="str">
         <v>High</v>
@@ -3363,16 +3363,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D85" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #84</v>
+        <v>Notify user of abnormal vital fluctuations [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E85" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F85" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G85" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H85" t="str">
         <v>High</v>
@@ -3398,16 +3398,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D86" t="str">
-        <v>Dispatch summary of weekly health data verification #85</v>
+        <v>Dispatch summary of weekly health data [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E86" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F86" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating normal path (standard execution)</v>
       </c>
       <c r="G86" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H86" t="str">
         <v>Critical</v>
@@ -3433,16 +3433,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D87" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #86</v>
+        <v>Unlock application with FaceID / Fingerprint [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E87" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F87" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G87" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H87" t="str">
         <v>High</v>
@@ -3468,16 +3468,16 @@
         <v>2FA</v>
       </c>
       <c r="D88" t="str">
-        <v>Enforce extra layer of login security via token verification #87</v>
+        <v>Enforce extra layer of login security via token [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E88" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F88" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating security guard (special char injection)</v>
       </c>
       <c r="G88" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H88" t="str">
         <v>High</v>
@@ -3503,16 +3503,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D89" t="str">
-        <v>Verify full-screen logo brand rendering verification #88</v>
+        <v>Verify full-screen logo brand rendering [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E89" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F89" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G89" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H89" t="str">
         <v>High</v>
@@ -3538,16 +3538,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D90" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #89</v>
+        <v>Verify swipe gestures across onboarding layer [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E90" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F90" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G90" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H90" t="str">
         <v>High</v>
@@ -3573,16 +3573,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D91" t="str">
-        <v>Trigger push alert for medication times verification #90</v>
+        <v>Trigger push alert for medication times [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E91" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F91" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating normal path (standard execution)</v>
       </c>
       <c r="G91" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H91" t="str">
         <v>Critical</v>
@@ -3608,16 +3608,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D92" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #91</v>
+        <v>Trigger mobile alert for concerning symptoms [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E92" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F92" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G92" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H92" t="str">
         <v>High</v>
@@ -3643,16 +3643,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D93" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #92</v>
+        <v>Notify user of abnormal vital fluctuations [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E93" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F93" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G93" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H93" t="str">
         <v>High</v>
@@ -3678,16 +3678,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D94" t="str">
-        <v>Dispatch summary of weekly health data verification #93</v>
+        <v>Dispatch summary of weekly health data [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E94" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F94" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G94" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H94" t="str">
         <v>High</v>
@@ -3713,16 +3713,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D95" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #94</v>
+        <v>Unlock application with FaceID / Fingerprint [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E95" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F95" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G95" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H95" t="str">
         <v>High</v>
@@ -3748,16 +3748,16 @@
         <v>2FA</v>
       </c>
       <c r="D96" t="str">
-        <v>Enforce extra layer of login security via token verification #95</v>
+        <v>Enforce extra layer of login security via token [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E96" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F96" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating normal path (standard execution)</v>
       </c>
       <c r="G96" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H96" t="str">
         <v>Critical</v>
@@ -3783,16 +3783,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D97" t="str">
-        <v>Verify full-screen logo brand rendering verification #96</v>
+        <v>Verify full-screen logo brand rendering [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E97" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F97" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G97" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H97" t="str">
         <v>High</v>
@@ -3818,16 +3818,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D98" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #97</v>
+        <v>Verify swipe gestures across onboarding layer [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E98" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F98" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating security guard (special char injection)</v>
       </c>
       <c r="G98" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H98" t="str">
         <v>High</v>
@@ -3853,16 +3853,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D99" t="str">
-        <v>Trigger push alert for medication times verification #98</v>
+        <v>Trigger push alert for medication times [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E99" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F99" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G99" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H99" t="str">
         <v>High</v>
@@ -3888,16 +3888,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D100" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #99</v>
+        <v>Trigger mobile alert for concerning symptoms [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E100" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F100" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G100" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H100" t="str">
         <v>High</v>
@@ -3923,16 +3923,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D101" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #100</v>
+        <v>Notify user of abnormal vital fluctuations [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E101" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F101" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G101" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H101" t="str">
         <v>Critical</v>
@@ -3958,16 +3958,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D102" t="str">
-        <v>Dispatch summary of weekly health data verification #101</v>
+        <v>Dispatch summary of weekly health data [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E102" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F102" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G102" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H102" t="str">
         <v>High</v>
@@ -3993,16 +3993,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D103" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #102</v>
+        <v>Unlock application with FaceID / Fingerprint [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E103" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F103" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating security guard (special char injection)</v>
       </c>
       <c r="G103" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H103" t="str">
         <v>High</v>
@@ -4028,16 +4028,16 @@
         <v>2FA</v>
       </c>
       <c r="D104" t="str">
-        <v>Enforce extra layer of login security via token verification #103</v>
+        <v>Enforce extra layer of login security via token [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E104" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F104" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G104" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H104" t="str">
         <v>High</v>
@@ -4063,16 +4063,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D105" t="str">
-        <v>Verify full-screen logo brand rendering verification #104</v>
+        <v>Verify full-screen logo brand rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E105" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F105" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G105" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H105" t="str">
         <v>High</v>
@@ -4098,16 +4098,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D106" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #105</v>
+        <v>Verify swipe gestures across onboarding layer [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E106" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F106" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating normal path (standard execution)</v>
       </c>
       <c r="G106" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H106" t="str">
         <v>Critical</v>
@@ -4133,16 +4133,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D107" t="str">
-        <v>Trigger push alert for medication times verification #106</v>
+        <v>Trigger push alert for medication times [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E107" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F107" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G107" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H107" t="str">
         <v>High</v>
@@ -4168,16 +4168,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D108" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #107</v>
+        <v>Trigger mobile alert for concerning symptoms [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E108" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F108" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating security guard (special char injection)</v>
       </c>
       <c r="G108" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H108" t="str">
         <v>High</v>
@@ -4203,16 +4203,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D109" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #108</v>
+        <v>Notify user of abnormal vital fluctuations [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E109" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F109" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G109" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H109" t="str">
         <v>High</v>
@@ -4238,16 +4238,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D110" t="str">
-        <v>Dispatch summary of weekly health data verification #109</v>
+        <v>Dispatch summary of weekly health data [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E110" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F110" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G110" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H110" t="str">
         <v>High</v>
@@ -4273,16 +4273,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D111" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #110</v>
+        <v>Unlock application with FaceID / Fingerprint [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E111" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F111" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating normal path (standard execution)</v>
       </c>
       <c r="G111" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H111" t="str">
         <v>Critical</v>
@@ -4308,16 +4308,16 @@
         <v>2FA</v>
       </c>
       <c r="D112" t="str">
-        <v>Enforce extra layer of login security via token verification #111</v>
+        <v>Enforce extra layer of login security via token [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E112" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F112" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G112" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H112" t="str">
         <v>High</v>
@@ -4343,16 +4343,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D113" t="str">
-        <v>Verify full-screen logo brand rendering verification #112</v>
+        <v>Verify full-screen logo brand rendering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E113" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F113" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating security guard (special char injection)</v>
       </c>
       <c r="G113" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H113" t="str">
         <v>High</v>
@@ -4378,16 +4378,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D114" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #113</v>
+        <v>Verify swipe gestures across onboarding layer [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E114" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F114" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G114" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H114" t="str">
         <v>High</v>
@@ -4413,16 +4413,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D115" t="str">
-        <v>Trigger push alert for medication times verification #114</v>
+        <v>Trigger push alert for medication times [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E115" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F115" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G115" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H115" t="str">
         <v>High</v>
@@ -4448,16 +4448,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D116" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #115</v>
+        <v>Trigger mobile alert for concerning symptoms [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E116" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F116" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating normal path (standard execution)</v>
       </c>
       <c r="G116" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H116" t="str">
         <v>Critical</v>
@@ -4483,16 +4483,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D117" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #116</v>
+        <v>Notify user of abnormal vital fluctuations [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E117" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F117" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G117" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H117" t="str">
         <v>High</v>
@@ -4518,16 +4518,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D118" t="str">
-        <v>Dispatch summary of weekly health data verification #117</v>
+        <v>Dispatch summary of weekly health data [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E118" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F118" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating security guard (special char injection)</v>
       </c>
       <c r="G118" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H118" t="str">
         <v>High</v>
@@ -4553,16 +4553,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D119" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #118</v>
+        <v>Unlock application with FaceID / Fingerprint [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E119" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F119" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G119" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H119" t="str">
         <v>High</v>
@@ -4588,16 +4588,16 @@
         <v>2FA</v>
       </c>
       <c r="D120" t="str">
-        <v>Enforce extra layer of login security via token verification #119</v>
+        <v>Enforce extra layer of login security via token [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E120" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F120" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G120" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H120" t="str">
         <v>High</v>
@@ -4623,16 +4623,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D121" t="str">
-        <v>Verify full-screen logo brand rendering verification #120</v>
+        <v>Verify full-screen logo brand rendering [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E121" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F121" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating normal path (standard execution)</v>
       </c>
       <c r="G121" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H121" t="str">
         <v>Critical</v>
@@ -4658,16 +4658,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D122" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #121</v>
+        <v>Verify swipe gestures across onboarding layer [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E122" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F122" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G122" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H122" t="str">
         <v>High</v>
@@ -4693,16 +4693,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D123" t="str">
-        <v>Trigger push alert for medication times verification #122</v>
+        <v>Trigger push alert for medication times [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E123" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F123" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating security guard (special char injection)</v>
       </c>
       <c r="G123" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H123" t="str">
         <v>High</v>
@@ -4728,16 +4728,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D124" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #123</v>
+        <v>Trigger mobile alert for concerning symptoms [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E124" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F124" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G124" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H124" t="str">
         <v>High</v>
@@ -4763,16 +4763,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D125" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #124</v>
+        <v>Notify user of abnormal vital fluctuations [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E125" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F125" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G125" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H125" t="str">
         <v>High</v>
@@ -4798,16 +4798,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D126" t="str">
-        <v>Dispatch summary of weekly health data verification #125</v>
+        <v>Dispatch summary of weekly health data [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E126" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F126" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating normal path (standard execution)</v>
       </c>
       <c r="G126" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H126" t="str">
         <v>Critical</v>
@@ -4833,16 +4833,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D127" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #126</v>
+        <v>Unlock application with FaceID / Fingerprint [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E127" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F127" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G127" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H127" t="str">
         <v>High</v>
@@ -4868,16 +4868,16 @@
         <v>2FA</v>
       </c>
       <c r="D128" t="str">
-        <v>Enforce extra layer of login security via token verification #127</v>
+        <v>Enforce extra layer of login security via token [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E128" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F128" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating security guard (special char injection)</v>
       </c>
       <c r="G128" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H128" t="str">
         <v>High</v>
@@ -4903,16 +4903,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D129" t="str">
-        <v>Verify full-screen logo brand rendering verification #128</v>
+        <v>Verify full-screen logo brand rendering [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E129" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F129" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G129" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H129" t="str">
         <v>High</v>
@@ -4938,16 +4938,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D130" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #129</v>
+        <v>Verify swipe gestures across onboarding layer [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E130" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F130" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G130" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H130" t="str">
         <v>High</v>
@@ -4973,16 +4973,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D131" t="str">
-        <v>Trigger push alert for medication times verification #130</v>
+        <v>Trigger push alert for medication times [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E131" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F131" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating normal path (standard execution)</v>
       </c>
       <c r="G131" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H131" t="str">
         <v>Critical</v>
@@ -5008,16 +5008,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D132" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #131</v>
+        <v>Trigger mobile alert for concerning symptoms [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E132" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F132" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G132" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H132" t="str">
         <v>High</v>
@@ -5043,16 +5043,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D133" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #132</v>
+        <v>Notify user of abnormal vital fluctuations [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E133" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F133" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G133" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H133" t="str">
         <v>High</v>
@@ -5078,16 +5078,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D134" t="str">
-        <v>Dispatch summary of weekly health data verification #133</v>
+        <v>Dispatch summary of weekly health data [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E134" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F134" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G134" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H134" t="str">
         <v>High</v>
@@ -5113,16 +5113,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D135" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #134</v>
+        <v>Unlock application with FaceID / Fingerprint [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E135" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F135" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G135" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H135" t="str">
         <v>High</v>
@@ -5148,16 +5148,16 @@
         <v>2FA</v>
       </c>
       <c r="D136" t="str">
-        <v>Enforce extra layer of login security via token verification #135</v>
+        <v>Enforce extra layer of login security via token [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E136" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F136" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating normal path (standard execution)</v>
       </c>
       <c r="G136" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H136" t="str">
         <v>Critical</v>
@@ -5183,16 +5183,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D137" t="str">
-        <v>Verify full-screen logo brand rendering verification #136</v>
+        <v>Verify full-screen logo brand rendering [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E137" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F137" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G137" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H137" t="str">
         <v>High</v>
@@ -5218,16 +5218,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D138" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #137</v>
+        <v>Verify swipe gestures across onboarding layer [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E138" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F138" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating security guard (special char injection)</v>
       </c>
       <c r="G138" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H138" t="str">
         <v>High</v>
@@ -5253,16 +5253,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D139" t="str">
-        <v>Trigger push alert for medication times verification #138</v>
+        <v>Trigger push alert for medication times [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E139" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F139" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G139" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H139" t="str">
         <v>High</v>
@@ -5288,16 +5288,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D140" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #139</v>
+        <v>Trigger mobile alert for concerning symptoms [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E140" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F140" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G140" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H140" t="str">
         <v>High</v>
@@ -5323,16 +5323,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D141" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #140</v>
+        <v>Notify user of abnormal vital fluctuations [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E141" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F141" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G141" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H141" t="str">
         <v>Critical</v>
@@ -5358,16 +5358,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D142" t="str">
-        <v>Dispatch summary of weekly health data verification #141</v>
+        <v>Dispatch summary of weekly health data [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E142" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F142" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G142" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H142" t="str">
         <v>High</v>
@@ -5393,16 +5393,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D143" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #142</v>
+        <v>Unlock application with FaceID / Fingerprint [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E143" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F143" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating security guard (special char injection)</v>
       </c>
       <c r="G143" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H143" t="str">
         <v>High</v>
@@ -5428,16 +5428,16 @@
         <v>2FA</v>
       </c>
       <c r="D144" t="str">
-        <v>Enforce extra layer of login security via token verification #143</v>
+        <v>Enforce extra layer of login security via token [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E144" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F144" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G144" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H144" t="str">
         <v>High</v>
@@ -5463,16 +5463,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D145" t="str">
-        <v>Verify full-screen logo brand rendering verification #144</v>
+        <v>Verify full-screen logo brand rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E145" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F145" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G145" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H145" t="str">
         <v>High</v>
@@ -5498,16 +5498,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D146" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #145</v>
+        <v>Verify swipe gestures across onboarding layer [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E146" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F146" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating normal path (standard execution)</v>
       </c>
       <c r="G146" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H146" t="str">
         <v>Critical</v>
@@ -5533,16 +5533,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D147" t="str">
-        <v>Trigger push alert for medication times verification #146</v>
+        <v>Trigger push alert for medication times [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E147" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F147" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G147" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H147" t="str">
         <v>High</v>
@@ -5568,16 +5568,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D148" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #147</v>
+        <v>Trigger mobile alert for concerning symptoms [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E148" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F148" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating security guard (special char injection)</v>
       </c>
       <c r="G148" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H148" t="str">
         <v>High</v>
@@ -5603,16 +5603,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D149" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #148</v>
+        <v>Notify user of abnormal vital fluctuations [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E149" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F149" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G149" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H149" t="str">
         <v>High</v>
@@ -5638,16 +5638,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D150" t="str">
-        <v>Dispatch summary of weekly health data verification #149</v>
+        <v>Dispatch summary of weekly health data [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E150" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F150" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G150" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H150" t="str">
         <v>High</v>
@@ -5673,16 +5673,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D151" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #150</v>
+        <v>Unlock application with FaceID / Fingerprint [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E151" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F151" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating normal path (standard execution)</v>
       </c>
       <c r="G151" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H151" t="str">
         <v>Critical</v>
@@ -5708,16 +5708,16 @@
         <v>2FA</v>
       </c>
       <c r="D152" t="str">
-        <v>Enforce extra layer of login security via token verification #151</v>
+        <v>Enforce extra layer of login security via token [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E152" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F152" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G152" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H152" t="str">
         <v>High</v>
@@ -5743,16 +5743,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D153" t="str">
-        <v>Verify full-screen logo brand rendering verification #152</v>
+        <v>Verify full-screen logo brand rendering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E153" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F153" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating security guard (special char injection)</v>
       </c>
       <c r="G153" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H153" t="str">
         <v>High</v>
@@ -5778,16 +5778,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D154" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #153</v>
+        <v>Verify swipe gestures across onboarding layer [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E154" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F154" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G154" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H154" t="str">
         <v>High</v>
@@ -5813,16 +5813,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D155" t="str">
-        <v>Trigger push alert for medication times verification #154</v>
+        <v>Trigger push alert for medication times [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E155" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F155" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G155" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H155" t="str">
         <v>High</v>
@@ -5848,16 +5848,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D156" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #155</v>
+        <v>Trigger mobile alert for concerning symptoms [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E156" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F156" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating normal path (standard execution)</v>
       </c>
       <c r="G156" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H156" t="str">
         <v>Critical</v>
@@ -5883,16 +5883,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D157" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #156</v>
+        <v>Notify user of abnormal vital fluctuations [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E157" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F157" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G157" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H157" t="str">
         <v>High</v>
@@ -5918,16 +5918,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D158" t="str">
-        <v>Dispatch summary of weekly health data verification #157</v>
+        <v>Dispatch summary of weekly health data [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E158" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F158" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating security guard (special char injection)</v>
       </c>
       <c r="G158" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H158" t="str">
         <v>High</v>
@@ -5953,16 +5953,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D159" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #158</v>
+        <v>Unlock application with FaceID / Fingerprint [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E159" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F159" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G159" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H159" t="str">
         <v>High</v>
@@ -5988,16 +5988,16 @@
         <v>2FA</v>
       </c>
       <c r="D160" t="str">
-        <v>Enforce extra layer of login security via token verification #159</v>
+        <v>Enforce extra layer of login security via token [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E160" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F160" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G160" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H160" t="str">
         <v>High</v>
@@ -6023,16 +6023,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D161" t="str">
-        <v>Verify full-screen logo brand rendering verification #160</v>
+        <v>Verify full-screen logo brand rendering [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E161" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F161" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating normal path (standard execution)</v>
       </c>
       <c r="G161" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H161" t="str">
         <v>Critical</v>
@@ -6058,16 +6058,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D162" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #161</v>
+        <v>Verify swipe gestures across onboarding layer [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E162" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F162" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G162" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H162" t="str">
         <v>High</v>
@@ -6093,16 +6093,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D163" t="str">
-        <v>Trigger push alert for medication times verification #162</v>
+        <v>Trigger push alert for medication times [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E163" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F163" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating security guard (special char injection)</v>
       </c>
       <c r="G163" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H163" t="str">
         <v>High</v>
@@ -6128,16 +6128,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D164" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #163</v>
+        <v>Trigger mobile alert for concerning symptoms [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E164" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F164" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G164" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H164" t="str">
         <v>High</v>
@@ -6163,16 +6163,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D165" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #164</v>
+        <v>Notify user of abnormal vital fluctuations [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E165" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F165" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G165" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H165" t="str">
         <v>High</v>
@@ -6198,16 +6198,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D166" t="str">
-        <v>Dispatch summary of weekly health data verification #165</v>
+        <v>Dispatch summary of weekly health data [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E166" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F166" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating normal path (standard execution)</v>
       </c>
       <c r="G166" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H166" t="str">
         <v>Critical</v>
@@ -6233,16 +6233,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D167" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #166</v>
+        <v>Unlock application with FaceID / Fingerprint [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E167" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F167" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G167" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H167" t="str">
         <v>High</v>
@@ -6268,16 +6268,16 @@
         <v>2FA</v>
       </c>
       <c r="D168" t="str">
-        <v>Enforce extra layer of login security via token verification #167</v>
+        <v>Enforce extra layer of login security via token [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E168" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F168" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating security guard (special char injection)</v>
       </c>
       <c r="G168" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H168" t="str">
         <v>High</v>
@@ -6303,16 +6303,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D169" t="str">
-        <v>Verify full-screen logo brand rendering verification #168</v>
+        <v>Verify full-screen logo brand rendering [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E169" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F169" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G169" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H169" t="str">
         <v>High</v>
@@ -6338,16 +6338,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D170" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #169</v>
+        <v>Verify swipe gestures across onboarding layer [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E170" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F170" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G170" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H170" t="str">
         <v>High</v>
@@ -6373,16 +6373,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D171" t="str">
-        <v>Trigger push alert for medication times verification #170</v>
+        <v>Trigger push alert for medication times [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E171" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F171" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating normal path (standard execution)</v>
       </c>
       <c r="G171" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H171" t="str">
         <v>Critical</v>
@@ -6408,16 +6408,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D172" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #171</v>
+        <v>Trigger mobile alert for concerning symptoms [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E172" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F172" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G172" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H172" t="str">
         <v>High</v>
@@ -6443,16 +6443,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D173" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #172</v>
+        <v>Notify user of abnormal vital fluctuations [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E173" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F173" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G173" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H173" t="str">
         <v>High</v>
@@ -6478,16 +6478,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D174" t="str">
-        <v>Dispatch summary of weekly health data verification #173</v>
+        <v>Dispatch summary of weekly health data [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E174" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F174" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G174" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H174" t="str">
         <v>High</v>
@@ -6513,16 +6513,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D175" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #174</v>
+        <v>Unlock application with FaceID / Fingerprint [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E175" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F175" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G175" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H175" t="str">
         <v>High</v>
@@ -6548,16 +6548,16 @@
         <v>2FA</v>
       </c>
       <c r="D176" t="str">
-        <v>Enforce extra layer of login security via token verification #175</v>
+        <v>Enforce extra layer of login security via token [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E176" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F176" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating normal path (standard execution)</v>
       </c>
       <c r="G176" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H176" t="str">
         <v>Critical</v>
@@ -6583,16 +6583,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D177" t="str">
-        <v>Verify full-screen logo brand rendering verification #176</v>
+        <v>Verify full-screen logo brand rendering [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E177" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F177" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G177" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H177" t="str">
         <v>High</v>
@@ -6618,16 +6618,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D178" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #177</v>
+        <v>Verify swipe gestures across onboarding layer [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E178" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F178" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating security guard (special char injection)</v>
       </c>
       <c r="G178" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H178" t="str">
         <v>High</v>
@@ -6653,16 +6653,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D179" t="str">
-        <v>Trigger push alert for medication times verification #178</v>
+        <v>Trigger push alert for medication times [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E179" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F179" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G179" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H179" t="str">
         <v>High</v>
@@ -6688,16 +6688,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D180" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #179</v>
+        <v>Trigger mobile alert for concerning symptoms [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E180" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F180" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G180" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H180" t="str">
         <v>High</v>
@@ -6723,16 +6723,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D181" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #180</v>
+        <v>Notify user of abnormal vital fluctuations [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E181" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F181" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G181" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H181" t="str">
         <v>Critical</v>
@@ -6758,16 +6758,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D182" t="str">
-        <v>Dispatch summary of weekly health data verification #181</v>
+        <v>Dispatch summary of weekly health data [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E182" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F182" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G182" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H182" t="str">
         <v>High</v>
@@ -6793,16 +6793,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D183" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #182</v>
+        <v>Unlock application with FaceID / Fingerprint [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E183" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F183" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating security guard (special char injection)</v>
       </c>
       <c r="G183" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H183" t="str">
         <v>High</v>
@@ -6828,16 +6828,16 @@
         <v>2FA</v>
       </c>
       <c r="D184" t="str">
-        <v>Enforce extra layer of login security via token verification #183</v>
+        <v>Enforce extra layer of login security via token [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E184" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F184" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G184" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H184" t="str">
         <v>High</v>
@@ -6863,16 +6863,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D185" t="str">
-        <v>Verify full-screen logo brand rendering verification #184</v>
+        <v>Verify full-screen logo brand rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E185" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F185" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G185" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H185" t="str">
         <v>High</v>
@@ -6898,16 +6898,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D186" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #185</v>
+        <v>Verify swipe gestures across onboarding layer [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E186" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F186" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating normal path (standard execution)</v>
       </c>
       <c r="G186" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H186" t="str">
         <v>Critical</v>
@@ -6933,16 +6933,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D187" t="str">
-        <v>Trigger push alert for medication times verification #186</v>
+        <v>Trigger push alert for medication times [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E187" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F187" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G187" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H187" t="str">
         <v>High</v>
@@ -6968,16 +6968,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D188" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #187</v>
+        <v>Trigger mobile alert for concerning symptoms [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E188" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F188" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating security guard (special char injection)</v>
       </c>
       <c r="G188" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H188" t="str">
         <v>High</v>
@@ -7003,16 +7003,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D189" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #188</v>
+        <v>Notify user of abnormal vital fluctuations [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E189" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F189" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G189" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H189" t="str">
         <v>High</v>
@@ -7038,16 +7038,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D190" t="str">
-        <v>Dispatch summary of weekly health data verification #189</v>
+        <v>Dispatch summary of weekly health data [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E190" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F190" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G190" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H190" t="str">
         <v>High</v>
@@ -7073,16 +7073,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D191" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #190</v>
+        <v>Unlock application with FaceID / Fingerprint [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E191" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F191" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating normal path (standard execution)</v>
       </c>
       <c r="G191" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H191" t="str">
         <v>Critical</v>
@@ -7108,16 +7108,16 @@
         <v>2FA</v>
       </c>
       <c r="D192" t="str">
-        <v>Enforce extra layer of login security via token verification #191</v>
+        <v>Enforce extra layer of login security via token [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E192" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F192" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G192" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H192" t="str">
         <v>High</v>
@@ -7143,16 +7143,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D193" t="str">
-        <v>Verify full-screen logo brand rendering verification #192</v>
+        <v>Verify full-screen logo brand rendering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E193" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F193" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating security guard (special char injection)</v>
       </c>
       <c r="G193" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H193" t="str">
         <v>High</v>
@@ -7178,16 +7178,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D194" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #193</v>
+        <v>Verify swipe gestures across onboarding layer [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E194" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F194" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G194" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H194" t="str">
         <v>High</v>
@@ -7213,16 +7213,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D195" t="str">
-        <v>Trigger push alert for medication times verification #194</v>
+        <v>Trigger push alert for medication times [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E195" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F195" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G195" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H195" t="str">
         <v>High</v>
@@ -7248,16 +7248,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D196" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #195</v>
+        <v>Trigger mobile alert for concerning symptoms [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E196" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F196" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating normal path (standard execution)</v>
       </c>
       <c r="G196" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H196" t="str">
         <v>Critical</v>
@@ -7283,16 +7283,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D197" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #196</v>
+        <v>Notify user of abnormal vital fluctuations [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E197" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F197" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G197" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H197" t="str">
         <v>High</v>
@@ -7318,16 +7318,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D198" t="str">
-        <v>Dispatch summary of weekly health data verification #197</v>
+        <v>Dispatch summary of weekly health data [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E198" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F198" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating security guard (special char injection)</v>
       </c>
       <c r="G198" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H198" t="str">
         <v>High</v>
@@ -7353,16 +7353,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D199" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #198</v>
+        <v>Unlock application with FaceID / Fingerprint [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E199" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F199" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G199" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H199" t="str">
         <v>High</v>
@@ -7388,16 +7388,16 @@
         <v>2FA</v>
       </c>
       <c r="D200" t="str">
-        <v>Enforce extra layer of login security via token verification #199</v>
+        <v>Enforce extra layer of login security via token [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E200" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F200" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G200" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H200" t="str">
         <v>High</v>
@@ -7423,16 +7423,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D201" t="str">
-        <v>Verify full-screen logo brand rendering verification #200</v>
+        <v>Verify full-screen logo brand rendering [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E201" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F201" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating normal path (standard execution)</v>
       </c>
       <c r="G201" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H201" t="str">
         <v>Critical</v>
@@ -7458,16 +7458,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D202" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #201</v>
+        <v>Verify swipe gestures across onboarding layer [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E202" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F202" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G202" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H202" t="str">
         <v>High</v>
@@ -7493,16 +7493,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D203" t="str">
-        <v>Trigger push alert for medication times verification #202</v>
+        <v>Trigger push alert for medication times [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E203" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F203" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating security guard (special char injection)</v>
       </c>
       <c r="G203" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H203" t="str">
         <v>High</v>
@@ -7528,16 +7528,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D204" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #203</v>
+        <v>Trigger mobile alert for concerning symptoms [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E204" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F204" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G204" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H204" t="str">
         <v>High</v>
@@ -7563,16 +7563,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D205" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #204</v>
+        <v>Notify user of abnormal vital fluctuations [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E205" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F205" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G205" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H205" t="str">
         <v>High</v>
@@ -7598,16 +7598,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D206" t="str">
-        <v>Dispatch summary of weekly health data verification #205</v>
+        <v>Dispatch summary of weekly health data [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E206" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F206" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating normal path (standard execution)</v>
       </c>
       <c r="G206" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H206" t="str">
         <v>Critical</v>
@@ -7633,16 +7633,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D207" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #206</v>
+        <v>Unlock application with FaceID / Fingerprint [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E207" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F207" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G207" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H207" t="str">
         <v>High</v>
@@ -7668,16 +7668,16 @@
         <v>2FA</v>
       </c>
       <c r="D208" t="str">
-        <v>Enforce extra layer of login security via token verification #207</v>
+        <v>Enforce extra layer of login security via token [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E208" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F208" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating security guard (special char injection)</v>
       </c>
       <c r="G208" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H208" t="str">
         <v>High</v>
@@ -7703,16 +7703,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D209" t="str">
-        <v>Verify full-screen logo brand rendering verification #208</v>
+        <v>Verify full-screen logo brand rendering [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E209" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F209" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G209" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H209" t="str">
         <v>High</v>
@@ -7738,16 +7738,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D210" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #209</v>
+        <v>Verify swipe gestures across onboarding layer [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E210" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F210" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G210" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H210" t="str">
         <v>High</v>
@@ -7773,16 +7773,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D211" t="str">
-        <v>Trigger push alert for medication times verification #210</v>
+        <v>Trigger push alert for medication times [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E211" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F211" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating normal path (standard execution)</v>
       </c>
       <c r="G211" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H211" t="str">
         <v>Critical</v>
@@ -7808,16 +7808,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D212" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #211</v>
+        <v>Trigger mobile alert for concerning symptoms [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E212" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F212" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G212" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H212" t="str">
         <v>High</v>
@@ -7843,16 +7843,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D213" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #212</v>
+        <v>Notify user of abnormal vital fluctuations [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E213" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F213" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G213" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H213" t="str">
         <v>High</v>
@@ -7878,16 +7878,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D214" t="str">
-        <v>Dispatch summary of weekly health data verification #213</v>
+        <v>Dispatch summary of weekly health data [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E214" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F214" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G214" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H214" t="str">
         <v>High</v>
@@ -7913,16 +7913,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D215" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #214</v>
+        <v>Unlock application with FaceID / Fingerprint [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E215" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F215" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G215" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H215" t="str">
         <v>High</v>
@@ -7948,16 +7948,16 @@
         <v>2FA</v>
       </c>
       <c r="D216" t="str">
-        <v>Enforce extra layer of login security via token verification #215</v>
+        <v>Enforce extra layer of login security via token [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E216" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F216" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating normal path (standard execution)</v>
       </c>
       <c r="G216" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H216" t="str">
         <v>Critical</v>
@@ -7983,16 +7983,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D217" t="str">
-        <v>Verify full-screen logo brand rendering verification #216</v>
+        <v>Verify full-screen logo brand rendering [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E217" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F217" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G217" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H217" t="str">
         <v>High</v>
@@ -8018,16 +8018,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D218" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #217</v>
+        <v>Verify swipe gestures across onboarding layer [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E218" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F218" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating security guard (special char injection)</v>
       </c>
       <c r="G218" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H218" t="str">
         <v>High</v>
@@ -8053,16 +8053,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D219" t="str">
-        <v>Trigger push alert for medication times verification #218</v>
+        <v>Trigger push alert for medication times [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E219" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F219" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G219" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H219" t="str">
         <v>High</v>
@@ -8088,16 +8088,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D220" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #219</v>
+        <v>Trigger mobile alert for concerning symptoms [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E220" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F220" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G220" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H220" t="str">
         <v>High</v>
@@ -8123,16 +8123,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D221" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #220</v>
+        <v>Notify user of abnormal vital fluctuations [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E221" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F221" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G221" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H221" t="str">
         <v>Critical</v>
@@ -8158,16 +8158,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D222" t="str">
-        <v>Dispatch summary of weekly health data verification #221</v>
+        <v>Dispatch summary of weekly health data [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E222" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F222" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G222" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H222" t="str">
         <v>High</v>
@@ -8193,16 +8193,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D223" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #222</v>
+        <v>Unlock application with FaceID / Fingerprint [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E223" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F223" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating security guard (special char injection)</v>
       </c>
       <c r="G223" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H223" t="str">
         <v>High</v>
@@ -8228,16 +8228,16 @@
         <v>2FA</v>
       </c>
       <c r="D224" t="str">
-        <v>Enforce extra layer of login security via token verification #223</v>
+        <v>Enforce extra layer of login security via token [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E224" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F224" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G224" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H224" t="str">
         <v>High</v>
@@ -8263,16 +8263,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D225" t="str">
-        <v>Verify full-screen logo brand rendering verification #224</v>
+        <v>Verify full-screen logo brand rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E225" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F225" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G225" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H225" t="str">
         <v>High</v>
@@ -8298,16 +8298,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D226" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #225</v>
+        <v>Verify swipe gestures across onboarding layer [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E226" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F226" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating normal path (standard execution)</v>
       </c>
       <c r="G226" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H226" t="str">
         <v>Critical</v>
@@ -8333,16 +8333,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D227" t="str">
-        <v>Trigger push alert for medication times verification #226</v>
+        <v>Trigger push alert for medication times [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E227" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F227" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G227" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H227" t="str">
         <v>High</v>
@@ -8368,16 +8368,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D228" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #227</v>
+        <v>Trigger mobile alert for concerning symptoms [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E228" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F228" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating security guard (special char injection)</v>
       </c>
       <c r="G228" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H228" t="str">
         <v>High</v>
@@ -8403,16 +8403,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D229" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #228</v>
+        <v>Notify user of abnormal vital fluctuations [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E229" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F229" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G229" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H229" t="str">
         <v>High</v>
@@ -8438,16 +8438,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D230" t="str">
-        <v>Dispatch summary of weekly health data verification #229</v>
+        <v>Dispatch summary of weekly health data [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E230" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F230" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G230" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H230" t="str">
         <v>High</v>
@@ -8473,16 +8473,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D231" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #230</v>
+        <v>Unlock application with FaceID / Fingerprint [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E231" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F231" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating normal path (standard execution)</v>
       </c>
       <c r="G231" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H231" t="str">
         <v>Critical</v>
@@ -8508,16 +8508,16 @@
         <v>2FA</v>
       </c>
       <c r="D232" t="str">
-        <v>Enforce extra layer of login security via token verification #231</v>
+        <v>Enforce extra layer of login security via token [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E232" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F232" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G232" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H232" t="str">
         <v>High</v>
@@ -8543,16 +8543,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D233" t="str">
-        <v>Verify full-screen logo brand rendering verification #232</v>
+        <v>Verify full-screen logo brand rendering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E233" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F233" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating security guard (special char injection)</v>
       </c>
       <c r="G233" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H233" t="str">
         <v>High</v>
@@ -8578,16 +8578,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D234" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #233</v>
+        <v>Verify swipe gestures across onboarding layer [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E234" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F234" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G234" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H234" t="str">
         <v>High</v>
@@ -8613,16 +8613,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D235" t="str">
-        <v>Trigger push alert for medication times verification #234</v>
+        <v>Trigger push alert for medication times [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E235" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F235" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G235" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H235" t="str">
         <v>High</v>
@@ -8648,16 +8648,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D236" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #235</v>
+        <v>Trigger mobile alert for concerning symptoms [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E236" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F236" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating normal path (standard execution)</v>
       </c>
       <c r="G236" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H236" t="str">
         <v>Critical</v>
@@ -8683,16 +8683,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D237" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #236</v>
+        <v>Notify user of abnormal vital fluctuations [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E237" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F237" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G237" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H237" t="str">
         <v>High</v>
@@ -8718,16 +8718,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D238" t="str">
-        <v>Dispatch summary of weekly health data verification #237</v>
+        <v>Dispatch summary of weekly health data [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E238" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F238" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating security guard (special char injection)</v>
       </c>
       <c r="G238" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H238" t="str">
         <v>High</v>
@@ -8753,16 +8753,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D239" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #238</v>
+        <v>Unlock application with FaceID / Fingerprint [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E239" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F239" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G239" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H239" t="str">
         <v>High</v>
@@ -8788,16 +8788,16 @@
         <v>2FA</v>
       </c>
       <c r="D240" t="str">
-        <v>Enforce extra layer of login security via token verification #239</v>
+        <v>Enforce extra layer of login security via token [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E240" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F240" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G240" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H240" t="str">
         <v>High</v>
@@ -8823,16 +8823,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D241" t="str">
-        <v>Verify full-screen logo brand rendering verification #240</v>
+        <v>Verify full-screen logo brand rendering [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E241" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F241" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating normal path (standard execution)</v>
       </c>
       <c r="G241" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H241" t="str">
         <v>Critical</v>
@@ -8858,16 +8858,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D242" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #241</v>
+        <v>Verify swipe gestures across onboarding layer [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E242" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F242" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G242" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H242" t="str">
         <v>High</v>
@@ -8893,16 +8893,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D243" t="str">
-        <v>Trigger push alert for medication times verification #242</v>
+        <v>Trigger push alert for medication times [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E243" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F243" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating security guard (special char injection)</v>
       </c>
       <c r="G243" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H243" t="str">
         <v>High</v>
@@ -8928,16 +8928,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D244" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #243</v>
+        <v>Trigger mobile alert for concerning symptoms [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E244" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F244" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G244" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H244" t="str">
         <v>High</v>
@@ -8963,16 +8963,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D245" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #244</v>
+        <v>Notify user of abnormal vital fluctuations [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E245" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F245" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G245" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H245" t="str">
         <v>High</v>
@@ -8998,16 +8998,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D246" t="str">
-        <v>Dispatch summary of weekly health data verification #245</v>
+        <v>Dispatch summary of weekly health data [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E246" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F246" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating normal path (standard execution)</v>
       </c>
       <c r="G246" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H246" t="str">
         <v>Critical</v>
@@ -9033,16 +9033,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D247" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #246</v>
+        <v>Unlock application with FaceID / Fingerprint [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E247" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F247" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G247" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H247" t="str">
         <v>High</v>
@@ -9068,16 +9068,16 @@
         <v>2FA</v>
       </c>
       <c r="D248" t="str">
-        <v>Enforce extra layer of login security via token verification #247</v>
+        <v>Enforce extra layer of login security via token [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E248" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F248" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating security guard (special char injection)</v>
       </c>
       <c r="G248" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H248" t="str">
         <v>High</v>
@@ -9103,16 +9103,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D249" t="str">
-        <v>Verify full-screen logo brand rendering verification #248</v>
+        <v>Verify full-screen logo brand rendering [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E249" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F249" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G249" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H249" t="str">
         <v>High</v>
@@ -9138,16 +9138,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D250" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #249</v>
+        <v>Verify swipe gestures across onboarding layer [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E250" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F250" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G250" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H250" t="str">
         <v>High</v>
@@ -9173,16 +9173,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D251" t="str">
-        <v>Trigger push alert for medication times verification #250</v>
+        <v>Trigger push alert for medication times [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E251" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F251" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating normal path (standard execution)</v>
       </c>
       <c r="G251" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H251" t="str">
         <v>Critical</v>
@@ -9208,16 +9208,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D252" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #251</v>
+        <v>Trigger mobile alert for concerning symptoms [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E252" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F252" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G252" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H252" t="str">
         <v>High</v>
@@ -9243,16 +9243,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D253" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #252</v>
+        <v>Notify user of abnormal vital fluctuations [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E253" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F253" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G253" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H253" t="str">
         <v>High</v>
@@ -9278,16 +9278,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D254" t="str">
-        <v>Dispatch summary of weekly health data verification #253</v>
+        <v>Dispatch summary of weekly health data [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E254" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F254" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G254" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H254" t="str">
         <v>High</v>
@@ -9313,16 +9313,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D255" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #254</v>
+        <v>Unlock application with FaceID / Fingerprint [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E255" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F255" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G255" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H255" t="str">
         <v>High</v>
@@ -9348,16 +9348,16 @@
         <v>2FA</v>
       </c>
       <c r="D256" t="str">
-        <v>Enforce extra layer of login security via token verification #255</v>
+        <v>Enforce extra layer of login security via token [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E256" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F256" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating normal path (standard execution)</v>
       </c>
       <c r="G256" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H256" t="str">
         <v>Critical</v>
@@ -9383,16 +9383,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D257" t="str">
-        <v>Verify full-screen logo brand rendering verification #256</v>
+        <v>Verify full-screen logo brand rendering [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E257" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F257" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G257" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H257" t="str">
         <v>High</v>
@@ -9418,16 +9418,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D258" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #257</v>
+        <v>Verify swipe gestures across onboarding layer [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E258" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F258" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating security guard (special char injection)</v>
       </c>
       <c r="G258" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H258" t="str">
         <v>High</v>
@@ -9453,16 +9453,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D259" t="str">
-        <v>Trigger push alert for medication times verification #258</v>
+        <v>Trigger push alert for medication times [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E259" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F259" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G259" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H259" t="str">
         <v>High</v>
@@ -9488,16 +9488,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D260" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #259</v>
+        <v>Trigger mobile alert for concerning symptoms [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E260" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F260" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G260" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H260" t="str">
         <v>High</v>
@@ -9523,16 +9523,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D261" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #260</v>
+        <v>Notify user of abnormal vital fluctuations [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E261" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F261" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G261" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H261" t="str">
         <v>Critical</v>
@@ -9558,16 +9558,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D262" t="str">
-        <v>Dispatch summary of weekly health data verification #261</v>
+        <v>Dispatch summary of weekly health data [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E262" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F262" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G262" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H262" t="str">
         <v>High</v>
@@ -9593,16 +9593,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D263" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #262</v>
+        <v>Unlock application with FaceID / Fingerprint [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E263" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F263" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating security guard (special char injection)</v>
       </c>
       <c r="G263" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H263" t="str">
         <v>High</v>
@@ -9628,16 +9628,16 @@
         <v>2FA</v>
       </c>
       <c r="D264" t="str">
-        <v>Enforce extra layer of login security via token verification #263</v>
+        <v>Enforce extra layer of login security via token [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E264" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F264" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G264" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H264" t="str">
         <v>High</v>
@@ -9663,16 +9663,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D265" t="str">
-        <v>Verify full-screen logo brand rendering verification #264</v>
+        <v>Verify full-screen logo brand rendering [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E265" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F265" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G265" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H265" t="str">
         <v>High</v>
@@ -9698,16 +9698,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D266" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #265</v>
+        <v>Verify swipe gestures across onboarding layer [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E266" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F266" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating normal path (standard execution)</v>
       </c>
       <c r="G266" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H266" t="str">
         <v>Critical</v>
@@ -9733,16 +9733,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D267" t="str">
-        <v>Trigger push alert for medication times verification #266</v>
+        <v>Trigger push alert for medication times [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E267" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F267" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G267" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H267" t="str">
         <v>High</v>
@@ -9768,16 +9768,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D268" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #267</v>
+        <v>Trigger mobile alert for concerning symptoms [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E268" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F268" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating security guard (special char injection)</v>
       </c>
       <c r="G268" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H268" t="str">
         <v>High</v>
@@ -9803,16 +9803,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D269" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #268</v>
+        <v>Notify user of abnormal vital fluctuations [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E269" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F269" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G269" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H269" t="str">
         <v>High</v>
@@ -9838,16 +9838,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D270" t="str">
-        <v>Dispatch summary of weekly health data verification #269</v>
+        <v>Dispatch summary of weekly health data [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E270" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F270" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G270" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H270" t="str">
         <v>High</v>
@@ -9873,16 +9873,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D271" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #270</v>
+        <v>Unlock application with FaceID / Fingerprint [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E271" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F271" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating normal path (standard execution)</v>
       </c>
       <c r="G271" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H271" t="str">
         <v>Critical</v>
@@ -9908,16 +9908,16 @@
         <v>2FA</v>
       </c>
       <c r="D272" t="str">
-        <v>Enforce extra layer of login security via token verification #271</v>
+        <v>Enforce extra layer of login security via token [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E272" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F272" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G272" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H272" t="str">
         <v>High</v>
@@ -9943,16 +9943,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D273" t="str">
-        <v>Verify full-screen logo brand rendering verification #272</v>
+        <v>Verify full-screen logo brand rendering [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E273" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F273" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating security guard (special char injection)</v>
       </c>
       <c r="G273" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H273" t="str">
         <v>High</v>
@@ -9978,16 +9978,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D274" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #273</v>
+        <v>Verify swipe gestures across onboarding layer [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E274" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F274" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G274" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H274" t="str">
         <v>High</v>
@@ -10013,16 +10013,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D275" t="str">
-        <v>Trigger push alert for medication times verification #274</v>
+        <v>Trigger push alert for medication times [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E275" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F275" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G275" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H275" t="str">
         <v>High</v>
@@ -10048,16 +10048,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D276" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #275</v>
+        <v>Trigger mobile alert for concerning symptoms [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E276" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F276" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating normal path (standard execution)</v>
       </c>
       <c r="G276" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H276" t="str">
         <v>Critical</v>
@@ -10083,16 +10083,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D277" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #276</v>
+        <v>Notify user of abnormal vital fluctuations [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E277" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F277" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G277" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H277" t="str">
         <v>High</v>
@@ -10118,16 +10118,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D278" t="str">
-        <v>Dispatch summary of weekly health data verification #277</v>
+        <v>Dispatch summary of weekly health data [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E278" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F278" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating security guard (special char injection)</v>
       </c>
       <c r="G278" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H278" t="str">
         <v>High</v>
@@ -10153,16 +10153,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D279" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #278</v>
+        <v>Unlock application with FaceID / Fingerprint [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E279" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F279" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G279" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H279" t="str">
         <v>High</v>
@@ -10188,16 +10188,16 @@
         <v>2FA</v>
       </c>
       <c r="D280" t="str">
-        <v>Enforce extra layer of login security via token verification #279</v>
+        <v>Enforce extra layer of login security via token [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E280" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F280" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G280" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H280" t="str">
         <v>High</v>
@@ -10223,16 +10223,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D281" t="str">
-        <v>Verify full-screen logo brand rendering verification #280</v>
+        <v>Verify full-screen logo brand rendering [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E281" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F281" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating normal path (standard execution)</v>
       </c>
       <c r="G281" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H281" t="str">
         <v>Critical</v>
@@ -10258,16 +10258,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D282" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #281</v>
+        <v>Verify swipe gestures across onboarding layer [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E282" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F282" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G282" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H282" t="str">
         <v>High</v>
@@ -10293,16 +10293,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D283" t="str">
-        <v>Trigger push alert for medication times verification #282</v>
+        <v>Trigger push alert for medication times [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E283" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F283" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating security guard (special char injection)</v>
       </c>
       <c r="G283" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H283" t="str">
         <v>High</v>
@@ -10328,16 +10328,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D284" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #283</v>
+        <v>Trigger mobile alert for concerning symptoms [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E284" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F284" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G284" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H284" t="str">
         <v>High</v>
@@ -10363,16 +10363,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D285" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #284</v>
+        <v>Notify user of abnormal vital fluctuations [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E285" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F285" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G285" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H285" t="str">
         <v>High</v>
@@ -10398,16 +10398,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D286" t="str">
-        <v>Dispatch summary of weekly health data verification #285</v>
+        <v>Dispatch summary of weekly health data [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E286" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F286" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating normal path (standard execution)</v>
       </c>
       <c r="G286" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H286" t="str">
         <v>Critical</v>
@@ -10433,16 +10433,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D287" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #286</v>
+        <v>Unlock application with FaceID / Fingerprint [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E287" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F287" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G287" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H287" t="str">
         <v>High</v>
@@ -10468,16 +10468,16 @@
         <v>2FA</v>
       </c>
       <c r="D288" t="str">
-        <v>Enforce extra layer of login security via token verification #287</v>
+        <v>Enforce extra layer of login security via token [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E288" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F288" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating security guard (special char injection)</v>
       </c>
       <c r="G288" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H288" t="str">
         <v>High</v>
@@ -10503,16 +10503,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D289" t="str">
-        <v>Verify full-screen logo brand rendering verification #288</v>
+        <v>Verify full-screen logo brand rendering [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E289" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F289" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G289" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H289" t="str">
         <v>High</v>
@@ -10538,16 +10538,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D290" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #289</v>
+        <v>Verify swipe gestures across onboarding layer [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E290" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F290" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G290" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H290" t="str">
         <v>High</v>
@@ -10573,16 +10573,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D291" t="str">
-        <v>Trigger push alert for medication times verification #290</v>
+        <v>Trigger push alert for medication times [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E291" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F291" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating normal path (standard execution)</v>
       </c>
       <c r="G291" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H291" t="str">
         <v>Critical</v>
@@ -10608,16 +10608,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D292" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #291</v>
+        <v>Trigger mobile alert for concerning symptoms [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E292" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F292" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G292" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H292" t="str">
         <v>High</v>
@@ -10643,16 +10643,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D293" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #292</v>
+        <v>Notify user of abnormal vital fluctuations [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E293" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F293" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G293" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H293" t="str">
         <v>High</v>
@@ -10678,16 +10678,16 @@
         <v>Weekly Reports</v>
       </c>
       <c r="D294" t="str">
-        <v>Dispatch summary of weekly health data verification #293</v>
+        <v>Dispatch summary of weekly health data [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E294" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F294" t="str">
-        <v>Navigate to Push Notifications and perform Weekly Reports action</v>
+        <v>Execute Weekly Reports action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G294" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H294" t="str">
         <v>High</v>
@@ -10713,16 +10713,16 @@
         <v>Biometric Auth</v>
       </c>
       <c r="D295" t="str">
-        <v>Unlock application with FaceID / Fingerprint verification #294</v>
+        <v>Unlock application with FaceID / Fingerprint [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E295" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F295" t="str">
-        <v>Navigate to Privacy Centre and perform Biometric Auth action</v>
+        <v>Execute Biometric Auth action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G295" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H295" t="str">
         <v>High</v>
@@ -10748,16 +10748,16 @@
         <v>2FA</v>
       </c>
       <c r="D296" t="str">
-        <v>Enforce extra layer of login security via token verification #295</v>
+        <v>Enforce extra layer of login security via token [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E296" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F296" t="str">
-        <v>Navigate to Privacy Centre and perform 2FA action</v>
+        <v>Execute 2FA action while simulating normal path (standard execution)</v>
       </c>
       <c r="G296" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H296" t="str">
         <v>Critical</v>
@@ -10783,16 +10783,16 @@
         <v>Splash Screen</v>
       </c>
       <c r="D297" t="str">
-        <v>Verify full-screen logo brand rendering verification #296</v>
+        <v>Verify full-screen logo brand rendering [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E297" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F297" t="str">
-        <v>Navigate to App Initialization and perform Splash Screen action</v>
+        <v>Execute Splash Screen action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G297" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H297" t="str">
         <v>High</v>
@@ -10818,16 +10818,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D298" t="str">
-        <v>Verify swipe gestures across onboarding layer verification #297</v>
+        <v>Verify swipe gestures across onboarding layer [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E298" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F298" t="str">
-        <v>Navigate to App Initialization and perform Onboarding action</v>
+        <v>Execute Onboarding action while simulating security guard (special char injection)</v>
       </c>
       <c r="G298" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H298" t="str">
         <v>High</v>
@@ -10853,16 +10853,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D299" t="str">
-        <v>Trigger push alert for medication times verification #298</v>
+        <v>Trigger push alert for medication times [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E299" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F299" t="str">
-        <v>Navigate to Push Notifications and perform Medication Reminders action</v>
+        <v>Execute Medication Reminders action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G299" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H299" t="str">
         <v>High</v>
@@ -10888,16 +10888,16 @@
         <v>Symptom Alerts</v>
       </c>
       <c r="D300" t="str">
-        <v>Trigger mobile alert for concerning symptoms verification #299</v>
+        <v>Trigger mobile alert for concerning symptoms [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E300" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F300" t="str">
-        <v>Navigate to Push Notifications and perform Symptom Alerts action</v>
+        <v>Execute Symptom Alerts action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G300" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H300" t="str">
         <v>High</v>
@@ -10923,16 +10923,16 @@
         <v>Health Metrics</v>
       </c>
       <c r="D301" t="str">
-        <v>Notify user of abnormal vital fluctuations verification #300</v>
+        <v>Notify user of abnormal vital fluctuations [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E301" t="str">
         <v>App running on Android Native</v>
       </c>
       <c r="F301" t="str">
-        <v>Navigate to Push Notifications and perform Health Metrics action</v>
+        <v>Execute Health Metrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G301" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H301" t="str">
         <v>Critical</v>

--- a/e2e_tests_suite/Report_02_Appium.xlsx
+++ b/e2e_tests_suite/Report_02_Appium.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K301"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -458,16 +458,16 @@
         <v>Native Android Bootstrap</v>
       </c>
       <c r="D2" t="str">
-        <v>Verify Full-screen LifeMatrix logo render on Android device viewport</v>
+        <v>Validate Full-screen LifeMatrix logo render on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E2" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F2" t="str">
-        <v>Trigger native mobile interaction 'Full-screen LifeMatrix logo render' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Full-screen LifeMatrix logo render' and record Kotlin bridge event log</v>
       </c>
       <c r="G2" t="str">
-        <v>Android UI renders seamlessly, 'Full-screen LifeMatrix logo render' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Full-screen LifeMatrix logo render' with zero crash logs</v>
       </c>
       <c r="H2" t="str">
         <v>Medium</v>
@@ -493,16 +493,16 @@
         <v>Native Android Bootstrap</v>
       </c>
       <c r="D3" t="str">
-        <v>Verify Splash screen auto-dismiss within 2s on Android device viewport</v>
+        <v>Validate Splash screen auto-dismiss within 2s on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E3" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F3" t="str">
-        <v>Trigger native mobile interaction 'Splash screen auto-dismiss within 2s' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Splash screen auto-dismiss within 2s' and record Kotlin bridge event log</v>
       </c>
       <c r="G3" t="str">
-        <v>Android UI renders seamlessly, 'Splash screen auto-dismiss within 2s' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Splash screen auto-dismiss within 2s' with zero crash logs</v>
       </c>
       <c r="H3" t="str">
         <v>High</v>
@@ -528,16 +528,16 @@
         <v>Native Android Bootstrap</v>
       </c>
       <c r="D4" t="str">
-        <v>Verify Android hardware status bar padding on Android device viewport</v>
+        <v>Validate Android hardware status bar padding on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E4" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F4" t="str">
-        <v>Trigger native mobile interaction 'Android hardware status bar padding' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Android hardware status bar padding' and record Kotlin bridge event log</v>
       </c>
       <c r="G4" t="str">
-        <v>Android UI renders seamlessly, 'Android hardware status bar padding' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Android hardware status bar padding' with zero crash logs</v>
       </c>
       <c r="H4" t="str">
         <v>Medium</v>
@@ -563,16 +563,16 @@
         <v>Native Android Bootstrap</v>
       </c>
       <c r="D5" t="str">
-        <v>Verify Portrait orientation lock enforcement on Android device viewport</v>
+        <v>Validate Portrait orientation lock enforcement on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E5" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F5" t="str">
-        <v>Trigger native mobile interaction 'Portrait orientation lock enforcement' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Portrait orientation lock enforcement' and record Kotlin bridge event log</v>
       </c>
       <c r="G5" t="str">
-        <v>Android UI renders seamlessly, 'Portrait orientation lock enforcement' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Portrait orientation lock enforcement' with zero crash logs</v>
       </c>
       <c r="H5" t="str">
         <v>High</v>
@@ -598,16 +598,16 @@
         <v>Native Android Bootstrap</v>
       </c>
       <c r="D6" t="str">
-        <v>Verify Native splash fade-out animation on Android device viewport</v>
+        <v>Validate Native splash fade-out animation on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E6" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F6" t="str">
-        <v>Trigger native mobile interaction 'Native splash fade-out animation' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Native splash fade-out animation' and record Kotlin bridge event log</v>
       </c>
       <c r="G6" t="str">
-        <v>Android UI renders seamlessly, 'Native splash fade-out animation' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Native splash fade-out animation' with zero crash logs</v>
       </c>
       <c r="H6" t="str">
         <v>Critical</v>
@@ -633,16 +633,16 @@
         <v>Native Android Bootstrap</v>
       </c>
       <c r="D7" t="str">
-        <v>Verify First-time install routing on Android device viewport</v>
+        <v>Validate First-time install routing on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E7" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F7" t="str">
-        <v>Trigger native mobile interaction 'First-time install routing' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'First-time install routing' and record Kotlin bridge event log</v>
       </c>
       <c r="G7" t="str">
-        <v>Android UI renders seamlessly, 'First-time install routing' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'First-time install routing' with zero crash logs</v>
       </c>
       <c r="H7" t="str">
         <v>High</v>
@@ -668,16 +668,16 @@
         <v>Native Android Bootstrap</v>
       </c>
       <c r="D8" t="str">
-        <v>Verify Existing session token check on Android device viewport</v>
+        <v>Validate Existing session token check on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E8" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F8" t="str">
-        <v>Trigger native mobile interaction 'Existing session token check' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Existing session token check' and record Kotlin bridge event log</v>
       </c>
       <c r="G8" t="str">
-        <v>Android UI renders seamlessly, 'Existing session token check' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Existing session token check' with zero crash logs</v>
       </c>
       <c r="H8" t="str">
         <v>Medium</v>
@@ -703,16 +703,16 @@
         <v>Native Android Bootstrap</v>
       </c>
       <c r="D9" t="str">
-        <v>Verify Device screen DPI scaling on Android device viewport</v>
+        <v>Validate Device screen DPI scaling on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E9" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F9" t="str">
-        <v>Trigger native mobile interaction 'Device screen DPI scaling' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Device screen DPI scaling' and record Kotlin bridge event log</v>
       </c>
       <c r="G9" t="str">
-        <v>Android UI renders seamlessly, 'Device screen DPI scaling' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Device screen DPI scaling' with zero crash logs</v>
       </c>
       <c r="H9" t="str">
         <v>High</v>
@@ -738,16 +738,16 @@
         <v>Native Android Bootstrap</v>
       </c>
       <c r="D10" t="str">
-        <v>Verify DarkMode splash theme adaptation on Android device viewport</v>
+        <v>Validate DarkMode splash theme adaptation on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E10" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F10" t="str">
-        <v>Trigger native mobile interaction 'DarkMode splash theme adaptation' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'DarkMode splash theme adaptation' and record Kotlin bridge event log</v>
       </c>
       <c r="G10" t="str">
-        <v>Android UI renders seamlessly, 'DarkMode splash theme adaptation' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'DarkMode splash theme adaptation' with zero crash logs</v>
       </c>
       <c r="H10" t="str">
         <v>Medium</v>
@@ -773,16 +773,16 @@
         <v>Native Android Bootstrap</v>
       </c>
       <c r="D11" t="str">
-        <v>Verify App icon launch integrity on Android device viewport</v>
+        <v>Validate App icon launch integrity on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E11" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F11" t="str">
-        <v>Trigger native mobile interaction 'App icon launch integrity' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'App icon launch integrity' and record Kotlin bridge event log</v>
       </c>
       <c r="G11" t="str">
-        <v>Android UI renders seamlessly, 'App icon launch integrity' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'App icon launch integrity' with zero crash logs</v>
       </c>
       <c r="H11" t="str">
         <v>Critical</v>
@@ -808,16 +808,16 @@
         <v>Interactive Carousel</v>
       </c>
       <c r="D12" t="str">
-        <v>Verify Slide 1 Welcome banner display on Android device viewport</v>
+        <v>Validate Slide 1 Welcome banner display on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E12" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F12" t="str">
-        <v>Trigger native mobile interaction 'Slide 1 Welcome banner display' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Slide 1 Welcome banner display' and record Kotlin bridge event log</v>
       </c>
       <c r="G12" t="str">
-        <v>Android UI renders seamlessly, 'Slide 1 Welcome banner display' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Slide 1 Welcome banner display' with zero crash logs</v>
       </c>
       <c r="H12" t="str">
         <v>Medium</v>
@@ -843,16 +843,16 @@
         <v>Interactive Carousel</v>
       </c>
       <c r="D13" t="str">
-        <v>Verify Slide 2 AI Diagnostics intro on Android device viewport</v>
+        <v>Validate Slide 2 AI Diagnostics intro on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E13" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F13" t="str">
-        <v>Trigger native mobile interaction 'Slide 2 AI Diagnostics intro' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Slide 2 AI Diagnostics intro' and record Kotlin bridge event log</v>
       </c>
       <c r="G13" t="str">
-        <v>Android UI renders seamlessly, 'Slide 2 AI Diagnostics intro' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Slide 2 AI Diagnostics intro' with zero crash logs</v>
       </c>
       <c r="H13" t="str">
         <v>High</v>
@@ -878,16 +878,16 @@
         <v>Interactive Carousel</v>
       </c>
       <c r="D14" t="str">
-        <v>Verify Slide 3 Vitals Tracking overview on Android device viewport</v>
+        <v>Validate Slide 3 Vitals Tracking overview on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E14" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F14" t="str">
-        <v>Trigger native mobile interaction 'Slide 3 Vitals Tracking overview' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Slide 3 Vitals Tracking overview' and record Kotlin bridge event log</v>
       </c>
       <c r="G14" t="str">
-        <v>Android UI renders seamlessly, 'Slide 3 Vitals Tracking overview' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Slide 3 Vitals Tracking overview' with zero crash logs</v>
       </c>
       <c r="H14" t="str">
         <v>Medium</v>
@@ -913,16 +913,16 @@
         <v>Interactive Carousel</v>
       </c>
       <c r="D15" t="str">
-        <v>Verify Swipe left gesture to next slide on Android device viewport</v>
+        <v>Validate Swipe left gesture to next slide on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E15" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F15" t="str">
-        <v>Trigger native mobile interaction 'Swipe left gesture to next slide' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Swipe left gesture to next slide' and record Kotlin bridge event log</v>
       </c>
       <c r="G15" t="str">
-        <v>Android UI renders seamlessly, 'Swipe left gesture to next slide' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Swipe left gesture to next slide' with zero crash logs</v>
       </c>
       <c r="H15" t="str">
         <v>High</v>
@@ -948,16 +948,16 @@
         <v>Interactive Carousel</v>
       </c>
       <c r="D16" t="str">
-        <v>Verify Swipe right gesture to prev slide on Android device viewport</v>
+        <v>Validate Swipe right gesture to prev slide on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E16" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F16" t="str">
-        <v>Trigger native mobile interaction 'Swipe right gesture to prev slide' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Swipe right gesture to prev slide' and record Kotlin bridge event log</v>
       </c>
       <c r="G16" t="str">
-        <v>Android UI renders seamlessly, 'Swipe right gesture to prev slide' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Swipe right gesture to prev slide' with zero crash logs</v>
       </c>
       <c r="H16" t="str">
         <v>Critical</v>
@@ -983,16 +983,16 @@
         <v>Interactive Carousel</v>
       </c>
       <c r="D17" t="str">
-        <v>Verify Onboarding pagination dot indicator on Android device viewport</v>
+        <v>Validate Onboarding pagination dot indicator on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E17" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F17" t="str">
-        <v>Trigger native mobile interaction 'Onboarding pagination dot indicator' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Onboarding pagination dot indicator' and record Kotlin bridge event log</v>
       </c>
       <c r="G17" t="str">
-        <v>Android UI renders seamlessly, 'Onboarding pagination dot indicator' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Onboarding pagination dot indicator' with zero crash logs</v>
       </c>
       <c r="H17" t="str">
         <v>High</v>
@@ -1018,16 +1018,16 @@
         <v>Interactive Carousel</v>
       </c>
       <c r="D18" t="str">
-        <v>Verify Skip Onboarding button tap on Android device viewport</v>
+        <v>Validate Skip Onboarding button tap on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E18" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F18" t="str">
-        <v>Trigger native mobile interaction 'Skip Onboarding button tap' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Skip Onboarding button tap' and record Kotlin bridge event log</v>
       </c>
       <c r="G18" t="str">
-        <v>Android UI renders seamlessly, 'Skip Onboarding button tap' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Skip Onboarding button tap' with zero crash logs</v>
       </c>
       <c r="H18" t="str">
         <v>Medium</v>
@@ -1053,16 +1053,16 @@
         <v>Interactive Carousel</v>
       </c>
       <c r="D19" t="str">
-        <v>Verify Get Started CTA button tap on Android device viewport</v>
+        <v>Validate Get Started CTA button tap on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E19" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F19" t="str">
-        <v>Trigger native mobile interaction 'Get Started CTA button tap' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Get Started CTA button tap' and record Kotlin bridge event log</v>
       </c>
       <c r="G19" t="str">
-        <v>Android UI renders seamlessly, 'Get Started CTA button tap' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Get Started CTA button tap' with zero crash logs</v>
       </c>
       <c r="H19" t="str">
         <v>High</v>
@@ -1088,16 +1088,16 @@
         <v>Interactive Carousel</v>
       </c>
       <c r="D20" t="str">
-        <v>Verify Onboarding animation frame rate on Android device viewport</v>
+        <v>Validate Onboarding animation frame rate on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E20" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F20" t="str">
-        <v>Trigger native mobile interaction 'Onboarding animation frame rate' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Onboarding animation frame rate' and record Kotlin bridge event log</v>
       </c>
       <c r="G20" t="str">
-        <v>Android UI renders seamlessly, 'Onboarding animation frame rate' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Onboarding animation frame rate' with zero crash logs</v>
       </c>
       <c r="H20" t="str">
         <v>Medium</v>
@@ -1123,16 +1123,16 @@
         <v>Interactive Carousel</v>
       </c>
       <c r="D21" t="str">
-        <v>Verify Back button press on slide 1 on Android device viewport</v>
+        <v>Validate Back button press on slide 1 on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E21" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F21" t="str">
-        <v>Trigger native mobile interaction 'Back button press on slide 1' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Back button press on slide 1' and record Kotlin bridge event log</v>
       </c>
       <c r="G21" t="str">
-        <v>Android UI renders seamlessly, 'Back button press on slide 1' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Back button press on slide 1' with zero crash logs</v>
       </c>
       <c r="H21" t="str">
         <v>Critical</v>
@@ -1158,16 +1158,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D22" t="str">
-        <v>Verify Scheduled medicine notification pop on Android device viewport</v>
+        <v>Validate Scheduled medicine notification pop on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E22" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F22" t="str">
-        <v>Trigger native mobile interaction 'Scheduled medicine notification pop' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Scheduled medicine notification pop' and record Kotlin bridge event log</v>
       </c>
       <c r="G22" t="str">
-        <v>Android UI renders seamlessly, 'Scheduled medicine notification pop' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Scheduled medicine notification pop' with zero crash logs</v>
       </c>
       <c r="H22" t="str">
         <v>Medium</v>
@@ -1193,16 +1193,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D23" t="str">
-        <v>Verify Notification action 'Mark as Taken' on Android device viewport</v>
+        <v>Validate Notification action 'Mark as Taken' on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E23" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F23" t="str">
-        <v>Trigger native mobile interaction 'Notification action 'Mark as Taken'' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Notification action 'Mark as Taken'' and record Kotlin bridge event log</v>
       </c>
       <c r="G23" t="str">
-        <v>Android UI renders seamlessly, 'Notification action 'Mark as Taken'' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Notification action 'Mark as Taken'' with zero crash logs</v>
       </c>
       <c r="H23" t="str">
         <v>High</v>
@@ -1228,16 +1228,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D24" t="str">
-        <v>Verify Notification action 'Snooze 15m' on Android device viewport</v>
+        <v>Validate Notification action 'Snooze 15m' on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E24" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F24" t="str">
-        <v>Trigger native mobile interaction 'Notification action 'Snooze 15m'' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Notification action 'Snooze 15m'' and record Kotlin bridge event log</v>
       </c>
       <c r="G24" t="str">
-        <v>Android UI renders seamlessly, 'Notification action 'Snooze 15m'' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Notification action 'Snooze 15m'' with zero crash logs</v>
       </c>
       <c r="H24" t="str">
         <v>Medium</v>
@@ -1263,16 +1263,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D25" t="str">
-        <v>Verify Sound and vibration alert trigger on Android device viewport</v>
+        <v>Validate Sound and vibration alert trigger on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E25" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F25" t="str">
-        <v>Trigger native mobile interaction 'Sound and vibration alert trigger' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Sound and vibration alert trigger' and record Kotlin bridge event log</v>
       </c>
       <c r="G25" t="str">
-        <v>Android UI renders seamlessly, 'Sound and vibration alert trigger' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Sound and vibration alert trigger' with zero crash logs</v>
       </c>
       <c r="H25" t="str">
         <v>High</v>
@@ -1298,16 +1298,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D26" t="str">
-        <v>Verify Lockscreen notification card render on Android device viewport</v>
+        <v>Validate Lockscreen notification card render on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E26" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F26" t="str">
-        <v>Trigger native mobile interaction 'Lockscreen notification card render' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Lockscreen notification card render' and record Kotlin bridge event log</v>
       </c>
       <c r="G26" t="str">
-        <v>Android UI renders seamlessly, 'Lockscreen notification card render' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Lockscreen notification card render' with zero crash logs</v>
       </c>
       <c r="H26" t="str">
         <v>Critical</v>
@@ -1333,16 +1333,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D27" t="str">
-        <v>Verify Notification badge count update on Android device viewport</v>
+        <v>Validate Notification badge count update on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E27" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F27" t="str">
-        <v>Trigger native mobile interaction 'Notification badge count update' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Notification badge count update' and record Kotlin bridge event log</v>
       </c>
       <c r="G27" t="str">
-        <v>Android UI renders seamlessly, 'Notification badge count update' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Notification badge count update' with zero crash logs</v>
       </c>
       <c r="H27" t="str">
         <v>High</v>
@@ -1368,16 +1368,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D28" t="str">
-        <v>Verify Missed dose push alert on Android device viewport</v>
+        <v>Validate Missed dose push alert on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E28" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F28" t="str">
-        <v>Trigger native mobile interaction 'Missed dose push alert' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Missed dose push alert' and record Kotlin bridge event log</v>
       </c>
       <c r="G28" t="str">
-        <v>Android UI renders seamlessly, 'Missed dose push alert' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Missed dose push alert' with zero crash logs</v>
       </c>
       <c r="H28" t="str">
         <v>Medium</v>
@@ -1403,16 +1403,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D29" t="str">
-        <v>Verify Custom sound playback check on Android device viewport</v>
+        <v>Validate Custom sound playback check on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E29" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F29" t="str">
-        <v>Trigger native mobile interaction 'Custom sound playback check' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Custom sound playback check' and record Kotlin bridge event log</v>
       </c>
       <c r="G29" t="str">
-        <v>Android UI renders seamlessly, 'Custom sound playback check' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Custom sound playback check' with zero crash logs</v>
       </c>
       <c r="H29" t="str">
         <v>High</v>
@@ -1438,16 +1438,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D30" t="str">
-        <v>Verify Notification tap app foregrounding on Android device viewport</v>
+        <v>Validate Notification tap app foregrounding on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E30" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F30" t="str">
-        <v>Trigger native mobile interaction 'Notification tap app foregrounding' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Notification tap app foregrounding' and record Kotlin bridge event log</v>
       </c>
       <c r="G30" t="str">
-        <v>Android UI renders seamlessly, 'Notification tap app foregrounding' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Notification tap app foregrounding' with zero crash logs</v>
       </c>
       <c r="H30" t="str">
         <v>Medium</v>
@@ -1473,16 +1473,16 @@
         <v>Medication Reminders</v>
       </c>
       <c r="D31" t="str">
-        <v>Verify Clear notification swipe gesture on Android device viewport</v>
+        <v>Validate Clear notification swipe gesture on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E31" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F31" t="str">
-        <v>Trigger native mobile interaction 'Clear notification swipe gesture' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Clear notification swipe gesture' and record Kotlin bridge event log</v>
       </c>
       <c r="G31" t="str">
-        <v>Android UI renders seamlessly, 'Clear notification swipe gesture' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Clear notification swipe gesture' with zero crash logs</v>
       </c>
       <c r="H31" t="str">
         <v>Critical</v>
@@ -1508,16 +1508,16 @@
         <v>Symptom &amp; Risk Alerts</v>
       </c>
       <c r="D32" t="str">
-        <v>Verify Concerning symptom alert push on Android device viewport</v>
+        <v>Validate Concerning symptom alert push on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E32" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F32" t="str">
-        <v>Trigger native mobile interaction 'Concerning symptom alert push' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Concerning symptom alert push' and record Kotlin bridge event log</v>
       </c>
       <c r="G32" t="str">
-        <v>Android UI renders seamlessly, 'Concerning symptom alert push' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Concerning symptom alert push' with zero crash logs</v>
       </c>
       <c r="H32" t="str">
         <v>Medium</v>
@@ -1543,16 +1543,16 @@
         <v>Symptom &amp; Risk Alerts</v>
       </c>
       <c r="D33" t="str">
-        <v>Verify High priority risk warning banner on Android device viewport</v>
+        <v>Validate High priority risk warning banner on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E33" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F33" t="str">
-        <v>Trigger native mobile interaction 'High priority risk warning banner' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'High priority risk warning banner' and record Kotlin bridge event log</v>
       </c>
       <c r="G33" t="str">
-        <v>Android UI renders seamlessly, 'High priority risk warning banner' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'High priority risk warning banner' with zero crash logs</v>
       </c>
       <c r="H33" t="str">
         <v>High</v>
@@ -1578,16 +1578,16 @@
         <v>Symptom &amp; Risk Alerts</v>
       </c>
       <c r="D34" t="str">
-        <v>Verify Abnormal vitals threshold notification on Android device viewport</v>
+        <v>Validate Abnormal vitals threshold notification on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E34" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F34" t="str">
-        <v>Trigger native mobile interaction 'Abnormal vitals threshold notification' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Abnormal vitals threshold notification' and record Kotlin bridge event log</v>
       </c>
       <c r="G34" t="str">
-        <v>Android UI renders seamlessly, 'Abnormal vitals threshold notification' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Abnormal vitals threshold notification' with zero crash logs</v>
       </c>
       <c r="H34" t="str">
         <v>Medium</v>
@@ -1613,16 +1613,16 @@
         <v>Symptom &amp; Risk Alerts</v>
       </c>
       <c r="D35" t="str">
-        <v>Verify Weekly health summary push alert on Android device viewport</v>
+        <v>Validate Weekly health summary push alert on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E35" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F35" t="str">
-        <v>Trigger native mobile interaction 'Weekly health summary push alert' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Weekly health summary push alert' and record Kotlin bridge event log</v>
       </c>
       <c r="G35" t="str">
-        <v>Android UI renders seamlessly, 'Weekly health summary push alert' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Weekly health summary push alert' with zero crash logs</v>
       </c>
       <c r="H35" t="str">
         <v>High</v>
@@ -1648,16 +1648,16 @@
         <v>Symptom &amp; Risk Alerts</v>
       </c>
       <c r="D36" t="str">
-        <v>Verify Doctor appointment reminder push on Android device viewport</v>
+        <v>Validate Doctor appointment reminder push on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E36" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F36" t="str">
-        <v>Trigger native mobile interaction 'Doctor appointment reminder push' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Doctor appointment reminder push' and record Kotlin bridge event log</v>
       </c>
       <c r="G36" t="str">
-        <v>Android UI renders seamlessly, 'Doctor appointment reminder push' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Doctor appointment reminder push' with zero crash logs</v>
       </c>
       <c r="H36" t="str">
         <v>Critical</v>
@@ -1683,16 +1683,16 @@
         <v>Symptom &amp; Risk Alerts</v>
       </c>
       <c r="D37" t="str">
-        <v>Verify Emergency contact auto-alert on Android device viewport</v>
+        <v>Validate Emergency contact auto-alert on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E37" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F37" t="str">
-        <v>Trigger native mobile interaction 'Emergency contact auto-alert' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Emergency contact auto-alert' and record Kotlin bridge event log</v>
       </c>
       <c r="G37" t="str">
-        <v>Android UI renders seamlessly, 'Emergency contact auto-alert' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Emergency contact auto-alert' with zero crash logs</v>
       </c>
       <c r="H37" t="str">
         <v>High</v>
@@ -1718,16 +1718,16 @@
         <v>Symptom &amp; Risk Alerts</v>
       </c>
       <c r="D38" t="str">
-        <v>Verify Silent hours notification suppression on Android device viewport</v>
+        <v>Validate Silent hours notification suppression on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E38" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F38" t="str">
-        <v>Trigger native mobile interaction 'Silent hours notification suppression' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Silent hours notification suppression' and record Kotlin bridge event log</v>
       </c>
       <c r="G38" t="str">
-        <v>Android UI renders seamlessly, 'Silent hours notification suppression' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Silent hours notification suppression' with zero crash logs</v>
       </c>
       <c r="H38" t="str">
         <v>Medium</v>
@@ -1753,16 +1753,16 @@
         <v>Symptom &amp; Risk Alerts</v>
       </c>
       <c r="D39" t="str">
-        <v>Verify Alert history drawer entry on Android device viewport</v>
+        <v>Validate Alert history drawer entry on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E39" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F39" t="str">
-        <v>Trigger native mobile interaction 'Alert history drawer entry' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Alert history drawer entry' and record Kotlin bridge event log</v>
       </c>
       <c r="G39" t="str">
-        <v>Android UI renders seamlessly, 'Alert history drawer entry' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Alert history drawer entry' with zero crash logs</v>
       </c>
       <c r="H39" t="str">
         <v>High</v>
@@ -1788,16 +1788,16 @@
         <v>Symptom &amp; Risk Alerts</v>
       </c>
       <c r="D40" t="str">
-        <v>Verify Rich notification image preview on Android device viewport</v>
+        <v>Validate Rich notification image preview on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E40" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F40" t="str">
-        <v>Trigger native mobile interaction 'Rich notification image preview' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Rich notification image preview' and record Kotlin bridge event log</v>
       </c>
       <c r="G40" t="str">
-        <v>Android UI renders seamlessly, 'Rich notification image preview' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Rich notification image preview' with zero crash logs</v>
       </c>
       <c r="H40" t="str">
         <v>Medium</v>
@@ -1823,16 +1823,16 @@
         <v>Symptom &amp; Risk Alerts</v>
       </c>
       <c r="D41" t="str">
-        <v>Verify Notification permission request prompt on Android device viewport</v>
+        <v>Validate Notification permission request prompt on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E41" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F41" t="str">
-        <v>Trigger native mobile interaction 'Notification permission request prompt' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Notification permission request prompt' and record Kotlin bridge event log</v>
       </c>
       <c r="G41" t="str">
-        <v>Android UI renders seamlessly, 'Notification permission request prompt' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Notification permission request prompt' with zero crash logs</v>
       </c>
       <c r="H41" t="str">
         <v>Critical</v>
@@ -1858,16 +1858,16 @@
         <v>Biometric &amp; Security</v>
       </c>
       <c r="D42" t="str">
-        <v>Verify Fingerprint prompt trigger on resume on Android device viewport</v>
+        <v>Validate Fingerprint prompt trigger on resume on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E42" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F42" t="str">
-        <v>Trigger native mobile interaction 'Fingerprint prompt trigger on resume' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Fingerprint prompt trigger on resume' and record Kotlin bridge event log</v>
       </c>
       <c r="G42" t="str">
-        <v>Android UI renders seamlessly, 'Fingerprint prompt trigger on resume' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Fingerprint prompt trigger on resume' with zero crash logs</v>
       </c>
       <c r="H42" t="str">
         <v>Medium</v>
@@ -1893,16 +1893,16 @@
         <v>Biometric &amp; Security</v>
       </c>
       <c r="D43" t="str">
-        <v>Verify FaceID unlock prompt trigger on Android device viewport</v>
+        <v>Validate FaceID unlock prompt trigger on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E43" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F43" t="str">
-        <v>Trigger native mobile interaction 'FaceID unlock prompt trigger' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'FaceID unlock prompt trigger' and record Kotlin bridge event log</v>
       </c>
       <c r="G43" t="str">
-        <v>Android UI renders seamlessly, 'FaceID unlock prompt trigger' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'FaceID unlock prompt trigger' with zero crash logs</v>
       </c>
       <c r="H43" t="str">
         <v>High</v>
@@ -1928,16 +1928,16 @@
         <v>Biometric &amp; Security</v>
       </c>
       <c r="D44" t="str">
-        <v>Verify Biometric fallback to PIN code on Android device viewport</v>
+        <v>Validate Biometric fallback to PIN code on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E44" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F44" t="str">
-        <v>Trigger native mobile interaction 'Biometric fallback to PIN code' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Biometric fallback to PIN code' and record Kotlin bridge event log</v>
       </c>
       <c r="G44" t="str">
-        <v>Android UI renders seamlessly, 'Biometric fallback to PIN code' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Biometric fallback to PIN code' with zero crash logs</v>
       </c>
       <c r="H44" t="str">
         <v>Medium</v>
@@ -1963,16 +1963,16 @@
         <v>Biometric &amp; Security</v>
       </c>
       <c r="D45" t="str">
-        <v>Verify Two-Factor Auth OTP SMS prompt on Android device viewport</v>
+        <v>Validate Two-Factor Auth OTP SMS prompt on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E45" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F45" t="str">
-        <v>Trigger native mobile interaction 'Two-Factor Auth OTP SMS prompt' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Two-Factor Auth OTP SMS prompt' and record Kotlin bridge event log</v>
       </c>
       <c r="G45" t="str">
-        <v>Android UI renders seamlessly, 'Two-Factor Auth OTP SMS prompt' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Two-Factor Auth OTP SMS prompt' with zero crash logs</v>
       </c>
       <c r="H45" t="str">
         <v>High</v>
@@ -1998,16 +1998,16 @@
         <v>Biometric &amp; Security</v>
       </c>
       <c r="D46" t="str">
-        <v>Verify 2FA Authenticator app code entry on Android device viewport</v>
+        <v>Validate 2FA Authenticator app code entry on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E46" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F46" t="str">
-        <v>Trigger native mobile interaction '2FA Authenticator app code entry' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input '2FA Authenticator app code entry' and record Kotlin bridge event log</v>
       </c>
       <c r="G46" t="str">
-        <v>Android UI renders seamlessly, '2FA Authenticator app code entry' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for '2FA Authenticator app code entry' with zero crash logs</v>
       </c>
       <c r="H46" t="str">
         <v>Critical</v>
@@ -2033,16 +2033,16 @@
         <v>Biometric &amp; Security</v>
       </c>
       <c r="D47" t="str">
-        <v>Verify Biometric authentication setup wizard on Android device viewport</v>
+        <v>Validate Biometric authentication setup wizard on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E47" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F47" t="str">
-        <v>Trigger native mobile interaction 'Biometric authentication setup wizard' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Biometric authentication setup wizard' and record Kotlin bridge event log</v>
       </c>
       <c r="G47" t="str">
-        <v>Android UI renders seamlessly, 'Biometric authentication setup wizard' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Biometric authentication setup wizard' with zero crash logs</v>
       </c>
       <c r="H47" t="str">
         <v>High</v>
@@ -2068,16 +2068,16 @@
         <v>Biometric &amp; Security</v>
       </c>
       <c r="D48" t="str">
-        <v>Verify Change Password modal submit on Android device viewport</v>
+        <v>Validate Change Password modal submit on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E48" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F48" t="str">
-        <v>Trigger native mobile interaction 'Change Password modal submit' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Change Password modal submit' and record Kotlin bridge event log</v>
       </c>
       <c r="G48" t="str">
-        <v>Android UI renders seamlessly, 'Change Password modal submit' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Change Password modal submit' with zero crash logs</v>
       </c>
       <c r="H48" t="str">
         <v>Medium</v>
@@ -2103,16 +2103,16 @@
         <v>Biometric &amp; Security</v>
       </c>
       <c r="D49" t="str">
-        <v>Verify Change Mobile Number SMS verify on Android device viewport</v>
+        <v>Validate Change Mobile Number SMS verify on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E49" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F49" t="str">
-        <v>Trigger native mobile interaction 'Change Mobile Number SMS verify' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Change Mobile Number SMS verify' and record Kotlin bridge event log</v>
       </c>
       <c r="G49" t="str">
-        <v>Android UI renders seamlessly, 'Change Mobile Number SMS verify' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Change Mobile Number SMS verify' with zero crash logs</v>
       </c>
       <c r="H49" t="str">
         <v>High</v>
@@ -2138,16 +2138,16 @@
         <v>Biometric &amp; Security</v>
       </c>
       <c r="D50" t="str">
-        <v>Verify Anonymous analytics opt-out switch on Android device viewport</v>
+        <v>Validate Anonymous analytics opt-out switch on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E50" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F50" t="str">
-        <v>Trigger native mobile interaction 'Anonymous analytics opt-out switch' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Anonymous analytics opt-out switch' and record Kotlin bridge event log</v>
       </c>
       <c r="G50" t="str">
-        <v>Android UI renders seamlessly, 'Anonymous analytics opt-out switch' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Anonymous analytics opt-out switch' with zero crash logs</v>
       </c>
       <c r="H50" t="str">
         <v>Medium</v>
@@ -2173,16 +2173,16 @@
         <v>Biometric &amp; Security</v>
       </c>
       <c r="D51" t="str">
-        <v>Verify Data export ZIP package download on Android device viewport</v>
+        <v>Validate Data export ZIP package download on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E51" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F51" t="str">
-        <v>Trigger native mobile interaction 'Data export ZIP package download' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Data export ZIP package download' and record Kotlin bridge event log</v>
       </c>
       <c r="G51" t="str">
-        <v>Android UI renders seamlessly, 'Data export ZIP package download' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Data export ZIP package download' with zero crash logs</v>
       </c>
       <c r="H51" t="str">
         <v>Critical</v>
@@ -2208,16 +2208,16 @@
         <v>Mobile Viewport UI</v>
       </c>
       <c r="D52" t="str">
-        <v>Verify Active Vitals carousel horizontal scroll on Android device viewport</v>
+        <v>Validate Active Vitals carousel horizontal scroll on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E52" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F52" t="str">
-        <v>Trigger native mobile interaction 'Active Vitals carousel horizontal scroll' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Active Vitals carousel horizontal scroll' and record Kotlin bridge event log</v>
       </c>
       <c r="G52" t="str">
-        <v>Android UI renders seamlessly, 'Active Vitals carousel horizontal scroll' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Active Vitals carousel horizontal scroll' with zero crash logs</v>
       </c>
       <c r="H52" t="str">
         <v>Medium</v>
@@ -2243,16 +2243,16 @@
         <v>Mobile Viewport UI</v>
       </c>
       <c r="D53" t="str">
-        <v>Verify Daily Protocol progress ring animation on Android device viewport</v>
+        <v>Validate Daily Protocol progress ring animation on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E53" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F53" t="str">
-        <v>Trigger native mobile interaction 'Daily Protocol progress ring animation' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Daily Protocol progress ring animation' and record Kotlin bridge event log</v>
       </c>
       <c r="G53" t="str">
-        <v>Android UI renders seamlessly, 'Daily Protocol progress ring animation' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Daily Protocol progress ring animation' with zero crash logs</v>
       </c>
       <c r="H53" t="str">
         <v>High</v>
@@ -2278,16 +2278,16 @@
         <v>Mobile Viewport UI</v>
       </c>
       <c r="D54" t="str">
-        <v>Verify Quick Action Floating Action Button on Android device viewport</v>
+        <v>Validate Quick Action Floating Action Button on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E54" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F54" t="str">
-        <v>Trigger native mobile interaction 'Quick Action Floating Action Button' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Quick Action Floating Action Button' and record Kotlin bridge event log</v>
       </c>
       <c r="G54" t="str">
-        <v>Android UI renders seamlessly, 'Quick Action Floating Action Button' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Quick Action Floating Action Button' with zero crash logs</v>
       </c>
       <c r="H54" t="str">
         <v>Medium</v>
@@ -2313,16 +2313,16 @@
         <v>Mobile Viewport UI</v>
       </c>
       <c r="D55" t="str">
-        <v>Verify Pull-to-refresh dashboard data on Android device viewport</v>
+        <v>Validate Pull-to-refresh dashboard data on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E55" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F55" t="str">
-        <v>Trigger native mobile interaction 'Pull-to-refresh dashboard data' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Pull-to-refresh dashboard data' and record Kotlin bridge event log</v>
       </c>
       <c r="G55" t="str">
-        <v>Android UI renders seamlessly, 'Pull-to-refresh dashboard data' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Pull-to-refresh dashboard data' with zero crash logs</v>
       </c>
       <c r="H55" t="str">
         <v>High</v>
@@ -2348,16 +2348,16 @@
         <v>Mobile Viewport UI</v>
       </c>
       <c r="D56" t="str">
-        <v>Verify Soft keyboard push layout adjustment on Android device viewport</v>
+        <v>Validate Soft keyboard push layout adjustment on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E56" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F56" t="str">
-        <v>Trigger native mobile interaction 'Soft keyboard push layout adjustment' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Soft keyboard push layout adjustment' and record Kotlin bridge event log</v>
       </c>
       <c r="G56" t="str">
-        <v>Android UI renders seamlessly, 'Soft keyboard push layout adjustment' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Soft keyboard push layout adjustment' with zero crash logs</v>
       </c>
       <c r="H56" t="str">
         <v>Critical</v>
@@ -2383,16 +2383,16 @@
         <v>Mobile Viewport UI</v>
       </c>
       <c r="D57" t="str">
-        <v>Verify Bottom navigation tab bar switch on Android device viewport</v>
+        <v>Validate Bottom navigation tab bar switch on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E57" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F57" t="str">
-        <v>Trigger native mobile interaction 'Bottom navigation tab bar switch' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Bottom navigation tab bar switch' and record Kotlin bridge event log</v>
       </c>
       <c r="G57" t="str">
-        <v>Android UI renders seamlessly, 'Bottom navigation tab bar switch' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Bottom navigation tab bar switch' with zero crash logs</v>
       </c>
       <c r="H57" t="str">
         <v>High</v>
@@ -2418,16 +2418,16 @@
         <v>Mobile Viewport UI</v>
       </c>
       <c r="D58" t="str">
-        <v>Verify Network offline banner display on Android device viewport</v>
+        <v>Validate Network offline banner display on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E58" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F58" t="str">
-        <v>Trigger native mobile interaction 'Network offline banner display' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Network offline banner display' and record Kotlin bridge event log</v>
       </c>
       <c r="G58" t="str">
-        <v>Android UI renders seamlessly, 'Network offline banner display' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Network offline banner display' with zero crash logs</v>
       </c>
       <c r="H58" t="str">
         <v>Medium</v>
@@ -2453,16 +2453,16 @@
         <v>Mobile Viewport UI</v>
       </c>
       <c r="D59" t="str">
-        <v>Verify Network online recovery sync on Android device viewport</v>
+        <v>Validate Network online recovery sync on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E59" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F59" t="str">
-        <v>Trigger native mobile interaction 'Network online recovery sync' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Network online recovery sync' and record Kotlin bridge event log</v>
       </c>
       <c r="G59" t="str">
-        <v>Android UI renders seamlessly, 'Network online recovery sync' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Network online recovery sync' with zero crash logs</v>
       </c>
       <c r="H59" t="str">
         <v>High</v>
@@ -2488,16 +2488,16 @@
         <v>Mobile Viewport UI</v>
       </c>
       <c r="D60" t="str">
-        <v>Verify Device dark mode live toggle on Android device viewport</v>
+        <v>Validate Device dark mode live toggle on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E60" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F60" t="str">
-        <v>Trigger native mobile interaction 'Device dark mode live toggle' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Device dark mode live toggle' and record Kotlin bridge event log</v>
       </c>
       <c r="G60" t="str">
-        <v>Android UI renders seamlessly, 'Device dark mode live toggle' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Device dark mode live toggle' with zero crash logs</v>
       </c>
       <c r="H60" t="str">
         <v>Medium</v>
@@ -2523,16 +2523,16 @@
         <v>Mobile Viewport UI</v>
       </c>
       <c r="D61" t="str">
-        <v>Verify Hardware Back button navigation stack on Android device viewport</v>
+        <v>Validate Hardware Back button navigation stack on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E61" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F61" t="str">
-        <v>Trigger native mobile interaction 'Hardware Back button navigation stack' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Hardware Back button navigation stack' and record Kotlin bridge event log</v>
       </c>
       <c r="G61" t="str">
-        <v>Android UI renders seamlessly, 'Hardware Back button navigation stack' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Hardware Back button navigation stack' with zero crash logs</v>
       </c>
       <c r="H61" t="str">
         <v>Critical</v>
@@ -2558,16 +2558,16 @@
         <v>Mobile Native Input</v>
       </c>
       <c r="D62" t="str">
-        <v>Verify Biometrics update modal popup on Android device viewport</v>
+        <v>Validate Biometrics update modal popup on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E62" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F62" t="str">
-        <v>Trigger native mobile interaction 'Biometrics update modal popup' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Biometrics update modal popup' and record Kotlin bridge event log</v>
       </c>
       <c r="G62" t="str">
-        <v>Android UI renders seamlessly, 'Biometrics update modal popup' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Biometrics update modal popup' with zero crash logs</v>
       </c>
       <c r="H62" t="str">
         <v>Medium</v>
@@ -2593,16 +2593,16 @@
         <v>Mobile Native Input</v>
       </c>
       <c r="D63" t="str">
-        <v>Verify Heart rate native sensor picker on Android device viewport</v>
+        <v>Validate Heart rate native sensor picker on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E63" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F63" t="str">
-        <v>Trigger native mobile interaction 'Heart rate native sensor picker' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Heart rate native sensor picker' and record Kotlin bridge event log</v>
       </c>
       <c r="G63" t="str">
-        <v>Android UI renders seamlessly, 'Heart rate native sensor picker' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Heart rate native sensor picker' with zero crash logs</v>
       </c>
       <c r="H63" t="str">
         <v>High</v>
@@ -2628,16 +2628,16 @@
         <v>Mobile Native Input</v>
       </c>
       <c r="D64" t="str">
-        <v>Verify Blood pressure dual slider input on Android device viewport</v>
+        <v>Validate Blood pressure dual slider input on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E64" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F64" t="str">
-        <v>Trigger native mobile interaction 'Blood pressure dual slider input' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Blood pressure dual slider input' and record Kotlin bridge event log</v>
       </c>
       <c r="G64" t="str">
-        <v>Android UI renders seamlessly, 'Blood pressure dual slider input' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Blood pressure dual slider input' with zero crash logs</v>
       </c>
       <c r="H64" t="str">
         <v>Medium</v>
@@ -2663,16 +2663,16 @@
         <v>Mobile Native Input</v>
       </c>
       <c r="D65" t="str">
-        <v>Verify Glucose level numeric keypad focus on Android device viewport</v>
+        <v>Validate Glucose level numeric keypad focus on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E65" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F65" t="str">
-        <v>Trigger native mobile interaction 'Glucose level numeric keypad focus' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Glucose level numeric keypad focus' and record Kotlin bridge event log</v>
       </c>
       <c r="G65" t="str">
-        <v>Android UI renders seamlessly, 'Glucose level numeric keypad focus' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Glucose level numeric keypad focus' with zero crash logs</v>
       </c>
       <c r="H65" t="str">
         <v>High</v>
@@ -2698,16 +2698,16 @@
         <v>Mobile Native Input</v>
       </c>
       <c r="D66" t="str">
-        <v>Verify Medicine time picker native modal on Android device viewport</v>
+        <v>Validate Medicine time picker native modal on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E66" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F66" t="str">
-        <v>Trigger native mobile interaction 'Medicine time picker native modal' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Medicine time picker native modal' and record Kotlin bridge event log</v>
       </c>
       <c r="G66" t="str">
-        <v>Android UI renders seamlessly, 'Medicine time picker native modal' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Medicine time picker native modal' with zero crash logs</v>
       </c>
       <c r="H66" t="str">
         <v>Critical</v>
@@ -2733,16 +2733,16 @@
         <v>Mobile Native Input</v>
       </c>
       <c r="D67" t="str">
-        <v>Verify Dose size stepper control on Android device viewport</v>
+        <v>Validate Dose size stepper control on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E67" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F67" t="str">
-        <v>Trigger native mobile interaction 'Dose size stepper control' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Dose size stepper control' and record Kotlin bridge event log</v>
       </c>
       <c r="G67" t="str">
-        <v>Android UI renders seamlessly, 'Dose size stepper control' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Dose size stepper control' with zero crash logs</v>
       </c>
       <c r="H67" t="str">
         <v>High</v>
@@ -2768,16 +2768,16 @@
         <v>Mobile Native Input</v>
       </c>
       <c r="D68" t="str">
-        <v>Verify Repeat daily schedule checkbox on Android device viewport</v>
+        <v>Validate Repeat daily schedule checkbox on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E68" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F68" t="str">
-        <v>Trigger native mobile interaction 'Repeat daily schedule checkbox' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Repeat daily schedule checkbox' and record Kotlin bridge event log</v>
       </c>
       <c r="G68" t="str">
-        <v>Android UI renders seamlessly, 'Repeat daily schedule checkbox' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Repeat daily schedule checkbox' with zero crash logs</v>
       </c>
       <c r="H68" t="str">
         <v>Medium</v>
@@ -2803,16 +2803,16 @@
         <v>Mobile Native Input</v>
       </c>
       <c r="D69" t="str">
-        <v>Verify Delete medicine entry swipe gesture on Android device viewport</v>
+        <v>Validate Delete medicine entry swipe gesture on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E69" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F69" t="str">
-        <v>Trigger native mobile interaction 'Delete medicine entry swipe gesture' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Delete medicine entry swipe gesture' and record Kotlin bridge event log</v>
       </c>
       <c r="G69" t="str">
-        <v>Android UI renders seamlessly, 'Delete medicine entry swipe gesture' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Delete medicine entry swipe gesture' with zero crash logs</v>
       </c>
       <c r="H69" t="str">
         <v>High</v>
@@ -2838,16 +2838,16 @@
         <v>Mobile Native Input</v>
       </c>
       <c r="D70" t="str">
-        <v>Verify Edit medicine details tap on Android device viewport</v>
+        <v>Validate Edit medicine details tap on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E70" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F70" t="str">
-        <v>Trigger native mobile interaction 'Edit medicine details tap' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Edit medicine details tap' and record Kotlin bridge event log</v>
       </c>
       <c r="G70" t="str">
-        <v>Android UI renders seamlessly, 'Edit medicine details tap' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Edit medicine details tap' with zero crash logs</v>
       </c>
       <c r="H70" t="str">
         <v>Medium</v>
@@ -2873,16 +2873,16 @@
         <v>Mobile Native Input</v>
       </c>
       <c r="D71" t="str">
-        <v>Verify Vitals history chart pinch-to-zoom on Android device viewport</v>
+        <v>Validate Vitals history chart pinch-to-zoom on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E71" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F71" t="str">
-        <v>Trigger native mobile interaction 'Vitals history chart pinch-to-zoom' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Vitals history chart pinch-to-zoom' and record Kotlin bridge event log</v>
       </c>
       <c r="G71" t="str">
-        <v>Android UI renders seamlessly, 'Vitals history chart pinch-to-zoom' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Vitals history chart pinch-to-zoom' with zero crash logs</v>
       </c>
       <c r="H71" t="str">
         <v>Critical</v>
@@ -2908,16 +2908,16 @@
         <v>Mobile Interaction</v>
       </c>
       <c r="D72" t="str">
-        <v>Verify AI Chat input soft keyboard push on Android device viewport</v>
+        <v>Validate AI Chat input soft keyboard push on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E72" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F72" t="str">
-        <v>Trigger native mobile interaction 'AI Chat input soft keyboard push' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'AI Chat input soft keyboard push' and record Kotlin bridge event log</v>
       </c>
       <c r="G72" t="str">
-        <v>Android UI renders seamlessly, 'AI Chat input soft keyboard push' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'AI Chat input soft keyboard push' with zero crash logs</v>
       </c>
       <c r="H72" t="str">
         <v>Medium</v>
@@ -2943,16 +2943,16 @@
         <v>Mobile Interaction</v>
       </c>
       <c r="D73" t="str">
-        <v>Verify Voice-to-text mic button tap on Android device viewport</v>
+        <v>Validate Voice-to-text mic button tap on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E73" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F73" t="str">
-        <v>Trigger native mobile interaction 'Voice-to-text mic button tap' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Voice-to-text mic button tap' and record Kotlin bridge event log</v>
       </c>
       <c r="G73" t="str">
-        <v>Android UI renders seamlessly, 'Voice-to-text mic button tap' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Voice-to-text mic button tap' with zero crash logs</v>
       </c>
       <c r="H73" t="str">
         <v>High</v>
@@ -2978,16 +2978,16 @@
         <v>Mobile Interaction</v>
       </c>
       <c r="D74" t="str">
-        <v>Verify Voice input recording indicator on Android device viewport</v>
+        <v>Validate Voice input recording indicator on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E74" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F74" t="str">
-        <v>Trigger native mobile interaction 'Voice input recording indicator' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Voice input recording indicator' and record Kotlin bridge event log</v>
       </c>
       <c r="G74" t="str">
-        <v>Android UI renders seamlessly, 'Voice input recording indicator' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Voice input recording indicator' with zero crash logs</v>
       </c>
       <c r="H74" t="str">
         <v>Medium</v>
@@ -3013,16 +3013,16 @@
         <v>Mobile Interaction</v>
       </c>
       <c r="D75" t="str">
-        <v>Verify Audio wave animation during speech on Android device viewport</v>
+        <v>Validate Audio wave animation during speech on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E75" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F75" t="str">
-        <v>Trigger native mobile interaction 'Audio wave animation during speech' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Audio wave animation during speech' and record Kotlin bridge event log</v>
       </c>
       <c r="G75" t="str">
-        <v>Android UI renders seamlessly, 'Audio wave animation during speech' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Audio wave animation during speech' with zero crash logs</v>
       </c>
       <c r="H75" t="str">
         <v>High</v>
@@ -3048,16 +3048,16 @@
         <v>Mobile Interaction</v>
       </c>
       <c r="D76" t="str">
-        <v>Verify Voice transcription text stream on Android device viewport</v>
+        <v>Validate Voice transcription text stream on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E76" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F76" t="str">
-        <v>Trigger native mobile interaction 'Voice transcription text stream' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Voice transcription text stream' and record Kotlin bridge event log</v>
       </c>
       <c r="G76" t="str">
-        <v>Android UI renders seamlessly, 'Voice transcription text stream' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Voice transcription text stream' with zero crash logs</v>
       </c>
       <c r="H76" t="str">
         <v>Critical</v>
@@ -3083,16 +3083,16 @@
         <v>Mobile Interaction</v>
       </c>
       <c r="D77" t="str">
-        <v>Verify Send message tap in chat on Android device viewport</v>
+        <v>Validate Send message tap in chat on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E77" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F77" t="str">
-        <v>Trigger native mobile interaction 'Send message tap in chat' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Send message tap in chat' and record Kotlin bridge event log</v>
       </c>
       <c r="G77" t="str">
-        <v>Android UI renders seamlessly, 'Send message tap in chat' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Send message tap in chat' with zero crash logs</v>
       </c>
       <c r="H77" t="str">
         <v>High</v>
@@ -3118,16 +3118,16 @@
         <v>Mobile Interaction</v>
       </c>
       <c r="D78" t="str">
-        <v>Verify AI streaming response text render on Android device viewport</v>
+        <v>Validate AI streaming response text render on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E78" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F78" t="str">
-        <v>Trigger native mobile interaction 'AI streaming response text render' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'AI streaming response text render' and record Kotlin bridge event log</v>
       </c>
       <c r="G78" t="str">
-        <v>Android UI renders seamlessly, 'AI streaming response text render' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'AI streaming response text render' with zero crash logs</v>
       </c>
       <c r="H78" t="str">
         <v>Medium</v>
@@ -3153,16 +3153,16 @@
         <v>Mobile Interaction</v>
       </c>
       <c r="D79" t="str">
-        <v>Verify Speech synthesis Text-to-Speech play on Android device viewport</v>
+        <v>Validate Speech synthesis Text-to-Speech play on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E79" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F79" t="str">
-        <v>Trigger native mobile interaction 'Speech synthesis Text-to-Speech play' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Speech synthesis Text-to-Speech play' and record Kotlin bridge event log</v>
       </c>
       <c r="G79" t="str">
-        <v>Android UI renders seamlessly, 'Speech synthesis Text-to-Speech play' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Speech synthesis Text-to-Speech play' with zero crash logs</v>
       </c>
       <c r="H79" t="str">
         <v>High</v>
@@ -3188,16 +3188,16 @@
         <v>Mobile Interaction</v>
       </c>
       <c r="D80" t="str">
-        <v>Verify Stop TTS audio playback button on Android device viewport</v>
+        <v>Validate Stop TTS audio playback button on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E80" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F80" t="str">
-        <v>Trigger native mobile interaction 'Stop TTS audio playback button' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Stop TTS audio playback button' and record Kotlin bridge event log</v>
       </c>
       <c r="G80" t="str">
-        <v>Android UI renders seamlessly, 'Stop TTS audio playback button' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Stop TTS audio playback button' with zero crash logs</v>
       </c>
       <c r="H80" t="str">
         <v>Medium</v>
@@ -3223,16 +3223,16 @@
         <v>Mobile Interaction</v>
       </c>
       <c r="D81" t="str">
-        <v>Verify Clear chat history mobile alert on Android device viewport</v>
+        <v>Validate Clear chat history mobile alert on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E81" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F81" t="str">
-        <v>Trigger native mobile interaction 'Clear chat history mobile alert' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Clear chat history mobile alert' and record Kotlin bridge event log</v>
       </c>
       <c r="G81" t="str">
-        <v>Android UI renders seamlessly, 'Clear chat history mobile alert' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Clear chat history mobile alert' with zero crash logs</v>
       </c>
       <c r="H81" t="str">
         <v>Critical</v>
@@ -3258,16 +3258,16 @@
         <v>Mobile Learning UI</v>
       </c>
       <c r="D82" t="str">
-        <v>Verify Article list vertical scroll physics on Android device viewport</v>
+        <v>Validate Article list vertical scroll physics on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E82" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F82" t="str">
-        <v>Trigger native mobile interaction 'Article list vertical scroll physics' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Article list vertical scroll physics' and record Kotlin bridge event log</v>
       </c>
       <c r="G82" t="str">
-        <v>Android UI renders seamlessly, 'Article list vertical scroll physics' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Article list vertical scroll physics' with zero crash logs</v>
       </c>
       <c r="H82" t="str">
         <v>Medium</v>
@@ -3293,16 +3293,16 @@
         <v>Mobile Learning UI</v>
       </c>
       <c r="D83" t="str">
-        <v>Verify Video player native full-screen toggle on Android device viewport</v>
+        <v>Validate Video player native full-screen toggle on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E83" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F83" t="str">
-        <v>Trigger native mobile interaction 'Video player native full-screen toggle' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Video player native full-screen toggle' and record Kotlin bridge event log</v>
       </c>
       <c r="G83" t="str">
-        <v>Android UI renders seamlessly, 'Video player native full-screen toggle' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Video player native full-screen toggle' with zero crash logs</v>
       </c>
       <c r="H83" t="str">
         <v>High</v>
@@ -3328,16 +3328,16 @@
         <v>Mobile Learning UI</v>
       </c>
       <c r="D84" t="str">
-        <v>Verify Audio guide background playback bar on Android device viewport</v>
+        <v>Validate Audio guide background playback bar on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E84" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F84" t="str">
-        <v>Trigger native mobile interaction 'Audio guide background playback bar' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Audio guide background playback bar' and record Kotlin bridge event log</v>
       </c>
       <c r="G84" t="str">
-        <v>Android UI renders seamlessly, 'Audio guide background playback bar' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Audio guide background playback bar' with zero crash logs</v>
       </c>
       <c r="H84" t="str">
         <v>Medium</v>
@@ -3363,16 +3363,16 @@
         <v>Mobile Learning UI</v>
       </c>
       <c r="D85" t="str">
-        <v>Verify Quiz question swipe transition on Android device viewport</v>
+        <v>Validate Quiz question swipe transition on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E85" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F85" t="str">
-        <v>Trigger native mobile interaction 'Quiz question swipe transition' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Quiz question swipe transition' and record Kotlin bridge event log</v>
       </c>
       <c r="G85" t="str">
-        <v>Android UI renders seamlessly, 'Quiz question swipe transition' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Quiz question swipe transition' with zero crash logs</v>
       </c>
       <c r="H85" t="str">
         <v>High</v>
@@ -3398,16 +3398,16 @@
         <v>Mobile Learning UI</v>
       </c>
       <c r="D86" t="str">
-        <v>Verify Quiz radio option tap feedback on Android device viewport</v>
+        <v>Validate Quiz radio option tap feedback on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E86" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F86" t="str">
-        <v>Trigger native mobile interaction 'Quiz radio option tap feedback' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Quiz radio option tap feedback' and record Kotlin bridge event log</v>
       </c>
       <c r="G86" t="str">
-        <v>Android UI renders seamlessly, 'Quiz radio option tap feedback' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Quiz radio option tap feedback' with zero crash logs</v>
       </c>
       <c r="H86" t="str">
         <v>Critical</v>
@@ -3433,16 +3433,16 @@
         <v>Mobile Learning UI</v>
       </c>
       <c r="D87" t="str">
-        <v>Verify Quiz countdown timer alert on Android device viewport</v>
+        <v>Validate Quiz countdown timer alert on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E87" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F87" t="str">
-        <v>Trigger native mobile interaction 'Quiz countdown timer alert' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Quiz countdown timer alert' and record Kotlin bridge event log</v>
       </c>
       <c r="G87" t="str">
-        <v>Android UI renders seamlessly, 'Quiz countdown timer alert' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Quiz countdown timer alert' with zero crash logs</v>
       </c>
       <c r="H87" t="str">
         <v>High</v>
@@ -3468,16 +3468,16 @@
         <v>Mobile Learning UI</v>
       </c>
       <c r="D88" t="str">
-        <v>Verify Score badge native share sheet on Android device viewport</v>
+        <v>Validate Score badge native share sheet on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E88" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F88" t="str">
-        <v>Trigger native mobile interaction 'Score badge native share sheet' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Score badge native share sheet' and record Kotlin bridge event log</v>
       </c>
       <c r="G88" t="str">
-        <v>Android UI renders seamlessly, 'Score badge native share sheet' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Score badge native share sheet' with zero crash logs</v>
       </c>
       <c r="H88" t="str">
         <v>Medium</v>
@@ -3503,16 +3503,16 @@
         <v>Mobile Learning UI</v>
       </c>
       <c r="D89" t="str">
-        <v>Verify Search topic mobile keypad submit on Android device viewport</v>
+        <v>Validate Search topic mobile keypad submit on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E89" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F89" t="str">
-        <v>Trigger native mobile interaction 'Search topic mobile keypad submit' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Search topic mobile keypad submit' and record Kotlin bridge event log</v>
       </c>
       <c r="G89" t="str">
-        <v>Android UI renders seamlessly, 'Search topic mobile keypad submit' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Search topic mobile keypad submit' with zero crash logs</v>
       </c>
       <c r="H89" t="str">
         <v>High</v>
@@ -3538,16 +3538,16 @@
         <v>Mobile Learning UI</v>
       </c>
       <c r="D90" t="str">
-        <v>Verify Bookmarked items offline cache on Android device viewport</v>
+        <v>Validate Bookmarked items offline cache on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E90" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F90" t="str">
-        <v>Trigger native mobile interaction 'Bookmarked items offline cache' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Bookmarked items offline cache' and record Kotlin bridge event log</v>
       </c>
       <c r="G90" t="str">
-        <v>Android UI renders seamlessly, 'Bookmarked items offline cache' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Bookmarked items offline cache' with zero crash logs</v>
       </c>
       <c r="H90" t="str">
         <v>Medium</v>
@@ -3573,16 +3573,16 @@
         <v>Mobile Learning UI</v>
       </c>
       <c r="D91" t="str">
-        <v>Verify Font scaling accessibility check on Android device viewport</v>
+        <v>Validate Font scaling accessibility check on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E91" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F91" t="str">
-        <v>Trigger native mobile interaction 'Font scaling accessibility check' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Font scaling accessibility check' and record Kotlin bridge event log</v>
       </c>
       <c r="G91" t="str">
-        <v>Android UI renders seamlessly, 'Font scaling accessibility check' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Font scaling accessibility check' with zero crash logs</v>
       </c>
       <c r="H91" t="str">
         <v>Critical</v>
@@ -3608,16 +3608,16 @@
         <v>Mobile Account Care</v>
       </c>
       <c r="D92" t="str">
-        <v>Verify Profile image camera capture on Android device viewport</v>
+        <v>Validate Profile image camera capture on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E92" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F92" t="str">
-        <v>Trigger native mobile interaction 'Profile image camera capture' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Profile image camera capture' and record Kotlin bridge event log</v>
       </c>
       <c r="G92" t="str">
-        <v>Android UI renders seamlessly, 'Profile image camera capture' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Profile image camera capture' with zero crash logs</v>
       </c>
       <c r="H92" t="str">
         <v>Medium</v>
@@ -3643,16 +3643,16 @@
         <v>Mobile Account Care</v>
       </c>
       <c r="D93" t="str">
-        <v>Verify Profile image gallery selection on Android device viewport</v>
+        <v>Validate Profile image gallery selection on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E93" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F93" t="str">
-        <v>Trigger native mobile interaction 'Profile image gallery selection' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Profile image gallery selection' and record Kotlin bridge event log</v>
       </c>
       <c r="G93" t="str">
-        <v>Android UI renders seamlessly, 'Profile image gallery selection' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Profile image gallery selection' with zero crash logs</v>
       </c>
       <c r="H93" t="str">
         <v>High</v>
@@ -3678,16 +3678,16 @@
         <v>Mobile Account Care</v>
       </c>
       <c r="D94" t="str">
-        <v>Verify Crop profile image gesture on Android device viewport</v>
+        <v>Validate Crop profile image gesture on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E94" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F94" t="str">
-        <v>Trigger native mobile interaction 'Crop profile image gesture' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Crop profile image gesture' and record Kotlin bridge event log</v>
       </c>
       <c r="G94" t="str">
-        <v>Android UI renders seamlessly, 'Crop profile image gesture' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Crop profile image gesture' with zero crash logs</v>
       </c>
       <c r="H94" t="str">
         <v>Medium</v>
@@ -3713,16 +3713,16 @@
         <v>Mobile Account Care</v>
       </c>
       <c r="D95" t="str">
-        <v>Verify Edit info native text input focus on Android device viewport</v>
+        <v>Validate Edit info native text input focus on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E95" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F95" t="str">
-        <v>Trigger native mobile interaction 'Edit info native text input focus' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Edit info native text input focus' and record Kotlin bridge event log</v>
       </c>
       <c r="G95" t="str">
-        <v>Android UI renders seamlessly, 'Edit info native text input focus' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Edit info native text input focus' with zero crash logs</v>
       </c>
       <c r="H95" t="str">
         <v>High</v>
@@ -3748,16 +3748,16 @@
         <v>Mobile Account Care</v>
       </c>
       <c r="D96" t="str">
-        <v>Verify Save profile native toast alert on Android device viewport</v>
+        <v>Validate Save profile native toast alert on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E96" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F96" t="str">
-        <v>Trigger native mobile interaction 'Save profile native toast alert' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Save profile native toast alert' and record Kotlin bridge event log</v>
       </c>
       <c r="G96" t="str">
-        <v>Android UI renders seamlessly, 'Save profile native toast alert' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Save profile native toast alert' with zero crash logs</v>
       </c>
       <c r="H96" t="str">
         <v>Critical</v>
@@ -3783,16 +3783,16 @@
         <v>Mobile Account Care</v>
       </c>
       <c r="D97" t="str">
-        <v>Verify Legal Privacy Policy scroll to end on Android device viewport</v>
+        <v>Validate Legal Privacy Policy scroll to end on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E97" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F97" t="str">
-        <v>Trigger native mobile interaction 'Legal Privacy Policy scroll to end' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Legal Privacy Policy scroll to end' and record Kotlin bridge event log</v>
       </c>
       <c r="G97" t="str">
-        <v>Android UI renders seamlessly, 'Legal Privacy Policy scroll to end' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Legal Privacy Policy scroll to end' with zero crash logs</v>
       </c>
       <c r="H97" t="str">
         <v>High</v>
@@ -3818,16 +3818,16 @@
         <v>Mobile Account Care</v>
       </c>
       <c r="D98" t="str">
-        <v>Verify Terms of Service agreement toggle on Android device viewport</v>
+        <v>Validate Terms of Service agreement toggle on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E98" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F98" t="str">
-        <v>Trigger native mobile interaction 'Terms of Service agreement toggle' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Terms of Service agreement toggle' and record Kotlin bridge event log</v>
       </c>
       <c r="G98" t="str">
-        <v>Android UI renders seamlessly, 'Terms of Service agreement toggle' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Terms of Service agreement toggle' with zero crash logs</v>
       </c>
       <c r="H98" t="str">
         <v>Medium</v>
@@ -3853,16 +3853,16 @@
         <v>Mobile Account Care</v>
       </c>
       <c r="D99" t="str">
-        <v>Verify Delete Account permanent confirm dialog on Android device viewport</v>
+        <v>Validate Delete Account permanent confirm dialog on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E99" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F99" t="str">
-        <v>Trigger native mobile interaction 'Delete Account permanent confirm dialog' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Delete Account permanent confirm dialog' and record Kotlin bridge event log</v>
       </c>
       <c r="G99" t="str">
-        <v>Android UI renders seamlessly, 'Delete Account permanent confirm dialog' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Delete Account permanent confirm dialog' with zero crash logs</v>
       </c>
       <c r="H99" t="str">
         <v>High</v>
@@ -3888,16 +3888,16 @@
         <v>Mobile Account Care</v>
       </c>
       <c r="D100" t="str">
-        <v>Verify Logout confirmation native popup on Android device viewport</v>
+        <v>Validate Logout confirmation native popup on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E100" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F100" t="str">
-        <v>Trigger native mobile interaction 'Logout confirmation native popup' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'Logout confirmation native popup' and record Kotlin bridge event log</v>
       </c>
       <c r="G100" t="str">
-        <v>Android UI renders seamlessly, 'Logout confirmation native popup' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'Logout confirmation native popup' with zero crash logs</v>
       </c>
       <c r="H100" t="str">
         <v>Medium</v>
@@ -3923,16 +3923,16 @@
         <v>Mobile Account Care</v>
       </c>
       <c r="D101" t="str">
-        <v>Verify App version build number display on Android device viewport</v>
+        <v>Validate App version build number display on Android 14 (Pixel 8 Pro) [Portrait Native Layout]</v>
       </c>
       <c r="E101" t="str">
-        <v>App running on Android 14 (Pixel 8 Pro Emulator / Physical Device)</v>
+        <v>App installed on Android 14 (Pixel 8 Pro) executing under Portrait Native Layout</v>
       </c>
       <c r="F101" t="str">
-        <v>Trigger native mobile interaction 'App version build number display' and observe UI response and Kotlin bridge logs</v>
+        <v>Perform gesture/input 'App version build number display' and record Kotlin bridge event log</v>
       </c>
       <c r="G101" t="str">
-        <v>Android UI renders seamlessly, 'App version build number display' operates with zero framework layout glitches</v>
+        <v>Native Android viewport updates flawlessly for 'App version build number display' with zero crash logs</v>
       </c>
       <c r="H101" t="str">
         <v>Critical</v>
@@ -3947,9 +3947,7009 @@
         <v>Pass</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>TC101</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Validate Full-screen LifeMatrix logo render on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E102" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Perform gesture/input 'Full-screen LifeMatrix logo render' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G102" t="str">
+        <v>Native Android viewport updates flawlessly for 'Full-screen LifeMatrix logo render' with zero crash logs</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I102" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J102" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K102" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>TC102</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Validate Splash screen auto-dismiss within 2s on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E103" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Perform gesture/input 'Splash screen auto-dismiss within 2s' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G103" t="str">
+        <v>Native Android viewport updates flawlessly for 'Splash screen auto-dismiss within 2s' with zero crash logs</v>
+      </c>
+      <c r="H103" t="str">
+        <v>High</v>
+      </c>
+      <c r="I103" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J103" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K103" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>TC103</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Validate Android hardware status bar padding on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E104" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Perform gesture/input 'Android hardware status bar padding' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G104" t="str">
+        <v>Native Android viewport updates flawlessly for 'Android hardware status bar padding' with zero crash logs</v>
+      </c>
+      <c r="H104" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I104" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J104" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K104" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>TC104</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Validate Portrait orientation lock enforcement on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E105" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F105" t="str">
+        <v>Perform gesture/input 'Portrait orientation lock enforcement' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G105" t="str">
+        <v>Native Android viewport updates flawlessly for 'Portrait orientation lock enforcement' with zero crash logs</v>
+      </c>
+      <c r="H105" t="str">
+        <v>High</v>
+      </c>
+      <c r="I105" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J105" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K105" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>TC105</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Validate Native splash fade-out animation on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E106" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Perform gesture/input 'Native splash fade-out animation' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G106" t="str">
+        <v>Native Android viewport updates flawlessly for 'Native splash fade-out animation' with zero crash logs</v>
+      </c>
+      <c r="H106" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I106" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J106" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K106" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>TC106</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Validate First-time install routing on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E107" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Perform gesture/input 'First-time install routing' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G107" t="str">
+        <v>Native Android viewport updates flawlessly for 'First-time install routing' with zero crash logs</v>
+      </c>
+      <c r="H107" t="str">
+        <v>High</v>
+      </c>
+      <c r="I107" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J107" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K107" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>TC107</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Validate Existing session token check on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E108" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Perform gesture/input 'Existing session token check' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G108" t="str">
+        <v>Native Android viewport updates flawlessly for 'Existing session token check' with zero crash logs</v>
+      </c>
+      <c r="H108" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I108" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J108" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K108" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>TC108</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Validate Device screen DPI scaling on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E109" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F109" t="str">
+        <v>Perform gesture/input 'Device screen DPI scaling' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G109" t="str">
+        <v>Native Android viewport updates flawlessly for 'Device screen DPI scaling' with zero crash logs</v>
+      </c>
+      <c r="H109" t="str">
+        <v>High</v>
+      </c>
+      <c r="I109" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J109" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K109" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>TC109</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Validate DarkMode splash theme adaptation on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E110" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F110" t="str">
+        <v>Perform gesture/input 'DarkMode splash theme adaptation' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G110" t="str">
+        <v>Native Android viewport updates flawlessly for 'DarkMode splash theme adaptation' with zero crash logs</v>
+      </c>
+      <c r="H110" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I110" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J110" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K110" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>TC110</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Validate App icon launch integrity on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E111" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F111" t="str">
+        <v>Perform gesture/input 'App icon launch integrity' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G111" t="str">
+        <v>Native Android viewport updates flawlessly for 'App icon launch integrity' with zero crash logs</v>
+      </c>
+      <c r="H111" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I111" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J111" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K111" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>TC111</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Validate Slide 1 Welcome banner display on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E112" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F112" t="str">
+        <v>Perform gesture/input 'Slide 1 Welcome banner display' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G112" t="str">
+        <v>Native Android viewport updates flawlessly for 'Slide 1 Welcome banner display' with zero crash logs</v>
+      </c>
+      <c r="H112" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I112" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J112" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K112" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>TC112</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Validate Slide 2 AI Diagnostics intro on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E113" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F113" t="str">
+        <v>Perform gesture/input 'Slide 2 AI Diagnostics intro' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G113" t="str">
+        <v>Native Android viewport updates flawlessly for 'Slide 2 AI Diagnostics intro' with zero crash logs</v>
+      </c>
+      <c r="H113" t="str">
+        <v>High</v>
+      </c>
+      <c r="I113" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J113" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K113" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>TC113</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Validate Slide 3 Vitals Tracking overview on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E114" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F114" t="str">
+        <v>Perform gesture/input 'Slide 3 Vitals Tracking overview' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G114" t="str">
+        <v>Native Android viewport updates flawlessly for 'Slide 3 Vitals Tracking overview' with zero crash logs</v>
+      </c>
+      <c r="H114" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I114" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J114" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K114" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>TC114</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Validate Swipe left gesture to next slide on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E115" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F115" t="str">
+        <v>Perform gesture/input 'Swipe left gesture to next slide' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G115" t="str">
+        <v>Native Android viewport updates flawlessly for 'Swipe left gesture to next slide' with zero crash logs</v>
+      </c>
+      <c r="H115" t="str">
+        <v>High</v>
+      </c>
+      <c r="I115" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J115" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K115" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>TC115</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Validate Swipe right gesture to prev slide on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E116" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F116" t="str">
+        <v>Perform gesture/input 'Swipe right gesture to prev slide' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G116" t="str">
+        <v>Native Android viewport updates flawlessly for 'Swipe right gesture to prev slide' with zero crash logs</v>
+      </c>
+      <c r="H116" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I116" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J116" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K116" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>TC116</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Validate Onboarding pagination dot indicator on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E117" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F117" t="str">
+        <v>Perform gesture/input 'Onboarding pagination dot indicator' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G117" t="str">
+        <v>Native Android viewport updates flawlessly for 'Onboarding pagination dot indicator' with zero crash logs</v>
+      </c>
+      <c r="H117" t="str">
+        <v>High</v>
+      </c>
+      <c r="I117" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J117" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K117" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>TC117</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Validate Skip Onboarding button tap on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E118" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F118" t="str">
+        <v>Perform gesture/input 'Skip Onboarding button tap' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G118" t="str">
+        <v>Native Android viewport updates flawlessly for 'Skip Onboarding button tap' with zero crash logs</v>
+      </c>
+      <c r="H118" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I118" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J118" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K118" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>TC118</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Validate Get Started CTA button tap on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E119" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F119" t="str">
+        <v>Perform gesture/input 'Get Started CTA button tap' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G119" t="str">
+        <v>Native Android viewport updates flawlessly for 'Get Started CTA button tap' with zero crash logs</v>
+      </c>
+      <c r="H119" t="str">
+        <v>High</v>
+      </c>
+      <c r="I119" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J119" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K119" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>TC119</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Validate Onboarding animation frame rate on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E120" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F120" t="str">
+        <v>Perform gesture/input 'Onboarding animation frame rate' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G120" t="str">
+        <v>Native Android viewport updates flawlessly for 'Onboarding animation frame rate' with zero crash logs</v>
+      </c>
+      <c r="H120" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I120" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J120" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K120" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>TC120</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Validate Back button press on slide 1 on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E121" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F121" t="str">
+        <v>Perform gesture/input 'Back button press on slide 1' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G121" t="str">
+        <v>Native Android viewport updates flawlessly for 'Back button press on slide 1' with zero crash logs</v>
+      </c>
+      <c r="H121" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I121" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J121" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K121" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>TC121</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Validate Scheduled medicine notification pop on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E122" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F122" t="str">
+        <v>Perform gesture/input 'Scheduled medicine notification pop' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G122" t="str">
+        <v>Native Android viewport updates flawlessly for 'Scheduled medicine notification pop' with zero crash logs</v>
+      </c>
+      <c r="H122" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I122" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J122" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K122" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>TC122</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Validate Notification action 'Mark as Taken' on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E123" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F123" t="str">
+        <v>Perform gesture/input 'Notification action 'Mark as Taken'' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G123" t="str">
+        <v>Native Android viewport updates flawlessly for 'Notification action 'Mark as Taken'' with zero crash logs</v>
+      </c>
+      <c r="H123" t="str">
+        <v>High</v>
+      </c>
+      <c r="I123" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J123" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K123" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>TC123</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Validate Notification action 'Snooze 15m' on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E124" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F124" t="str">
+        <v>Perform gesture/input 'Notification action 'Snooze 15m'' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G124" t="str">
+        <v>Native Android viewport updates flawlessly for 'Notification action 'Snooze 15m'' with zero crash logs</v>
+      </c>
+      <c r="H124" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I124" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J124" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K124" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>TC124</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Validate Sound and vibration alert trigger on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E125" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F125" t="str">
+        <v>Perform gesture/input 'Sound and vibration alert trigger' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G125" t="str">
+        <v>Native Android viewport updates flawlessly for 'Sound and vibration alert trigger' with zero crash logs</v>
+      </c>
+      <c r="H125" t="str">
+        <v>High</v>
+      </c>
+      <c r="I125" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J125" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K125" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>TC125</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Validate Lockscreen notification card render on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E126" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F126" t="str">
+        <v>Perform gesture/input 'Lockscreen notification card render' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G126" t="str">
+        <v>Native Android viewport updates flawlessly for 'Lockscreen notification card render' with zero crash logs</v>
+      </c>
+      <c r="H126" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I126" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J126" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K126" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>TC126</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Validate Notification badge count update on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E127" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F127" t="str">
+        <v>Perform gesture/input 'Notification badge count update' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G127" t="str">
+        <v>Native Android viewport updates flawlessly for 'Notification badge count update' with zero crash logs</v>
+      </c>
+      <c r="H127" t="str">
+        <v>High</v>
+      </c>
+      <c r="I127" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J127" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K127" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>TC127</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Validate Missed dose push alert on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E128" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F128" t="str">
+        <v>Perform gesture/input 'Missed dose push alert' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G128" t="str">
+        <v>Native Android viewport updates flawlessly for 'Missed dose push alert' with zero crash logs</v>
+      </c>
+      <c r="H128" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I128" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J128" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K128" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>TC128</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Validate Custom sound playback check on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E129" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F129" t="str">
+        <v>Perform gesture/input 'Custom sound playback check' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G129" t="str">
+        <v>Native Android viewport updates flawlessly for 'Custom sound playback check' with zero crash logs</v>
+      </c>
+      <c r="H129" t="str">
+        <v>High</v>
+      </c>
+      <c r="I129" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J129" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K129" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>TC129</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Validate Notification tap app foregrounding on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E130" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F130" t="str">
+        <v>Perform gesture/input 'Notification tap app foregrounding' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G130" t="str">
+        <v>Native Android viewport updates flawlessly for 'Notification tap app foregrounding' with zero crash logs</v>
+      </c>
+      <c r="H130" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I130" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J130" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K130" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>TC130</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Validate Clear notification swipe gesture on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E131" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F131" t="str">
+        <v>Perform gesture/input 'Clear notification swipe gesture' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G131" t="str">
+        <v>Native Android viewport updates flawlessly for 'Clear notification swipe gesture' with zero crash logs</v>
+      </c>
+      <c r="H131" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I131" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J131" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K131" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>TC131</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Validate Concerning symptom alert push on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E132" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F132" t="str">
+        <v>Perform gesture/input 'Concerning symptom alert push' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G132" t="str">
+        <v>Native Android viewport updates flawlessly for 'Concerning symptom alert push' with zero crash logs</v>
+      </c>
+      <c r="H132" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I132" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J132" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K132" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>TC132</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Validate High priority risk warning banner on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E133" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F133" t="str">
+        <v>Perform gesture/input 'High priority risk warning banner' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G133" t="str">
+        <v>Native Android viewport updates flawlessly for 'High priority risk warning banner' with zero crash logs</v>
+      </c>
+      <c r="H133" t="str">
+        <v>High</v>
+      </c>
+      <c r="I133" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J133" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K133" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>TC133</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Validate Abnormal vitals threshold notification on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E134" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F134" t="str">
+        <v>Perform gesture/input 'Abnormal vitals threshold notification' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G134" t="str">
+        <v>Native Android viewport updates flawlessly for 'Abnormal vitals threshold notification' with zero crash logs</v>
+      </c>
+      <c r="H134" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I134" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J134" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K134" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>TC134</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Validate Weekly health summary push alert on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E135" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F135" t="str">
+        <v>Perform gesture/input 'Weekly health summary push alert' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G135" t="str">
+        <v>Native Android viewport updates flawlessly for 'Weekly health summary push alert' with zero crash logs</v>
+      </c>
+      <c r="H135" t="str">
+        <v>High</v>
+      </c>
+      <c r="I135" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J135" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K135" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>TC135</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D136" t="str">
+        <v>Validate Doctor appointment reminder push on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E136" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F136" t="str">
+        <v>Perform gesture/input 'Doctor appointment reminder push' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G136" t="str">
+        <v>Native Android viewport updates flawlessly for 'Doctor appointment reminder push' with zero crash logs</v>
+      </c>
+      <c r="H136" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I136" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J136" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K136" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>TC136</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Validate Emergency contact auto-alert on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E137" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F137" t="str">
+        <v>Perform gesture/input 'Emergency contact auto-alert' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G137" t="str">
+        <v>Native Android viewport updates flawlessly for 'Emergency contact auto-alert' with zero crash logs</v>
+      </c>
+      <c r="H137" t="str">
+        <v>High</v>
+      </c>
+      <c r="I137" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J137" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K137" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>TC137</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Validate Silent hours notification suppression on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E138" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F138" t="str">
+        <v>Perform gesture/input 'Silent hours notification suppression' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G138" t="str">
+        <v>Native Android viewport updates flawlessly for 'Silent hours notification suppression' with zero crash logs</v>
+      </c>
+      <c r="H138" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I138" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J138" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K138" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>TC138</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D139" t="str">
+        <v>Validate Alert history drawer entry on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E139" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F139" t="str">
+        <v>Perform gesture/input 'Alert history drawer entry' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G139" t="str">
+        <v>Native Android viewport updates flawlessly for 'Alert history drawer entry' with zero crash logs</v>
+      </c>
+      <c r="H139" t="str">
+        <v>High</v>
+      </c>
+      <c r="I139" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J139" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K139" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>TC139</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Validate Rich notification image preview on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E140" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F140" t="str">
+        <v>Perform gesture/input 'Rich notification image preview' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G140" t="str">
+        <v>Native Android viewport updates flawlessly for 'Rich notification image preview' with zero crash logs</v>
+      </c>
+      <c r="H140" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I140" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J140" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K140" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>TC140</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D141" t="str">
+        <v>Validate Notification permission request prompt on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E141" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F141" t="str">
+        <v>Perform gesture/input 'Notification permission request prompt' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G141" t="str">
+        <v>Native Android viewport updates flawlessly for 'Notification permission request prompt' with zero crash logs</v>
+      </c>
+      <c r="H141" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I141" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J141" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K141" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>TC141</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D142" t="str">
+        <v>Validate Fingerprint prompt trigger on resume on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E142" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F142" t="str">
+        <v>Perform gesture/input 'Fingerprint prompt trigger on resume' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G142" t="str">
+        <v>Native Android viewport updates flawlessly for 'Fingerprint prompt trigger on resume' with zero crash logs</v>
+      </c>
+      <c r="H142" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I142" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J142" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K142" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>TC142</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D143" t="str">
+        <v>Validate FaceID unlock prompt trigger on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E143" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F143" t="str">
+        <v>Perform gesture/input 'FaceID unlock prompt trigger' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G143" t="str">
+        <v>Native Android viewport updates flawlessly for 'FaceID unlock prompt trigger' with zero crash logs</v>
+      </c>
+      <c r="H143" t="str">
+        <v>High</v>
+      </c>
+      <c r="I143" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J143" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K143" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>TC143</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D144" t="str">
+        <v>Validate Biometric fallback to PIN code on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E144" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F144" t="str">
+        <v>Perform gesture/input 'Biometric fallback to PIN code' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G144" t="str">
+        <v>Native Android viewport updates flawlessly for 'Biometric fallback to PIN code' with zero crash logs</v>
+      </c>
+      <c r="H144" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I144" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J144" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K144" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>TC144</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Validate Two-Factor Auth OTP SMS prompt on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E145" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F145" t="str">
+        <v>Perform gesture/input 'Two-Factor Auth OTP SMS prompt' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G145" t="str">
+        <v>Native Android viewport updates flawlessly for 'Two-Factor Auth OTP SMS prompt' with zero crash logs</v>
+      </c>
+      <c r="H145" t="str">
+        <v>High</v>
+      </c>
+      <c r="I145" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J145" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K145" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>TC145</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D146" t="str">
+        <v>Validate 2FA Authenticator app code entry on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E146" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F146" t="str">
+        <v>Perform gesture/input '2FA Authenticator app code entry' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G146" t="str">
+        <v>Native Android viewport updates flawlessly for '2FA Authenticator app code entry' with zero crash logs</v>
+      </c>
+      <c r="H146" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I146" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J146" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K146" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>TC146</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Validate Biometric authentication setup wizard on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E147" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F147" t="str">
+        <v>Perform gesture/input 'Biometric authentication setup wizard' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G147" t="str">
+        <v>Native Android viewport updates flawlessly for 'Biometric authentication setup wizard' with zero crash logs</v>
+      </c>
+      <c r="H147" t="str">
+        <v>High</v>
+      </c>
+      <c r="I147" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J147" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K147" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>TC147</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Validate Change Password modal submit on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E148" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F148" t="str">
+        <v>Perform gesture/input 'Change Password modal submit' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G148" t="str">
+        <v>Native Android viewport updates flawlessly for 'Change Password modal submit' with zero crash logs</v>
+      </c>
+      <c r="H148" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I148" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J148" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K148" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>TC148</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D149" t="str">
+        <v>Validate Change Mobile Number SMS verify on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E149" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F149" t="str">
+        <v>Perform gesture/input 'Change Mobile Number SMS verify' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G149" t="str">
+        <v>Native Android viewport updates flawlessly for 'Change Mobile Number SMS verify' with zero crash logs</v>
+      </c>
+      <c r="H149" t="str">
+        <v>High</v>
+      </c>
+      <c r="I149" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J149" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K149" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>TC149</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Validate Anonymous analytics opt-out switch on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E150" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F150" t="str">
+        <v>Perform gesture/input 'Anonymous analytics opt-out switch' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G150" t="str">
+        <v>Native Android viewport updates flawlessly for 'Anonymous analytics opt-out switch' with zero crash logs</v>
+      </c>
+      <c r="H150" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I150" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J150" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K150" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>TC150</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Validate Data export ZIP package download on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E151" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F151" t="str">
+        <v>Perform gesture/input 'Data export ZIP package download' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G151" t="str">
+        <v>Native Android viewport updates flawlessly for 'Data export ZIP package download' with zero crash logs</v>
+      </c>
+      <c r="H151" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I151" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J151" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K151" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>TC151</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Validate Active Vitals carousel horizontal scroll on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E152" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F152" t="str">
+        <v>Perform gesture/input 'Active Vitals carousel horizontal scroll' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G152" t="str">
+        <v>Native Android viewport updates flawlessly for 'Active Vitals carousel horizontal scroll' with zero crash logs</v>
+      </c>
+      <c r="H152" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I152" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J152" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K152" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>TC152</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Validate Daily Protocol progress ring animation on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E153" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F153" t="str">
+        <v>Perform gesture/input 'Daily Protocol progress ring animation' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G153" t="str">
+        <v>Native Android viewport updates flawlessly for 'Daily Protocol progress ring animation' with zero crash logs</v>
+      </c>
+      <c r="H153" t="str">
+        <v>High</v>
+      </c>
+      <c r="I153" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J153" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K153" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>TC153</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Validate Quick Action Floating Action Button on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E154" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F154" t="str">
+        <v>Perform gesture/input 'Quick Action Floating Action Button' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G154" t="str">
+        <v>Native Android viewport updates flawlessly for 'Quick Action Floating Action Button' with zero crash logs</v>
+      </c>
+      <c r="H154" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I154" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J154" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K154" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>TC154</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D155" t="str">
+        <v>Validate Pull-to-refresh dashboard data on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E155" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F155" t="str">
+        <v>Perform gesture/input 'Pull-to-refresh dashboard data' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G155" t="str">
+        <v>Native Android viewport updates flawlessly for 'Pull-to-refresh dashboard data' with zero crash logs</v>
+      </c>
+      <c r="H155" t="str">
+        <v>High</v>
+      </c>
+      <c r="I155" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J155" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K155" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>TC155</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Validate Soft keyboard push layout adjustment on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E156" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F156" t="str">
+        <v>Perform gesture/input 'Soft keyboard push layout adjustment' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G156" t="str">
+        <v>Native Android viewport updates flawlessly for 'Soft keyboard push layout adjustment' with zero crash logs</v>
+      </c>
+      <c r="H156" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I156" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J156" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K156" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>TC156</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Validate Bottom navigation tab bar switch on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E157" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F157" t="str">
+        <v>Perform gesture/input 'Bottom navigation tab bar switch' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G157" t="str">
+        <v>Native Android viewport updates flawlessly for 'Bottom navigation tab bar switch' with zero crash logs</v>
+      </c>
+      <c r="H157" t="str">
+        <v>High</v>
+      </c>
+      <c r="I157" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J157" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K157" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>TC157</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Validate Network offline banner display on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E158" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F158" t="str">
+        <v>Perform gesture/input 'Network offline banner display' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G158" t="str">
+        <v>Native Android viewport updates flawlessly for 'Network offline banner display' with zero crash logs</v>
+      </c>
+      <c r="H158" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I158" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J158" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K158" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>TC158</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D159" t="str">
+        <v>Validate Network online recovery sync on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E159" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F159" t="str">
+        <v>Perform gesture/input 'Network online recovery sync' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G159" t="str">
+        <v>Native Android viewport updates flawlessly for 'Network online recovery sync' with zero crash logs</v>
+      </c>
+      <c r="H159" t="str">
+        <v>High</v>
+      </c>
+      <c r="I159" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J159" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K159" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>TC159</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Validate Device dark mode live toggle on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E160" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F160" t="str">
+        <v>Perform gesture/input 'Device dark mode live toggle' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G160" t="str">
+        <v>Native Android viewport updates flawlessly for 'Device dark mode live toggle' with zero crash logs</v>
+      </c>
+      <c r="H160" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I160" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J160" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K160" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>TC160</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D161" t="str">
+        <v>Validate Hardware Back button navigation stack on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E161" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F161" t="str">
+        <v>Perform gesture/input 'Hardware Back button navigation stack' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G161" t="str">
+        <v>Native Android viewport updates flawlessly for 'Hardware Back button navigation stack' with zero crash logs</v>
+      </c>
+      <c r="H161" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I161" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J161" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K161" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>TC161</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D162" t="str">
+        <v>Validate Biometrics update modal popup on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E162" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F162" t="str">
+        <v>Perform gesture/input 'Biometrics update modal popup' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G162" t="str">
+        <v>Native Android viewport updates flawlessly for 'Biometrics update modal popup' with zero crash logs</v>
+      </c>
+      <c r="H162" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I162" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J162" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K162" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>TC162</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D163" t="str">
+        <v>Validate Heart rate native sensor picker on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E163" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F163" t="str">
+        <v>Perform gesture/input 'Heart rate native sensor picker' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G163" t="str">
+        <v>Native Android viewport updates flawlessly for 'Heart rate native sensor picker' with zero crash logs</v>
+      </c>
+      <c r="H163" t="str">
+        <v>High</v>
+      </c>
+      <c r="I163" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J163" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K163" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>TC163</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D164" t="str">
+        <v>Validate Blood pressure dual slider input on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E164" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F164" t="str">
+        <v>Perform gesture/input 'Blood pressure dual slider input' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G164" t="str">
+        <v>Native Android viewport updates flawlessly for 'Blood pressure dual slider input' with zero crash logs</v>
+      </c>
+      <c r="H164" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I164" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J164" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K164" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>TC164</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D165" t="str">
+        <v>Validate Glucose level numeric keypad focus on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E165" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F165" t="str">
+        <v>Perform gesture/input 'Glucose level numeric keypad focus' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G165" t="str">
+        <v>Native Android viewport updates flawlessly for 'Glucose level numeric keypad focus' with zero crash logs</v>
+      </c>
+      <c r="H165" t="str">
+        <v>High</v>
+      </c>
+      <c r="I165" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J165" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K165" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>TC165</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D166" t="str">
+        <v>Validate Medicine time picker native modal on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E166" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F166" t="str">
+        <v>Perform gesture/input 'Medicine time picker native modal' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G166" t="str">
+        <v>Native Android viewport updates flawlessly for 'Medicine time picker native modal' with zero crash logs</v>
+      </c>
+      <c r="H166" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I166" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J166" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K166" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>TC166</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D167" t="str">
+        <v>Validate Dose size stepper control on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E167" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F167" t="str">
+        <v>Perform gesture/input 'Dose size stepper control' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G167" t="str">
+        <v>Native Android viewport updates flawlessly for 'Dose size stepper control' with zero crash logs</v>
+      </c>
+      <c r="H167" t="str">
+        <v>High</v>
+      </c>
+      <c r="I167" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J167" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K167" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>TC167</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D168" t="str">
+        <v>Validate Repeat daily schedule checkbox on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E168" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F168" t="str">
+        <v>Perform gesture/input 'Repeat daily schedule checkbox' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G168" t="str">
+        <v>Native Android viewport updates flawlessly for 'Repeat daily schedule checkbox' with zero crash logs</v>
+      </c>
+      <c r="H168" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I168" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J168" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K168" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>TC168</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D169" t="str">
+        <v>Validate Delete medicine entry swipe gesture on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E169" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F169" t="str">
+        <v>Perform gesture/input 'Delete medicine entry swipe gesture' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G169" t="str">
+        <v>Native Android viewport updates flawlessly for 'Delete medicine entry swipe gesture' with zero crash logs</v>
+      </c>
+      <c r="H169" t="str">
+        <v>High</v>
+      </c>
+      <c r="I169" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J169" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K169" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>TC169</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Validate Edit medicine details tap on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E170" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F170" t="str">
+        <v>Perform gesture/input 'Edit medicine details tap' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G170" t="str">
+        <v>Native Android viewport updates flawlessly for 'Edit medicine details tap' with zero crash logs</v>
+      </c>
+      <c r="H170" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I170" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J170" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K170" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>TC170</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D171" t="str">
+        <v>Validate Vitals history chart pinch-to-zoom on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E171" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F171" t="str">
+        <v>Perform gesture/input 'Vitals history chart pinch-to-zoom' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G171" t="str">
+        <v>Native Android viewport updates flawlessly for 'Vitals history chart pinch-to-zoom' with zero crash logs</v>
+      </c>
+      <c r="H171" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I171" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J171" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K171" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>TC171</v>
+      </c>
+      <c r="B172" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D172" t="str">
+        <v>Validate AI Chat input soft keyboard push on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E172" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F172" t="str">
+        <v>Perform gesture/input 'AI Chat input soft keyboard push' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G172" t="str">
+        <v>Native Android viewport updates flawlessly for 'AI Chat input soft keyboard push' with zero crash logs</v>
+      </c>
+      <c r="H172" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I172" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J172" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K172" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>TC172</v>
+      </c>
+      <c r="B173" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D173" t="str">
+        <v>Validate Voice-to-text mic button tap on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E173" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F173" t="str">
+        <v>Perform gesture/input 'Voice-to-text mic button tap' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G173" t="str">
+        <v>Native Android viewport updates flawlessly for 'Voice-to-text mic button tap' with zero crash logs</v>
+      </c>
+      <c r="H173" t="str">
+        <v>High</v>
+      </c>
+      <c r="I173" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J173" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K173" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>TC173</v>
+      </c>
+      <c r="B174" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D174" t="str">
+        <v>Validate Voice input recording indicator on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E174" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F174" t="str">
+        <v>Perform gesture/input 'Voice input recording indicator' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G174" t="str">
+        <v>Native Android viewport updates flawlessly for 'Voice input recording indicator' with zero crash logs</v>
+      </c>
+      <c r="H174" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I174" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J174" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K174" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>TC174</v>
+      </c>
+      <c r="B175" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Validate Audio wave animation during speech on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E175" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F175" t="str">
+        <v>Perform gesture/input 'Audio wave animation during speech' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G175" t="str">
+        <v>Native Android viewport updates flawlessly for 'Audio wave animation during speech' with zero crash logs</v>
+      </c>
+      <c r="H175" t="str">
+        <v>High</v>
+      </c>
+      <c r="I175" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J175" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K175" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>TC175</v>
+      </c>
+      <c r="B176" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D176" t="str">
+        <v>Validate Voice transcription text stream on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E176" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F176" t="str">
+        <v>Perform gesture/input 'Voice transcription text stream' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G176" t="str">
+        <v>Native Android viewport updates flawlessly for 'Voice transcription text stream' with zero crash logs</v>
+      </c>
+      <c r="H176" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I176" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J176" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K176" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>TC176</v>
+      </c>
+      <c r="B177" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D177" t="str">
+        <v>Validate Send message tap in chat on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E177" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F177" t="str">
+        <v>Perform gesture/input 'Send message tap in chat' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G177" t="str">
+        <v>Native Android viewport updates flawlessly for 'Send message tap in chat' with zero crash logs</v>
+      </c>
+      <c r="H177" t="str">
+        <v>High</v>
+      </c>
+      <c r="I177" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J177" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K177" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>TC177</v>
+      </c>
+      <c r="B178" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D178" t="str">
+        <v>Validate AI streaming response text render on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E178" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F178" t="str">
+        <v>Perform gesture/input 'AI streaming response text render' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G178" t="str">
+        <v>Native Android viewport updates flawlessly for 'AI streaming response text render' with zero crash logs</v>
+      </c>
+      <c r="H178" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I178" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J178" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K178" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>TC178</v>
+      </c>
+      <c r="B179" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Validate Speech synthesis Text-to-Speech play on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E179" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F179" t="str">
+        <v>Perform gesture/input 'Speech synthesis Text-to-Speech play' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G179" t="str">
+        <v>Native Android viewport updates flawlessly for 'Speech synthesis Text-to-Speech play' with zero crash logs</v>
+      </c>
+      <c r="H179" t="str">
+        <v>High</v>
+      </c>
+      <c r="I179" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J179" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K179" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>TC179</v>
+      </c>
+      <c r="B180" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D180" t="str">
+        <v>Validate Stop TTS audio playback button on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E180" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F180" t="str">
+        <v>Perform gesture/input 'Stop TTS audio playback button' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G180" t="str">
+        <v>Native Android viewport updates flawlessly for 'Stop TTS audio playback button' with zero crash logs</v>
+      </c>
+      <c r="H180" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I180" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J180" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K180" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>TC180</v>
+      </c>
+      <c r="B181" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D181" t="str">
+        <v>Validate Clear chat history mobile alert on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E181" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F181" t="str">
+        <v>Perform gesture/input 'Clear chat history mobile alert' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G181" t="str">
+        <v>Native Android viewport updates flawlessly for 'Clear chat history mobile alert' with zero crash logs</v>
+      </c>
+      <c r="H181" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I181" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J181" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K181" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>TC181</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D182" t="str">
+        <v>Validate Article list vertical scroll physics on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E182" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F182" t="str">
+        <v>Perform gesture/input 'Article list vertical scroll physics' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G182" t="str">
+        <v>Native Android viewport updates flawlessly for 'Article list vertical scroll physics' with zero crash logs</v>
+      </c>
+      <c r="H182" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I182" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J182" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K182" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>TC182</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D183" t="str">
+        <v>Validate Video player native full-screen toggle on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E183" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F183" t="str">
+        <v>Perform gesture/input 'Video player native full-screen toggle' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G183" t="str">
+        <v>Native Android viewport updates flawlessly for 'Video player native full-screen toggle' with zero crash logs</v>
+      </c>
+      <c r="H183" t="str">
+        <v>High</v>
+      </c>
+      <c r="I183" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J183" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K183" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>TC183</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D184" t="str">
+        <v>Validate Audio guide background playback bar on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E184" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F184" t="str">
+        <v>Perform gesture/input 'Audio guide background playback bar' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G184" t="str">
+        <v>Native Android viewport updates flawlessly for 'Audio guide background playback bar' with zero crash logs</v>
+      </c>
+      <c r="H184" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I184" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J184" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K184" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>TC184</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D185" t="str">
+        <v>Validate Quiz question swipe transition on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E185" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F185" t="str">
+        <v>Perform gesture/input 'Quiz question swipe transition' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G185" t="str">
+        <v>Native Android viewport updates flawlessly for 'Quiz question swipe transition' with zero crash logs</v>
+      </c>
+      <c r="H185" t="str">
+        <v>High</v>
+      </c>
+      <c r="I185" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J185" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K185" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>TC185</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D186" t="str">
+        <v>Validate Quiz radio option tap feedback on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E186" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F186" t="str">
+        <v>Perform gesture/input 'Quiz radio option tap feedback' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G186" t="str">
+        <v>Native Android viewport updates flawlessly for 'Quiz radio option tap feedback' with zero crash logs</v>
+      </c>
+      <c r="H186" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I186" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J186" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K186" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>TC186</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D187" t="str">
+        <v>Validate Quiz countdown timer alert on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E187" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F187" t="str">
+        <v>Perform gesture/input 'Quiz countdown timer alert' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G187" t="str">
+        <v>Native Android viewport updates flawlessly for 'Quiz countdown timer alert' with zero crash logs</v>
+      </c>
+      <c r="H187" t="str">
+        <v>High</v>
+      </c>
+      <c r="I187" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J187" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K187" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>TC187</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D188" t="str">
+        <v>Validate Score badge native share sheet on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E188" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F188" t="str">
+        <v>Perform gesture/input 'Score badge native share sheet' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G188" t="str">
+        <v>Native Android viewport updates flawlessly for 'Score badge native share sheet' with zero crash logs</v>
+      </c>
+      <c r="H188" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I188" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J188" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K188" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>TC188</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C189" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Validate Search topic mobile keypad submit on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E189" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F189" t="str">
+        <v>Perform gesture/input 'Search topic mobile keypad submit' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G189" t="str">
+        <v>Native Android viewport updates flawlessly for 'Search topic mobile keypad submit' with zero crash logs</v>
+      </c>
+      <c r="H189" t="str">
+        <v>High</v>
+      </c>
+      <c r="I189" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J189" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K189" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>TC189</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D190" t="str">
+        <v>Validate Bookmarked items offline cache on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E190" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F190" t="str">
+        <v>Perform gesture/input 'Bookmarked items offline cache' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G190" t="str">
+        <v>Native Android viewport updates flawlessly for 'Bookmarked items offline cache' with zero crash logs</v>
+      </c>
+      <c r="H190" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I190" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J190" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K190" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>TC190</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D191" t="str">
+        <v>Validate Font scaling accessibility check on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E191" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F191" t="str">
+        <v>Perform gesture/input 'Font scaling accessibility check' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G191" t="str">
+        <v>Native Android viewport updates flawlessly for 'Font scaling accessibility check' with zero crash logs</v>
+      </c>
+      <c r="H191" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I191" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J191" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K191" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>TC191</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D192" t="str">
+        <v>Validate Profile image camera capture on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E192" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F192" t="str">
+        <v>Perform gesture/input 'Profile image camera capture' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G192" t="str">
+        <v>Native Android viewport updates flawlessly for 'Profile image camera capture' with zero crash logs</v>
+      </c>
+      <c r="H192" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I192" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J192" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K192" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>TC192</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Validate Profile image gallery selection on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E193" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F193" t="str">
+        <v>Perform gesture/input 'Profile image gallery selection' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G193" t="str">
+        <v>Native Android viewport updates flawlessly for 'Profile image gallery selection' with zero crash logs</v>
+      </c>
+      <c r="H193" t="str">
+        <v>High</v>
+      </c>
+      <c r="I193" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J193" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K193" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>TC193</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Validate Crop profile image gesture on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E194" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F194" t="str">
+        <v>Perform gesture/input 'Crop profile image gesture' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G194" t="str">
+        <v>Native Android viewport updates flawlessly for 'Crop profile image gesture' with zero crash logs</v>
+      </c>
+      <c r="H194" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I194" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J194" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K194" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>TC194</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D195" t="str">
+        <v>Validate Edit info native text input focus on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E195" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F195" t="str">
+        <v>Perform gesture/input 'Edit info native text input focus' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G195" t="str">
+        <v>Native Android viewport updates flawlessly for 'Edit info native text input focus' with zero crash logs</v>
+      </c>
+      <c r="H195" t="str">
+        <v>High</v>
+      </c>
+      <c r="I195" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J195" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K195" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>TC195</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D196" t="str">
+        <v>Validate Save profile native toast alert on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E196" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F196" t="str">
+        <v>Perform gesture/input 'Save profile native toast alert' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G196" t="str">
+        <v>Native Android viewport updates flawlessly for 'Save profile native toast alert' with zero crash logs</v>
+      </c>
+      <c r="H196" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I196" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J196" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K196" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>TC196</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D197" t="str">
+        <v>Validate Legal Privacy Policy scroll to end on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E197" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F197" t="str">
+        <v>Perform gesture/input 'Legal Privacy Policy scroll to end' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G197" t="str">
+        <v>Native Android viewport updates flawlessly for 'Legal Privacy Policy scroll to end' with zero crash logs</v>
+      </c>
+      <c r="H197" t="str">
+        <v>High</v>
+      </c>
+      <c r="I197" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J197" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K197" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>TC197</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Validate Terms of Service agreement toggle on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E198" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F198" t="str">
+        <v>Perform gesture/input 'Terms of Service agreement toggle' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G198" t="str">
+        <v>Native Android viewport updates flawlessly for 'Terms of Service agreement toggle' with zero crash logs</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I198" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J198" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K198" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>TC198</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D199" t="str">
+        <v>Validate Delete Account permanent confirm dialog on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E199" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F199" t="str">
+        <v>Perform gesture/input 'Delete Account permanent confirm dialog' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G199" t="str">
+        <v>Native Android viewport updates flawlessly for 'Delete Account permanent confirm dialog' with zero crash logs</v>
+      </c>
+      <c r="H199" t="str">
+        <v>High</v>
+      </c>
+      <c r="I199" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J199" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K199" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>TC199</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D200" t="str">
+        <v>Validate Logout confirmation native popup on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E200" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F200" t="str">
+        <v>Perform gesture/input 'Logout confirmation native popup' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G200" t="str">
+        <v>Native Android viewport updates flawlessly for 'Logout confirmation native popup' with zero crash logs</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I200" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J200" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K200" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>TC200</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Validate App version build number display on Android 13 (Samsung Galaxy S23) [Landscape Orientation Lock]</v>
+      </c>
+      <c r="E201" t="str">
+        <v>App installed on Android 13 (Samsung Galaxy S23) executing under Landscape Orientation Lock</v>
+      </c>
+      <c r="F201" t="str">
+        <v>Perform gesture/input 'App version build number display' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G201" t="str">
+        <v>Native Android viewport updates flawlessly for 'App version build number display' with zero crash logs</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I201" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J201" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K201" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>TC201</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Validate Full-screen LifeMatrix logo render on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E202" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F202" t="str">
+        <v>Perform gesture/input 'Full-screen LifeMatrix logo render' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G202" t="str">
+        <v>Native Android viewport updates flawlessly for 'Full-screen LifeMatrix logo render' with zero crash logs</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I202" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J202" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K202" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>TC202</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D203" t="str">
+        <v>Validate Splash screen auto-dismiss within 2s on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E203" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F203" t="str">
+        <v>Perform gesture/input 'Splash screen auto-dismiss within 2s' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G203" t="str">
+        <v>Native Android viewport updates flawlessly for 'Splash screen auto-dismiss within 2s' with zero crash logs</v>
+      </c>
+      <c r="H203" t="str">
+        <v>High</v>
+      </c>
+      <c r="I203" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J203" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K203" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>TC203</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D204" t="str">
+        <v>Validate Android hardware status bar padding on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E204" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F204" t="str">
+        <v>Perform gesture/input 'Android hardware status bar padding' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G204" t="str">
+        <v>Native Android viewport updates flawlessly for 'Android hardware status bar padding' with zero crash logs</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I204" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J204" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K204" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>TC204</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D205" t="str">
+        <v>Validate Portrait orientation lock enforcement on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E205" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F205" t="str">
+        <v>Perform gesture/input 'Portrait orientation lock enforcement' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G205" t="str">
+        <v>Native Android viewport updates flawlessly for 'Portrait orientation lock enforcement' with zero crash logs</v>
+      </c>
+      <c r="H205" t="str">
+        <v>High</v>
+      </c>
+      <c r="I205" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J205" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K205" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>TC205</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D206" t="str">
+        <v>Validate Native splash fade-out animation on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E206" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F206" t="str">
+        <v>Perform gesture/input 'Native splash fade-out animation' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G206" t="str">
+        <v>Native Android viewport updates flawlessly for 'Native splash fade-out animation' with zero crash logs</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I206" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J206" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K206" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>TC206</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D207" t="str">
+        <v>Validate First-time install routing on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E207" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F207" t="str">
+        <v>Perform gesture/input 'First-time install routing' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G207" t="str">
+        <v>Native Android viewport updates flawlessly for 'First-time install routing' with zero crash logs</v>
+      </c>
+      <c r="H207" t="str">
+        <v>High</v>
+      </c>
+      <c r="I207" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J207" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K207" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>TC207</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D208" t="str">
+        <v>Validate Existing session token check on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E208" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F208" t="str">
+        <v>Perform gesture/input 'Existing session token check' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G208" t="str">
+        <v>Native Android viewport updates flawlessly for 'Existing session token check' with zero crash logs</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I208" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J208" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K208" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>TC208</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D209" t="str">
+        <v>Validate Device screen DPI scaling on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E209" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F209" t="str">
+        <v>Perform gesture/input 'Device screen DPI scaling' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G209" t="str">
+        <v>Native Android viewport updates flawlessly for 'Device screen DPI scaling' with zero crash logs</v>
+      </c>
+      <c r="H209" t="str">
+        <v>High</v>
+      </c>
+      <c r="I209" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J209" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K209" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>TC209</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Validate DarkMode splash theme adaptation on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E210" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F210" t="str">
+        <v>Perform gesture/input 'DarkMode splash theme adaptation' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G210" t="str">
+        <v>Native Android viewport updates flawlessly for 'DarkMode splash theme adaptation' with zero crash logs</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I210" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J210" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K210" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>TC210</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Splash &amp; Launch</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Native Android Bootstrap</v>
+      </c>
+      <c r="D211" t="str">
+        <v>Validate App icon launch integrity on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E211" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F211" t="str">
+        <v>Perform gesture/input 'App icon launch integrity' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G211" t="str">
+        <v>Native Android viewport updates flawlessly for 'App icon launch integrity' with zero crash logs</v>
+      </c>
+      <c r="H211" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I211" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J211" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K211" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>TC211</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D212" t="str">
+        <v>Validate Slide 1 Welcome banner display on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E212" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F212" t="str">
+        <v>Perform gesture/input 'Slide 1 Welcome banner display' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G212" t="str">
+        <v>Native Android viewport updates flawlessly for 'Slide 1 Welcome banner display' with zero crash logs</v>
+      </c>
+      <c r="H212" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I212" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J212" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K212" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>TC212</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D213" t="str">
+        <v>Validate Slide 2 AI Diagnostics intro on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E213" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F213" t="str">
+        <v>Perform gesture/input 'Slide 2 AI Diagnostics intro' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G213" t="str">
+        <v>Native Android viewport updates flawlessly for 'Slide 2 AI Diagnostics intro' with zero crash logs</v>
+      </c>
+      <c r="H213" t="str">
+        <v>High</v>
+      </c>
+      <c r="I213" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J213" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K213" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>TC213</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D214" t="str">
+        <v>Validate Slide 3 Vitals Tracking overview on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E214" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F214" t="str">
+        <v>Perform gesture/input 'Slide 3 Vitals Tracking overview' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G214" t="str">
+        <v>Native Android viewport updates flawlessly for 'Slide 3 Vitals Tracking overview' with zero crash logs</v>
+      </c>
+      <c r="H214" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I214" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J214" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K214" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>TC214</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D215" t="str">
+        <v>Validate Swipe left gesture to next slide on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E215" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F215" t="str">
+        <v>Perform gesture/input 'Swipe left gesture to next slide' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G215" t="str">
+        <v>Native Android viewport updates flawlessly for 'Swipe left gesture to next slide' with zero crash logs</v>
+      </c>
+      <c r="H215" t="str">
+        <v>High</v>
+      </c>
+      <c r="I215" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J215" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K215" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>TC215</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D216" t="str">
+        <v>Validate Swipe right gesture to prev slide on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E216" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F216" t="str">
+        <v>Perform gesture/input 'Swipe right gesture to prev slide' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G216" t="str">
+        <v>Native Android viewport updates flawlessly for 'Swipe right gesture to prev slide' with zero crash logs</v>
+      </c>
+      <c r="H216" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I216" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J216" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K216" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>TC216</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D217" t="str">
+        <v>Validate Onboarding pagination dot indicator on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E217" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F217" t="str">
+        <v>Perform gesture/input 'Onboarding pagination dot indicator' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G217" t="str">
+        <v>Native Android viewport updates flawlessly for 'Onboarding pagination dot indicator' with zero crash logs</v>
+      </c>
+      <c r="H217" t="str">
+        <v>High</v>
+      </c>
+      <c r="I217" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J217" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K217" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>TC217</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D218" t="str">
+        <v>Validate Skip Onboarding button tap on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E218" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F218" t="str">
+        <v>Perform gesture/input 'Skip Onboarding button tap' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G218" t="str">
+        <v>Native Android viewport updates flawlessly for 'Skip Onboarding button tap' with zero crash logs</v>
+      </c>
+      <c r="H218" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I218" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J218" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K218" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>TC218</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D219" t="str">
+        <v>Validate Get Started CTA button tap on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E219" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F219" t="str">
+        <v>Perform gesture/input 'Get Started CTA button tap' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G219" t="str">
+        <v>Native Android viewport updates flawlessly for 'Get Started CTA button tap' with zero crash logs</v>
+      </c>
+      <c r="H219" t="str">
+        <v>High</v>
+      </c>
+      <c r="I219" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J219" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K219" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>TC219</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D220" t="str">
+        <v>Validate Onboarding animation frame rate on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E220" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F220" t="str">
+        <v>Perform gesture/input 'Onboarding animation frame rate' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G220" t="str">
+        <v>Native Android viewport updates flawlessly for 'Onboarding animation frame rate' with zero crash logs</v>
+      </c>
+      <c r="H220" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I220" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J220" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K220" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>TC220</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Onboarding Flow</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Interactive Carousel</v>
+      </c>
+      <c r="D221" t="str">
+        <v>Validate Back button press on slide 1 on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E221" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F221" t="str">
+        <v>Perform gesture/input 'Back button press on slide 1' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G221" t="str">
+        <v>Native Android viewport updates flawlessly for 'Back button press on slide 1' with zero crash logs</v>
+      </c>
+      <c r="H221" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I221" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J221" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K221" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>TC221</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D222" t="str">
+        <v>Validate Scheduled medicine notification pop on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E222" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F222" t="str">
+        <v>Perform gesture/input 'Scheduled medicine notification pop' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G222" t="str">
+        <v>Native Android viewport updates flawlessly for 'Scheduled medicine notification pop' with zero crash logs</v>
+      </c>
+      <c r="H222" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I222" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J222" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K222" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>TC222</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D223" t="str">
+        <v>Validate Notification action 'Mark as Taken' on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E223" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F223" t="str">
+        <v>Perform gesture/input 'Notification action 'Mark as Taken'' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G223" t="str">
+        <v>Native Android viewport updates flawlessly for 'Notification action 'Mark as Taken'' with zero crash logs</v>
+      </c>
+      <c r="H223" t="str">
+        <v>High</v>
+      </c>
+      <c r="I223" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J223" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K223" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>TC223</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D224" t="str">
+        <v>Validate Notification action 'Snooze 15m' on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E224" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F224" t="str">
+        <v>Perform gesture/input 'Notification action 'Snooze 15m'' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G224" t="str">
+        <v>Native Android viewport updates flawlessly for 'Notification action 'Snooze 15m'' with zero crash logs</v>
+      </c>
+      <c r="H224" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I224" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J224" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K224" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>TC224</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D225" t="str">
+        <v>Validate Sound and vibration alert trigger on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E225" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F225" t="str">
+        <v>Perform gesture/input 'Sound and vibration alert trigger' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G225" t="str">
+        <v>Native Android viewport updates flawlessly for 'Sound and vibration alert trigger' with zero crash logs</v>
+      </c>
+      <c r="H225" t="str">
+        <v>High</v>
+      </c>
+      <c r="I225" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J225" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K225" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>TC225</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D226" t="str">
+        <v>Validate Lockscreen notification card render on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E226" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F226" t="str">
+        <v>Perform gesture/input 'Lockscreen notification card render' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G226" t="str">
+        <v>Native Android viewport updates flawlessly for 'Lockscreen notification card render' with zero crash logs</v>
+      </c>
+      <c r="H226" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I226" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J226" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K226" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>TC226</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C227" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D227" t="str">
+        <v>Validate Notification badge count update on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E227" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F227" t="str">
+        <v>Perform gesture/input 'Notification badge count update' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G227" t="str">
+        <v>Native Android viewport updates flawlessly for 'Notification badge count update' with zero crash logs</v>
+      </c>
+      <c r="H227" t="str">
+        <v>High</v>
+      </c>
+      <c r="I227" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J227" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K227" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>TC227</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C228" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D228" t="str">
+        <v>Validate Missed dose push alert on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E228" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F228" t="str">
+        <v>Perform gesture/input 'Missed dose push alert' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G228" t="str">
+        <v>Native Android viewport updates flawlessly for 'Missed dose push alert' with zero crash logs</v>
+      </c>
+      <c r="H228" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I228" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J228" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K228" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>TC228</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C229" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D229" t="str">
+        <v>Validate Custom sound playback check on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E229" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F229" t="str">
+        <v>Perform gesture/input 'Custom sound playback check' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G229" t="str">
+        <v>Native Android viewport updates flawlessly for 'Custom sound playback check' with zero crash logs</v>
+      </c>
+      <c r="H229" t="str">
+        <v>High</v>
+      </c>
+      <c r="I229" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J229" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K229" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>TC229</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C230" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D230" t="str">
+        <v>Validate Notification tap app foregrounding on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E230" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F230" t="str">
+        <v>Perform gesture/input 'Notification tap app foregrounding' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G230" t="str">
+        <v>Native Android viewport updates flawlessly for 'Notification tap app foregrounding' with zero crash logs</v>
+      </c>
+      <c r="H230" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I230" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J230" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K230" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>TC230</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Medication Reminders</v>
+      </c>
+      <c r="D231" t="str">
+        <v>Validate Clear notification swipe gesture on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E231" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F231" t="str">
+        <v>Perform gesture/input 'Clear notification swipe gesture' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G231" t="str">
+        <v>Native Android viewport updates flawlessly for 'Clear notification swipe gesture' with zero crash logs</v>
+      </c>
+      <c r="H231" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I231" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J231" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K231" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>TC231</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D232" t="str">
+        <v>Validate Concerning symptom alert push on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E232" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F232" t="str">
+        <v>Perform gesture/input 'Concerning symptom alert push' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G232" t="str">
+        <v>Native Android viewport updates flawlessly for 'Concerning symptom alert push' with zero crash logs</v>
+      </c>
+      <c r="H232" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I232" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J232" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K232" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>TC232</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D233" t="str">
+        <v>Validate High priority risk warning banner on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E233" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F233" t="str">
+        <v>Perform gesture/input 'High priority risk warning banner' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G233" t="str">
+        <v>Native Android viewport updates flawlessly for 'High priority risk warning banner' with zero crash logs</v>
+      </c>
+      <c r="H233" t="str">
+        <v>High</v>
+      </c>
+      <c r="I233" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J233" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K233" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>TC233</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D234" t="str">
+        <v>Validate Abnormal vitals threshold notification on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E234" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F234" t="str">
+        <v>Perform gesture/input 'Abnormal vitals threshold notification' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G234" t="str">
+        <v>Native Android viewport updates flawlessly for 'Abnormal vitals threshold notification' with zero crash logs</v>
+      </c>
+      <c r="H234" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I234" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J234" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K234" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>TC234</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C235" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D235" t="str">
+        <v>Validate Weekly health summary push alert on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E235" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F235" t="str">
+        <v>Perform gesture/input 'Weekly health summary push alert' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G235" t="str">
+        <v>Native Android viewport updates flawlessly for 'Weekly health summary push alert' with zero crash logs</v>
+      </c>
+      <c r="H235" t="str">
+        <v>High</v>
+      </c>
+      <c r="I235" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J235" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K235" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>TC235</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C236" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D236" t="str">
+        <v>Validate Doctor appointment reminder push on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E236" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F236" t="str">
+        <v>Perform gesture/input 'Doctor appointment reminder push' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G236" t="str">
+        <v>Native Android viewport updates flawlessly for 'Doctor appointment reminder push' with zero crash logs</v>
+      </c>
+      <c r="H236" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I236" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J236" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K236" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>TC236</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C237" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D237" t="str">
+        <v>Validate Emergency contact auto-alert on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E237" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F237" t="str">
+        <v>Perform gesture/input 'Emergency contact auto-alert' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G237" t="str">
+        <v>Native Android viewport updates flawlessly for 'Emergency contact auto-alert' with zero crash logs</v>
+      </c>
+      <c r="H237" t="str">
+        <v>High</v>
+      </c>
+      <c r="I237" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J237" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K237" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>TC237</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C238" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D238" t="str">
+        <v>Validate Silent hours notification suppression on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E238" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F238" t="str">
+        <v>Perform gesture/input 'Silent hours notification suppression' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G238" t="str">
+        <v>Native Android viewport updates flawlessly for 'Silent hours notification suppression' with zero crash logs</v>
+      </c>
+      <c r="H238" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I238" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J238" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K238" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>TC238</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C239" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D239" t="str">
+        <v>Validate Alert history drawer entry on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E239" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F239" t="str">
+        <v>Perform gesture/input 'Alert history drawer entry' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G239" t="str">
+        <v>Native Android viewport updates flawlessly for 'Alert history drawer entry' with zero crash logs</v>
+      </c>
+      <c r="H239" t="str">
+        <v>High</v>
+      </c>
+      <c r="I239" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J239" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K239" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>TC239</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C240" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D240" t="str">
+        <v>Validate Rich notification image preview on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E240" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F240" t="str">
+        <v>Perform gesture/input 'Rich notification image preview' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G240" t="str">
+        <v>Native Android viewport updates flawlessly for 'Rich notification image preview' with zero crash logs</v>
+      </c>
+      <c r="H240" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I240" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J240" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K240" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>TC240</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Push Notifications</v>
+      </c>
+      <c r="C241" t="str">
+        <v>Symptom &amp; Risk Alerts</v>
+      </c>
+      <c r="D241" t="str">
+        <v>Validate Notification permission request prompt on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E241" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F241" t="str">
+        <v>Perform gesture/input 'Notification permission request prompt' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G241" t="str">
+        <v>Native Android viewport updates flawlessly for 'Notification permission request prompt' with zero crash logs</v>
+      </c>
+      <c r="H241" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I241" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J241" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K241" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>TC241</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D242" t="str">
+        <v>Validate Fingerprint prompt trigger on resume on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E242" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F242" t="str">
+        <v>Perform gesture/input 'Fingerprint prompt trigger on resume' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G242" t="str">
+        <v>Native Android viewport updates flawlessly for 'Fingerprint prompt trigger on resume' with zero crash logs</v>
+      </c>
+      <c r="H242" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I242" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J242" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K242" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>TC242</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C243" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D243" t="str">
+        <v>Validate FaceID unlock prompt trigger on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E243" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F243" t="str">
+        <v>Perform gesture/input 'FaceID unlock prompt trigger' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G243" t="str">
+        <v>Native Android viewport updates flawlessly for 'FaceID unlock prompt trigger' with zero crash logs</v>
+      </c>
+      <c r="H243" t="str">
+        <v>High</v>
+      </c>
+      <c r="I243" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J243" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K243" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>TC243</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C244" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D244" t="str">
+        <v>Validate Biometric fallback to PIN code on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E244" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F244" t="str">
+        <v>Perform gesture/input 'Biometric fallback to PIN code' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G244" t="str">
+        <v>Native Android viewport updates flawlessly for 'Biometric fallback to PIN code' with zero crash logs</v>
+      </c>
+      <c r="H244" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I244" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J244" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K244" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>TC244</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D245" t="str">
+        <v>Validate Two-Factor Auth OTP SMS prompt on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E245" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F245" t="str">
+        <v>Perform gesture/input 'Two-Factor Auth OTP SMS prompt' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G245" t="str">
+        <v>Native Android viewport updates flawlessly for 'Two-Factor Auth OTP SMS prompt' with zero crash logs</v>
+      </c>
+      <c r="H245" t="str">
+        <v>High</v>
+      </c>
+      <c r="I245" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J245" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K245" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>TC245</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C246" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D246" t="str">
+        <v>Validate 2FA Authenticator app code entry on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E246" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F246" t="str">
+        <v>Perform gesture/input '2FA Authenticator app code entry' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G246" t="str">
+        <v>Native Android viewport updates flawlessly for '2FA Authenticator app code entry' with zero crash logs</v>
+      </c>
+      <c r="H246" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I246" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J246" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K246" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>TC246</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C247" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D247" t="str">
+        <v>Validate Biometric authentication setup wizard on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E247" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F247" t="str">
+        <v>Perform gesture/input 'Biometric authentication setup wizard' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G247" t="str">
+        <v>Native Android viewport updates flawlessly for 'Biometric authentication setup wizard' with zero crash logs</v>
+      </c>
+      <c r="H247" t="str">
+        <v>High</v>
+      </c>
+      <c r="I247" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J247" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K247" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>TC247</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C248" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D248" t="str">
+        <v>Validate Change Password modal submit on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E248" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F248" t="str">
+        <v>Perform gesture/input 'Change Password modal submit' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G248" t="str">
+        <v>Native Android viewport updates flawlessly for 'Change Password modal submit' with zero crash logs</v>
+      </c>
+      <c r="H248" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I248" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J248" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K248" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>TC248</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C249" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D249" t="str">
+        <v>Validate Change Mobile Number SMS verify on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E249" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F249" t="str">
+        <v>Perform gesture/input 'Change Mobile Number SMS verify' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G249" t="str">
+        <v>Native Android viewport updates flawlessly for 'Change Mobile Number SMS verify' with zero crash logs</v>
+      </c>
+      <c r="H249" t="str">
+        <v>High</v>
+      </c>
+      <c r="I249" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J249" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K249" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>TC249</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C250" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D250" t="str">
+        <v>Validate Anonymous analytics opt-out switch on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E250" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F250" t="str">
+        <v>Perform gesture/input 'Anonymous analytics opt-out switch' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G250" t="str">
+        <v>Native Android viewport updates flawlessly for 'Anonymous analytics opt-out switch' with zero crash logs</v>
+      </c>
+      <c r="H250" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I250" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J250" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K250" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>TC250</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Privacy Centre</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Biometric &amp; Security</v>
+      </c>
+      <c r="D251" t="str">
+        <v>Validate Data export ZIP package download on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E251" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F251" t="str">
+        <v>Perform gesture/input 'Data export ZIP package download' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G251" t="str">
+        <v>Native Android viewport updates flawlessly for 'Data export ZIP package download' with zero crash logs</v>
+      </c>
+      <c r="H251" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I251" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J251" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K251" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>TC251</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C252" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D252" t="str">
+        <v>Validate Active Vitals carousel horizontal scroll on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E252" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F252" t="str">
+        <v>Perform gesture/input 'Active Vitals carousel horizontal scroll' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G252" t="str">
+        <v>Native Android viewport updates flawlessly for 'Active Vitals carousel horizontal scroll' with zero crash logs</v>
+      </c>
+      <c r="H252" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I252" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J252" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K252" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>TC252</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C253" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D253" t="str">
+        <v>Validate Daily Protocol progress ring animation on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E253" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F253" t="str">
+        <v>Perform gesture/input 'Daily Protocol progress ring animation' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G253" t="str">
+        <v>Native Android viewport updates flawlessly for 'Daily Protocol progress ring animation' with zero crash logs</v>
+      </c>
+      <c r="H253" t="str">
+        <v>High</v>
+      </c>
+      <c r="I253" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J253" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K253" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>TC253</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C254" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D254" t="str">
+        <v>Validate Quick Action Floating Action Button on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E254" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F254" t="str">
+        <v>Perform gesture/input 'Quick Action Floating Action Button' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G254" t="str">
+        <v>Native Android viewport updates flawlessly for 'Quick Action Floating Action Button' with zero crash logs</v>
+      </c>
+      <c r="H254" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I254" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J254" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K254" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>TC254</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C255" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D255" t="str">
+        <v>Validate Pull-to-refresh dashboard data on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E255" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F255" t="str">
+        <v>Perform gesture/input 'Pull-to-refresh dashboard data' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G255" t="str">
+        <v>Native Android viewport updates flawlessly for 'Pull-to-refresh dashboard data' with zero crash logs</v>
+      </c>
+      <c r="H255" t="str">
+        <v>High</v>
+      </c>
+      <c r="I255" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J255" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K255" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>TC255</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C256" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D256" t="str">
+        <v>Validate Soft keyboard push layout adjustment on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E256" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F256" t="str">
+        <v>Perform gesture/input 'Soft keyboard push layout adjustment' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G256" t="str">
+        <v>Native Android viewport updates flawlessly for 'Soft keyboard push layout adjustment' with zero crash logs</v>
+      </c>
+      <c r="H256" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I256" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J256" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K256" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>TC256</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C257" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D257" t="str">
+        <v>Validate Bottom navigation tab bar switch on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E257" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F257" t="str">
+        <v>Perform gesture/input 'Bottom navigation tab bar switch' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G257" t="str">
+        <v>Native Android viewport updates flawlessly for 'Bottom navigation tab bar switch' with zero crash logs</v>
+      </c>
+      <c r="H257" t="str">
+        <v>High</v>
+      </c>
+      <c r="I257" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J257" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K257" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>TC257</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C258" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D258" t="str">
+        <v>Validate Network offline banner display on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E258" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F258" t="str">
+        <v>Perform gesture/input 'Network offline banner display' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G258" t="str">
+        <v>Native Android viewport updates flawlessly for 'Network offline banner display' with zero crash logs</v>
+      </c>
+      <c r="H258" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I258" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J258" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K258" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>TC258</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C259" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D259" t="str">
+        <v>Validate Network online recovery sync on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E259" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F259" t="str">
+        <v>Perform gesture/input 'Network online recovery sync' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G259" t="str">
+        <v>Native Android viewport updates flawlessly for 'Network online recovery sync' with zero crash logs</v>
+      </c>
+      <c r="H259" t="str">
+        <v>High</v>
+      </c>
+      <c r="I259" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J259" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K259" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>TC259</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C260" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D260" t="str">
+        <v>Validate Device dark mode live toggle on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E260" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F260" t="str">
+        <v>Perform gesture/input 'Device dark mode live toggle' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G260" t="str">
+        <v>Native Android viewport updates flawlessly for 'Device dark mode live toggle' with zero crash logs</v>
+      </c>
+      <c r="H260" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I260" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J260" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K260" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>TC260</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Home Dashboard</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Mobile Viewport UI</v>
+      </c>
+      <c r="D261" t="str">
+        <v>Validate Hardware Back button navigation stack on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E261" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F261" t="str">
+        <v>Perform gesture/input 'Hardware Back button navigation stack' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G261" t="str">
+        <v>Native Android viewport updates flawlessly for 'Hardware Back button navigation stack' with zero crash logs</v>
+      </c>
+      <c r="H261" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I261" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J261" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K261" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>TC261</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C262" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D262" t="str">
+        <v>Validate Biometrics update modal popup on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E262" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F262" t="str">
+        <v>Perform gesture/input 'Biometrics update modal popup' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G262" t="str">
+        <v>Native Android viewport updates flawlessly for 'Biometrics update modal popup' with zero crash logs</v>
+      </c>
+      <c r="H262" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I262" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J262" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K262" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>TC262</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C263" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D263" t="str">
+        <v>Validate Heart rate native sensor picker on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E263" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F263" t="str">
+        <v>Perform gesture/input 'Heart rate native sensor picker' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G263" t="str">
+        <v>Native Android viewport updates flawlessly for 'Heart rate native sensor picker' with zero crash logs</v>
+      </c>
+      <c r="H263" t="str">
+        <v>High</v>
+      </c>
+      <c r="I263" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J263" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K263" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>TC263</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C264" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D264" t="str">
+        <v>Validate Blood pressure dual slider input on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E264" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F264" t="str">
+        <v>Perform gesture/input 'Blood pressure dual slider input' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G264" t="str">
+        <v>Native Android viewport updates flawlessly for 'Blood pressure dual slider input' with zero crash logs</v>
+      </c>
+      <c r="H264" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I264" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J264" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K264" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>TC264</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C265" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D265" t="str">
+        <v>Validate Glucose level numeric keypad focus on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E265" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F265" t="str">
+        <v>Perform gesture/input 'Glucose level numeric keypad focus' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G265" t="str">
+        <v>Native Android viewport updates flawlessly for 'Glucose level numeric keypad focus' with zero crash logs</v>
+      </c>
+      <c r="H265" t="str">
+        <v>High</v>
+      </c>
+      <c r="I265" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J265" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K265" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>TC265</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C266" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D266" t="str">
+        <v>Validate Medicine time picker native modal on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E266" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F266" t="str">
+        <v>Perform gesture/input 'Medicine time picker native modal' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G266" t="str">
+        <v>Native Android viewport updates flawlessly for 'Medicine time picker native modal' with zero crash logs</v>
+      </c>
+      <c r="H266" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I266" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J266" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K266" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>TC266</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C267" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D267" t="str">
+        <v>Validate Dose size stepper control on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E267" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F267" t="str">
+        <v>Perform gesture/input 'Dose size stepper control' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G267" t="str">
+        <v>Native Android viewport updates flawlessly for 'Dose size stepper control' with zero crash logs</v>
+      </c>
+      <c r="H267" t="str">
+        <v>High</v>
+      </c>
+      <c r="I267" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J267" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K267" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>TC267</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C268" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D268" t="str">
+        <v>Validate Repeat daily schedule checkbox on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E268" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F268" t="str">
+        <v>Perform gesture/input 'Repeat daily schedule checkbox' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G268" t="str">
+        <v>Native Android viewport updates flawlessly for 'Repeat daily schedule checkbox' with zero crash logs</v>
+      </c>
+      <c r="H268" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I268" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J268" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K268" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>TC268</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C269" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D269" t="str">
+        <v>Validate Delete medicine entry swipe gesture on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E269" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F269" t="str">
+        <v>Perform gesture/input 'Delete medicine entry swipe gesture' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G269" t="str">
+        <v>Native Android viewport updates flawlessly for 'Delete medicine entry swipe gesture' with zero crash logs</v>
+      </c>
+      <c r="H269" t="str">
+        <v>High</v>
+      </c>
+      <c r="I269" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J269" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K269" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>TC269</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C270" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D270" t="str">
+        <v>Validate Edit medicine details tap on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E270" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F270" t="str">
+        <v>Perform gesture/input 'Edit medicine details tap' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G270" t="str">
+        <v>Native Android viewport updates flawlessly for 'Edit medicine details tap' with zero crash logs</v>
+      </c>
+      <c r="H270" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I270" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J270" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K270" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>TC270</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Vitals &amp; Reminders</v>
+      </c>
+      <c r="C271" t="str">
+        <v>Mobile Native Input</v>
+      </c>
+      <c r="D271" t="str">
+        <v>Validate Vitals history chart pinch-to-zoom on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E271" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F271" t="str">
+        <v>Perform gesture/input 'Vitals history chart pinch-to-zoom' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G271" t="str">
+        <v>Native Android viewport updates flawlessly for 'Vitals history chart pinch-to-zoom' with zero crash logs</v>
+      </c>
+      <c r="H271" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I271" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J271" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K271" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>TC271</v>
+      </c>
+      <c r="B272" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C272" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D272" t="str">
+        <v>Validate AI Chat input soft keyboard push on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E272" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F272" t="str">
+        <v>Perform gesture/input 'AI Chat input soft keyboard push' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G272" t="str">
+        <v>Native Android viewport updates flawlessly for 'AI Chat input soft keyboard push' with zero crash logs</v>
+      </c>
+      <c r="H272" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I272" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J272" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K272" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>TC272</v>
+      </c>
+      <c r="B273" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C273" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D273" t="str">
+        <v>Validate Voice-to-text mic button tap on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E273" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F273" t="str">
+        <v>Perform gesture/input 'Voice-to-text mic button tap' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G273" t="str">
+        <v>Native Android viewport updates flawlessly for 'Voice-to-text mic button tap' with zero crash logs</v>
+      </c>
+      <c r="H273" t="str">
+        <v>High</v>
+      </c>
+      <c r="I273" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J273" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K273" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>TC273</v>
+      </c>
+      <c r="B274" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C274" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D274" t="str">
+        <v>Validate Voice input recording indicator on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E274" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F274" t="str">
+        <v>Perform gesture/input 'Voice input recording indicator' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G274" t="str">
+        <v>Native Android viewport updates flawlessly for 'Voice input recording indicator' with zero crash logs</v>
+      </c>
+      <c r="H274" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I274" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J274" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K274" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>TC274</v>
+      </c>
+      <c r="B275" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C275" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D275" t="str">
+        <v>Validate Audio wave animation during speech on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E275" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F275" t="str">
+        <v>Perform gesture/input 'Audio wave animation during speech' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G275" t="str">
+        <v>Native Android viewport updates flawlessly for 'Audio wave animation during speech' with zero crash logs</v>
+      </c>
+      <c r="H275" t="str">
+        <v>High</v>
+      </c>
+      <c r="I275" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J275" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K275" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>TC275</v>
+      </c>
+      <c r="B276" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C276" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D276" t="str">
+        <v>Validate Voice transcription text stream on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E276" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F276" t="str">
+        <v>Perform gesture/input 'Voice transcription text stream' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G276" t="str">
+        <v>Native Android viewport updates flawlessly for 'Voice transcription text stream' with zero crash logs</v>
+      </c>
+      <c r="H276" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I276" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J276" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K276" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>TC276</v>
+      </c>
+      <c r="B277" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C277" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D277" t="str">
+        <v>Validate Send message tap in chat on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E277" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F277" t="str">
+        <v>Perform gesture/input 'Send message tap in chat' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G277" t="str">
+        <v>Native Android viewport updates flawlessly for 'Send message tap in chat' with zero crash logs</v>
+      </c>
+      <c r="H277" t="str">
+        <v>High</v>
+      </c>
+      <c r="I277" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J277" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K277" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>TC277</v>
+      </c>
+      <c r="B278" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C278" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D278" t="str">
+        <v>Validate AI streaming response text render on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E278" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F278" t="str">
+        <v>Perform gesture/input 'AI streaming response text render' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G278" t="str">
+        <v>Native Android viewport updates flawlessly for 'AI streaming response text render' with zero crash logs</v>
+      </c>
+      <c r="H278" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I278" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J278" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K278" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>TC278</v>
+      </c>
+      <c r="B279" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C279" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D279" t="str">
+        <v>Validate Speech synthesis Text-to-Speech play on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E279" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F279" t="str">
+        <v>Perform gesture/input 'Speech synthesis Text-to-Speech play' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G279" t="str">
+        <v>Native Android viewport updates flawlessly for 'Speech synthesis Text-to-Speech play' with zero crash logs</v>
+      </c>
+      <c r="H279" t="str">
+        <v>High</v>
+      </c>
+      <c r="I279" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J279" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K279" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>TC279</v>
+      </c>
+      <c r="B280" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C280" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D280" t="str">
+        <v>Validate Stop TTS audio playback button on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E280" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F280" t="str">
+        <v>Perform gesture/input 'Stop TTS audio playback button' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G280" t="str">
+        <v>Native Android viewport updates flawlessly for 'Stop TTS audio playback button' with zero crash logs</v>
+      </c>
+      <c r="H280" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I280" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J280" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K280" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>TC280</v>
+      </c>
+      <c r="B281" t="str">
+        <v>AI Chat &amp; Voice</v>
+      </c>
+      <c r="C281" t="str">
+        <v>Mobile Interaction</v>
+      </c>
+      <c r="D281" t="str">
+        <v>Validate Clear chat history mobile alert on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E281" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F281" t="str">
+        <v>Perform gesture/input 'Clear chat history mobile alert' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G281" t="str">
+        <v>Native Android viewport updates flawlessly for 'Clear chat history mobile alert' with zero crash logs</v>
+      </c>
+      <c r="H281" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I281" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J281" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K281" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>TC281</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C282" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D282" t="str">
+        <v>Validate Article list vertical scroll physics on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E282" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F282" t="str">
+        <v>Perform gesture/input 'Article list vertical scroll physics' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G282" t="str">
+        <v>Native Android viewport updates flawlessly for 'Article list vertical scroll physics' with zero crash logs</v>
+      </c>
+      <c r="H282" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I282" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J282" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K282" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>TC282</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C283" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D283" t="str">
+        <v>Validate Video player native full-screen toggle on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E283" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F283" t="str">
+        <v>Perform gesture/input 'Video player native full-screen toggle' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G283" t="str">
+        <v>Native Android viewport updates flawlessly for 'Video player native full-screen toggle' with zero crash logs</v>
+      </c>
+      <c r="H283" t="str">
+        <v>High</v>
+      </c>
+      <c r="I283" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J283" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K283" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>TC283</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C284" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D284" t="str">
+        <v>Validate Audio guide background playback bar on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E284" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F284" t="str">
+        <v>Perform gesture/input 'Audio guide background playback bar' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G284" t="str">
+        <v>Native Android viewport updates flawlessly for 'Audio guide background playback bar' with zero crash logs</v>
+      </c>
+      <c r="H284" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I284" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J284" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K284" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>TC284</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C285" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D285" t="str">
+        <v>Validate Quiz question swipe transition on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E285" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F285" t="str">
+        <v>Perform gesture/input 'Quiz question swipe transition' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G285" t="str">
+        <v>Native Android viewport updates flawlessly for 'Quiz question swipe transition' with zero crash logs</v>
+      </c>
+      <c r="H285" t="str">
+        <v>High</v>
+      </c>
+      <c r="I285" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J285" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K285" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>TC285</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C286" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D286" t="str">
+        <v>Validate Quiz radio option tap feedback on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E286" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F286" t="str">
+        <v>Perform gesture/input 'Quiz radio option tap feedback' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G286" t="str">
+        <v>Native Android viewport updates flawlessly for 'Quiz radio option tap feedback' with zero crash logs</v>
+      </c>
+      <c r="H286" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I286" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J286" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K286" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>TC286</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C287" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D287" t="str">
+        <v>Validate Quiz countdown timer alert on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E287" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F287" t="str">
+        <v>Perform gesture/input 'Quiz countdown timer alert' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G287" t="str">
+        <v>Native Android viewport updates flawlessly for 'Quiz countdown timer alert' with zero crash logs</v>
+      </c>
+      <c r="H287" t="str">
+        <v>High</v>
+      </c>
+      <c r="I287" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J287" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K287" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>TC287</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C288" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D288" t="str">
+        <v>Validate Score badge native share sheet on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E288" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F288" t="str">
+        <v>Perform gesture/input 'Score badge native share sheet' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G288" t="str">
+        <v>Native Android viewport updates flawlessly for 'Score badge native share sheet' with zero crash logs</v>
+      </c>
+      <c r="H288" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I288" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J288" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K288" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>TC288</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C289" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D289" t="str">
+        <v>Validate Search topic mobile keypad submit on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E289" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F289" t="str">
+        <v>Perform gesture/input 'Search topic mobile keypad submit' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G289" t="str">
+        <v>Native Android viewport updates flawlessly for 'Search topic mobile keypad submit' with zero crash logs</v>
+      </c>
+      <c r="H289" t="str">
+        <v>High</v>
+      </c>
+      <c r="I289" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J289" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K289" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>TC289</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C290" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D290" t="str">
+        <v>Validate Bookmarked items offline cache on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E290" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F290" t="str">
+        <v>Perform gesture/input 'Bookmarked items offline cache' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G290" t="str">
+        <v>Native Android viewport updates flawlessly for 'Bookmarked items offline cache' with zero crash logs</v>
+      </c>
+      <c r="H290" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I290" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J290" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K290" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>TC290</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Learn &amp; Quizzes</v>
+      </c>
+      <c r="C291" t="str">
+        <v>Mobile Learning UI</v>
+      </c>
+      <c r="D291" t="str">
+        <v>Validate Font scaling accessibility check on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E291" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F291" t="str">
+        <v>Perform gesture/input 'Font scaling accessibility check' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G291" t="str">
+        <v>Native Android viewport updates flawlessly for 'Font scaling accessibility check' with zero crash logs</v>
+      </c>
+      <c r="H291" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I291" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J291" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K291" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>TC291</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C292" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D292" t="str">
+        <v>Validate Profile image camera capture on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E292" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F292" t="str">
+        <v>Perform gesture/input 'Profile image camera capture' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G292" t="str">
+        <v>Native Android viewport updates flawlessly for 'Profile image camera capture' with zero crash logs</v>
+      </c>
+      <c r="H292" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I292" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J292" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K292" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>TC292</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C293" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D293" t="str">
+        <v>Validate Profile image gallery selection on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E293" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F293" t="str">
+        <v>Perform gesture/input 'Profile image gallery selection' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G293" t="str">
+        <v>Native Android viewport updates flawlessly for 'Profile image gallery selection' with zero crash logs</v>
+      </c>
+      <c r="H293" t="str">
+        <v>High</v>
+      </c>
+      <c r="I293" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J293" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K293" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>TC293</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C294" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D294" t="str">
+        <v>Validate Crop profile image gesture on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E294" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F294" t="str">
+        <v>Perform gesture/input 'Crop profile image gesture' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G294" t="str">
+        <v>Native Android viewport updates flawlessly for 'Crop profile image gesture' with zero crash logs</v>
+      </c>
+      <c r="H294" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I294" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J294" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K294" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>TC294</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C295" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D295" t="str">
+        <v>Validate Edit info native text input focus on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E295" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F295" t="str">
+        <v>Perform gesture/input 'Edit info native text input focus' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G295" t="str">
+        <v>Native Android viewport updates flawlessly for 'Edit info native text input focus' with zero crash logs</v>
+      </c>
+      <c r="H295" t="str">
+        <v>High</v>
+      </c>
+      <c r="I295" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J295" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K295" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>TC295</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C296" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D296" t="str">
+        <v>Validate Save profile native toast alert on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E296" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F296" t="str">
+        <v>Perform gesture/input 'Save profile native toast alert' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G296" t="str">
+        <v>Native Android viewport updates flawlessly for 'Save profile native toast alert' with zero crash logs</v>
+      </c>
+      <c r="H296" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I296" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J296" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K296" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>TC296</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C297" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D297" t="str">
+        <v>Validate Legal Privacy Policy scroll to end on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E297" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F297" t="str">
+        <v>Perform gesture/input 'Legal Privacy Policy scroll to end' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G297" t="str">
+        <v>Native Android viewport updates flawlessly for 'Legal Privacy Policy scroll to end' with zero crash logs</v>
+      </c>
+      <c r="H297" t="str">
+        <v>High</v>
+      </c>
+      <c r="I297" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J297" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K297" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>TC297</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C298" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D298" t="str">
+        <v>Validate Terms of Service agreement toggle on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E298" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F298" t="str">
+        <v>Perform gesture/input 'Terms of Service agreement toggle' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G298" t="str">
+        <v>Native Android viewport updates flawlessly for 'Terms of Service agreement toggle' with zero crash logs</v>
+      </c>
+      <c r="H298" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I298" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J298" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K298" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>TC298</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C299" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D299" t="str">
+        <v>Validate Delete Account permanent confirm dialog on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E299" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F299" t="str">
+        <v>Perform gesture/input 'Delete Account permanent confirm dialog' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G299" t="str">
+        <v>Native Android viewport updates flawlessly for 'Delete Account permanent confirm dialog' with zero crash logs</v>
+      </c>
+      <c r="H299" t="str">
+        <v>High</v>
+      </c>
+      <c r="I299" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J299" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K299" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>TC299</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C300" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D300" t="str">
+        <v>Validate Logout confirmation native popup on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E300" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F300" t="str">
+        <v>Perform gesture/input 'Logout confirmation native popup' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G300" t="str">
+        <v>Native Android viewport updates flawlessly for 'Logout confirmation native popup' with zero crash logs</v>
+      </c>
+      <c r="H300" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I300" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J300" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K300" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>TC300</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Profile &amp; Account</v>
+      </c>
+      <c r="C301" t="str">
+        <v>Mobile Account Care</v>
+      </c>
+      <c r="D301" t="str">
+        <v>Validate App version build number display on Android 12 (Tablet Viewport 10-inch) [Split-Screen Multi-Window]</v>
+      </c>
+      <c r="E301" t="str">
+        <v>App installed on Android 12 (Tablet Viewport 10-inch) executing under Split-Screen Multi-Window</v>
+      </c>
+      <c r="F301" t="str">
+        <v>Perform gesture/input 'App version build number display' and record Kotlin bridge event log</v>
+      </c>
+      <c r="G301" t="str">
+        <v>Native Android viewport updates flawlessly for 'App version build number display' with zero crash logs</v>
+      </c>
+      <c r="H301" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I301" t="str">
+        <v>Mobile E2E</v>
+      </c>
+      <c r="J301" t="str">
+        <v>Android Native</v>
+      </c>
+      <c r="K301" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K301"/>
   </ignoredErrors>
 </worksheet>
 </file>